--- a/Results/Hydrogen/hydrogen resource use fossils results.xlsx
+++ b/Results/Hydrogen/hydrogen resource use fossils results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>410.3914677474583</v>
+        <v>410.3914677474596</v>
       </c>
       <c r="C2" t="n">
-        <v>433.5097743491372</v>
+        <v>433.5097743491357</v>
       </c>
       <c r="D2" t="n">
-        <v>516.9436849857874</v>
+        <v>516.9436849857864</v>
       </c>
       <c r="E2" t="n">
-        <v>433.5097743491372</v>
+        <v>433.5097743491357</v>
       </c>
       <c r="F2" t="n">
-        <v>433.5097743491372</v>
+        <v>433.5097743491357</v>
       </c>
       <c r="G2" t="n">
-        <v>540.2280851423974</v>
+        <v>540.2280851423961</v>
       </c>
       <c r="H2" t="n">
-        <v>1077.656843516061</v>
+        <v>1077.656843516059</v>
       </c>
       <c r="I2" t="n">
-        <v>433.5097743491372</v>
+        <v>433.5097743491357</v>
       </c>
       <c r="J2" t="n">
-        <v>833.635208960349</v>
+        <v>833.6352089603465</v>
       </c>
       <c r="K2" t="n">
-        <v>514.8108253616953</v>
+        <v>514.8108253616947</v>
       </c>
       <c r="L2" t="n">
-        <v>953.8447060460196</v>
+        <v>294.4015286840936</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.881779997743496</v>
+        <v>6.881779997743518</v>
       </c>
       <c r="C3" t="n">
-        <v>6.720405657890902</v>
+        <v>6.720405657890912</v>
       </c>
       <c r="D3" t="n">
-        <v>6.881779997743496</v>
+        <v>6.881779997743518</v>
       </c>
       <c r="E3" t="n">
-        <v>6.840461302603811</v>
+        <v>6.840461302603824</v>
       </c>
       <c r="F3" t="n">
-        <v>6.840461302603809</v>
+        <v>6.840461302603814</v>
       </c>
       <c r="G3" t="n">
-        <v>6.883312304235127</v>
+        <v>6.883312304235101</v>
       </c>
       <c r="H3" t="n">
-        <v>6.881779997743496</v>
+        <v>6.881779997743518</v>
       </c>
       <c r="I3" t="n">
-        <v>6.891784265264755</v>
+        <v>6.89178426526477</v>
       </c>
       <c r="J3" t="n">
-        <v>6.881779997743496</v>
+        <v>6.881779997743518</v>
       </c>
       <c r="K3" t="n">
-        <v>6.881779997743496</v>
+        <v>6.881779997743518</v>
       </c>
       <c r="L3" t="n">
-        <v>6.881779997743496</v>
+        <v>6.881779997743518</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>878.1733875504337</v>
+        <v>732.8382158274557</v>
       </c>
       <c r="C4" t="n">
-        <v>732.716332434678</v>
+        <v>732.7163324346784</v>
       </c>
       <c r="D4" t="n">
-        <v>732.9204592843857</v>
+        <v>732.9204669115744</v>
       </c>
       <c r="E4" t="n">
-        <v>660.5709690455778</v>
+        <v>660.5709690455789</v>
       </c>
       <c r="F4" t="n">
         <v>732.8904934557916</v>
       </c>
       <c r="G4" t="n">
-        <v>878.1749198569254</v>
+        <v>878.1749198569258</v>
       </c>
       <c r="H4" t="n">
         <v>878.9973925037941</v>
       </c>
       <c r="I4" t="n">
-        <v>878.1833918179555</v>
+        <v>732.8482200949768</v>
       </c>
       <c r="J4" t="n">
-        <v>770.029032497597</v>
+        <v>770.0290324975963</v>
       </c>
       <c r="K4" t="n">
-        <v>732.9155438128969</v>
+        <v>732.9155438128975</v>
       </c>
       <c r="L4" t="n">
-        <v>733.0272241740076</v>
+        <v>733.0272241740071</v>
       </c>
     </row>
     <row r="5">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.63909357296172</v>
+        <v>14.63909357296167</v>
       </c>
       <c r="C5" t="n">
-        <v>14.649097840483</v>
+        <v>14.64909784048299</v>
       </c>
       <c r="D5" t="n">
-        <v>14.63900801096118</v>
+        <v>14.63900801096119</v>
       </c>
       <c r="E5" t="n">
         <v>14.6516737225958</v>
@@ -650,22 +650,22 @@
         <v>14.6516737225958</v>
       </c>
       <c r="G5" t="n">
-        <v>14.64062587945336</v>
+        <v>14.64062587945338</v>
       </c>
       <c r="H5" t="n">
-        <v>14.63909357296172</v>
+        <v>14.63909357296167</v>
       </c>
       <c r="I5" t="n">
-        <v>14.649097840483</v>
+        <v>14.64909784048299</v>
       </c>
       <c r="J5" t="n">
-        <v>14.63909357296172</v>
+        <v>14.63909357296167</v>
       </c>
       <c r="K5" t="n">
-        <v>14.63909357296172</v>
+        <v>14.63909357296167</v>
       </c>
       <c r="L5" t="n">
-        <v>14.63909357296172</v>
+        <v>14.63909357296167</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.01000425062154</v>
+        <v>18.01000425062157</v>
       </c>
       <c r="C6" t="n">
-        <v>26.4555906543412</v>
+        <v>26.45559065434121</v>
       </c>
       <c r="D6" t="n">
-        <v>28.1897483426697</v>
+        <v>28.18974834266977</v>
       </c>
       <c r="E6" t="n">
-        <v>24.1492777961481</v>
+        <v>24.14927779614814</v>
       </c>
       <c r="F6" t="n">
         <v>18.28885957448014</v>
       </c>
       <c r="G6" t="n">
-        <v>26.44296834345943</v>
+        <v>26.44296834345946</v>
       </c>
       <c r="H6" t="n">
-        <v>26.44143603697067</v>
+        <v>26.44143603697068</v>
       </c>
       <c r="I6" t="n">
         <v>26.45144030448908</v>
       </c>
       <c r="J6" t="n">
-        <v>26.44309304288859</v>
+        <v>26.44309304288856</v>
       </c>
       <c r="K6" t="n">
-        <v>17.85338607753872</v>
+        <v>17.85338607753869</v>
       </c>
       <c r="L6" t="n">
-        <v>35.24877155143803</v>
+        <v>35.24877155143805</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39.0855573615555</v>
+        <v>39.08555736155554</v>
       </c>
       <c r="C7" t="n">
-        <v>48.59392129914499</v>
+        <v>48.59392129914497</v>
       </c>
       <c r="D7" t="n">
-        <v>48.58391924583061</v>
+        <v>48.58391924583067</v>
       </c>
       <c r="E7" t="n">
-        <v>59.5548133193791</v>
+        <v>59.55481331937909</v>
       </c>
       <c r="F7" t="n">
-        <v>48.59390878485382</v>
+        <v>48.59390878485371</v>
       </c>
       <c r="G7" t="n">
-        <v>48.58544933811533</v>
+        <v>48.58544933811537</v>
       </c>
       <c r="H7" t="n">
-        <v>48.58391703162363</v>
+        <v>48.5839170316237</v>
       </c>
       <c r="I7" t="n">
-        <v>48.59392129914499</v>
+        <v>48.59392129914497</v>
       </c>
       <c r="J7" t="n">
-        <v>48.58391703162363</v>
+        <v>48.5839170316237</v>
       </c>
       <c r="K7" t="n">
-        <v>36.62378618192859</v>
+        <v>43.08053106713635</v>
       </c>
       <c r="L7" t="n">
-        <v>48.58391703162363</v>
+        <v>48.5839170316237</v>
       </c>
     </row>
     <row r="8">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>166.0979387017248</v>
+        <v>166.097938701725</v>
       </c>
       <c r="C8" t="n">
         <v>170.6597270395064</v>
@@ -779,10 +779,10 @@
         <v>170.6597270395064</v>
       </c>
       <c r="J8" t="n">
-        <v>158.2352607227446</v>
+        <v>158.2352607227447</v>
       </c>
       <c r="K8" t="n">
-        <v>164.119707145285</v>
+        <v>164.1197071452851</v>
       </c>
       <c r="L8" t="n">
         <v>169.4770512910057</v>
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168.6829509667457</v>
+        <v>168.6829509667459</v>
       </c>
       <c r="C9" t="n">
-        <v>173.4167242064196</v>
+        <v>173.4167242064194</v>
       </c>
       <c r="D9" t="n">
-        <v>167.8592818486329</v>
+        <v>167.859281848633</v>
       </c>
       <c r="E9" t="n">
-        <v>173.4167242064196</v>
+        <v>173.4167242064194</v>
       </c>
       <c r="F9" t="n">
-        <v>173.4167242064196</v>
+        <v>173.4167242064194</v>
       </c>
       <c r="G9" t="n">
-        <v>167.7497415837514</v>
+        <v>167.7497415837515</v>
       </c>
       <c r="H9" t="n">
-        <v>164.045999966668</v>
+        <v>164.0459999666681</v>
       </c>
       <c r="I9" t="n">
-        <v>173.4167242064196</v>
+        <v>173.4167242064194</v>
       </c>
       <c r="J9" t="n">
-        <v>165.4869374399329</v>
+        <v>165.4869374399328</v>
       </c>
       <c r="K9" t="n">
-        <v>167.8778067300369</v>
+        <v>167.877806730037</v>
       </c>
       <c r="L9" t="n">
-        <v>170.0633819909908</v>
+        <v>170.063381990991</v>
       </c>
     </row>
   </sheetData>
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.48809248194749</v>
+        <v>18.48809248194744</v>
       </c>
       <c r="C2" t="n">
         <v>122.4481448371878</v>
       </c>
       <c r="D2" t="n">
-        <v>192.5479933755525</v>
+        <v>192.547993375553</v>
       </c>
       <c r="E2" t="n">
         <v>122.4481448371878</v>
@@ -926,7 +926,7 @@
         <v>122.4481448371878</v>
       </c>
       <c r="G2" t="n">
-        <v>181.9048108973672</v>
+        <v>181.9048108973663</v>
       </c>
       <c r="H2" t="n">
         <v>168.9616817326346</v>
@@ -935,13 +935,13 @@
         <v>122.4481448371878</v>
       </c>
       <c r="J2" t="n">
-        <v>416.1249985428268</v>
+        <v>416.1249985428269</v>
       </c>
       <c r="K2" t="n">
-        <v>91.66042070128533</v>
+        <v>91.66042070128542</v>
       </c>
       <c r="L2" t="n">
-        <v>97.80341346027171</v>
+        <v>187.97575428933</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.28023602145599</v>
+        <v>4.280236021455981</v>
       </c>
       <c r="C3" t="n">
-        <v>4.029122088491814</v>
+        <v>4.029122088491798</v>
       </c>
       <c r="D3" t="n">
-        <v>4.28023602145599</v>
+        <v>4.280236021455981</v>
       </c>
       <c r="E3" t="n">
-        <v>4.108068726987832</v>
+        <v>4.108068726987806</v>
       </c>
       <c r="F3" t="n">
-        <v>4.108068726987832</v>
+        <v>4.10806872698781</v>
       </c>
       <c r="G3" t="n">
-        <v>4.282695655925261</v>
+        <v>4.282695655925256</v>
       </c>
       <c r="H3" t="n">
-        <v>4.28023602145599</v>
+        <v>4.280236021455981</v>
       </c>
       <c r="I3" t="n">
-        <v>4.295895729931653</v>
+        <v>4.29589572993163</v>
       </c>
       <c r="J3" t="n">
-        <v>4.28023602145599</v>
+        <v>4.280236021455981</v>
       </c>
       <c r="K3" t="n">
-        <v>4.28023602145599</v>
+        <v>4.280236021455981</v>
       </c>
       <c r="L3" t="n">
-        <v>4.28023602145599</v>
+        <v>4.280236021455981</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>760.5635690724328</v>
+        <v>760.5635690724331</v>
       </c>
       <c r="C4" t="n">
-        <v>635.854114984839</v>
+        <v>635.8541149848393</v>
       </c>
       <c r="D4" t="n">
-        <v>636.0427773370675</v>
+        <v>760.7401889354423</v>
       </c>
       <c r="E4" t="n">
-        <v>573.0447007240194</v>
+        <v>573.0447007240197</v>
       </c>
       <c r="F4" t="n">
-        <v>635.9747000441064</v>
+        <v>635.9747000441066</v>
       </c>
       <c r="G4" t="n">
-        <v>760.5660287069011</v>
+        <v>635.9502880673654</v>
       </c>
       <c r="H4" t="n">
-        <v>761.1528852937508</v>
+        <v>761.1528852937507</v>
       </c>
       <c r="I4" t="n">
-        <v>635.9634881413714</v>
+        <v>635.9634881413713</v>
       </c>
       <c r="J4" t="n">
         <v>760.9355327713204</v>
       </c>
       <c r="K4" t="n">
-        <v>635.8404015101698</v>
+        <v>635.8404015101695</v>
       </c>
       <c r="L4" t="n">
-        <v>635.9988393959345</v>
+        <v>635.998839395935</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.100792920163016</v>
+        <v>9.100792920163004</v>
       </c>
       <c r="C5" t="n">
-        <v>9.116452628638699</v>
+        <v>9.116452628638649</v>
       </c>
       <c r="D5" t="n">
-        <v>9.100788468893564</v>
+        <v>9.100788468893542</v>
       </c>
       <c r="E5" t="n">
-        <v>9.076834994310433</v>
+        <v>9.07683499431039</v>
       </c>
       <c r="F5" t="n">
-        <v>9.076834994310433</v>
+        <v>9.07683499431039</v>
       </c>
       <c r="G5" t="n">
-        <v>9.103252554632304</v>
+        <v>9.103252554632276</v>
       </c>
       <c r="H5" t="n">
-        <v>9.100792920163016</v>
+        <v>9.100792920163004</v>
       </c>
       <c r="I5" t="n">
-        <v>9.116452628638699</v>
+        <v>9.116452628638649</v>
       </c>
       <c r="J5" t="n">
-        <v>9.100792920163016</v>
+        <v>9.100792920163004</v>
       </c>
       <c r="K5" t="n">
-        <v>9.100792920163016</v>
+        <v>9.100792920163004</v>
       </c>
       <c r="L5" t="n">
-        <v>9.100792920163016</v>
+        <v>9.100792920163004</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.42350965867989</v>
+        <v>10.42350965867985</v>
       </c>
       <c r="C6" t="n">
-        <v>15.00665389482574</v>
+        <v>15.00665389482566</v>
       </c>
       <c r="D6" t="n">
-        <v>15.98282373314833</v>
+        <v>15.98282373314828</v>
       </c>
       <c r="E6" t="n">
-        <v>13.75135439748241</v>
+        <v>13.75135439748235</v>
       </c>
       <c r="F6" t="n">
-        <v>10.56149480125933</v>
+        <v>10.5614948012593</v>
       </c>
       <c r="G6" t="n">
-        <v>15.0305032553108</v>
+        <v>15.03050325531073</v>
       </c>
       <c r="H6" t="n">
-        <v>15.02804362085084</v>
+        <v>15.02804362085081</v>
       </c>
       <c r="I6" t="n">
-        <v>15.04370332931718</v>
+        <v>15.0437033293171</v>
       </c>
       <c r="J6" t="n">
-        <v>15.02894853719645</v>
+        <v>15.0289485371964</v>
       </c>
       <c r="K6" t="n">
-        <v>10.33797807692743</v>
+        <v>10.33797807692741</v>
       </c>
       <c r="L6" t="n">
-        <v>19.83786436313635</v>
+        <v>19.83786436313628</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.67388379812851</v>
+        <v>18.67388379812844</v>
       </c>
       <c r="C7" t="n">
-        <v>22.97536181629383</v>
+        <v>22.97536181629374</v>
       </c>
       <c r="D7" t="n">
-        <v>22.95970643722466</v>
+        <v>22.95970643722458</v>
       </c>
       <c r="E7" t="n">
-        <v>27.92110668527068</v>
+        <v>27.92110668527062</v>
       </c>
       <c r="F7" t="n">
-        <v>22.9753598162382</v>
+        <v>22.97535981623813</v>
       </c>
       <c r="G7" t="n">
-        <v>22.96216174228743</v>
+        <v>22.96216174228737</v>
       </c>
       <c r="H7" t="n">
-        <v>22.95970210781814</v>
+        <v>22.95970210781812</v>
       </c>
       <c r="I7" t="n">
-        <v>22.97536181629383</v>
+        <v>22.97536181629374</v>
       </c>
       <c r="J7" t="n">
-        <v>22.95970210781814</v>
+        <v>22.95970210781812</v>
       </c>
       <c r="K7" t="n">
-        <v>20.47648396840812</v>
+        <v>20.47648396840806</v>
       </c>
       <c r="L7" t="n">
-        <v>22.95970210781814</v>
+        <v>22.95970210781812</v>
       </c>
     </row>
     <row r="8">
@@ -1166,22 +1166,22 @@
         <v>174.292336715524</v>
       </c>
       <c r="G8" t="n">
-        <v>168.052475706485</v>
+        <v>168.0524757064851</v>
       </c>
       <c r="H8" t="n">
-        <v>168.7837654212</v>
+        <v>168.7837654211999</v>
       </c>
       <c r="I8" t="n">
         <v>174.292336715524</v>
       </c>
       <c r="J8" t="n">
-        <v>162.9282439966441</v>
+        <v>162.9282439966442</v>
       </c>
       <c r="K8" t="n">
-        <v>170.2049880577376</v>
+        <v>170.2049880577377</v>
       </c>
       <c r="L8" t="n">
-        <v>170.3995687742439</v>
+        <v>168.6190307920876</v>
       </c>
     </row>
     <row r="9">
@@ -1191,34 +1191,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.7700747465042</v>
+        <v>169.7700747465041</v>
       </c>
       <c r="C9" t="n">
-        <v>173.3789468212091</v>
+        <v>173.3789468212092</v>
       </c>
       <c r="D9" t="n">
-        <v>167.8680312848983</v>
+        <v>167.8680312848982</v>
       </c>
       <c r="E9" t="n">
-        <v>173.3789468212091</v>
+        <v>173.3789468212092</v>
       </c>
       <c r="F9" t="n">
-        <v>173.3789468212091</v>
+        <v>173.3789468212092</v>
       </c>
       <c r="G9" t="n">
         <v>168.0590775364415</v>
       </c>
       <c r="H9" t="n">
-        <v>168.3675675572774</v>
+        <v>168.3675675572776</v>
       </c>
       <c r="I9" t="n">
-        <v>173.3789468212091</v>
+        <v>173.3789468212092</v>
       </c>
       <c r="J9" t="n">
         <v>165.982791965191</v>
       </c>
       <c r="K9" t="n">
-        <v>168.9430025530727</v>
+        <v>168.9430025530729</v>
       </c>
       <c r="L9" t="n">
         <v>169.0237648154994</v>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>179.2920817887907</v>
+        <v>179.2920817887911</v>
       </c>
       <c r="C2" t="n">
-        <v>175.076211727726</v>
+        <v>175.0762117277262</v>
       </c>
       <c r="D2" t="n">
-        <v>314.0101212438041</v>
+        <v>314.0101212438434</v>
       </c>
       <c r="E2" t="n">
-        <v>268.7089523503519</v>
+        <v>268.7089523503525</v>
       </c>
       <c r="F2" t="n">
-        <v>268.7089523503519</v>
+        <v>268.7089523503525</v>
       </c>
       <c r="G2" t="n">
-        <v>317.1512962838825</v>
+        <v>317.1512962838814</v>
       </c>
       <c r="H2" t="n">
-        <v>521.7882955971168</v>
+        <v>521.788295597116</v>
       </c>
       <c r="I2" t="n">
-        <v>268.7089523503519</v>
+        <v>268.7089523503525</v>
       </c>
       <c r="J2" t="n">
-        <v>520.8070941645251</v>
+        <v>520.8070941645258</v>
       </c>
       <c r="K2" t="n">
-        <v>295.6496422311662</v>
+        <v>295.649642231156</v>
       </c>
       <c r="L2" t="n">
-        <v>291.3728714991355</v>
+        <v>291.3728714991367</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.548362515101098</v>
+        <v>5.548362515101058</v>
       </c>
       <c r="C3" t="n">
-        <v>5.142961417072008</v>
+        <v>5.142961417072006</v>
       </c>
       <c r="D3" t="n">
-        <v>5.548362515101098</v>
+        <v>5.548362515101058</v>
       </c>
       <c r="E3" t="n">
-        <v>5.444198230014985</v>
+        <v>5.444198230014987</v>
       </c>
       <c r="F3" t="n">
-        <v>5.444198230014992</v>
+        <v>5.444198230014988</v>
       </c>
       <c r="G3" t="n">
-        <v>5.540662554093148</v>
+        <v>5.540662554093154</v>
       </c>
       <c r="H3" t="n">
-        <v>5.548362515101098</v>
+        <v>5.548362515101058</v>
       </c>
       <c r="I3" t="n">
-        <v>5.496501766652314</v>
+        <v>5.496501766652287</v>
       </c>
       <c r="J3" t="n">
-        <v>5.548362515101064</v>
+        <v>5.548362515101058</v>
       </c>
       <c r="K3" t="n">
-        <v>5.548362515101098</v>
+        <v>5.548362515101058</v>
       </c>
       <c r="L3" t="n">
-        <v>5.548362515101098</v>
+        <v>5.548362515101058</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>805.5474111790145</v>
+        <v>672.8663679934546</v>
       </c>
       <c r="C4" t="n">
-        <v>672.5649981157987</v>
+        <v>672.5649981157984</v>
       </c>
       <c r="D4" t="n">
-        <v>672.9306773344848</v>
+        <v>672.9306706220424</v>
       </c>
       <c r="E4" t="n">
-        <v>606.3730749276913</v>
+        <v>606.3730749276908</v>
       </c>
       <c r="F4" t="n">
-        <v>672.8393026684184</v>
+        <v>672.8393026684187</v>
       </c>
       <c r="G4" t="n">
-        <v>805.5397112180073</v>
+        <v>805.5397112180067</v>
       </c>
       <c r="H4" t="n">
-        <v>806.5328949303017</v>
+        <v>806.5328949303026</v>
       </c>
       <c r="I4" t="n">
-        <v>805.4955504305645</v>
+        <v>805.4955504305656</v>
       </c>
       <c r="J4" t="n">
-        <v>805.9831179786112</v>
+        <v>805.983117978612</v>
       </c>
       <c r="K4" t="n">
-        <v>672.8867626481776</v>
+        <v>672.8867626481759</v>
       </c>
       <c r="L4" t="n">
-        <v>672.8950240144796</v>
+        <v>672.8950240144785</v>
       </c>
     </row>
     <row r="5">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.94839378560619</v>
+        <v>11.94839378560625</v>
       </c>
       <c r="C5" t="n">
-        <v>11.93715832941097</v>
+        <v>11.93715832941094</v>
       </c>
       <c r="D5" t="n">
-        <v>11.94838721209417</v>
+        <v>11.94838721209421</v>
       </c>
       <c r="E5" t="n">
         <v>11.89839331301318</v>
@@ -1442,22 +1442,22 @@
         <v>11.89839331301318</v>
       </c>
       <c r="G5" t="n">
-        <v>11.94069382459831</v>
+        <v>11.94069382459834</v>
       </c>
       <c r="H5" t="n">
-        <v>11.94839378560619</v>
+        <v>11.94839378560625</v>
       </c>
       <c r="I5" t="n">
-        <v>11.89653303715743</v>
+        <v>11.89653303715748</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94839378560619</v>
+        <v>11.94839378560625</v>
       </c>
       <c r="K5" t="n">
-        <v>11.94839378560619</v>
+        <v>11.94839378560625</v>
       </c>
       <c r="L5" t="n">
-        <v>11.94839378560619</v>
+        <v>11.94839378560625</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.51517986777364</v>
+        <v>14.51517986777366</v>
       </c>
       <c r="C6" t="n">
-        <v>21.34689143541064</v>
+        <v>21.34689143553981</v>
       </c>
       <c r="D6" t="n">
-        <v>22.77336274721322</v>
+        <v>22.77336274721333</v>
       </c>
       <c r="E6" t="n">
-        <v>19.43535805279066</v>
+        <v>19.43535805279068</v>
       </c>
       <c r="F6" t="n">
-        <v>14.68124666803873</v>
+        <v>14.68124666803876</v>
       </c>
       <c r="G6" t="n">
-        <v>21.34736753041463</v>
+        <v>21.34736753041465</v>
       </c>
       <c r="H6" t="n">
-        <v>21.35506749145026</v>
+        <v>21.35506749145034</v>
       </c>
       <c r="I6" t="n">
-        <v>21.30320674297374</v>
+        <v>21.30320674297378</v>
       </c>
       <c r="J6" t="n">
-        <v>21.3564117147027</v>
+        <v>21.35641171470282</v>
       </c>
       <c r="K6" t="n">
-        <v>14.3881254445003</v>
+        <v>14.38812544450028</v>
       </c>
       <c r="L6" t="n">
-        <v>28.49990204656912</v>
+        <v>28.49990204656911</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.80141712480704</v>
+        <v>26.80141712480654</v>
       </c>
       <c r="C7" t="n">
-        <v>33.16508374528455</v>
+        <v>33.16508374528419</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17632383053082</v>
+        <v>33.17632383053106</v>
       </c>
       <c r="E7" t="n">
-        <v>40.48095852540411</v>
+        <v>40.48095852540419</v>
       </c>
       <c r="F7" t="n">
-        <v>33.1244537019004</v>
+        <v>33.12445370189974</v>
       </c>
       <c r="G7" t="n">
-        <v>33.16861924047237</v>
+        <v>33.16861924047158</v>
       </c>
       <c r="H7" t="n">
-        <v>33.17631920147992</v>
+        <v>33.17631920147947</v>
       </c>
       <c r="I7" t="n">
-        <v>33.12445845303127</v>
+        <v>33.12445845303073</v>
       </c>
       <c r="J7" t="n">
-        <v>33.17631920147992</v>
+        <v>33.17631920147947</v>
       </c>
       <c r="K7" t="n">
-        <v>25.14917837120189</v>
+        <v>29.48267784904393</v>
       </c>
       <c r="L7" t="n">
-        <v>33.17631920147992</v>
+        <v>33.17631920147947</v>
       </c>
     </row>
     <row r="8">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>163.3501429267518</v>
+        <v>163.3501429267516</v>
       </c>
       <c r="C8" t="n">
         <v>165.3972036468965</v>
       </c>
       <c r="D8" t="n">
-        <v>165.6016664516029</v>
+        <v>165.6016664516009</v>
       </c>
       <c r="E8" t="n">
         <v>165.0178081187632</v>
@@ -1562,19 +1562,19 @@
         <v>165.0178081187632</v>
       </c>
       <c r="G8" t="n">
-        <v>164.3242484449759</v>
+        <v>164.3242484449758</v>
       </c>
       <c r="H8" t="n">
-        <v>162.2122347051115</v>
+        <v>162.2122347051116</v>
       </c>
       <c r="I8" t="n">
         <v>165.0178081187632</v>
       </c>
       <c r="J8" t="n">
-        <v>172.1008621900336</v>
+        <v>172.1008621900337</v>
       </c>
       <c r="K8" t="n">
-        <v>172.6604825504218</v>
+        <v>172.660482550422</v>
       </c>
       <c r="L8" t="n">
         <v>179.3152408247453</v>
@@ -1587,19 +1587,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163.0743701340255</v>
+        <v>163.0743701340254</v>
       </c>
       <c r="C9" t="n">
         <v>165.0464810570723</v>
       </c>
       <c r="D9" t="n">
-        <v>167.1619685237092</v>
+        <v>167.1619685237093</v>
       </c>
       <c r="E9" t="n">
-        <v>165.947760975769</v>
+        <v>165.9477609757689</v>
       </c>
       <c r="F9" t="n">
-        <v>165.947760975769</v>
+        <v>165.9477609757689</v>
       </c>
       <c r="G9" t="n">
         <v>165.8251161092018</v>
@@ -1608,13 +1608,13 @@
         <v>165.7911115775445</v>
       </c>
       <c r="I9" t="n">
-        <v>165.947760975769</v>
+        <v>165.9477609757689</v>
       </c>
       <c r="J9" t="n">
-        <v>175.9728047334174</v>
+        <v>175.9728047334176</v>
       </c>
       <c r="K9" t="n">
-        <v>173.8492832567788</v>
+        <v>173.8492832567793</v>
       </c>
       <c r="L9" t="n">
         <v>179.844363725994</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93.17274804148957</v>
+        <v>93.1727480414894</v>
       </c>
       <c r="C2" t="n">
-        <v>117.0729928457</v>
+        <v>117.0729928456997</v>
       </c>
       <c r="D2" t="n">
-        <v>230.2708382866052</v>
+        <v>230.270838286605</v>
       </c>
       <c r="E2" t="n">
-        <v>133.3116406713089</v>
+        <v>133.3116406713084</v>
       </c>
       <c r="F2" t="n">
-        <v>133.3116406713089</v>
+        <v>133.3116406713084</v>
       </c>
       <c r="G2" t="n">
-        <v>204.4987689914507</v>
+        <v>204.4987689914499</v>
       </c>
       <c r="H2" t="n">
-        <v>286.3411992164337</v>
+        <v>286.3411992164336</v>
       </c>
       <c r="I2" t="n">
-        <v>133.3116406713089</v>
+        <v>133.3116406713084</v>
       </c>
       <c r="J2" t="n">
-        <v>377.2726568119446</v>
+        <v>377.2726568119442</v>
       </c>
       <c r="K2" t="n">
-        <v>143.2330090556283</v>
+        <v>143.233009055628</v>
       </c>
       <c r="L2" t="n">
-        <v>149.5663970054841</v>
+        <v>149.5663970054837</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.65403215681926</v>
+        <v>4.654032156819115</v>
       </c>
       <c r="C3" t="n">
-        <v>4.327819788408811</v>
+        <v>4.327819788408807</v>
       </c>
       <c r="D3" t="n">
-        <v>4.65403215681926</v>
+        <v>4.654032156819115</v>
       </c>
       <c r="E3" t="n">
-        <v>4.500522190496557</v>
+        <v>4.50052219049654</v>
       </c>
       <c r="F3" t="n">
-        <v>4.500522190496556</v>
+        <v>4.500522190496547</v>
       </c>
       <c r="G3" t="n">
-        <v>4.645411735598472</v>
+        <v>4.645411735598366</v>
       </c>
       <c r="H3" t="n">
-        <v>4.65403215681926</v>
+        <v>4.654032156819115</v>
       </c>
       <c r="I3" t="n">
-        <v>4.596127718719712</v>
+        <v>4.596127718719708</v>
       </c>
       <c r="J3" t="n">
-        <v>4.65403215681926</v>
+        <v>4.654032156819115</v>
       </c>
       <c r="K3" t="n">
-        <v>4.65403215681926</v>
+        <v>4.654032156819115</v>
       </c>
       <c r="L3" t="n">
-        <v>4.65403215681926</v>
+        <v>4.654032156819115</v>
       </c>
     </row>
     <row r="4">
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>761.3589314122838</v>
+        <v>761.3589314122839</v>
       </c>
       <c r="C4" t="n">
-        <v>636.1188614623723</v>
+        <v>636.1188614623718</v>
       </c>
       <c r="D4" t="n">
-        <v>636.423489509952</v>
+        <v>761.5675668045438</v>
       </c>
       <c r="E4" t="n">
         <v>573.2908886521617</v>
@@ -1798,22 +1798,22 @@
         <v>636.2468724138856</v>
       </c>
       <c r="G4" t="n">
-        <v>636.2938016015572</v>
+        <v>636.2938016015568</v>
       </c>
       <c r="H4" t="n">
         <v>762.1470385037624</v>
       </c>
       <c r="I4" t="n">
-        <v>636.2445175846785</v>
+        <v>636.2445175846781</v>
       </c>
       <c r="J4" t="n">
-        <v>668.5807281776995</v>
+        <v>668.5807281776996</v>
       </c>
       <c r="K4" t="n">
-        <v>636.2371950889307</v>
+        <v>636.2371950889305</v>
       </c>
       <c r="L4" t="n">
-        <v>636.3198821526283</v>
+        <v>636.3198821526271</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.08387289981458</v>
+        <v>10.08387289981451</v>
       </c>
       <c r="C5" t="n">
-        <v>10.07468776439313</v>
+        <v>10.07468776439312</v>
       </c>
       <c r="D5" t="n">
-        <v>10.0838693464213</v>
+        <v>10.08386934642133</v>
       </c>
       <c r="E5" t="n">
-        <v>10.01955768622232</v>
+        <v>10.01955768622231</v>
       </c>
       <c r="F5" t="n">
-        <v>10.01955768622232</v>
+        <v>10.01955768622231</v>
       </c>
       <c r="G5" t="n">
-        <v>10.07525247859375</v>
+        <v>10.07525247859378</v>
       </c>
       <c r="H5" t="n">
-        <v>10.08387289981458</v>
+        <v>10.08387289981451</v>
       </c>
       <c r="I5" t="n">
-        <v>10.02596846171506</v>
+        <v>10.02596846171505</v>
       </c>
       <c r="J5" t="n">
-        <v>10.08387289981458</v>
+        <v>10.08387289981451</v>
       </c>
       <c r="K5" t="n">
-        <v>10.08387289981458</v>
+        <v>10.08387289981451</v>
       </c>
       <c r="L5" t="n">
-        <v>10.08387289981458</v>
+        <v>10.08387289981451</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.03714459011217</v>
+        <v>12.03714459011187</v>
       </c>
       <c r="C6" t="n">
-        <v>17.63023241631926</v>
+        <v>17.63023241642053</v>
       </c>
       <c r="D6" t="n">
-        <v>18.80722802680994</v>
+        <v>18.80722802680982</v>
       </c>
       <c r="E6" t="n">
-        <v>16.048547864456</v>
+        <v>16.04854786445596</v>
       </c>
       <c r="F6" t="n">
-        <v>12.15316261322481</v>
+        <v>12.15316261322478</v>
       </c>
       <c r="G6" t="n">
-        <v>17.635884842044</v>
+        <v>17.63588484204398</v>
       </c>
       <c r="H6" t="n">
-        <v>17.64450526328463</v>
+        <v>17.64450526328448</v>
       </c>
       <c r="I6" t="n">
-        <v>17.58660082516526</v>
+        <v>17.58660082516523</v>
       </c>
       <c r="J6" t="n">
-        <v>17.64560726154337</v>
+        <v>17.64560726154332</v>
       </c>
       <c r="K6" t="n">
-        <v>11.93298498757848</v>
+        <v>11.93298498757819</v>
       </c>
       <c r="L6" t="n">
-        <v>23.50186235811939</v>
+        <v>23.50186235811909</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.40697900961925</v>
+        <v>20.40697900961904</v>
       </c>
       <c r="C7" t="n">
-        <v>25.15313360717938</v>
+        <v>25.15313360717934</v>
       </c>
       <c r="D7" t="n">
-        <v>25.16232288867124</v>
+        <v>25.16232288867118</v>
       </c>
       <c r="E7" t="n">
-        <v>30.59197548370666</v>
+        <v>30.59197548370663</v>
       </c>
       <c r="F7" t="n">
-        <v>25.10441127160053</v>
+        <v>25.10441127160049</v>
       </c>
       <c r="G7" t="n">
-        <v>25.15369832138009</v>
+        <v>25.15369832137996</v>
       </c>
       <c r="H7" t="n">
-        <v>25.16231874260079</v>
+        <v>25.1623187426007</v>
       </c>
       <c r="I7" t="n">
-        <v>25.1044143045013</v>
+        <v>25.10441430450127</v>
       </c>
       <c r="J7" t="n">
-        <v>25.16231874260079</v>
+        <v>25.1623187426007</v>
       </c>
       <c r="K7" t="n">
-        <v>22.40705796947224</v>
+        <v>22.40705796947208</v>
       </c>
       <c r="L7" t="n">
-        <v>25.16231874260079</v>
+        <v>25.1623187426007</v>
       </c>
     </row>
     <row r="8">
@@ -1946,7 +1946,7 @@
         <v>164.6376622185687</v>
       </c>
       <c r="C8" t="n">
-        <v>166.1166456253176</v>
+        <v>166.1166456253175</v>
       </c>
       <c r="D8" t="n">
         <v>166.1673071425723</v>
@@ -1961,19 +1961,19 @@
         <v>166.1259830746846</v>
       </c>
       <c r="H8" t="n">
-        <v>165.6137950311644</v>
+        <v>165.6137950311643</v>
       </c>
       <c r="I8" t="n">
         <v>167.1570913551207</v>
       </c>
       <c r="J8" t="n">
-        <v>173.9393196470939</v>
+        <v>173.9393196470937</v>
       </c>
       <c r="K8" t="n">
-        <v>175.1481084081328</v>
+        <v>175.1481084081326</v>
       </c>
       <c r="L8" t="n">
-        <v>181.4233716428732</v>
+        <v>181.423371642873</v>
       </c>
     </row>
     <row r="9">
@@ -1986,10 +1986,10 @@
         <v>163.2982484286498</v>
       </c>
       <c r="C9" t="n">
-        <v>165.089677291842</v>
+        <v>165.0896772918421</v>
       </c>
       <c r="D9" t="n">
-        <v>166.776408502098</v>
+        <v>166.7764085020979</v>
       </c>
       <c r="E9" t="n">
         <v>166.3671850357485</v>
@@ -1998,22 +1998,22 @@
         <v>166.3671850357485</v>
       </c>
       <c r="G9" t="n">
-        <v>166.2905118839966</v>
+        <v>166.2905118839965</v>
       </c>
       <c r="H9" t="n">
-        <v>166.5564876508733</v>
+        <v>166.5564876508731</v>
       </c>
       <c r="I9" t="n">
         <v>166.3671850357485</v>
       </c>
       <c r="J9" t="n">
-        <v>176.2334407230931</v>
+        <v>176.2334407230928</v>
       </c>
       <c r="K9" t="n">
-        <v>174.3829473298673</v>
+        <v>174.3829473298672</v>
       </c>
       <c r="L9" t="n">
-        <v>180.3811599867714</v>
+        <v>180.3811599867713</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.90281054143438</v>
+        <v>41.90281054143465</v>
       </c>
       <c r="C2" t="n">
-        <v>75.62186661498899</v>
+        <v>75.62186661499562</v>
       </c>
       <c r="D2" t="n">
-        <v>179.7509796498915</v>
+        <v>179.750979649901</v>
       </c>
       <c r="E2" t="n">
-        <v>47.59177106935275</v>
+        <v>47.59177106935247</v>
       </c>
       <c r="F2" t="n">
-        <v>47.59177106935275</v>
+        <v>47.59177106935247</v>
       </c>
       <c r="G2" t="n">
-        <v>136.6908737782674</v>
+        <v>136.690873778271</v>
       </c>
       <c r="H2" t="n">
-        <v>173.3901601173734</v>
+        <v>173.390160117372</v>
       </c>
       <c r="I2" t="n">
-        <v>47.59177106935275</v>
+        <v>47.59177106935247</v>
       </c>
       <c r="J2" t="n">
-        <v>284.3814951317996</v>
+        <v>284.3814951317976</v>
       </c>
       <c r="K2" t="n">
-        <v>60.37286861775038</v>
+        <v>60.37286861775041</v>
       </c>
       <c r="L2" t="n">
-        <v>71.43816753738837</v>
+        <v>71.43816753738896</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.033430896842562</v>
+        <v>4.033430896842621</v>
       </c>
       <c r="C3" t="n">
         <v>3.792653835049977</v>
       </c>
       <c r="D3" t="n">
-        <v>4.033430896842562</v>
+        <v>4.033430896842622</v>
       </c>
       <c r="E3" t="n">
         <v>3.8209658820942</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8209658820942</v>
+        <v>3.820965882094202</v>
       </c>
       <c r="G3" t="n">
-        <v>4.024148004457738</v>
+        <v>4.024148004457774</v>
       </c>
       <c r="H3" t="n">
-        <v>4.033430896842562</v>
+        <v>4.033430896842622</v>
       </c>
       <c r="I3" t="n">
-        <v>3.971152062712585</v>
+        <v>3.971152062712598</v>
       </c>
       <c r="J3" t="n">
-        <v>4.033430896842562</v>
+        <v>4.033430896842621</v>
       </c>
       <c r="K3" t="n">
-        <v>4.033430896842562</v>
+        <v>4.033430896842622</v>
       </c>
       <c r="L3" t="n">
-        <v>4.033430896842562</v>
+        <v>4.033430896842622</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>759.9230567086329</v>
+        <v>635.333953495126</v>
       </c>
       <c r="C4" t="n">
-        <v>635.2157570335362</v>
+        <v>635.2157570335353</v>
       </c>
       <c r="D4" t="n">
-        <v>635.4862881666726</v>
+        <v>635.4862881666839</v>
       </c>
       <c r="E4" t="n">
-        <v>572.3050697076364</v>
+        <v>572.3050697076369</v>
       </c>
       <c r="F4" t="n">
-        <v>635.2566451833884</v>
+        <v>635.2566451833879</v>
       </c>
       <c r="G4" t="n">
-        <v>635.324670602741</v>
+        <v>759.9137738162481</v>
       </c>
       <c r="H4" t="n">
         <v>760.5663447728617</v>
       </c>
       <c r="I4" t="n">
-        <v>635.2716746609955</v>
+        <v>759.8607778745026</v>
       </c>
       <c r="J4" t="n">
-        <v>667.5695796759229</v>
+        <v>760.2578805838834</v>
       </c>
       <c r="K4" t="n">
-        <v>635.2340297995701</v>
+        <v>635.2340297995697</v>
       </c>
       <c r="L4" t="n">
-        <v>635.3484419680619</v>
+        <v>635.348441968062</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.994890379058505</v>
+        <v>8.994890379058573</v>
       </c>
       <c r="C5" t="n">
-        <v>8.987021207959453</v>
+        <v>8.987021207959403</v>
       </c>
       <c r="D5" t="n">
-        <v>8.994882019361249</v>
+        <v>8.994882019361253</v>
       </c>
       <c r="E5" t="n">
-        <v>8.913490612020034</v>
+        <v>8.913490612020004</v>
       </c>
       <c r="F5" t="n">
-        <v>8.913490612020034</v>
+        <v>8.913490612020004</v>
       </c>
       <c r="G5" t="n">
-        <v>8.985607486673814</v>
+        <v>8.985607486673723</v>
       </c>
       <c r="H5" t="n">
-        <v>8.994890379058505</v>
+        <v>8.994890379058573</v>
       </c>
       <c r="I5" t="n">
-        <v>8.932611544928591</v>
+        <v>8.932611544928582</v>
       </c>
       <c r="J5" t="n">
-        <v>8.994890379058505</v>
+        <v>8.994890379058573</v>
       </c>
       <c r="K5" t="n">
-        <v>8.994890379058505</v>
+        <v>8.994890379058573</v>
       </c>
       <c r="L5" t="n">
-        <v>8.994890379058505</v>
+        <v>8.994890379058573</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.57088262809963</v>
+        <v>10.57088262809954</v>
       </c>
       <c r="C6" t="n">
-        <v>15.46994079168756</v>
+        <v>15.46994079159981</v>
       </c>
       <c r="D6" t="n">
         <v>16.51625629870694</v>
       </c>
       <c r="E6" t="n">
-        <v>14.07067416570982</v>
+        <v>14.07067416570983</v>
       </c>
       <c r="F6" t="n">
-        <v>10.65329461153435</v>
+        <v>10.65329461153436</v>
       </c>
       <c r="G6" t="n">
-        <v>15.48588978609799</v>
+        <v>15.48588978609794</v>
       </c>
       <c r="H6" t="n">
         <v>15.49517267849279</v>
       </c>
       <c r="I6" t="n">
-        <v>15.43289384435278</v>
+        <v>15.43289384435282</v>
       </c>
       <c r="J6" t="n">
-        <v>15.49614043549104</v>
+        <v>15.49614043549112</v>
       </c>
       <c r="K6" t="n">
-        <v>10.47941141292247</v>
+        <v>10.47941141292248</v>
       </c>
       <c r="L6" t="n">
-        <v>20.63900539197374</v>
+        <v>20.6390053919737</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.90810999663437</v>
+        <v>16.90810999663429</v>
       </c>
       <c r="C7" t="n">
-        <v>20.79614452025055</v>
+        <v>20.79614452025038</v>
       </c>
       <c r="D7" t="n">
-        <v>20.80401715849967</v>
+        <v>20.80401715849939</v>
       </c>
       <c r="E7" t="n">
-        <v>25.23752516979613</v>
+        <v>25.2375251697961</v>
       </c>
       <c r="F7" t="n">
-        <v>20.7417323941371</v>
+        <v>20.74173239413653</v>
       </c>
       <c r="G7" t="n">
         <v>20.7947307989649</v>
       </c>
       <c r="H7" t="n">
-        <v>20.80401369134961</v>
+        <v>20.80401369134982</v>
       </c>
       <c r="I7" t="n">
-        <v>20.74173485721967</v>
+        <v>20.74173485721957</v>
       </c>
       <c r="J7" t="n">
-        <v>20.80401369134961</v>
+        <v>20.80401369134982</v>
       </c>
       <c r="K7" t="n">
-        <v>18.45513157747683</v>
+        <v>15.89837462474266</v>
       </c>
       <c r="L7" t="n">
-        <v>20.80401369134961</v>
+        <v>20.80401369134982</v>
       </c>
     </row>
     <row r="8">
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>165.4862733937211</v>
+        <v>165.4862733937213</v>
       </c>
       <c r="C8" t="n">
-        <v>166.7777969210057</v>
+        <v>166.7777969210055</v>
       </c>
       <c r="D8" t="n">
-        <v>166.558195953706</v>
+        <v>166.5581959537062</v>
       </c>
       <c r="E8" t="n">
         <v>168.7046078054658</v>
@@ -2363,10 +2363,10 @@
         <v>168.7046078054658</v>
       </c>
       <c r="J8" t="n">
-        <v>175.3465556616987</v>
+        <v>175.3465556616989</v>
       </c>
       <c r="K8" t="n">
-        <v>177.0805907819433</v>
+        <v>177.0805907819434</v>
       </c>
       <c r="L8" t="n">
         <v>182.6090944023933</v>
@@ -2379,19 +2379,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163.4375417826227</v>
+        <v>163.4375417826225</v>
       </c>
       <c r="C9" t="n">
-        <v>165.1765634717209</v>
+        <v>165.1765634717208</v>
       </c>
       <c r="D9" t="n">
         <v>166.4540434908918</v>
       </c>
       <c r="E9" t="n">
-        <v>166.6997116919295</v>
+        <v>166.6997116919294</v>
       </c>
       <c r="F9" t="n">
-        <v>166.6997116919295</v>
+        <v>166.6997116919294</v>
       </c>
       <c r="G9" t="n">
         <v>166.7238658762157</v>
@@ -2400,16 +2400,16 @@
         <v>166.7202790965732</v>
       </c>
       <c r="I9" t="n">
-        <v>166.6997116919295</v>
+        <v>166.6997116919294</v>
       </c>
       <c r="J9" t="n">
-        <v>176.380024286043</v>
+        <v>176.3800242860432</v>
       </c>
       <c r="K9" t="n">
         <v>175.1275041280697</v>
       </c>
       <c r="L9" t="n">
-        <v>180.5994611207726</v>
+        <v>180.5994611207727</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94.35419197869609</v>
+        <v>94.35419197869672</v>
       </c>
       <c r="C2" t="n">
-        <v>39.61709796133677</v>
+        <v>39.61709796133784</v>
       </c>
       <c r="D2" t="n">
-        <v>212.3513906828524</v>
+        <v>212.3513906828592</v>
       </c>
       <c r="E2" t="n">
-        <v>178.3728855687162</v>
+        <v>178.3728855687187</v>
       </c>
       <c r="F2" t="n">
-        <v>178.3728855687162</v>
+        <v>178.3728855687187</v>
       </c>
       <c r="G2" t="n">
-        <v>228.5169528456166</v>
+        <v>228.5169528456253</v>
       </c>
       <c r="H2" t="n">
-        <v>462.7769158990591</v>
+        <v>462.7769158990602</v>
       </c>
       <c r="I2" t="n">
-        <v>178.3728855687162</v>
+        <v>178.3728855687187</v>
       </c>
       <c r="J2" t="n">
-        <v>482.0952792099476</v>
+        <v>482.0952792099491</v>
       </c>
       <c r="K2" t="n">
-        <v>218.4135435433686</v>
+        <v>218.4135435433685</v>
       </c>
       <c r="L2" t="n">
-        <v>216.0365139386736</v>
+        <v>216.0365139386748</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.9509174653024</v>
+        <v>4.950917465302438</v>
       </c>
       <c r="C3" t="n">
-        <v>4.49113100856427</v>
+        <v>4.491131008564323</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9509174653024</v>
+        <v>4.950917465302438</v>
       </c>
       <c r="E3" t="n">
-        <v>4.814511809198762</v>
+        <v>4.814511809198767</v>
       </c>
       <c r="F3" t="n">
-        <v>4.814511809198756</v>
+        <v>4.814511809198768</v>
       </c>
       <c r="G3" t="n">
-        <v>4.943425219573125</v>
+        <v>4.943425219573128</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9509174653024</v>
+        <v>4.950917465302438</v>
       </c>
       <c r="I3" t="n">
-        <v>4.900438303293948</v>
+        <v>4.900438303293964</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9509174653024</v>
+        <v>4.950917465302438</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9509174653024</v>
+        <v>4.950917465302438</v>
       </c>
       <c r="L3" t="n">
-        <v>4.9509174653024</v>
+        <v>4.950917465302438</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>804.0576469182126</v>
+        <v>671.8823159171984</v>
       </c>
       <c r="C4" t="n">
-        <v>671.4847386258185</v>
+        <v>671.4847386258182</v>
       </c>
       <c r="D4" t="n">
-        <v>671.9145504720125</v>
+        <v>671.9145504719751</v>
       </c>
       <c r="E4" t="n">
-        <v>605.3979045119115</v>
+        <v>605.397904511913</v>
       </c>
       <c r="F4" t="n">
-        <v>671.8521436927875</v>
+        <v>671.8521436927873</v>
       </c>
       <c r="G4" t="n">
         <v>671.8748236714696</v>
       </c>
       <c r="H4" t="n">
-        <v>805.0336973200042</v>
+        <v>805.0336973200033</v>
       </c>
       <c r="I4" t="n">
-        <v>804.0071677562045</v>
+        <v>671.8318367551897</v>
       </c>
       <c r="J4" t="n">
         <v>804.4783920828395</v>
       </c>
       <c r="K4" t="n">
-        <v>671.9229190371922</v>
+        <v>671.9229190371918</v>
       </c>
       <c r="L4" t="n">
-        <v>671.9164913473563</v>
+        <v>671.9164913473567</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.87471595029861</v>
+        <v>10.8747159502987</v>
       </c>
       <c r="C5" t="n">
-        <v>10.86274033071379</v>
+        <v>10.8627403307138</v>
       </c>
       <c r="D5" t="n">
-        <v>10.87472225877024</v>
+        <v>10.87472225877037</v>
       </c>
       <c r="E5" t="n">
-        <v>10.81836696555444</v>
+        <v>10.81836696555451</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81836696555444</v>
+        <v>10.81836696555451</v>
       </c>
       <c r="G5" t="n">
-        <v>10.86722370456933</v>
+        <v>10.86722370456941</v>
       </c>
       <c r="H5" t="n">
-        <v>10.87471595029861</v>
+        <v>10.8747159502987</v>
       </c>
       <c r="I5" t="n">
-        <v>10.82423678829015</v>
+        <v>10.82423678829025</v>
       </c>
       <c r="J5" t="n">
-        <v>10.87471595029861</v>
+        <v>10.8747159502987</v>
       </c>
       <c r="K5" t="n">
-        <v>10.87471595029861</v>
+        <v>10.8747159502987</v>
       </c>
       <c r="L5" t="n">
-        <v>10.87471595029861</v>
+        <v>10.8747159502987</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.11850900200014</v>
+        <v>13.11850900200021</v>
       </c>
       <c r="C6" t="n">
-        <v>19.34988864308495</v>
+        <v>19.34988864308504</v>
       </c>
       <c r="D6" t="n">
-        <v>20.66185219817963</v>
+        <v>20.66185219817975</v>
       </c>
       <c r="E6" t="n">
-        <v>17.60320185635498</v>
+        <v>17.60320185635516</v>
       </c>
       <c r="F6" t="n">
-        <v>13.26257061728785</v>
+        <v>13.2625706172879</v>
       </c>
       <c r="G6" t="n">
-        <v>19.35883428734169</v>
+        <v>19.35883428734184</v>
       </c>
       <c r="H6" t="n">
-        <v>19.36632653309866</v>
+        <v>19.36632653309879</v>
       </c>
       <c r="I6" t="n">
-        <v>19.31584737106252</v>
+        <v>19.31584737106271</v>
       </c>
       <c r="J6" t="n">
-        <v>19.36755439751728</v>
+        <v>19.36755439751738</v>
       </c>
       <c r="K6" t="n">
-        <v>13.00245258466838</v>
+        <v>13.00245258466844</v>
       </c>
       <c r="L6" t="n">
-        <v>25.89269436833883</v>
+        <v>25.8926943683389</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.56508642736606</v>
+        <v>23.56508642736583</v>
       </c>
       <c r="C7" t="n">
-        <v>29.16154621998503</v>
+        <v>29.16154621998511</v>
       </c>
       <c r="D7" t="n">
-        <v>29.17352525324819</v>
+        <v>29.17352525324904</v>
       </c>
       <c r="E7" t="n">
-        <v>35.59505600852167</v>
+        <v>35.59505600852175</v>
       </c>
       <c r="F7" t="n">
-        <v>29.12303843550053</v>
+        <v>29.12303843550102</v>
       </c>
       <c r="G7" t="n">
-        <v>29.16602959384056</v>
+        <v>29.16602959384025</v>
       </c>
       <c r="H7" t="n">
-        <v>29.17352183956985</v>
+        <v>29.17352183956983</v>
       </c>
       <c r="I7" t="n">
-        <v>29.1230426775614</v>
+        <v>29.12304267756166</v>
       </c>
       <c r="J7" t="n">
-        <v>29.17352183956985</v>
+        <v>29.17352183956983</v>
       </c>
       <c r="K7" t="n">
-        <v>22.11149966867307</v>
+        <v>22.11149966867396</v>
       </c>
       <c r="L7" t="n">
-        <v>29.17352183956985</v>
+        <v>29.17352183956983</v>
       </c>
     </row>
     <row r="8">
@@ -2741,28 +2741,28 @@
         <v>167.7646917008386</v>
       </c>
       <c r="D8" t="n">
-        <v>167.17380093503</v>
+        <v>167.1738009350294</v>
       </c>
       <c r="E8" t="n">
-        <v>166.4415408791668</v>
+        <v>166.4415408791667</v>
       </c>
       <c r="F8" t="n">
-        <v>166.4415408791668</v>
+        <v>166.4415408791667</v>
       </c>
       <c r="G8" t="n">
-        <v>165.2514057182714</v>
+        <v>165.2514057182711</v>
       </c>
       <c r="H8" t="n">
         <v>162.6391275551879</v>
       </c>
       <c r="I8" t="n">
-        <v>166.4415408791668</v>
+        <v>166.4415408791667</v>
       </c>
       <c r="J8" t="n">
-        <v>172.4600929918983</v>
+        <v>172.4600929918982</v>
       </c>
       <c r="K8" t="n">
-        <v>173.5141624099638</v>
+        <v>173.5141624099637</v>
       </c>
       <c r="L8" t="n">
         <v>180.3865360521725</v>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157.9040437327917</v>
+        <v>157.9040437327918</v>
       </c>
       <c r="C9" t="n">
-        <v>165.6242077267932</v>
+        <v>165.6242077267931</v>
       </c>
       <c r="D9" t="n">
-        <v>167.3588370944452</v>
+        <v>167.3588370944451</v>
       </c>
       <c r="E9" t="n">
         <v>166.1615605125498</v>
@@ -2799,7 +2799,7 @@
         <v>166.1615605125498</v>
       </c>
       <c r="J9" t="n">
-        <v>175.8407248644212</v>
+        <v>175.8407248644211</v>
       </c>
       <c r="K9" t="n">
         <v>173.6689055426259</v>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.88337365128432</v>
+        <v>38.8833736512843</v>
       </c>
       <c r="C2" t="n">
-        <v>15.97818552545487</v>
+        <v>15.97818552545488</v>
       </c>
       <c r="D2" t="n">
-        <v>89.1488272939408</v>
+        <v>89.14882729394085</v>
       </c>
       <c r="E2" t="n">
-        <v>66.38358347312713</v>
+        <v>66.38358347312729</v>
       </c>
       <c r="F2" t="n">
-        <v>66.38358347312713</v>
+        <v>66.38358347312729</v>
       </c>
       <c r="G2" t="n">
-        <v>84.29988258805196</v>
+        <v>84.29988258805173</v>
       </c>
       <c r="H2" t="n">
         <v>182.5678933623369</v>
       </c>
       <c r="I2" t="n">
-        <v>66.38358347312713</v>
+        <v>66.38358347312729</v>
       </c>
       <c r="J2" t="n">
         <v>213.3979686179301</v>
       </c>
       <c r="K2" t="n">
-        <v>58.74005408497108</v>
+        <v>58.74005408497111</v>
       </c>
       <c r="L2" t="n">
-        <v>46.41916111726325</v>
+        <v>46.41916111726326</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.100153940537441</v>
+        <v>4.100153940537505</v>
       </c>
       <c r="C3" t="n">
-        <v>3.733332373093396</v>
+        <v>3.733332373093398</v>
       </c>
       <c r="D3" t="n">
-        <v>4.100153940537441</v>
+        <v>4.100153940537505</v>
       </c>
       <c r="E3" t="n">
-        <v>3.976689586979306</v>
+        <v>3.976689586979303</v>
       </c>
       <c r="F3" t="n">
-        <v>3.976689586979306</v>
+        <v>3.976689586979303</v>
       </c>
       <c r="G3" t="n">
-        <v>4.093837882289738</v>
+        <v>4.093837882289714</v>
       </c>
       <c r="H3" t="n">
-        <v>4.100153940537441</v>
+        <v>4.100153940537505</v>
       </c>
       <c r="I3" t="n">
-        <v>4.057043847464441</v>
+        <v>4.057043847464437</v>
       </c>
       <c r="J3" t="n">
-        <v>4.100153940537441</v>
+        <v>4.100153940537505</v>
       </c>
       <c r="K3" t="n">
-        <v>4.100153940537441</v>
+        <v>4.100153940537505</v>
       </c>
       <c r="L3" t="n">
-        <v>4.100153940537441</v>
+        <v>4.100153940537505</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.3849698868564</v>
+        <v>635.384969886856</v>
       </c>
       <c r="C4" t="n">
-        <v>635.1980208022019</v>
+        <v>635.1980208022017</v>
       </c>
       <c r="D4" t="n">
-        <v>760.0575075649192</v>
+        <v>635.4170416519902</v>
       </c>
       <c r="E4" t="n">
         <v>572.4685304161827</v>
       </c>
       <c r="F4" t="n">
-        <v>635.3464584545243</v>
+        <v>635.3464584545233</v>
       </c>
       <c r="G4" t="n">
-        <v>635.3786538286088</v>
+        <v>759.8606180200685</v>
       </c>
       <c r="H4" t="n">
-        <v>760.7026177637041</v>
+        <v>760.7026177637032</v>
       </c>
       <c r="I4" t="n">
-        <v>635.3418597937833</v>
+        <v>759.8238239852435</v>
       </c>
       <c r="J4" t="n">
-        <v>667.6057578093581</v>
+        <v>667.605757809358</v>
       </c>
       <c r="K4" t="n">
         <v>635.3515812425295</v>
       </c>
       <c r="L4" t="n">
-        <v>635.3875420276713</v>
+        <v>635.3875420276706</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.90971674025867</v>
+        <v>8.909716740258695</v>
       </c>
       <c r="C5" t="n">
-        <v>8.902446820574463</v>
+        <v>8.902446820574438</v>
       </c>
       <c r="D5" t="n">
-        <v>8.909735293927216</v>
+        <v>8.909735293927245</v>
       </c>
       <c r="E5" t="n">
-        <v>8.85718148998323</v>
+        <v>8.857181489983239</v>
       </c>
       <c r="F5" t="n">
-        <v>8.85718148998323</v>
+        <v>8.857181489983239</v>
       </c>
       <c r="G5" t="n">
-        <v>8.90340068201097</v>
+        <v>8.903400682010988</v>
       </c>
       <c r="H5" t="n">
-        <v>8.90971674025867</v>
+        <v>8.909716740258695</v>
       </c>
       <c r="I5" t="n">
         <v>8.866606647185668</v>
       </c>
       <c r="J5" t="n">
-        <v>8.90971674025867</v>
+        <v>8.909716740258695</v>
       </c>
       <c r="K5" t="n">
-        <v>8.90971674025867</v>
+        <v>8.909716740258695</v>
       </c>
       <c r="L5" t="n">
-        <v>8.90971674025867</v>
+        <v>8.909716740258695</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.42659120529152</v>
+        <v>10.42659120529155</v>
       </c>
       <c r="C6" t="n">
-        <v>15.25863066327083</v>
+        <v>15.25863066327085</v>
       </c>
       <c r="D6" t="n">
-        <v>16.27920497077704</v>
+        <v>16.27920497077702</v>
       </c>
       <c r="E6" t="n">
-        <v>13.89798576413128</v>
+        <v>13.89798576413126</v>
       </c>
       <c r="F6" t="n">
-        <v>10.53150451863473</v>
+        <v>10.53150451863472</v>
       </c>
       <c r="G6" t="n">
-        <v>15.26773627087254</v>
+        <v>15.26773627087255</v>
       </c>
       <c r="H6" t="n">
-        <v>15.27405232915452</v>
+        <v>15.27405232915451</v>
       </c>
       <c r="I6" t="n">
-        <v>15.23094223604724</v>
+        <v>15.23094223604723</v>
       </c>
       <c r="J6" t="n">
-        <v>15.27500498451138</v>
+        <v>15.27500498451141</v>
       </c>
       <c r="K6" t="n">
-        <v>10.33654712708657</v>
+        <v>10.33654712708653</v>
       </c>
       <c r="L6" t="n">
-        <v>20.33763080211135</v>
+        <v>20.3376308021113</v>
       </c>
     </row>
     <row r="7">
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.94303941550412</v>
+        <v>16.94303941550414</v>
       </c>
       <c r="C7" t="n">
-        <v>20.84779883769764</v>
+        <v>20.84779883769766</v>
       </c>
       <c r="D7" t="n">
-        <v>20.85507094716012</v>
+        <v>20.8550709471601</v>
       </c>
       <c r="E7" t="n">
         <v>25.3263570655724</v>
@@ -3106,22 +3106,22 @@
         <v>20.81195667202446</v>
       </c>
       <c r="G7" t="n">
-        <v>20.84875269913415</v>
+        <v>20.84875269913413</v>
       </c>
       <c r="H7" t="n">
-        <v>20.85506875738184</v>
+        <v>20.85506875738187</v>
       </c>
       <c r="I7" t="n">
         <v>20.81195866430885</v>
       </c>
       <c r="J7" t="n">
-        <v>20.85506875738184</v>
+        <v>20.85506875738187</v>
       </c>
       <c r="K7" t="n">
-        <v>18.5884245139853</v>
+        <v>15.92912495364678</v>
       </c>
       <c r="L7" t="n">
-        <v>20.85506875738184</v>
+        <v>20.85506875738187</v>
       </c>
     </row>
     <row r="8">
@@ -3131,34 +3131,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157.7414760657431</v>
+        <v>157.7414760657433</v>
       </c>
       <c r="C8" t="n">
-        <v>167.8663210510701</v>
+        <v>167.86632105107</v>
       </c>
       <c r="D8" t="n">
         <v>168.8539789700452</v>
       </c>
       <c r="E8" t="n">
-        <v>168.0781724920834</v>
+        <v>168.0781724920832</v>
       </c>
       <c r="F8" t="n">
-        <v>168.0781724920834</v>
+        <v>168.0781724920832</v>
       </c>
       <c r="G8" t="n">
-        <v>167.5443998807484</v>
+        <v>167.5443998807485</v>
       </c>
       <c r="H8" t="n">
         <v>167.0915614054946</v>
       </c>
       <c r="I8" t="n">
-        <v>168.0781724920834</v>
+        <v>168.0781724920832</v>
       </c>
       <c r="J8" t="n">
-        <v>177.0713915612118</v>
+        <v>177.0713915612116</v>
       </c>
       <c r="K8" t="n">
-        <v>175.9115431136734</v>
+        <v>175.9115431136735</v>
       </c>
       <c r="L8" t="n">
         <v>183.1115777791237</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155.7727780445749</v>
+        <v>155.7727780445751</v>
       </c>
       <c r="C9" t="n">
-        <v>165.4318276807244</v>
+        <v>165.4318276807246</v>
       </c>
       <c r="D9" t="n">
         <v>167.4388736808459</v>
@@ -3186,7 +3186,7 @@
         <v>166.3460007402072</v>
       </c>
       <c r="G9" t="n">
-        <v>166.0482225955169</v>
+        <v>166.048222595517</v>
       </c>
       <c r="H9" t="n">
         <v>166.7245874331483</v>
@@ -3287,34 +3287,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.96581352492505</v>
+        <v>20.96581352492507</v>
       </c>
       <c r="C2" t="n">
-        <v>11.67518110329354</v>
+        <v>11.67518110329364</v>
       </c>
       <c r="D2" t="n">
-        <v>78.44566520481015</v>
+        <v>78.44566520480981</v>
       </c>
       <c r="E2" t="n">
-        <v>26.12022231020529</v>
+        <v>26.12022231020545</v>
       </c>
       <c r="F2" t="n">
-        <v>26.12022231020529</v>
+        <v>26.12022231020545</v>
       </c>
       <c r="G2" t="n">
-        <v>44.7547286237923</v>
+        <v>44.75472862379282</v>
       </c>
       <c r="H2" t="n">
-        <v>124.9384103100265</v>
+        <v>124.9384103100264</v>
       </c>
       <c r="I2" t="n">
-        <v>26.12022231020529</v>
+        <v>26.12022231020545</v>
       </c>
       <c r="J2" t="n">
-        <v>80.00509154785902</v>
+        <v>80.00509154785871</v>
       </c>
       <c r="K2" t="n">
-        <v>17.4993681441818</v>
+        <v>17.49936814418119</v>
       </c>
       <c r="L2" t="n">
         <v>13.2135181744545</v>
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.577126551821693</v>
+        <v>3.577126551821705</v>
       </c>
       <c r="C3" t="n">
-        <v>3.245569032837268</v>
+        <v>3.245569032837281</v>
       </c>
       <c r="D3" t="n">
-        <v>3.577126551821693</v>
+        <v>3.577126551821705</v>
       </c>
       <c r="E3" t="n">
-        <v>3.417275828195289</v>
+        <v>3.417275828195275</v>
       </c>
       <c r="F3" t="n">
-        <v>3.417275828195289</v>
+        <v>3.417275828195276</v>
       </c>
       <c r="G3" t="n">
-        <v>3.570854608417035</v>
+        <v>3.57085460841741</v>
       </c>
       <c r="H3" t="n">
-        <v>3.577126551821693</v>
+        <v>3.577126551821705</v>
       </c>
       <c r="I3" t="n">
-        <v>3.534162566131508</v>
+        <v>3.534162566131825</v>
       </c>
       <c r="J3" t="n">
-        <v>3.577126551821693</v>
+        <v>3.577126551821705</v>
       </c>
       <c r="K3" t="n">
-        <v>3.577126551821693</v>
+        <v>3.577126551821705</v>
       </c>
       <c r="L3" t="n">
-        <v>3.577126551821693</v>
+        <v>3.577126551821705</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>758.7569898762098</v>
+        <v>758.756989876209</v>
       </c>
       <c r="C4" t="n">
-        <v>634.5205044659799</v>
+        <v>634.5205044659804</v>
       </c>
       <c r="D4" t="n">
-        <v>634.7285468302883</v>
+        <v>634.7285468302888</v>
       </c>
       <c r="E4" t="n">
-        <v>571.7394412108605</v>
+        <v>571.7394412108603</v>
       </c>
       <c r="F4" t="n">
-        <v>634.5927613105714</v>
+        <v>634.5927613105715</v>
       </c>
       <c r="G4" t="n">
-        <v>758.7507179328049</v>
+        <v>758.7507179328036</v>
       </c>
       <c r="H4" t="n">
         <v>759.4837006525111</v>
       </c>
       <c r="I4" t="n">
-        <v>634.5983682858737</v>
+        <v>634.5983682858728</v>
       </c>
       <c r="J4" t="n">
-        <v>759.088281077206</v>
+        <v>759.0882810772071</v>
       </c>
       <c r="K4" t="n">
-        <v>634.5896377999279</v>
+        <v>634.5896377999177</v>
       </c>
       <c r="L4" t="n">
-        <v>634.640488301362</v>
+        <v>634.6404883013613</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.966227511815229</v>
+        <v>7.966227511815243</v>
       </c>
       <c r="C5" t="n">
-        <v>7.960573003186343</v>
+        <v>7.960573003186357</v>
       </c>
       <c r="D5" t="n">
-        <v>7.966251021504551</v>
+        <v>7.966251021504561</v>
       </c>
       <c r="E5" t="n">
-        <v>7.902363342675272</v>
+        <v>7.902363342675264</v>
       </c>
       <c r="F5" t="n">
-        <v>7.902363342675272</v>
+        <v>7.902363342675264</v>
       </c>
       <c r="G5" t="n">
-        <v>7.959955568410572</v>
+        <v>7.959955568410578</v>
       </c>
       <c r="H5" t="n">
-        <v>7.966227511815229</v>
+        <v>7.966227511815243</v>
       </c>
       <c r="I5" t="n">
-        <v>7.923263526125045</v>
+        <v>7.923263526125027</v>
       </c>
       <c r="J5" t="n">
-        <v>7.966227511815229</v>
+        <v>7.966227511815243</v>
       </c>
       <c r="K5" t="n">
-        <v>7.966227511815229</v>
+        <v>7.966227511815243</v>
       </c>
       <c r="L5" t="n">
-        <v>7.966227511815229</v>
+        <v>7.966227511815243</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.112675711765185</v>
+        <v>9.112675711765212</v>
       </c>
       <c r="C6" t="n">
-        <v>13.28046781928151</v>
+        <v>13.28046781928149</v>
       </c>
       <c r="D6" t="n">
-        <v>14.17477073480942</v>
+        <v>14.17477073480945</v>
       </c>
       <c r="E6" t="n">
-        <v>12.09860537909303</v>
+        <v>12.09860537909304</v>
       </c>
       <c r="F6" t="n">
-        <v>9.190132146597213</v>
+        <v>9.190132146597209</v>
       </c>
       <c r="G6" t="n">
-        <v>13.29911318202632</v>
+        <v>13.2991131820263</v>
       </c>
       <c r="H6" t="n">
-        <v>13.30538512546544</v>
+        <v>13.30538512546546</v>
       </c>
       <c r="I6" t="n">
-        <v>13.2624211397408</v>
+        <v>13.26242113974081</v>
       </c>
       <c r="J6" t="n">
-        <v>13.30620910514127</v>
+        <v>13.30620910514129</v>
       </c>
       <c r="K6" t="n">
-        <v>9.034793982581093</v>
+        <v>9.034793982581103</v>
       </c>
       <c r="L6" t="n">
-        <v>17.68502068931021</v>
+        <v>17.68502068931025</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.46628913794595</v>
+        <v>14.46628913794601</v>
       </c>
       <c r="C7" t="n">
-        <v>17.76609383590693</v>
+        <v>17.76609383590695</v>
       </c>
       <c r="D7" t="n">
-        <v>17.77174979587892</v>
+        <v>17.77174979587902</v>
       </c>
       <c r="E7" t="n">
-        <v>21.54321327458048</v>
+        <v>21.54321327458037</v>
       </c>
       <c r="F7" t="n">
-        <v>17.72878257196835</v>
+        <v>17.72878257196839</v>
       </c>
       <c r="G7" t="n">
-        <v>17.76547640113117</v>
+        <v>17.76547640113116</v>
       </c>
       <c r="H7" t="n">
-        <v>17.77174834453582</v>
+        <v>17.7717483445358</v>
       </c>
       <c r="I7" t="n">
-        <v>17.72878435884563</v>
+        <v>17.72878435884572</v>
       </c>
       <c r="J7" t="n">
-        <v>17.77174834453582</v>
+        <v>17.7717483445358</v>
       </c>
       <c r="K7" t="n">
-        <v>15.85655290912681</v>
+        <v>15.77885095217556</v>
       </c>
       <c r="L7" t="n">
-        <v>17.77174834453582</v>
+        <v>17.7717483445358</v>
       </c>
     </row>
     <row r="8">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>154.1516047794874</v>
+        <v>154.1516047794871</v>
       </c>
       <c r="C8" t="n">
         <v>167.8177593128153</v>
@@ -3542,7 +3542,7 @@
         <v>168.6961632596245</v>
       </c>
       <c r="G8" t="n">
-        <v>168.0855687954223</v>
+        <v>168.0855687954221</v>
       </c>
       <c r="H8" t="n">
         <v>167.7249434046072</v>
@@ -3551,10 +3551,10 @@
         <v>168.6961632596245</v>
       </c>
       <c r="J8" t="n">
-        <v>179.4140955470433</v>
+        <v>179.4140955470432</v>
       </c>
       <c r="K8" t="n">
-        <v>177.2718222416553</v>
+        <v>177.2718222416554</v>
       </c>
       <c r="L8" t="n">
         <v>183.4234106757945</v>
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151.9971797689411</v>
+        <v>151.9971797689409</v>
       </c>
       <c r="C9" t="n">
-        <v>165.3279913628163</v>
+        <v>165.3279913628164</v>
       </c>
       <c r="D9" t="n">
         <v>166.950287456705</v>
       </c>
       <c r="E9" t="n">
-        <v>166.3962240747647</v>
+        <v>166.3962240747646</v>
       </c>
       <c r="F9" t="n">
-        <v>166.3962240747647</v>
+        <v>166.3962240747646</v>
       </c>
       <c r="G9" t="n">
-        <v>166.0433094381086</v>
+        <v>166.0433094381085</v>
       </c>
       <c r="H9" t="n">
         <v>166.6339507622188</v>
       </c>
       <c r="I9" t="n">
-        <v>166.3962240747647</v>
+        <v>166.3962240747646</v>
       </c>
       <c r="J9" t="n">
-        <v>177.6537589125205</v>
+        <v>177.6537589125202</v>
       </c>
       <c r="K9" t="n">
         <v>174.7184147590548</v>
       </c>
       <c r="L9" t="n">
-        <v>180.6945521391108</v>
+        <v>180.6945521391107</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.57775513306673</v>
+        <v>79.57775513306632</v>
       </c>
       <c r="C2" t="n">
-        <v>25.07411827773002</v>
+        <v>25.07411827772989</v>
       </c>
       <c r="D2" t="n">
-        <v>128.2756330762766</v>
+        <v>128.2756330762655</v>
       </c>
       <c r="E2" t="n">
-        <v>150.8821779887765</v>
+        <v>150.8821779887758</v>
       </c>
       <c r="F2" t="n">
-        <v>150.8821779887765</v>
+        <v>150.8821779887758</v>
       </c>
       <c r="G2" t="n">
-        <v>161.7614436835521</v>
+        <v>161.7614436835527</v>
       </c>
       <c r="H2" t="n">
-        <v>398.6381048524843</v>
+        <v>398.6381048524841</v>
       </c>
       <c r="I2" t="n">
-        <v>150.8821779887765</v>
+        <v>150.8821779887758</v>
       </c>
       <c r="J2" t="n">
-        <v>322.1565127440267</v>
+        <v>322.1565127440264</v>
       </c>
       <c r="K2" t="n">
-        <v>148.750858327889</v>
+        <v>148.7508583278887</v>
       </c>
       <c r="L2" t="n">
-        <v>168.496546353592</v>
+        <v>168.4965463535912</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.69113957298823</v>
+        <v>4.691139572988048</v>
       </c>
       <c r="C3" t="n">
-        <v>4.278018885682607</v>
+        <v>4.278018885682595</v>
       </c>
       <c r="D3" t="n">
-        <v>4.69113957298823</v>
+        <v>4.691139572988048</v>
       </c>
       <c r="E3" t="n">
-        <v>4.583376414147608</v>
+        <v>4.583376414147607</v>
       </c>
       <c r="F3" t="n">
-        <v>4.583376414147605</v>
+        <v>4.583376414147607</v>
       </c>
       <c r="G3" t="n">
-        <v>4.685179530613965</v>
+        <v>4.68517953061391</v>
       </c>
       <c r="H3" t="n">
-        <v>4.69113957298823</v>
+        <v>4.691139572988048</v>
       </c>
       <c r="I3" t="n">
-        <v>4.650436806301331</v>
+        <v>4.650436806301339</v>
       </c>
       <c r="J3" t="n">
-        <v>4.69113957298823</v>
+        <v>4.691139572988048</v>
       </c>
       <c r="K3" t="n">
-        <v>4.69113957298823</v>
+        <v>4.691139572988048</v>
       </c>
       <c r="L3" t="n">
-        <v>4.69113957298823</v>
+        <v>4.691139572988048</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>803.2602769559398</v>
+        <v>671.4017095096924</v>
       </c>
       <c r="C4" t="n">
         <v>671.088235939243</v>
       </c>
       <c r="D4" t="n">
-        <v>671.3682906260427</v>
+        <v>671.3682906259861</v>
       </c>
       <c r="E4" t="n">
         <v>604.9948366489941</v>
       </c>
       <c r="F4" t="n">
-        <v>671.3823961697983</v>
+        <v>671.3823961697976</v>
       </c>
       <c r="G4" t="n">
-        <v>803.254316913566</v>
+        <v>803.2543169135646</v>
       </c>
       <c r="H4" t="n">
-        <v>804.2226650239338</v>
+        <v>804.222665023934</v>
       </c>
       <c r="I4" t="n">
-        <v>671.3610067430066</v>
+        <v>803.2195741892518</v>
       </c>
       <c r="J4" t="n">
-        <v>803.6666258256951</v>
+        <v>803.6666258256945</v>
       </c>
       <c r="K4" t="n">
-        <v>671.4043627515873</v>
+        <v>671.4043627515857</v>
       </c>
       <c r="L4" t="n">
-        <v>671.4268492574683</v>
+        <v>671.4268492574671</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.25822312751428</v>
+        <v>10.25822312751425</v>
       </c>
       <c r="C5" t="n">
         <v>10.24861595955486</v>
       </c>
       <c r="D5" t="n">
-        <v>10.25823033888279</v>
+        <v>10.25823033888261</v>
       </c>
       <c r="E5" t="n">
-        <v>10.21095280556375</v>
+        <v>10.21095280556371</v>
       </c>
       <c r="F5" t="n">
-        <v>10.21095280556375</v>
+        <v>10.21095280556371</v>
       </c>
       <c r="G5" t="n">
-        <v>10.25226308513997</v>
+        <v>10.25226308513986</v>
       </c>
       <c r="H5" t="n">
-        <v>10.25822312751428</v>
+        <v>10.25822312751425</v>
       </c>
       <c r="I5" t="n">
-        <v>10.21752036082738</v>
+        <v>10.21752036082737</v>
       </c>
       <c r="J5" t="n">
-        <v>10.25822312751428</v>
+        <v>10.25822312751425</v>
       </c>
       <c r="K5" t="n">
-        <v>10.25822312751428</v>
+        <v>10.25822312751425</v>
       </c>
       <c r="L5" t="n">
-        <v>10.25822312751428</v>
+        <v>10.25822312751425</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.23075921582345</v>
+        <v>12.23075921582324</v>
       </c>
       <c r="C6" t="n">
-        <v>17.99133318874395</v>
+        <v>17.9913331887439</v>
       </c>
       <c r="D6" t="n">
-        <v>19.20372820721198</v>
+        <v>19.20372820721187</v>
       </c>
       <c r="E6" t="n">
-        <v>16.38133390412055</v>
+        <v>16.38133390412051</v>
       </c>
       <c r="F6" t="n">
-        <v>12.36920560730756</v>
+        <v>12.36920560730758</v>
       </c>
       <c r="G6" t="n">
-        <v>18.00020097809372</v>
+        <v>18.00020097809357</v>
       </c>
       <c r="H6" t="n">
-        <v>18.00616102049701</v>
+        <v>18.0061610204969</v>
       </c>
       <c r="I6" t="n">
-        <v>17.96545825378115</v>
+        <v>17.9654582537811</v>
       </c>
       <c r="J6" t="n">
-        <v>18.00729604188055</v>
+        <v>18.00729604188044</v>
       </c>
       <c r="K6" t="n">
-        <v>12.12347816313096</v>
+        <v>12.12347816313081</v>
       </c>
       <c r="L6" t="n">
-        <v>24.0390511269044</v>
+        <v>24.03905112690422</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.56288835132207</v>
+        <v>21.56288835132144</v>
       </c>
       <c r="C7" t="n">
-        <v>26.64789102333462</v>
+        <v>26.64789102333421</v>
       </c>
       <c r="D7" t="n">
-        <v>26.65750021947743</v>
+        <v>26.65750021947695</v>
       </c>
       <c r="E7" t="n">
-        <v>32.49586425030404</v>
+        <v>32.49586425030315</v>
       </c>
       <c r="F7" t="n">
-        <v>26.61679163269651</v>
+        <v>26.61679163269609</v>
       </c>
       <c r="G7" t="n">
-        <v>26.65153814891922</v>
+        <v>26.65153814891919</v>
       </c>
       <c r="H7" t="n">
-        <v>26.65749819129342</v>
+        <v>26.65749819129353</v>
       </c>
       <c r="I7" t="n">
-        <v>26.61679542460698</v>
+        <v>26.61679542460672</v>
       </c>
       <c r="J7" t="n">
-        <v>26.65749819129342</v>
+        <v>26.65749819129353</v>
       </c>
       <c r="K7" t="n">
-        <v>23.58590229354322</v>
+        <v>23.70566209498309</v>
       </c>
       <c r="L7" t="n">
-        <v>26.65749819129342</v>
+        <v>26.65749819129353</v>
       </c>
     </row>
     <row r="8">
@@ -3923,34 +3923,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157.41419334238</v>
+        <v>157.4141933423799</v>
       </c>
       <c r="C8" t="n">
-        <v>167.2528914636489</v>
+        <v>167.252891463649</v>
       </c>
       <c r="D8" t="n">
-        <v>168.7612203629305</v>
+        <v>168.7612203629309</v>
       </c>
       <c r="E8" t="n">
-        <v>166.7185249690421</v>
+        <v>166.7185249690422</v>
       </c>
       <c r="F8" t="n">
-        <v>166.7185249690421</v>
+        <v>166.7185249690422</v>
       </c>
       <c r="G8" t="n">
-        <v>166.1342365704934</v>
+        <v>166.1342365704932</v>
       </c>
       <c r="H8" t="n">
         <v>163.5912511901874</v>
       </c>
       <c r="I8" t="n">
-        <v>166.7185249690421</v>
+        <v>166.7185249690422</v>
       </c>
       <c r="J8" t="n">
         <v>175.5029919916132</v>
       </c>
       <c r="K8" t="n">
-        <v>174.2394155929079</v>
+        <v>174.2394155929076</v>
       </c>
       <c r="L8" t="n">
         <v>181.0904687764512</v>
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155.947662500424</v>
+        <v>155.9476625004235</v>
       </c>
       <c r="C9" t="n">
-        <v>164.9329545799288</v>
+        <v>164.9329545799289</v>
       </c>
       <c r="D9" t="n">
         <v>167.8015490759853</v>
       </c>
       <c r="E9" t="n">
-        <v>166.072839547986</v>
+        <v>166.0728395479861</v>
       </c>
       <c r="F9" t="n">
-        <v>166.072839547986</v>
+        <v>166.0728395479861</v>
       </c>
       <c r="G9" t="n">
         <v>165.6009038671066</v>
       </c>
       <c r="H9" t="n">
-        <v>165.7032710279781</v>
+        <v>165.7032710279779</v>
       </c>
       <c r="I9" t="n">
-        <v>166.072839547986</v>
+        <v>166.0728395479861</v>
       </c>
       <c r="J9" t="n">
-        <v>176.8109573828066</v>
+        <v>176.8109573828065</v>
       </c>
       <c r="K9" t="n">
-        <v>173.4590157473392</v>
+        <v>173.4590157473391</v>
       </c>
       <c r="L9" t="n">
-        <v>180.1785779312254</v>
+        <v>180.1785779312252</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.98122813827485</v>
+        <v>35.9812281382748</v>
       </c>
       <c r="C2" t="n">
-        <v>15.10419504429628</v>
+        <v>15.10419504429626</v>
       </c>
       <c r="D2" t="n">
-        <v>93.78777186637254</v>
+        <v>93.78777186637267</v>
       </c>
       <c r="E2" t="n">
-        <v>57.56636978825646</v>
+        <v>57.56636978825627</v>
       </c>
       <c r="F2" t="n">
-        <v>57.56636978825646</v>
+        <v>57.56636978825627</v>
       </c>
       <c r="G2" t="n">
-        <v>67.24666116460557</v>
+        <v>67.24666116460536</v>
       </c>
       <c r="H2" t="n">
-        <v>150.986772534201</v>
+        <v>150.9867725342007</v>
       </c>
       <c r="I2" t="n">
-        <v>57.56636978825646</v>
+        <v>57.56636978825627</v>
       </c>
       <c r="J2" t="n">
         <v>108.4141494893389</v>
       </c>
       <c r="K2" t="n">
-        <v>43.69594633337627</v>
+        <v>43.69594633337608</v>
       </c>
       <c r="L2" t="n">
-        <v>15.81241838808105</v>
+        <v>15.81241838808091</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.89111489993572</v>
+        <v>3.891114899935738</v>
       </c>
       <c r="C3" t="n">
-        <v>3.562740872424735</v>
+        <v>3.562740872424731</v>
       </c>
       <c r="D3" t="n">
-        <v>3.89111489993572</v>
+        <v>3.891114899935738</v>
       </c>
       <c r="E3" t="n">
-        <v>3.767695882959752</v>
+        <v>3.76769588295975</v>
       </c>
       <c r="F3" t="n">
-        <v>3.767695882959753</v>
+        <v>3.767695882959751</v>
       </c>
       <c r="G3" t="n">
-        <v>3.885998812272009</v>
+        <v>3.885998812272014</v>
       </c>
       <c r="H3" t="n">
-        <v>3.89111489993572</v>
+        <v>3.891114899935738</v>
       </c>
       <c r="I3" t="n">
-        <v>3.855849284448297</v>
+        <v>3.855849284448283</v>
       </c>
       <c r="J3" t="n">
-        <v>3.89111489993572</v>
+        <v>3.891114899935738</v>
       </c>
       <c r="K3" t="n">
-        <v>3.89111489993572</v>
+        <v>3.891114899935738</v>
       </c>
       <c r="L3" t="n">
-        <v>3.89111489993572</v>
+        <v>3.891114899935738</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>759.3726103755058</v>
+        <v>635.0533787217905</v>
       </c>
       <c r="C4" t="n">
-        <v>634.8982157565911</v>
+        <v>634.8982157565908</v>
       </c>
       <c r="D4" t="n">
-        <v>635.1200073649129</v>
+        <v>635.1199924345856</v>
       </c>
       <c r="E4" t="n">
-        <v>572.1695117880586</v>
+        <v>572.169511788058</v>
       </c>
       <c r="F4" t="n">
-        <v>635.0210307859073</v>
+        <v>635.0210307859066</v>
       </c>
       <c r="G4" t="n">
-        <v>635.0482626341272</v>
+        <v>635.0482626341264</v>
       </c>
       <c r="H4" t="n">
-        <v>760.1874482620158</v>
+        <v>760.1874482620156</v>
       </c>
       <c r="I4" t="n">
-        <v>635.0181131063032</v>
+        <v>759.3373447600183</v>
       </c>
       <c r="J4" t="n">
-        <v>667.2287975903166</v>
+        <v>759.7233385758896</v>
       </c>
       <c r="K4" t="n">
-        <v>635.0072499962025</v>
+        <v>635.0072499962016</v>
       </c>
       <c r="L4" t="n">
-        <v>635.0492678975949</v>
+        <v>635.0492678975947</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.449333672326256</v>
+        <v>8.449333672326199</v>
       </c>
       <c r="C5" t="n">
-        <v>8.443013885141211</v>
+        <v>8.443013885141214</v>
       </c>
       <c r="D5" t="n">
         <v>8.44934794363623</v>
       </c>
       <c r="E5" t="n">
-        <v>8.400464022989942</v>
+        <v>8.400464022989953</v>
       </c>
       <c r="F5" t="n">
-        <v>8.400464022989942</v>
+        <v>8.400464022989953</v>
       </c>
       <c r="G5" t="n">
-        <v>8.44421758466245</v>
+        <v>8.444217584662475</v>
       </c>
       <c r="H5" t="n">
-        <v>8.449333672326256</v>
+        <v>8.449333672326199</v>
       </c>
       <c r="I5" t="n">
-        <v>8.414068056838744</v>
+        <v>8.414068056838756</v>
       </c>
       <c r="J5" t="n">
-        <v>8.449333672326256</v>
+        <v>8.449333672326199</v>
       </c>
       <c r="K5" t="n">
-        <v>8.449333672326256</v>
+        <v>8.449333672326199</v>
       </c>
       <c r="L5" t="n">
-        <v>8.449333672326256</v>
+        <v>8.449333672326199</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.745025342104466</v>
+        <v>9.745025342104464</v>
       </c>
       <c r="C6" t="n">
-        <v>14.19820083847182</v>
+        <v>14.19820083847179</v>
       </c>
       <c r="D6" t="n">
-        <v>15.14397126130219</v>
+        <v>15.14397126130214</v>
       </c>
       <c r="E6" t="n">
-        <v>12.94764199129915</v>
+        <v>12.94764199129913</v>
       </c>
       <c r="F6" t="n">
-        <v>9.843381994193138</v>
+        <v>9.84338199419312</v>
       </c>
       <c r="G6" t="n">
-        <v>14.21161736668481</v>
+        <v>14.21161736668478</v>
       </c>
       <c r="H6" t="n">
-        <v>14.21673345438765</v>
+        <v>14.21673345438756</v>
       </c>
       <c r="I6" t="n">
-        <v>14.1814678388611</v>
+        <v>14.18146783886107</v>
       </c>
       <c r="J6" t="n">
-        <v>14.21761226429298</v>
+        <v>14.21761226429293</v>
       </c>
       <c r="K6" t="n">
-        <v>9.66196106894054</v>
+        <v>9.661961068940615</v>
       </c>
       <c r="L6" t="n">
-        <v>18.88780648750052</v>
+        <v>18.88780648750054</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.16889186888728</v>
+        <v>16.16889186888723</v>
       </c>
       <c r="C7" t="n">
-        <v>19.88544989703529</v>
+        <v>19.88544989703525</v>
       </c>
       <c r="D7" t="n">
-        <v>19.89177163110043</v>
+        <v>19.89177163110036</v>
       </c>
       <c r="E7" t="n">
-        <v>24.15262584005141</v>
+        <v>24.15262584005139</v>
       </c>
       <c r="F7" t="n">
-        <v>19.85650242893026</v>
+        <v>19.85650242893024</v>
       </c>
       <c r="G7" t="n">
-        <v>19.88665359655652</v>
+        <v>19.88665359655653</v>
       </c>
       <c r="H7" t="n">
-        <v>19.8917696842203</v>
+        <v>19.89176968422026</v>
       </c>
       <c r="I7" t="n">
-        <v>19.85650406873281</v>
+        <v>19.85650406873279</v>
       </c>
       <c r="J7" t="n">
-        <v>19.8917696842203</v>
+        <v>19.89176968422026</v>
       </c>
       <c r="K7" t="n">
-        <v>15.20400147878702</v>
+        <v>17.73472047599701</v>
       </c>
       <c r="L7" t="n">
-        <v>19.8917696842203</v>
+        <v>19.89176968422026</v>
       </c>
     </row>
     <row r="8">
@@ -4322,16 +4322,16 @@
         <v>138.284122224884</v>
       </c>
       <c r="C8" t="n">
-        <v>166.556631715875</v>
+        <v>166.5566317158751</v>
       </c>
       <c r="D8" t="n">
-        <v>168.4674026071027</v>
+        <v>168.4674026071028</v>
       </c>
       <c r="E8" t="n">
         <v>167.562393960894</v>
       </c>
       <c r="F8" t="n">
-        <v>167.562393960894</v>
+        <v>167.5623939608941</v>
       </c>
       <c r="G8" t="n">
         <v>165.607321818474</v>
@@ -4340,16 +4340,16 @@
         <v>167.4980581397496</v>
       </c>
       <c r="I8" t="n">
-        <v>167.562393960894</v>
+        <v>167.5623939608941</v>
       </c>
       <c r="J8" t="n">
-        <v>179.0578103295423</v>
+        <v>179.0578103295421</v>
       </c>
       <c r="K8" t="n">
-        <v>174.0769404675182</v>
+        <v>174.0769404675183</v>
       </c>
       <c r="L8" t="n">
-        <v>183.5464368708611</v>
+        <v>183.5464368708612</v>
       </c>
     </row>
     <row r="9">
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136.5810625287658</v>
+        <v>136.5810625287657</v>
       </c>
       <c r="C9" t="n">
-        <v>164.1314335102908</v>
+        <v>164.1314335102907</v>
       </c>
       <c r="D9" t="n">
-        <v>167.1246982474523</v>
+        <v>167.1246982474525</v>
       </c>
       <c r="E9" t="n">
         <v>165.7163733351333</v>
@@ -4386,7 +4386,7 @@
         <v>177.6810623645385</v>
       </c>
       <c r="K9" t="n">
-        <v>171.9387421881015</v>
+        <v>171.9387421881016</v>
       </c>
       <c r="L9" t="n">
         <v>180.8455949270466</v>
@@ -4475,34 +4475,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.73383667465115</v>
+        <v>20.73383667465116</v>
       </c>
       <c r="C2" t="n">
-        <v>11.34440422524635</v>
+        <v>11.34440422524625</v>
       </c>
       <c r="D2" t="n">
-        <v>93.44216036394577</v>
+        <v>93.4421603639458</v>
       </c>
       <c r="E2" t="n">
-        <v>21.35183556280414</v>
+        <v>21.35183556280407</v>
       </c>
       <c r="F2" t="n">
-        <v>21.35183556280414</v>
+        <v>21.35183556280407</v>
       </c>
       <c r="G2" t="n">
-        <v>46.04419400599365</v>
+        <v>46.04419400599361</v>
       </c>
       <c r="H2" t="n">
-        <v>114.674501696752</v>
+        <v>114.6745016967521</v>
       </c>
       <c r="I2" t="n">
-        <v>21.35183556280414</v>
+        <v>21.35183556280407</v>
       </c>
       <c r="J2" t="n">
-        <v>63.73476159041781</v>
+        <v>63.73476159041789</v>
       </c>
       <c r="K2" t="n">
-        <v>19.87471466096457</v>
+        <v>19.87471466096459</v>
       </c>
       <c r="L2" t="n">
         <v>12.44592307208802</v>
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.352573259842932</v>
+        <v>3.352573259842935</v>
       </c>
       <c r="C3" t="n">
-        <v>3.062108742018134</v>
+        <v>3.062108742018052</v>
       </c>
       <c r="D3" t="n">
-        <v>3.352573259842932</v>
+        <v>3.352573259842935</v>
       </c>
       <c r="E3" t="n">
-        <v>3.231237136263351</v>
+        <v>3.231237136263355</v>
       </c>
       <c r="F3" t="n">
-        <v>3.231237136263345</v>
+        <v>3.231237136263356</v>
       </c>
       <c r="G3" t="n">
-        <v>3.350016733967895</v>
+        <v>3.350016733967897</v>
       </c>
       <c r="H3" t="n">
-        <v>3.352573259842932</v>
+        <v>3.352573259842935</v>
       </c>
       <c r="I3" t="n">
-        <v>3.33434093725582</v>
+        <v>3.334340937255822</v>
       </c>
       <c r="J3" t="n">
-        <v>3.352573259842932</v>
+        <v>3.352573259842935</v>
       </c>
       <c r="K3" t="n">
-        <v>3.352573259842932</v>
+        <v>3.352573259842935</v>
       </c>
       <c r="L3" t="n">
-        <v>3.352573259842932</v>
+        <v>3.352573259842935</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>758.3168363328424</v>
+        <v>634.3368085006531</v>
       </c>
       <c r="C4" t="n">
-        <v>634.2220350742107</v>
+        <v>634.2220350742103</v>
       </c>
       <c r="D4" t="n">
-        <v>634.4450739538125</v>
+        <v>634.4450739538123</v>
       </c>
       <c r="E4" t="n">
-        <v>571.4687593975456</v>
+        <v>571.4687593975458</v>
       </c>
       <c r="F4" t="n">
-        <v>634.3115547975866</v>
+        <v>634.3115547975868</v>
       </c>
       <c r="G4" t="n">
-        <v>758.314279806968</v>
+        <v>758.314279806967</v>
       </c>
       <c r="H4" t="n">
-        <v>759.0102398169188</v>
+        <v>759.0102398169186</v>
       </c>
       <c r="I4" t="n">
-        <v>634.3185761780665</v>
+        <v>758.2986040102548</v>
       </c>
       <c r="J4" t="n">
-        <v>758.6281463452615</v>
+        <v>666.480468061166</v>
       </c>
       <c r="K4" t="n">
-        <v>634.2847461594478</v>
+        <v>634.2847461594481</v>
       </c>
       <c r="L4" t="n">
-        <v>634.3358272898599</v>
+        <v>634.3358272898602</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.54707811122455</v>
+        <v>7.547078111224542</v>
       </c>
       <c r="C5" t="n">
-        <v>7.541876157291337</v>
+        <v>7.541876157291278</v>
       </c>
       <c r="D5" t="n">
-        <v>7.54709095472339</v>
+        <v>7.547090954723383</v>
       </c>
       <c r="E5" t="n">
-        <v>7.51211143924805</v>
+        <v>7.512111439248045</v>
       </c>
       <c r="F5" t="n">
-        <v>7.51211143924805</v>
+        <v>7.512111439248045</v>
       </c>
       <c r="G5" t="n">
-        <v>7.544521585349509</v>
+        <v>7.544521585349502</v>
       </c>
       <c r="H5" t="n">
-        <v>7.54707811122455</v>
+        <v>7.547078111224542</v>
       </c>
       <c r="I5" t="n">
-        <v>7.528845788637434</v>
+        <v>7.528845788637431</v>
       </c>
       <c r="J5" t="n">
-        <v>7.54707811122455</v>
+        <v>7.547078111224542</v>
       </c>
       <c r="K5" t="n">
-        <v>7.54707811122455</v>
+        <v>7.547078111224542</v>
       </c>
       <c r="L5" t="n">
-        <v>7.54707811122455</v>
+        <v>7.547078111224542</v>
       </c>
     </row>
     <row r="6">
@@ -4635,34 +4635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.490300581310308</v>
+        <v>8.490300581310317</v>
       </c>
       <c r="C6" t="n">
-        <v>12.32475319943169</v>
+        <v>12.32475319943163</v>
       </c>
       <c r="D6" t="n">
-        <v>13.14463935327346</v>
+        <v>13.14463935327345</v>
       </c>
       <c r="E6" t="n">
-        <v>11.25911114962812</v>
+        <v>11.25911114962814</v>
       </c>
       <c r="F6" t="n">
-        <v>8.584274755982397</v>
+        <v>8.584274755982399</v>
       </c>
       <c r="G6" t="n">
         <v>12.34272700115274</v>
       </c>
       <c r="H6" t="n">
-        <v>12.34528352706519</v>
+        <v>12.3452835270652</v>
       </c>
       <c r="I6" t="n">
-        <v>12.32705120444068</v>
+        <v>12.32705120444067</v>
       </c>
       <c r="J6" t="n">
-        <v>12.3460411352183</v>
+        <v>12.34604113521831</v>
       </c>
       <c r="K6" t="n">
-        <v>8.418692294529679</v>
+        <v>8.418692294529675</v>
       </c>
       <c r="L6" t="n">
         <v>16.37213555623944</v>
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.99929701972376</v>
+        <v>13.99929701972374</v>
       </c>
       <c r="C7" t="n">
-        <v>17.19552952731755</v>
+        <v>17.19552952731749</v>
       </c>
       <c r="D7" t="n">
-        <v>17.20073299210801</v>
+        <v>17.20073299210802</v>
       </c>
       <c r="E7" t="n">
-        <v>20.87688600502203</v>
+        <v>20.876886005022</v>
       </c>
       <c r="F7" t="n">
-        <v>17.18249755334294</v>
+        <v>17.18249755334288</v>
       </c>
       <c r="G7" t="n">
-        <v>17.19817495537573</v>
+        <v>17.19817495537574</v>
       </c>
       <c r="H7" t="n">
-        <v>17.2007314812508</v>
+        <v>17.20073148125076</v>
       </c>
       <c r="I7" t="n">
-        <v>17.18249915866366</v>
+        <v>17.18249915866362</v>
       </c>
       <c r="J7" t="n">
-        <v>17.2007314812508</v>
+        <v>17.20073148125076</v>
       </c>
       <c r="K7" t="n">
-        <v>15.27055178355447</v>
+        <v>15.27055178355444</v>
       </c>
       <c r="L7" t="n">
-        <v>17.2007314812508</v>
+        <v>17.20073148125076</v>
       </c>
     </row>
     <row r="8">
@@ -4715,34 +4715,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.94153299843909</v>
+        <v>84.94153299843899</v>
       </c>
       <c r="C8" t="n">
-        <v>166.0241795584538</v>
+        <v>166.0241795584537</v>
       </c>
       <c r="D8" t="n">
         <v>167.8833525394915</v>
       </c>
       <c r="E8" t="n">
-        <v>168.3253492753853</v>
+        <v>168.3253492753852</v>
       </c>
       <c r="F8" t="n">
-        <v>168.3253492753853</v>
+        <v>168.3253492753852</v>
       </c>
       <c r="G8" t="n">
-        <v>161.2175722584882</v>
+        <v>161.2175722584881</v>
       </c>
       <c r="H8" t="n">
         <v>167.6878697767208</v>
       </c>
       <c r="I8" t="n">
-        <v>168.3253492753853</v>
+        <v>168.3253492753852</v>
       </c>
       <c r="J8" t="n">
-        <v>179.3720552412972</v>
+        <v>179.3720552412973</v>
       </c>
       <c r="K8" t="n">
-        <v>175.7727656767249</v>
+        <v>175.7727656767247</v>
       </c>
       <c r="L8" t="n">
         <v>183.2458491362292</v>
@@ -4755,19 +4755,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.86836588048064</v>
+        <v>83.86836588048051</v>
       </c>
       <c r="C9" t="n">
-        <v>163.5588814006605</v>
+        <v>163.5588814006607</v>
       </c>
       <c r="D9" t="n">
         <v>166.5482308966538</v>
       </c>
       <c r="E9" t="n">
-        <v>165.965522097012</v>
+        <v>165.9655220970119</v>
       </c>
       <c r="F9" t="n">
-        <v>165.965522097012</v>
+        <v>165.9655220970119</v>
       </c>
       <c r="G9" t="n">
         <v>159.3015061780957</v>
@@ -4776,13 +4776,13 @@
         <v>166.470794687125</v>
       </c>
       <c r="I9" t="n">
-        <v>165.965522097012</v>
+        <v>165.9655220970119</v>
       </c>
       <c r="J9" t="n">
         <v>177.3958365527734</v>
       </c>
       <c r="K9" t="n">
-        <v>173.2772924797818</v>
+        <v>173.2772924797814</v>
       </c>
       <c r="L9" t="n">
         <v>180.5113773618771</v>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>305.6860047247386</v>
+        <v>305.6860047247388</v>
       </c>
       <c r="C2" t="n">
-        <v>359.4913397268888</v>
+        <v>359.4913397268894</v>
       </c>
       <c r="D2" t="n">
-        <v>452.3271091309337</v>
+        <v>452.3271091309342</v>
       </c>
       <c r="E2" t="n">
-        <v>359.4913397268888</v>
+        <v>359.4913397268894</v>
       </c>
       <c r="F2" t="n">
-        <v>359.4913397268888</v>
+        <v>359.4913397268894</v>
       </c>
       <c r="G2" t="n">
         <v>469.0465593164394</v>
       </c>
       <c r="H2" t="n">
-        <v>914.0472642742866</v>
+        <v>914.04726427429</v>
       </c>
       <c r="I2" t="n">
-        <v>359.4913397268888</v>
+        <v>359.4913397268894</v>
       </c>
       <c r="J2" t="n">
-        <v>775.9036907805416</v>
+        <v>775.90369078054</v>
       </c>
       <c r="K2" t="n">
-        <v>419.8657180231298</v>
+        <v>419.8657180231308</v>
       </c>
       <c r="L2" t="n">
-        <v>278.4957696128083</v>
+        <v>278.4957696128072</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.393019524793</v>
+        <v>6.393019524793012</v>
       </c>
       <c r="C3" t="n">
-        <v>6.264945026727182</v>
+        <v>6.264945026727172</v>
       </c>
       <c r="D3" t="n">
-        <v>6.393019524793</v>
+        <v>6.393019524793012</v>
       </c>
       <c r="E3" t="n">
-        <v>6.368416706125285</v>
+        <v>6.368416706125283</v>
       </c>
       <c r="F3" t="n">
-        <v>6.368416706125285</v>
+        <v>6.368416706125283</v>
       </c>
       <c r="G3" t="n">
-        <v>6.394586042587134</v>
+        <v>6.39458604258712</v>
       </c>
       <c r="H3" t="n">
-        <v>6.393019524793</v>
+        <v>6.393019524793012</v>
       </c>
       <c r="I3" t="n">
-        <v>6.403189469656183</v>
+        <v>6.403189469656192</v>
       </c>
       <c r="J3" t="n">
-        <v>6.393019524793</v>
+        <v>6.393019524793012</v>
       </c>
       <c r="K3" t="n">
-        <v>6.393019524793</v>
+        <v>6.393019524793012</v>
       </c>
       <c r="L3" t="n">
-        <v>6.393019524793</v>
+        <v>6.393019524793012</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>821.2786513019792</v>
+        <v>821.2786513019782</v>
       </c>
       <c r="C4" t="n">
-        <v>685.4445364719264</v>
+        <v>685.4445364719261</v>
       </c>
       <c r="D4" t="n">
-        <v>685.6140073834149</v>
+        <v>685.6140073834143</v>
       </c>
       <c r="E4" t="n">
-        <v>617.9462738964675</v>
+        <v>617.9462738964679</v>
       </c>
       <c r="F4" t="n">
-        <v>685.602921412864</v>
+        <v>685.6029214128637</v>
       </c>
       <c r="G4" t="n">
-        <v>685.5630340776269</v>
+        <v>821.2802178197719</v>
       </c>
       <c r="H4" t="n">
-        <v>685.7600057729601</v>
+        <v>822.0188530314774</v>
       </c>
       <c r="I4" t="n">
-        <v>821.2888212468426</v>
+        <v>821.2888212468414</v>
       </c>
       <c r="J4" t="n">
-        <v>821.6387534898872</v>
+        <v>821.638753489887</v>
       </c>
       <c r="K4" t="n">
-        <v>685.5787170139845</v>
+        <v>685.5787170139841</v>
       </c>
       <c r="L4" t="n">
-        <v>685.7344109721657</v>
+        <v>685.7344109721663</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.33270605228191</v>
+        <v>13.33270605228193</v>
       </c>
       <c r="C5" t="n">
-        <v>13.34287599714508</v>
+        <v>13.34287599714509</v>
       </c>
       <c r="D5" t="n">
-        <v>13.33262820661586</v>
+        <v>13.33262820661591</v>
       </c>
       <c r="E5" t="n">
-        <v>13.349564616459</v>
+        <v>13.34956461645898</v>
       </c>
       <c r="F5" t="n">
-        <v>13.349564616459</v>
+        <v>13.34956461645898</v>
       </c>
       <c r="G5" t="n">
         <v>13.33427257007603</v>
       </c>
       <c r="H5" t="n">
-        <v>13.33270605228191</v>
+        <v>13.33270605228193</v>
       </c>
       <c r="I5" t="n">
-        <v>13.34287599714508</v>
+        <v>13.34287599714509</v>
       </c>
       <c r="J5" t="n">
-        <v>13.33270605228191</v>
+        <v>13.33270605228193</v>
       </c>
       <c r="K5" t="n">
-        <v>13.33270605228191</v>
+        <v>13.33270605228193</v>
       </c>
       <c r="L5" t="n">
-        <v>13.33270605228191</v>
+        <v>13.33270605228193</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.22319002203986</v>
+        <v>16.22319002203983</v>
       </c>
       <c r="C6" t="n">
-        <v>23.67457693977574</v>
+        <v>23.67457693977576</v>
       </c>
       <c r="D6" t="n">
-        <v>25.1978762000539</v>
+        <v>25.19787620005394</v>
       </c>
       <c r="E6" t="n">
-        <v>21.64083667799318</v>
+        <v>21.64083667799321</v>
       </c>
       <c r="F6" t="n">
-        <v>16.47302175906845</v>
+        <v>16.47302175906847</v>
       </c>
       <c r="G6" t="n">
-        <v>23.6580921551372</v>
+        <v>23.65809215513722</v>
       </c>
       <c r="H6" t="n">
-        <v>23.65652563734975</v>
+        <v>23.65652563734986</v>
       </c>
       <c r="I6" t="n">
-        <v>23.66669558220625</v>
+        <v>23.66669558220626</v>
       </c>
       <c r="J6" t="n">
-        <v>23.65798649030984</v>
+        <v>23.65798649030989</v>
       </c>
       <c r="K6" t="n">
-        <v>16.0851119976201</v>
+        <v>16.08511199762015</v>
       </c>
       <c r="L6" t="n">
-        <v>31.42126624317224</v>
+        <v>31.42126624317233</v>
       </c>
     </row>
     <row r="7">
@@ -5071,34 +5071,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.42465025647584</v>
+        <v>32.42465025647586</v>
       </c>
       <c r="C7" t="n">
-        <v>40.15079967008782</v>
+        <v>40.15079967008781</v>
       </c>
       <c r="D7" t="n">
-        <v>40.14063210255201</v>
+        <v>40.14063210255203</v>
       </c>
       <c r="E7" t="n">
-        <v>49.05486524177362</v>
+        <v>49.05486524177363</v>
       </c>
       <c r="F7" t="n">
         <v>40.15078904679788</v>
       </c>
       <c r="G7" t="n">
-        <v>40.14219624301879</v>
+        <v>40.14219624301883</v>
       </c>
       <c r="H7" t="n">
         <v>40.14062972522471</v>
       </c>
       <c r="I7" t="n">
-        <v>40.15079967008782</v>
+        <v>40.15079967008781</v>
       </c>
       <c r="J7" t="n">
         <v>40.14062972522471</v>
       </c>
       <c r="K7" t="n">
-        <v>35.66996191793677</v>
+        <v>35.66996191793683</v>
       </c>
       <c r="L7" t="n">
         <v>40.14062972522471</v>
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>167.5568624308522</v>
+        <v>167.556862430852</v>
       </c>
       <c r="C8" t="n">
-        <v>171.0339059979305</v>
+        <v>171.0339059979306</v>
       </c>
       <c r="D8" t="n">
-        <v>164.3470894822648</v>
+        <v>164.3470894822649</v>
       </c>
       <c r="E8" t="n">
-        <v>171.0339059979305</v>
+        <v>171.0339059979306</v>
       </c>
       <c r="F8" t="n">
-        <v>171.0339059979305</v>
+        <v>171.0339059979306</v>
       </c>
       <c r="G8" t="n">
-        <v>164.1999810996375</v>
+        <v>164.1999810996376</v>
       </c>
       <c r="H8" t="n">
-        <v>156.1327962007703</v>
+        <v>156.1327962007702</v>
       </c>
       <c r="I8" t="n">
-        <v>171.0339059979305</v>
+        <v>171.0339059979306</v>
       </c>
       <c r="J8" t="n">
         <v>157.98081840302</v>
       </c>
       <c r="K8" t="n">
-        <v>165.1156865523963</v>
+        <v>165.1156865523961</v>
       </c>
       <c r="L8" t="n">
-        <v>157.7971858110607</v>
+        <v>169.0691798020906</v>
       </c>
     </row>
     <row r="9">
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.0761472287815</v>
+        <v>169.0761472287817</v>
       </c>
       <c r="C9" t="n">
         <v>173.3478161035096</v>
       </c>
       <c r="D9" t="n">
-        <v>167.7691012376137</v>
+        <v>167.7691012376136</v>
       </c>
       <c r="E9" t="n">
         <v>173.3478161035096</v>
@@ -5166,10 +5166,10 @@
         <v>173.3478161035096</v>
       </c>
       <c r="G9" t="n">
-        <v>167.7012294925742</v>
+        <v>167.701229492574</v>
       </c>
       <c r="H9" t="n">
-        <v>164.4404627606493</v>
+        <v>164.440462760649</v>
       </c>
       <c r="I9" t="n">
         <v>173.3478161035096</v>
@@ -5178,10 +5178,10 @@
         <v>165.1822556200745</v>
       </c>
       <c r="K9" t="n">
-        <v>168.0823777026627</v>
+        <v>168.0823777026625</v>
       </c>
       <c r="L9" t="n">
-        <v>165.1138795785789</v>
+        <v>169.6962905164547</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>234.8504957905397</v>
+        <v>234.8504957905396</v>
       </c>
       <c r="C2" t="n">
-        <v>314.6250134467258</v>
+        <v>314.625013446726</v>
       </c>
       <c r="D2" t="n">
-        <v>391.2931990020708</v>
+        <v>391.2931990020682</v>
       </c>
       <c r="E2" t="n">
-        <v>314.6250134467258</v>
+        <v>314.625013446726</v>
       </c>
       <c r="F2" t="n">
-        <v>314.6250134467258</v>
+        <v>314.625013446726</v>
       </c>
       <c r="G2" t="n">
-        <v>403.206890875531</v>
+        <v>403.2068908755313</v>
       </c>
       <c r="H2" t="n">
-        <v>759.0247025789191</v>
+        <v>759.0247025789193</v>
       </c>
       <c r="I2" t="n">
-        <v>314.6250134467258</v>
+        <v>314.625013446726</v>
       </c>
       <c r="J2" t="n">
-        <v>622.7442161198838</v>
+        <v>622.744216119884</v>
       </c>
       <c r="K2" t="n">
-        <v>315.8294433826152</v>
+        <v>315.8294433826154</v>
       </c>
       <c r="L2" t="n">
-        <v>755.00715968214</v>
+        <v>296.861680101439</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.803489097629502</v>
+        <v>5.803489097629615</v>
       </c>
       <c r="C3" t="n">
-        <v>5.619173032330085</v>
+        <v>5.619173032330088</v>
       </c>
       <c r="D3" t="n">
-        <v>5.803489097629502</v>
+        <v>5.803489097629619</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711289625537536</v>
+        <v>5.711289625537544</v>
       </c>
       <c r="F3" t="n">
-        <v>5.711289625537542</v>
+        <v>5.711289625537544</v>
       </c>
       <c r="G3" t="n">
-        <v>5.805396815265043</v>
+        <v>5.805396815265095</v>
       </c>
       <c r="H3" t="n">
-        <v>5.803489097629502</v>
+        <v>5.803489097629619</v>
       </c>
       <c r="I3" t="n">
-        <v>5.815789563676551</v>
+        <v>5.815789563676556</v>
       </c>
       <c r="J3" t="n">
-        <v>5.803489097629502</v>
+        <v>5.803489097629619</v>
       </c>
       <c r="K3" t="n">
-        <v>5.803489097629502</v>
+        <v>5.803489097629619</v>
       </c>
       <c r="L3" t="n">
-        <v>5.803489097629502</v>
+        <v>5.803489097629619</v>
       </c>
     </row>
     <row r="4">
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>638.4926161528125</v>
+        <v>764.6097616453008</v>
       </c>
       <c r="C4" t="n">
-        <v>638.4027566683189</v>
+        <v>638.4027566683181</v>
       </c>
       <c r="D4" t="n">
-        <v>638.5551621612947</v>
+        <v>638.5551621612939</v>
       </c>
       <c r="E4" t="n">
         <v>575.5274528078405</v>
@@ -5362,22 +5362,22 @@
         <v>638.5368178237597</v>
       </c>
       <c r="G4" t="n">
-        <v>638.4945238704479</v>
+        <v>764.6116693629366</v>
       </c>
       <c r="H4" t="n">
         <v>765.2864784525019</v>
       </c>
       <c r="I4" t="n">
-        <v>638.5049166188595</v>
+        <v>764.6220621113478</v>
       </c>
       <c r="J4" t="n">
-        <v>670.8754224779384</v>
+        <v>764.9563340984697</v>
       </c>
       <c r="K4" t="n">
         <v>638.4633752209605</v>
       </c>
       <c r="L4" t="n">
-        <v>638.6523050249689</v>
+        <v>638.6523050249688</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.88282253578687</v>
+        <v>11.882822535787</v>
       </c>
       <c r="C5" t="n">
         <v>11.89512300183397</v>
       </c>
       <c r="D5" t="n">
-        <v>11.88277782592235</v>
+        <v>11.88277782592244</v>
       </c>
       <c r="E5" t="n">
-        <v>11.8785277826538</v>
+        <v>11.87852778265381</v>
       </c>
       <c r="F5" t="n">
-        <v>11.8785277826538</v>
+        <v>11.87852778265381</v>
       </c>
       <c r="G5" t="n">
-        <v>11.88473025342247</v>
+        <v>11.88473025342251</v>
       </c>
       <c r="H5" t="n">
-        <v>11.88282253578687</v>
+        <v>11.88282253578701</v>
       </c>
       <c r="I5" t="n">
         <v>11.89512300183397</v>
       </c>
       <c r="J5" t="n">
-        <v>11.88282253578687</v>
+        <v>11.88282253578701</v>
       </c>
       <c r="K5" t="n">
-        <v>11.88282253578687</v>
+        <v>11.88282253578701</v>
       </c>
       <c r="L5" t="n">
-        <v>11.88282253578687</v>
+        <v>11.88282253578701</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.27236109126948</v>
+        <v>14.27236109126942</v>
       </c>
       <c r="C6" t="n">
-        <v>20.63823169654718</v>
+        <v>20.63823169662226</v>
       </c>
       <c r="D6" t="n">
-        <v>21.96105570388194</v>
+        <v>21.9610557038819</v>
       </c>
       <c r="E6" t="n">
-        <v>18.89819363377378</v>
+        <v>18.89819363377377</v>
       </c>
       <c r="F6" t="n">
-        <v>14.4766506670683</v>
+        <v>14.47665066706828</v>
       </c>
       <c r="G6" t="n">
-        <v>20.64247448932033</v>
+        <v>20.64247448932037</v>
       </c>
       <c r="H6" t="n">
-        <v>20.64056677169814</v>
+        <v>20.64056677169813</v>
       </c>
       <c r="I6" t="n">
-        <v>20.65286723773184</v>
+        <v>20.65286723773182</v>
       </c>
       <c r="J6" t="n">
-        <v>20.64181829815288</v>
+        <v>20.64181829815297</v>
       </c>
       <c r="K6" t="n">
-        <v>14.15406840206155</v>
+        <v>14.15406840206161</v>
       </c>
       <c r="L6" t="n">
-        <v>27.29269009771595</v>
+        <v>27.29269009771594</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.10997852465945</v>
+        <v>27.10997852465947</v>
       </c>
       <c r="C7" t="n">
-        <v>33.44436905660422</v>
+        <v>33.44436905660414</v>
       </c>
       <c r="D7" t="n">
-        <v>33.43207097389107</v>
+        <v>33.43207097389111</v>
       </c>
       <c r="E7" t="n">
-        <v>40.73991811256926</v>
+        <v>40.73991811256916</v>
       </c>
       <c r="F7" t="n">
-        <v>33.44436026892236</v>
+        <v>33.44436026892232</v>
       </c>
       <c r="G7" t="n">
         <v>33.43397630819272</v>
       </c>
       <c r="H7" t="n">
-        <v>33.43206859055712</v>
+        <v>33.43206859055721</v>
       </c>
       <c r="I7" t="n">
-        <v>33.44436905660422</v>
+        <v>33.44436905660414</v>
       </c>
       <c r="J7" t="n">
-        <v>33.43206859055712</v>
+        <v>33.43206859055721</v>
       </c>
       <c r="K7" t="n">
-        <v>25.47142809079759</v>
+        <v>25.4714280907976</v>
       </c>
       <c r="L7" t="n">
-        <v>33.43206859055712</v>
+        <v>33.43206859055721</v>
       </c>
     </row>
     <row r="8">
@@ -5510,34 +5510,34 @@
         <v>168.4516714278703</v>
       </c>
       <c r="C8" t="n">
-        <v>170.957235803279</v>
+        <v>170.9572358032791</v>
       </c>
       <c r="D8" t="n">
         <v>164.4534021574637</v>
       </c>
       <c r="E8" t="n">
-        <v>170.957235803279</v>
+        <v>170.9572358032791</v>
       </c>
       <c r="F8" t="n">
-        <v>170.957235803279</v>
+        <v>170.9572358032791</v>
       </c>
       <c r="G8" t="n">
-        <v>164.4110449669011</v>
+        <v>164.4110449669012</v>
       </c>
       <c r="H8" t="n">
-        <v>157.713455722964</v>
+        <v>157.7134557229642</v>
       </c>
       <c r="I8" t="n">
-        <v>170.957235803279</v>
+        <v>170.9572358032791</v>
       </c>
       <c r="J8" t="n">
         <v>159.8379139760527</v>
       </c>
       <c r="K8" t="n">
-        <v>165.990122075093</v>
+        <v>165.9901220750931</v>
       </c>
       <c r="L8" t="n">
-        <v>158.4734934328394</v>
+        <v>167.7000486797229</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.161753687766</v>
+        <v>169.1617536877661</v>
       </c>
       <c r="C9" t="n">
-        <v>173.0329961491225</v>
+        <v>173.0329961491226</v>
       </c>
       <c r="D9" t="n">
-        <v>167.5335425887048</v>
+        <v>167.5335425887049</v>
       </c>
       <c r="E9" t="n">
-        <v>173.0329961491225</v>
+        <v>173.0329961491226</v>
       </c>
       <c r="F9" t="n">
-        <v>173.0329961491225</v>
+        <v>173.0329961491226</v>
       </c>
       <c r="G9" t="n">
-        <v>167.5093246465937</v>
+        <v>167.5093246465939</v>
       </c>
       <c r="H9" t="n">
-        <v>164.8034930387959</v>
+        <v>164.803493038796</v>
       </c>
       <c r="I9" t="n">
-        <v>173.0329961491225</v>
+        <v>173.0329961491226</v>
       </c>
       <c r="J9" t="n">
-        <v>165.6589035034036</v>
+        <v>165.658903503404</v>
       </c>
       <c r="K9" t="n">
-        <v>168.1596144994331</v>
+        <v>168.1596144994332</v>
       </c>
       <c r="L9" t="n">
-        <v>168.8604720181128</v>
+        <v>168.860472018113</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>211.5089467282465</v>
+        <v>211.5089467282458</v>
       </c>
       <c r="C2" t="n">
-        <v>281.0989276554196</v>
+        <v>281.0989276554192</v>
       </c>
       <c r="D2" t="n">
-        <v>348.4969734715212</v>
+        <v>348.4969734715206</v>
       </c>
       <c r="E2" t="n">
-        <v>281.0989276554196</v>
+        <v>281.0989276554192</v>
       </c>
       <c r="F2" t="n">
-        <v>281.0989276554196</v>
+        <v>281.0989276554192</v>
       </c>
       <c r="G2" t="n">
-        <v>361.8634637409385</v>
+        <v>361.8634637409376</v>
       </c>
       <c r="H2" t="n">
-        <v>655.1574525448218</v>
+        <v>655.1574525448239</v>
       </c>
       <c r="I2" t="n">
-        <v>281.0989276554196</v>
+        <v>281.0989276554192</v>
       </c>
       <c r="J2" t="n">
-        <v>577.4402553467673</v>
+        <v>577.4402553467671</v>
       </c>
       <c r="K2" t="n">
-        <v>220.7772391376418</v>
+        <v>220.7772391376409</v>
       </c>
       <c r="L2" t="n">
-        <v>676.2593697945761</v>
+        <v>676.2593697945763</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.414732734499746</v>
+        <v>5.414732734499733</v>
       </c>
       <c r="C3" t="n">
-        <v>5.118513738462844</v>
+        <v>5.118513738462823</v>
       </c>
       <c r="D3" t="n">
-        <v>5.414732734499746</v>
+        <v>5.414732734499734</v>
       </c>
       <c r="E3" t="n">
-        <v>5.213324080369578</v>
+        <v>5.213324080369569</v>
       </c>
       <c r="F3" t="n">
-        <v>5.21332408036958</v>
+        <v>5.213324080369566</v>
       </c>
       <c r="G3" t="n">
-        <v>5.416564734255892</v>
+        <v>5.416564734255883</v>
       </c>
       <c r="H3" t="n">
-        <v>5.414732734499746</v>
+        <v>5.414732734499734</v>
       </c>
       <c r="I3" t="n">
-        <v>5.426556475908016</v>
+        <v>5.426556475908</v>
       </c>
       <c r="J3" t="n">
-        <v>5.414732734499746</v>
+        <v>5.414732734499734</v>
       </c>
       <c r="K3" t="n">
-        <v>5.414732734499746</v>
+        <v>5.414732734499734</v>
       </c>
       <c r="L3" t="n">
-        <v>5.414732734499746</v>
+        <v>5.414732734499734</v>
       </c>
     </row>
     <row r="4">
@@ -5743,34 +5743,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>637.8933897211318</v>
+        <v>637.8933897211321</v>
       </c>
       <c r="C4" t="n">
-        <v>637.8106541082985</v>
+        <v>637.810654108298</v>
       </c>
       <c r="D4" t="n">
-        <v>763.8878732799785</v>
+        <v>763.8878732799783</v>
       </c>
       <c r="E4" t="n">
-        <v>574.9533037842057</v>
+        <v>574.9533037842054</v>
       </c>
       <c r="F4" t="n">
-        <v>637.9496126672092</v>
+        <v>637.9496126672088</v>
       </c>
       <c r="G4" t="n">
-        <v>637.8952217208886</v>
+        <v>637.8952217208885</v>
       </c>
       <c r="H4" t="n">
-        <v>764.4166472274936</v>
+        <v>764.4166472274939</v>
       </c>
       <c r="I4" t="n">
-        <v>763.7356666713001</v>
+        <v>763.7356666713004</v>
       </c>
       <c r="J4" t="n">
-        <v>764.0896214672904</v>
+        <v>670.278844987645</v>
       </c>
       <c r="K4" t="n">
-        <v>637.7781037846445</v>
+        <v>637.7781037846438</v>
       </c>
       <c r="L4" t="n">
         <v>638.0653605053975</v>
@@ -5786,34 +5786,34 @@
         <v>11.22630093006511</v>
       </c>
       <c r="C5" t="n">
-        <v>11.2381246714734</v>
+        <v>11.23812467147337</v>
       </c>
       <c r="D5" t="n">
-        <v>11.22628357731549</v>
+        <v>11.22628357731547</v>
       </c>
       <c r="E5" t="n">
-        <v>11.19042374670141</v>
+        <v>11.19042374670139</v>
       </c>
       <c r="F5" t="n">
-        <v>11.19042374670141</v>
+        <v>11.19042374670139</v>
       </c>
       <c r="G5" t="n">
-        <v>11.22813292982127</v>
+        <v>11.22813292982125</v>
       </c>
       <c r="H5" t="n">
-        <v>11.22630093006511</v>
+        <v>11.2263009300651</v>
       </c>
       <c r="I5" t="n">
-        <v>11.2381246714734</v>
+        <v>11.23812467147337</v>
       </c>
       <c r="J5" t="n">
-        <v>11.22630093006511</v>
+        <v>11.2263009300651</v>
       </c>
       <c r="K5" t="n">
-        <v>11.22630093006511</v>
+        <v>11.2263009300651</v>
       </c>
       <c r="L5" t="n">
-        <v>11.22630093006511</v>
+        <v>11.2263009300651</v>
       </c>
     </row>
     <row r="6">
@@ -5826,34 +5826,34 @@
         <v>13.39695351108848</v>
       </c>
       <c r="C6" t="n">
-        <v>19.3492045702985</v>
+        <v>19.34920457029845</v>
       </c>
       <c r="D6" t="n">
-        <v>20.62288675670564</v>
+        <v>20.6228867567056</v>
       </c>
       <c r="E6" t="n">
-        <v>17.71717029320106</v>
+        <v>17.71717029320102</v>
       </c>
       <c r="F6" t="n">
-        <v>13.57004444321024</v>
+        <v>13.5700444432102</v>
       </c>
       <c r="G6" t="n">
-        <v>19.38370641866643</v>
+        <v>19.38370641866639</v>
       </c>
       <c r="H6" t="n">
-        <v>19.38187441892635</v>
+        <v>19.38187441892632</v>
       </c>
       <c r="I6" t="n">
-        <v>19.39369816031856</v>
+        <v>19.39369816031851</v>
       </c>
       <c r="J6" t="n">
-        <v>19.38305061977989</v>
+        <v>19.38305061977987</v>
       </c>
       <c r="K6" t="n">
-        <v>13.28578053323017</v>
+        <v>13.28578053323016</v>
       </c>
       <c r="L6" t="n">
-        <v>25.63362475101873</v>
+        <v>25.63362475101866</v>
       </c>
     </row>
     <row r="7">
@@ -5866,34 +5866,34 @@
         <v>24.31996547969077</v>
       </c>
       <c r="C7" t="n">
-        <v>29.95755940982544</v>
+        <v>29.95755940982545</v>
       </c>
       <c r="D7" t="n">
-        <v>29.94573800708403</v>
+        <v>29.945738007084</v>
       </c>
       <c r="E7" t="n">
-        <v>36.44957096835985</v>
+        <v>36.44957096835981</v>
       </c>
       <c r="F7" t="n">
-        <v>29.95755135561306</v>
+        <v>29.95755135561301</v>
       </c>
       <c r="G7" t="n">
-        <v>29.94756766817331</v>
+        <v>29.94756766817337</v>
       </c>
       <c r="H7" t="n">
-        <v>29.94573566841718</v>
+        <v>29.94573566841716</v>
       </c>
       <c r="I7" t="n">
-        <v>29.95755940982544</v>
+        <v>29.95755940982545</v>
       </c>
       <c r="J7" t="n">
-        <v>29.94573566841718</v>
+        <v>29.94573566841716</v>
       </c>
       <c r="K7" t="n">
         <v>26.68614331059909</v>
       </c>
       <c r="L7" t="n">
-        <v>29.94573566841718</v>
+        <v>29.94573566841716</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>168.4291506132147</v>
+        <v>168.4291506132149</v>
       </c>
       <c r="C8" t="n">
-        <v>171.3558151439406</v>
+        <v>171.3558151439407</v>
       </c>
       <c r="D8" t="n">
-        <v>164.7879589536107</v>
+        <v>164.7879589536109</v>
       </c>
       <c r="E8" t="n">
-        <v>171.3558151439406</v>
+        <v>171.3558151439407</v>
       </c>
       <c r="F8" t="n">
-        <v>171.3558151439406</v>
+        <v>171.3558151439407</v>
       </c>
       <c r="G8" t="n">
-        <v>164.7647330200326</v>
+        <v>164.7647330200325</v>
       </c>
       <c r="H8" t="n">
-        <v>158.9005609108995</v>
+        <v>158.9005609108997</v>
       </c>
       <c r="I8" t="n">
-        <v>171.3558151439406</v>
+        <v>171.3558151439407</v>
       </c>
       <c r="J8" t="n">
-        <v>160.4796804260005</v>
+        <v>160.4796804260006</v>
       </c>
       <c r="K8" t="n">
-        <v>167.7432096036151</v>
+        <v>167.7432096036154</v>
       </c>
       <c r="L8" t="n">
-        <v>159.476157350274</v>
+        <v>159.4761573502741</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168.9038857210299</v>
+        <v>168.9038857210302</v>
       </c>
       <c r="C9" t="n">
-        <v>172.9569925073837</v>
+        <v>172.9569925073838</v>
       </c>
       <c r="D9" t="n">
-        <v>167.4210898239193</v>
+        <v>167.4210898239196</v>
       </c>
       <c r="E9" t="n">
-        <v>172.9569925073837</v>
+        <v>172.9569925073838</v>
       </c>
       <c r="F9" t="n">
-        <v>172.9569925073837</v>
+        <v>172.9569925073838</v>
       </c>
       <c r="G9" t="n">
-        <v>167.4041695795842</v>
+        <v>167.4041695795844</v>
       </c>
       <c r="H9" t="n">
-        <v>165.0367942314373</v>
+        <v>165.0367942314375</v>
       </c>
       <c r="I9" t="n">
-        <v>172.9569925073837</v>
+        <v>172.9569925073838</v>
       </c>
       <c r="J9" t="n">
-        <v>165.6711873059515</v>
+        <v>165.6711873059517</v>
       </c>
       <c r="K9" t="n">
-        <v>168.6248251219158</v>
+        <v>168.6248251219161</v>
       </c>
       <c r="L9" t="n">
-        <v>165.2682151304428</v>
+        <v>165.2682151304431</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.057689120619</v>
+        <v>73.05768912061903</v>
       </c>
       <c r="C2" t="n">
-        <v>300.7677103846683</v>
+        <v>300.7677103846681</v>
       </c>
       <c r="D2" t="n">
-        <v>231.5563869718603</v>
+        <v>231.55638697186</v>
       </c>
       <c r="E2" t="n">
-        <v>300.7677103846683</v>
+        <v>300.7677103846681</v>
       </c>
       <c r="F2" t="n">
-        <v>300.7677103846683</v>
+        <v>300.7677103846681</v>
       </c>
       <c r="G2" t="n">
-        <v>281.9878043972369</v>
+        <v>281.9878043972368</v>
       </c>
       <c r="H2" t="n">
         <v>383.5767044631112</v>
       </c>
       <c r="I2" t="n">
-        <v>300.7677103846683</v>
+        <v>300.7677103846681</v>
       </c>
       <c r="J2" t="n">
-        <v>820.6404925507704</v>
+        <v>820.640492550769</v>
       </c>
       <c r="K2" t="n">
-        <v>274.0372077716469</v>
+        <v>274.0372077716466</v>
       </c>
       <c r="L2" t="n">
-        <v>131.8701477610972</v>
+        <v>510.6925341865314</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.475968144444794</v>
+        <v>5.47596814444473</v>
       </c>
       <c r="C3" t="n">
-        <v>5.318284639216492</v>
+        <v>5.318284639216489</v>
       </c>
       <c r="D3" t="n">
-        <v>5.475968144444794</v>
+        <v>5.47596814444473</v>
       </c>
       <c r="E3" t="n">
-        <v>5.41648883108242</v>
+        <v>5.416488831082416</v>
       </c>
       <c r="F3" t="n">
-        <v>5.41648883108242</v>
+        <v>5.416488831082418</v>
       </c>
       <c r="G3" t="n">
-        <v>5.48144335169197</v>
+        <v>5.481443351691945</v>
       </c>
       <c r="H3" t="n">
-        <v>5.475968144444794</v>
+        <v>5.47596814444473</v>
       </c>
       <c r="I3" t="n">
         <v>5.511038847544608</v>
       </c>
       <c r="J3" t="n">
-        <v>5.475968144444794</v>
+        <v>5.47596814444473</v>
       </c>
       <c r="K3" t="n">
-        <v>5.475968144444794</v>
+        <v>5.47596814444473</v>
       </c>
       <c r="L3" t="n">
-        <v>5.475968144444794</v>
+        <v>5.47596814444473</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>684.1844525236565</v>
+        <v>684.1844525236561</v>
       </c>
       <c r="C4" t="n">
-        <v>684.2408462866675</v>
+        <v>684.240846286668</v>
       </c>
       <c r="D4" t="n">
-        <v>684.1037713367816</v>
+        <v>818.7827579837133</v>
       </c>
       <c r="E4" t="n">
-        <v>616.7727567525819</v>
+        <v>616.7727567525817</v>
       </c>
       <c r="F4" t="n">
-        <v>684.2615505532016</v>
+        <v>684.2615505532018</v>
       </c>
       <c r="G4" t="n">
-        <v>818.6089244037848</v>
+        <v>684.1899277309044</v>
       </c>
       <c r="H4" t="n">
-        <v>819.3169477219463</v>
+        <v>819.3169477219468</v>
       </c>
       <c r="I4" t="n">
-        <v>818.6385198996378</v>
+        <v>684.2195232267572</v>
       </c>
       <c r="J4" t="n">
-        <v>819.0120731419158</v>
+        <v>819.0120731419154</v>
       </c>
       <c r="K4" t="n">
         <v>684.2101511598296</v>
       </c>
       <c r="L4" t="n">
-        <v>684.284079677996</v>
+        <v>684.2840796779967</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.32842056291678</v>
+        <v>11.32842056291677</v>
       </c>
       <c r="C5" t="n">
-        <v>11.36349126601663</v>
+        <v>11.36349126601664</v>
       </c>
       <c r="D5" t="n">
         <v>11.32839095601244</v>
       </c>
       <c r="E5" t="n">
-        <v>11.33530438149656</v>
+        <v>11.33530438149657</v>
       </c>
       <c r="F5" t="n">
-        <v>11.33530438149656</v>
+        <v>11.33530438149657</v>
       </c>
       <c r="G5" t="n">
-        <v>11.33389577016399</v>
+        <v>11.33389577016396</v>
       </c>
       <c r="H5" t="n">
-        <v>11.32842056291678</v>
+        <v>11.32842056291677</v>
       </c>
       <c r="I5" t="n">
-        <v>11.36349126601663</v>
+        <v>11.36349126601664</v>
       </c>
       <c r="J5" t="n">
-        <v>11.32842056291678</v>
+        <v>11.32842056291677</v>
       </c>
       <c r="K5" t="n">
-        <v>11.32842056291678</v>
+        <v>11.32842056291677</v>
       </c>
       <c r="L5" t="n">
-        <v>11.32842056291678</v>
+        <v>11.32842056291677</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.29275968247891</v>
+        <v>13.2927596824789</v>
       </c>
       <c r="C6" t="n">
-        <v>19.20653449656804</v>
+        <v>19.20653449648836</v>
       </c>
       <c r="D6" t="n">
-        <v>20.42164118405635</v>
+        <v>20.42164118405633</v>
       </c>
       <c r="E6" t="n">
-        <v>17.5945004198117</v>
+        <v>17.59450041981172</v>
       </c>
       <c r="F6" t="n">
-        <v>13.49819792132513</v>
+        <v>13.49819792132516</v>
       </c>
       <c r="G6" t="n">
-        <v>19.20277213061333</v>
+        <v>19.20277213061335</v>
       </c>
       <c r="H6" t="n">
-        <v>19.1972969233748</v>
+        <v>19.19729692337479</v>
       </c>
       <c r="I6" t="n">
-        <v>19.23236762646598</v>
+        <v>19.23236762646602</v>
       </c>
       <c r="J6" t="n">
-        <v>19.198457325203</v>
+        <v>19.19845732520298</v>
       </c>
       <c r="K6" t="n">
-        <v>13.18307987258568</v>
+        <v>13.18307987258566</v>
       </c>
       <c r="L6" t="n">
-        <v>25.36507979258057</v>
+        <v>25.36507979258058</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.84693286367273</v>
+        <v>26.84693286367268</v>
       </c>
       <c r="C7" t="n">
-        <v>33.20044616446162</v>
+        <v>33.2004461644616</v>
       </c>
       <c r="D7" t="n">
-        <v>33.16537910498748</v>
+        <v>33.16537910498745</v>
       </c>
       <c r="E7" t="n">
         <v>40.49179299084972</v>
       </c>
       <c r="F7" t="n">
-        <v>33.20044196247625</v>
+        <v>33.20044196247624</v>
       </c>
       <c r="G7" t="n">
         <v>33.17085066860894</v>
       </c>
       <c r="H7" t="n">
-        <v>33.16537546136175</v>
+        <v>33.16537546136173</v>
       </c>
       <c r="I7" t="n">
-        <v>33.20044616446162</v>
+        <v>33.2004461644616</v>
       </c>
       <c r="J7" t="n">
-        <v>33.16537546136175</v>
+        <v>33.16537546136173</v>
       </c>
       <c r="K7" t="n">
-        <v>25.20932744850725</v>
+        <v>29.5044465383166</v>
       </c>
       <c r="L7" t="n">
-        <v>33.16537546136175</v>
+        <v>33.16537546136173</v>
       </c>
     </row>
     <row r="8">
@@ -6299,13 +6299,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.0102313130305</v>
+        <v>172.0102313130304</v>
       </c>
       <c r="C8" t="n">
         <v>171.4452028116781</v>
       </c>
       <c r="D8" t="n">
-        <v>167.8535267143938</v>
+        <v>167.8535267143937</v>
       </c>
       <c r="E8" t="n">
         <v>171.4452028116781</v>
@@ -6314,22 +6314,22 @@
         <v>171.4452028116781</v>
       </c>
       <c r="G8" t="n">
-        <v>166.9786491847112</v>
+        <v>166.9786491847111</v>
       </c>
       <c r="H8" t="n">
-        <v>165.0367597437985</v>
+        <v>165.0367597437984</v>
       </c>
       <c r="I8" t="n">
         <v>171.4452028116781</v>
       </c>
       <c r="J8" t="n">
-        <v>155.9340385252218</v>
+        <v>155.9340385252217</v>
       </c>
       <c r="K8" t="n">
         <v>166.9872135807211</v>
       </c>
       <c r="L8" t="n">
-        <v>163.2792014811772</v>
+        <v>170.9811421751772</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170.2788250504326</v>
+        <v>170.2788250504325</v>
       </c>
       <c r="C9" t="n">
-        <v>172.9596292856737</v>
+        <v>172.9596292856736</v>
       </c>
       <c r="D9" t="n">
-        <v>168.5859788918749</v>
+        <v>168.5859788918748</v>
       </c>
       <c r="E9" t="n">
-        <v>172.9596292856737</v>
+        <v>172.9596292856736</v>
       </c>
       <c r="F9" t="n">
-        <v>172.9596292856737</v>
+        <v>172.9596292856736</v>
       </c>
       <c r="G9" t="n">
-        <v>168.231484600671</v>
+        <v>168.2314846006709</v>
       </c>
       <c r="H9" t="n">
         <v>167.446571906796</v>
       </c>
       <c r="I9" t="n">
-        <v>172.9596292856737</v>
+        <v>172.9596292856736</v>
       </c>
       <c r="J9" t="n">
         <v>163.7378443115297</v>
       </c>
       <c r="K9" t="n">
-        <v>168.2333331469635</v>
+        <v>168.2333331469633</v>
       </c>
       <c r="L9" t="n">
-        <v>169.8616584474305</v>
+        <v>166.7305704126944</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.35624651889999</v>
+        <v>23.3562465189001</v>
       </c>
       <c r="C2" t="n">
-        <v>203.7080562314734</v>
+        <v>203.7080562314733</v>
       </c>
       <c r="D2" t="n">
-        <v>175.1613056640239</v>
+        <v>175.161305664024</v>
       </c>
       <c r="E2" t="n">
-        <v>203.7080562314734</v>
+        <v>203.7080562314733</v>
       </c>
       <c r="F2" t="n">
-        <v>203.7080562314734</v>
+        <v>203.7080562314733</v>
       </c>
       <c r="G2" t="n">
-        <v>185.2819746375583</v>
+        <v>185.2819746375578</v>
       </c>
       <c r="H2" t="n">
-        <v>129.5966377805292</v>
+        <v>129.5966377805293</v>
       </c>
       <c r="I2" t="n">
-        <v>203.7080562314734</v>
+        <v>203.7080562314733</v>
       </c>
       <c r="J2" t="n">
-        <v>451.9055817030422</v>
+        <v>451.9055817030423</v>
       </c>
       <c r="K2" t="n">
-        <v>118.6935159272514</v>
+        <v>118.6935159272517</v>
       </c>
       <c r="L2" t="n">
-        <v>43.03751382128451</v>
+        <v>43.03751382128457</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.624377729841959</v>
+        <v>4.62437772984206</v>
       </c>
       <c r="C3" t="n">
-        <v>4.482830058134617</v>
+        <v>4.482830058134606</v>
       </c>
       <c r="D3" t="n">
-        <v>4.624377729841959</v>
+        <v>4.62437772984206</v>
       </c>
       <c r="E3" t="n">
-        <v>4.557371291551746</v>
+        <v>4.55737129155174</v>
       </c>
       <c r="F3" t="n">
         <v>4.557371291551745</v>
       </c>
       <c r="G3" t="n">
-        <v>4.629881182954006</v>
+        <v>4.629881182953985</v>
       </c>
       <c r="H3" t="n">
-        <v>4.624377729841959</v>
+        <v>4.62437772984206</v>
       </c>
       <c r="I3" t="n">
-        <v>4.65944989069907</v>
+        <v>4.659449890699057</v>
       </c>
       <c r="J3" t="n">
-        <v>4.624377729841959</v>
+        <v>4.62437772984206</v>
       </c>
       <c r="K3" t="n">
-        <v>4.624377729841959</v>
+        <v>4.62437772984206</v>
       </c>
       <c r="L3" t="n">
-        <v>4.624377729841959</v>
+        <v>4.62437772984206</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>636.5060712411655</v>
+        <v>761.2124839580674</v>
       </c>
       <c r="C4" t="n">
-        <v>636.5847472894976</v>
+        <v>636.5847472894977</v>
       </c>
       <c r="D4" t="n">
-        <v>636.5339286196415</v>
+        <v>636.533928783074</v>
       </c>
       <c r="E4" t="n">
-        <v>573.762294958127</v>
+        <v>573.7622949581266</v>
       </c>
       <c r="F4" t="n">
-        <v>636.5904263738787</v>
+        <v>636.5904263738786</v>
       </c>
       <c r="G4" t="n">
-        <v>636.5115746942768</v>
+        <v>636.5115746942774</v>
       </c>
       <c r="H4" t="n">
-        <v>761.7292938424422</v>
+        <v>636.5293377704467</v>
       </c>
       <c r="I4" t="n">
-        <v>636.5411434020226</v>
+        <v>636.5411434020227</v>
       </c>
       <c r="J4" t="n">
-        <v>668.8325825627119</v>
+        <v>761.5718092781718</v>
       </c>
       <c r="K4" t="n">
-        <v>636.3944404170485</v>
+        <v>636.3944404170486</v>
       </c>
       <c r="L4" t="n">
-        <v>636.5882030650397</v>
+        <v>636.5882030650396</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.495515880461127</v>
+        <v>9.495515880461129</v>
       </c>
       <c r="C5" t="n">
-        <v>9.530588041318204</v>
+        <v>9.530588041318184</v>
       </c>
       <c r="D5" t="n">
-        <v>9.495497876427631</v>
+        <v>9.49549787642761</v>
       </c>
       <c r="E5" t="n">
-        <v>9.500153436516477</v>
+        <v>9.500153436516467</v>
       </c>
       <c r="F5" t="n">
-        <v>9.500153436516477</v>
+        <v>9.500153436516467</v>
       </c>
       <c r="G5" t="n">
-        <v>9.501019333573096</v>
+        <v>9.501019333573185</v>
       </c>
       <c r="H5" t="n">
-        <v>9.495515880461127</v>
+        <v>9.495515880461129</v>
       </c>
       <c r="I5" t="n">
-        <v>9.530588041318204</v>
+        <v>9.530588041318184</v>
       </c>
       <c r="J5" t="n">
-        <v>9.495515880461127</v>
+        <v>9.495515880461129</v>
       </c>
       <c r="K5" t="n">
-        <v>9.495515880461127</v>
+        <v>9.495515880461129</v>
       </c>
       <c r="L5" t="n">
-        <v>9.495515880461127</v>
+        <v>9.495515880461129</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.78005252547414</v>
+        <v>10.78005252547426</v>
       </c>
       <c r="C6" t="n">
-        <v>15.39734947121003</v>
+        <v>15.39734947121002</v>
       </c>
       <c r="D6" t="n">
-        <v>16.34653922932254</v>
+        <v>16.34653922932251</v>
       </c>
       <c r="E6" t="n">
-        <v>14.13948779675217</v>
+        <v>14.13948779675214</v>
       </c>
       <c r="F6" t="n">
-        <v>10.94312464141115</v>
+        <v>10.94312464141113</v>
       </c>
       <c r="G6" t="n">
-        <v>15.39603071241724</v>
+        <v>15.39603071241727</v>
       </c>
       <c r="H6" t="n">
-        <v>15.39052725930326</v>
+        <v>15.39052725930323</v>
       </c>
       <c r="I6" t="n">
-        <v>15.4255994201623</v>
+        <v>15.42559942016229</v>
       </c>
       <c r="J6" t="n">
-        <v>15.39143334325497</v>
+        <v>15.3914333432549</v>
       </c>
       <c r="K6" t="n">
-        <v>10.69441059082474</v>
+        <v>10.69441059082482</v>
       </c>
       <c r="L6" t="n">
-        <v>20.20655363443906</v>
+        <v>20.20655363443908</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.6769114163924</v>
+        <v>20.67691141639246</v>
       </c>
       <c r="C7" t="n">
-        <v>25.45573130080182</v>
+        <v>25.4557313008018</v>
       </c>
       <c r="D7" t="n">
-        <v>25.42066351426293</v>
+        <v>25.42066351426281</v>
       </c>
       <c r="E7" t="n">
-        <v>30.9299181499681</v>
+        <v>30.92991814996808</v>
       </c>
       <c r="F7" t="n">
-        <v>25.45573018527802</v>
+        <v>25.45573018527799</v>
       </c>
       <c r="G7" t="n">
-        <v>25.4261625930567</v>
+        <v>25.42616259305676</v>
       </c>
       <c r="H7" t="n">
-        <v>25.42065913994477</v>
+        <v>25.42065913994463</v>
       </c>
       <c r="I7" t="n">
-        <v>25.45573130080182</v>
+        <v>25.4557313008018</v>
       </c>
       <c r="J7" t="n">
-        <v>25.42065913994477</v>
+        <v>25.42065913994463</v>
       </c>
       <c r="K7" t="n">
-        <v>22.56060283014223</v>
+        <v>22.56060283014227</v>
       </c>
       <c r="L7" t="n">
-        <v>25.42065913994477</v>
+        <v>25.42065913994463</v>
       </c>
     </row>
     <row r="8">
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.2793143277126</v>
+        <v>172.2793143277125</v>
       </c>
       <c r="C8" t="n">
         <v>172.3757941877958</v>
@@ -6719,7 +6719,7 @@
         <v>172.3757941877958</v>
       </c>
       <c r="J8" t="n">
-        <v>161.6305152875139</v>
+        <v>161.6305152875138</v>
       </c>
       <c r="K8" t="n">
         <v>169.6939127074645</v>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.8788617552627</v>
+        <v>169.8788617552626</v>
       </c>
       <c r="C9" t="n">
         <v>172.7981612541917</v>
@@ -6750,7 +6750,7 @@
         <v>172.7981612541917</v>
       </c>
       <c r="G9" t="n">
-        <v>168.1191069519915</v>
+        <v>168.1191069519913</v>
       </c>
       <c r="H9" t="n">
         <v>168.7593367651579</v>
@@ -6759,13 +6759,13 @@
         <v>172.7981612541917</v>
       </c>
       <c r="J9" t="n">
-        <v>165.5459157371506</v>
+        <v>165.5459157371505</v>
       </c>
       <c r="K9" t="n">
         <v>168.826005760733</v>
       </c>
       <c r="L9" t="n">
-        <v>169.706687819464</v>
+        <v>167.3491684362777</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.6963069776996</v>
+        <v>21.69630697769957</v>
       </c>
       <c r="C2" t="n">
-        <v>144.1807006542419</v>
+        <v>144.180700654242</v>
       </c>
       <c r="D2" t="n">
-        <v>110.2551592780783</v>
+        <v>110.2551592780781</v>
       </c>
       <c r="E2" t="n">
-        <v>144.1807006542419</v>
+        <v>144.180700654242</v>
       </c>
       <c r="F2" t="n">
-        <v>144.1807006542419</v>
+        <v>144.180700654242</v>
       </c>
       <c r="G2" t="n">
-        <v>136.369786440166</v>
+        <v>136.3697864401665</v>
       </c>
       <c r="H2" t="n">
-        <v>134.9204580178755</v>
+        <v>134.9204580178757</v>
       </c>
       <c r="I2" t="n">
-        <v>144.1807006542419</v>
+        <v>144.180700654242</v>
       </c>
       <c r="J2" t="n">
-        <v>276.962282391279</v>
+        <v>276.9622823912787</v>
       </c>
       <c r="K2" t="n">
-        <v>58.11921457723703</v>
+        <v>58.11921457723713</v>
       </c>
       <c r="L2" t="n">
-        <v>68.47163475217495</v>
+        <v>262.9024968540979</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.15364313471108</v>
+        <v>4.153643134711057</v>
       </c>
       <c r="C3" t="n">
-        <v>3.997550746337664</v>
+        <v>3.997550746337672</v>
       </c>
       <c r="D3" t="n">
-        <v>4.15364313471108</v>
+        <v>4.153643134711057</v>
       </c>
       <c r="E3" t="n">
-        <v>4.065393212876841</v>
+        <v>4.065393212876855</v>
       </c>
       <c r="F3" t="n">
-        <v>4.065393212876842</v>
+        <v>4.065393212876852</v>
       </c>
       <c r="G3" t="n">
-        <v>4.158690180722127</v>
+        <v>4.158690180722157</v>
       </c>
       <c r="H3" t="n">
-        <v>4.15364313471108</v>
+        <v>4.153643134711057</v>
       </c>
       <c r="I3" t="n">
-        <v>4.185720998562387</v>
+        <v>4.185720998562402</v>
       </c>
       <c r="J3" t="n">
-        <v>4.15364313471108</v>
+        <v>4.153643134711057</v>
       </c>
       <c r="K3" t="n">
-        <v>4.15364313471108</v>
+        <v>4.153643134711057</v>
       </c>
       <c r="L3" t="n">
-        <v>4.15364313471108</v>
+        <v>4.153643134711057</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.6706864026595</v>
+        <v>635.6706864026596</v>
       </c>
       <c r="C4" t="n">
-        <v>635.720011001476</v>
+        <v>635.7200110014758</v>
       </c>
       <c r="D4" t="n">
-        <v>760.1986630116644</v>
+        <v>635.6543819012978</v>
       </c>
       <c r="E4" t="n">
-        <v>572.9250182385717</v>
+        <v>572.9250182385711</v>
       </c>
       <c r="F4" t="n">
-        <v>635.7413919370118</v>
+        <v>635.7413919370121</v>
       </c>
       <c r="G4" t="n">
-        <v>635.6757334486711</v>
+        <v>760.0894326357819</v>
       </c>
       <c r="H4" t="n">
-        <v>760.5392574583369</v>
+        <v>760.5392574583368</v>
       </c>
       <c r="I4" t="n">
-        <v>635.7027642665107</v>
+        <v>635.7027642665111</v>
       </c>
       <c r="J4" t="n">
-        <v>667.9267294349162</v>
+        <v>760.404810253703</v>
       </c>
       <c r="K4" t="n">
-        <v>635.5427548006639</v>
+        <v>635.5427548006643</v>
       </c>
       <c r="L4" t="n">
-        <v>635.7551932434866</v>
+        <v>635.7551932434864</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.693812630791642</v>
+        <v>8.693812630791729</v>
       </c>
       <c r="C5" t="n">
-        <v>8.725890494643046</v>
+        <v>8.725890494643068</v>
       </c>
       <c r="D5" t="n">
-        <v>8.693803778236939</v>
+        <v>8.693803778236967</v>
       </c>
       <c r="E5" t="n">
-        <v>8.693100217210553</v>
+        <v>8.693100217210571</v>
       </c>
       <c r="F5" t="n">
-        <v>8.693100217210553</v>
+        <v>8.693100217210571</v>
       </c>
       <c r="G5" t="n">
-        <v>8.698859676802858</v>
+        <v>8.69885967680284</v>
       </c>
       <c r="H5" t="n">
-        <v>8.693812630791642</v>
+        <v>8.693812630791729</v>
       </c>
       <c r="I5" t="n">
-        <v>8.725890494643046</v>
+        <v>8.725890494643068</v>
       </c>
       <c r="J5" t="n">
-        <v>8.693812630791642</v>
+        <v>8.693812630791729</v>
       </c>
       <c r="K5" t="n">
-        <v>8.693812630791642</v>
+        <v>8.693812630791729</v>
       </c>
       <c r="L5" t="n">
-        <v>8.693812630791642</v>
+        <v>8.693812630791729</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.686032244097641</v>
+        <v>9.686032244097621</v>
       </c>
       <c r="C6" t="n">
-        <v>13.81324133255419</v>
+        <v>13.81324133258957</v>
       </c>
       <c r="D6" t="n">
-        <v>14.66727224376594</v>
+        <v>14.66727224376595</v>
       </c>
       <c r="E6" t="n">
-        <v>12.68820296605152</v>
+        <v>12.68820296605154</v>
       </c>
       <c r="F6" t="n">
-        <v>9.82933401205216</v>
+        <v>9.829334012052181</v>
       </c>
       <c r="G6" t="n">
-        <v>13.81682006402262</v>
+        <v>13.81682006402259</v>
       </c>
       <c r="H6" t="n">
-        <v>13.81177301800421</v>
+        <v>13.81177301800423</v>
       </c>
       <c r="I6" t="n">
-        <v>13.84385088186279</v>
+        <v>13.84385088186284</v>
       </c>
       <c r="J6" t="n">
-        <v>13.81258383878843</v>
+        <v>13.81258383878836</v>
       </c>
       <c r="K6" t="n">
-        <v>9.609394491532306</v>
+        <v>9.609394491532269</v>
       </c>
       <c r="L6" t="n">
-        <v>18.12145424010371</v>
+        <v>18.12145424010372</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.64680788441677</v>
+        <v>17.64680788441681</v>
       </c>
       <c r="C7" t="n">
-        <v>21.67621920360141</v>
+        <v>21.67621920360147</v>
       </c>
       <c r="D7" t="n">
-        <v>21.64414415008793</v>
+        <v>21.64414415008796</v>
       </c>
       <c r="E7" t="n">
-        <v>26.28905789050658</v>
+        <v>26.28905789050662</v>
       </c>
       <c r="F7" t="n">
-        <v>21.67621768050141</v>
+        <v>21.67621768050147</v>
       </c>
       <c r="G7" t="n">
-        <v>21.64918838576117</v>
+        <v>21.64918838576123</v>
       </c>
       <c r="H7" t="n">
-        <v>21.6441413397501</v>
+        <v>21.64414133975012</v>
       </c>
       <c r="I7" t="n">
-        <v>21.67621920360141</v>
+        <v>21.67621920360147</v>
       </c>
       <c r="J7" t="n">
-        <v>21.6441413397501</v>
+        <v>21.64414133975012</v>
       </c>
       <c r="K7" t="n">
-        <v>19.32807181900714</v>
+        <v>19.234105838898</v>
       </c>
       <c r="L7" t="n">
-        <v>21.6441413397501</v>
+        <v>21.64414133975012</v>
       </c>
     </row>
     <row r="8">
@@ -7094,34 +7094,34 @@
         <v>171.7934853478498</v>
       </c>
       <c r="C8" t="n">
-        <v>173.475310105841</v>
+        <v>173.4753101058409</v>
       </c>
       <c r="D8" t="n">
         <v>169.4039654778224</v>
       </c>
       <c r="E8" t="n">
-        <v>173.475310105841</v>
+        <v>173.4753101058409</v>
       </c>
       <c r="F8" t="n">
-        <v>173.475310105841</v>
+        <v>173.4753101058409</v>
       </c>
       <c r="G8" t="n">
-        <v>168.8355537660292</v>
+        <v>168.8355537660291</v>
       </c>
       <c r="H8" t="n">
         <v>169.1402978879384</v>
       </c>
       <c r="I8" t="n">
-        <v>173.475310105841</v>
+        <v>173.4753101058409</v>
       </c>
       <c r="J8" t="n">
         <v>165.595753026944</v>
       </c>
       <c r="K8" t="n">
-        <v>170.77219520785</v>
+        <v>170.7721952078501</v>
       </c>
       <c r="L8" t="n">
-        <v>170.7404831378609</v>
+        <v>170.740483137861</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.3826488564068</v>
+        <v>169.3826488564067</v>
       </c>
       <c r="C9" t="n">
-        <v>172.9002735605055</v>
+        <v>172.9002735605054</v>
       </c>
       <c r="D9" t="n">
-        <v>168.409487749879</v>
+        <v>168.4094877498789</v>
       </c>
       <c r="E9" t="n">
-        <v>172.9002735605055</v>
+        <v>172.9002735605054</v>
       </c>
       <c r="F9" t="n">
-        <v>172.9002735605055</v>
+        <v>172.9002735605054</v>
       </c>
       <c r="G9" t="n">
-        <v>168.1780890457876</v>
+        <v>168.1780890457875</v>
       </c>
       <c r="H9" t="n">
-        <v>168.304904421546</v>
+        <v>168.3049044215459</v>
       </c>
       <c r="I9" t="n">
-        <v>172.9002735605055</v>
+        <v>172.9002735605054</v>
       </c>
       <c r="J9" t="n">
-        <v>166.8608852704676</v>
+        <v>166.8608852704675</v>
       </c>
       <c r="K9" t="n">
-        <v>168.966761314554</v>
+        <v>168.9667613145539</v>
       </c>
       <c r="L9" t="n">
-        <v>168.954883898869</v>
+        <v>167.2484199957098</v>
       </c>
     </row>
   </sheetData>
@@ -7250,34 +7250,34 @@
         <v>209.2554450735241</v>
       </c>
       <c r="C2" t="n">
-        <v>347.1066907474913</v>
+        <v>347.1066907474911</v>
       </c>
       <c r="D2" t="n">
-        <v>419.7047469670039</v>
+        <v>419.7047469670048</v>
       </c>
       <c r="E2" t="n">
-        <v>347.1066907474913</v>
+        <v>347.1066907474911</v>
       </c>
       <c r="F2" t="n">
-        <v>347.1066907474913</v>
+        <v>347.1066907474911</v>
       </c>
       <c r="G2" t="n">
-        <v>412.2738247660022</v>
+        <v>412.2738247660015</v>
       </c>
       <c r="H2" t="n">
-        <v>818.8148297677677</v>
+        <v>818.814829767769</v>
       </c>
       <c r="I2" t="n">
-        <v>347.1066907474913</v>
+        <v>347.1066907474911</v>
       </c>
       <c r="J2" t="n">
-        <v>780.6101405223995</v>
+        <v>780.6101405224009</v>
       </c>
       <c r="K2" t="n">
-        <v>370.5363191480631</v>
+        <v>370.5363191480636</v>
       </c>
       <c r="L2" t="n">
-        <v>782.1467505618526</v>
+        <v>782.1467505618538</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.116027450505937</v>
+        <v>6.116027450505943</v>
       </c>
       <c r="C3" t="n">
-        <v>5.967899912943412</v>
+        <v>5.967899912943421</v>
       </c>
       <c r="D3" t="n">
-        <v>6.116027450505937</v>
+        <v>6.116027450505943</v>
       </c>
       <c r="E3" t="n">
-        <v>6.07109475310738</v>
+        <v>6.07109475310739</v>
       </c>
       <c r="F3" t="n">
-        <v>6.071094753107379</v>
+        <v>6.07109475310739</v>
       </c>
       <c r="G3" t="n">
-        <v>6.118710984388342</v>
+        <v>6.118710984388352</v>
       </c>
       <c r="H3" t="n">
-        <v>6.116027450505937</v>
+        <v>6.116027450505943</v>
       </c>
       <c r="I3" t="n">
-        <v>6.133303606429251</v>
+        <v>6.133303606429272</v>
       </c>
       <c r="J3" t="n">
-        <v>6.116027450505939</v>
+        <v>6.116027450505943</v>
       </c>
       <c r="K3" t="n">
-        <v>6.116027450505937</v>
+        <v>6.116027450505943</v>
       </c>
       <c r="L3" t="n">
-        <v>6.116027450505937</v>
+        <v>6.116027450505943</v>
       </c>
     </row>
     <row r="4">
@@ -7327,34 +7327,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685.1809146360043</v>
+        <v>685.180914636004</v>
       </c>
       <c r="C4" t="n">
-        <v>685.1217623073821</v>
+        <v>685.1217623073815</v>
       </c>
       <c r="D4" t="n">
-        <v>685.2787644461828</v>
+        <v>685.2787644461835</v>
       </c>
       <c r="E4" t="n">
-        <v>617.6323547644752</v>
+        <v>617.6323547644757</v>
       </c>
       <c r="F4" t="n">
-        <v>685.2391544507108</v>
+        <v>685.23915445071</v>
       </c>
       <c r="G4" t="n">
-        <v>820.5276561826009</v>
+        <v>820.5276561826007</v>
       </c>
       <c r="H4" t="n">
-        <v>821.2870037832763</v>
+        <v>821.2870037832761</v>
       </c>
       <c r="I4" t="n">
-        <v>685.1981907919279</v>
+        <v>820.542248804642</v>
       </c>
       <c r="J4" t="n">
         <v>820.912905590616</v>
       </c>
       <c r="K4" t="n">
-        <v>685.1930306767131</v>
+        <v>685.1930306767127</v>
       </c>
       <c r="L4" t="n">
         <v>685.3421533395093</v>
@@ -7370,25 +7370,25 @@
         <v>12.6526811708047</v>
       </c>
       <c r="C5" t="n">
-        <v>12.669957326728</v>
+        <v>12.66995732672803</v>
       </c>
       <c r="D5" t="n">
-        <v>12.65262098206367</v>
+        <v>12.65262098206368</v>
       </c>
       <c r="E5" t="n">
-        <v>12.66356419467175</v>
+        <v>12.66356419467177</v>
       </c>
       <c r="F5" t="n">
-        <v>12.66356419467175</v>
+        <v>12.66356419467177</v>
       </c>
       <c r="G5" t="n">
-        <v>12.65536470468709</v>
+        <v>12.65536470468711</v>
       </c>
       <c r="H5" t="n">
         <v>12.6526811708047</v>
       </c>
       <c r="I5" t="n">
-        <v>12.669957326728</v>
+        <v>12.66995732672803</v>
       </c>
       <c r="J5" t="n">
         <v>12.6526811708047</v>
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.21258570635867</v>
+        <v>15.21258570635869</v>
       </c>
       <c r="C6" t="n">
-        <v>22.10622366080018</v>
+        <v>22.10622366091033</v>
       </c>
       <c r="D6" t="n">
-        <v>23.52055307477725</v>
+        <v>23.52055307477728</v>
       </c>
       <c r="E6" t="n">
-        <v>20.22485615331569</v>
+        <v>20.22485615331576</v>
       </c>
       <c r="F6" t="n">
-        <v>15.4442048996766</v>
+        <v>15.44420489967665</v>
       </c>
       <c r="G6" t="n">
-        <v>22.09639115423166</v>
+        <v>22.0963911542317</v>
       </c>
       <c r="H6" t="n">
-        <v>22.09370762035468</v>
+        <v>22.09370762035471</v>
       </c>
       <c r="I6" t="n">
-        <v>22.11098377627256</v>
+        <v>22.11098377627262</v>
       </c>
       <c r="J6" t="n">
-        <v>22.09505994788204</v>
+        <v>22.09505994788211</v>
       </c>
       <c r="K6" t="n">
-        <v>15.08476533490727</v>
+        <v>15.08476533490729</v>
       </c>
       <c r="L6" t="n">
-        <v>29.28161484016794</v>
+        <v>29.281614840168</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.87968158569798</v>
+        <v>30.879681585698</v>
       </c>
       <c r="C7" t="n">
-        <v>38.22480409958552</v>
+        <v>38.22480409958558</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20752927872329</v>
+        <v>38.20752927872336</v>
       </c>
       <c r="E7" t="n">
-        <v>46.6809719444309</v>
+        <v>46.68097194443095</v>
       </c>
       <c r="F7" t="n">
-        <v>38.22479395264796</v>
+        <v>38.22479395264804</v>
       </c>
       <c r="G7" t="n">
-        <v>38.21021147754459</v>
+        <v>38.21021147754463</v>
       </c>
       <c r="H7" t="n">
-        <v>38.20752794366218</v>
+        <v>38.20752794366225</v>
       </c>
       <c r="I7" t="n">
-        <v>38.22480409958552</v>
+        <v>38.22480409958558</v>
       </c>
       <c r="J7" t="n">
-        <v>38.20752794366218</v>
+        <v>38.20752794366225</v>
       </c>
       <c r="K7" t="n">
-        <v>33.78948873747049</v>
+        <v>33.96174554670612</v>
       </c>
       <c r="L7" t="n">
-        <v>38.20752794366218</v>
+        <v>38.20752794366225</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>169.4649912777722</v>
+        <v>169.4649912777723</v>
       </c>
       <c r="C8" t="n">
-        <v>170.9666710066143</v>
+        <v>170.9666710066142</v>
       </c>
       <c r="D8" t="n">
-        <v>164.2944725063374</v>
+        <v>164.2944725063375</v>
       </c>
       <c r="E8" t="n">
-        <v>170.9666710066143</v>
+        <v>170.9666710066142</v>
       </c>
       <c r="F8" t="n">
-        <v>170.9666710066143</v>
+        <v>170.9666710066142</v>
       </c>
       <c r="G8" t="n">
-        <v>164.8506391760574</v>
+        <v>164.8506391760572</v>
       </c>
       <c r="H8" t="n">
         <v>156.2218583229033</v>
       </c>
       <c r="I8" t="n">
-        <v>170.9666710066143</v>
+        <v>170.9666710066142</v>
       </c>
       <c r="J8" t="n">
         <v>157.5164491198476</v>
       </c>
       <c r="K8" t="n">
-        <v>165.6770475304355</v>
+        <v>165.6770475304354</v>
       </c>
       <c r="L8" t="n">
-        <v>169.9262912875153</v>
+        <v>159.0288026519805</v>
       </c>
     </row>
     <row r="9">
@@ -7530,34 +7530,34 @@
         <v>169.6495660846568</v>
       </c>
       <c r="C9" t="n">
-        <v>173.131187581627</v>
+        <v>173.1311875816268</v>
       </c>
       <c r="D9" t="n">
-        <v>167.5439128712752</v>
+        <v>167.5439128712753</v>
       </c>
       <c r="E9" t="n">
-        <v>173.131187581627</v>
+        <v>173.1311875816268</v>
       </c>
       <c r="F9" t="n">
-        <v>173.131187581627</v>
+        <v>173.1311875816268</v>
       </c>
       <c r="G9" t="n">
-        <v>167.7653934767316</v>
+        <v>167.7653934767317</v>
       </c>
       <c r="H9" t="n">
-        <v>164.2725779881566</v>
+        <v>164.2725779881565</v>
       </c>
       <c r="I9" t="n">
-        <v>173.131187581627</v>
+        <v>173.1311875816268</v>
       </c>
       <c r="J9" t="n">
         <v>164.7894144780929</v>
       </c>
       <c r="K9" t="n">
-        <v>168.1072183133283</v>
+        <v>168.1072183133282</v>
       </c>
       <c r="L9" t="n">
-        <v>169.8407352326214</v>
+        <v>165.4105608834736</v>
       </c>
     </row>
   </sheetData>
@@ -7649,7 +7649,7 @@
         <v>210.4159433237724</v>
       </c>
       <c r="D2" t="n">
-        <v>328.9336053313741</v>
+        <v>328.9336053313745</v>
       </c>
       <c r="E2" t="n">
         <v>210.4159433237724</v>
@@ -7658,22 +7658,22 @@
         <v>210.4159433237724</v>
       </c>
       <c r="G2" t="n">
-        <v>261.570678771116</v>
+        <v>261.5706787711161</v>
       </c>
       <c r="H2" t="n">
-        <v>258.2960407722236</v>
+        <v>258.2960407722234</v>
       </c>
       <c r="I2" t="n">
         <v>210.4159433237724</v>
       </c>
       <c r="J2" t="n">
-        <v>552.0751121092054</v>
+        <v>552.0751121092048</v>
       </c>
       <c r="K2" t="n">
-        <v>148.3853257188758</v>
+        <v>148.3853257188756</v>
       </c>
       <c r="L2" t="n">
-        <v>557.6878014776809</v>
+        <v>89.14113660583185</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.970664711016249</v>
+        <v>4.970664711016122</v>
       </c>
       <c r="C3" t="n">
-        <v>4.789416540477672</v>
+        <v>4.789416540477657</v>
       </c>
       <c r="D3" t="n">
-        <v>4.970664711016249</v>
+        <v>4.970664711016122</v>
       </c>
       <c r="E3" t="n">
-        <v>4.872284262234999</v>
+        <v>4.872284262234992</v>
       </c>
       <c r="F3" t="n">
-        <v>4.872284262234999</v>
+        <v>4.872284262234991</v>
       </c>
       <c r="G3" t="n">
-        <v>4.973513692045666</v>
+        <v>4.973513692045545</v>
       </c>
       <c r="H3" t="n">
-        <v>4.970664711016163</v>
+        <v>4.970664711016122</v>
       </c>
       <c r="I3" t="n">
-        <v>4.988877766756781</v>
+        <v>4.988877766756772</v>
       </c>
       <c r="J3" t="n">
-        <v>4.970664711016249</v>
+        <v>4.970664711016122</v>
       </c>
       <c r="K3" t="n">
-        <v>4.970664711016249</v>
+        <v>4.970664711016122</v>
       </c>
       <c r="L3" t="n">
-        <v>4.970664711016249</v>
+        <v>4.970664711016122</v>
       </c>
     </row>
     <row r="4">
@@ -7723,34 +7723,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>637.106777159639</v>
+        <v>762.3455331340629</v>
       </c>
       <c r="C4" t="n">
         <v>637.0511875181369</v>
       </c>
       <c r="D4" t="n">
-        <v>637.3393319232667</v>
+        <v>637.3393319232659</v>
       </c>
       <c r="E4" t="n">
-        <v>574.2085370840424</v>
+        <v>574.2085370840417</v>
       </c>
       <c r="F4" t="n">
-        <v>637.1494377171092</v>
+        <v>637.1494377171093</v>
       </c>
       <c r="G4" t="n">
-        <v>762.3483821150926</v>
+        <v>637.1096261406681</v>
       </c>
       <c r="H4" t="n">
-        <v>762.953097360498</v>
+        <v>762.9530973604982</v>
       </c>
       <c r="I4" t="n">
-        <v>762.3637461898031</v>
+        <v>762.3637461898034</v>
       </c>
       <c r="J4" t="n">
-        <v>762.7228989444914</v>
+        <v>669.457483507405</v>
       </c>
       <c r="K4" t="n">
-        <v>636.9583517212764</v>
+        <v>636.9583517212758</v>
       </c>
       <c r="L4" t="n">
         <v>637.2441024631651</v>
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.25610017899665</v>
+        <v>10.25610017899659</v>
       </c>
       <c r="C5" t="n">
-        <v>10.27431323473725</v>
+        <v>10.27431323473724</v>
       </c>
       <c r="D5" t="n">
-        <v>10.2560730596767</v>
+        <v>10.25607305967668</v>
       </c>
       <c r="E5" t="n">
-        <v>10.25223910823255</v>
+        <v>10.25223910823254</v>
       </c>
       <c r="F5" t="n">
-        <v>10.25223910823255</v>
+        <v>10.25223910823254</v>
       </c>
       <c r="G5" t="n">
-        <v>10.25894916002607</v>
+        <v>10.25894916002601</v>
       </c>
       <c r="H5" t="n">
-        <v>10.25610017899665</v>
+        <v>10.25610017899659</v>
       </c>
       <c r="I5" t="n">
-        <v>10.27431323473725</v>
+        <v>10.27431323473724</v>
       </c>
       <c r="J5" t="n">
-        <v>10.25610017899665</v>
+        <v>10.25610017899659</v>
       </c>
       <c r="K5" t="n">
-        <v>10.25610017899665</v>
+        <v>10.25610017899659</v>
       </c>
       <c r="L5" t="n">
-        <v>10.25610017899665</v>
+        <v>10.25610017899659</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.99576467836343</v>
+        <v>11.99576467836347</v>
       </c>
       <c r="C6" t="n">
-        <v>17.27491319862532</v>
+        <v>17.27491319868625</v>
       </c>
       <c r="D6" t="n">
-        <v>18.3718696704659</v>
+        <v>18.37186967046584</v>
       </c>
       <c r="E6" t="n">
-        <v>15.83278881392587</v>
+        <v>15.83278881392586</v>
       </c>
       <c r="F6" t="n">
-        <v>12.16822662451318</v>
+        <v>12.16822662451316</v>
       </c>
       <c r="G6" t="n">
-        <v>17.2796594123715</v>
+        <v>17.27965941237147</v>
       </c>
       <c r="H6" t="n">
-        <v>17.27681043135031</v>
+        <v>17.27681043135023</v>
       </c>
       <c r="I6" t="n">
-        <v>17.29502348708269</v>
+        <v>17.2950234870827</v>
       </c>
       <c r="J6" t="n">
-        <v>17.2778483006639</v>
+        <v>17.27784830066388</v>
       </c>
       <c r="K6" t="n">
-        <v>11.89766654286729</v>
+        <v>11.89766654286724</v>
       </c>
       <c r="L6" t="n">
-        <v>22.79330430721538</v>
+        <v>22.7933043072153</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.80618643562449</v>
+        <v>22.80618643562444</v>
       </c>
       <c r="C7" t="n">
-        <v>28.11266539537585</v>
+        <v>28.11266539537583</v>
       </c>
       <c r="D7" t="n">
-        <v>28.09445740346666</v>
+        <v>28.09445740346669</v>
       </c>
       <c r="E7" t="n">
-        <v>34.21521295458714</v>
+        <v>34.21521295458713</v>
       </c>
       <c r="F7" t="n">
-        <v>28.11266240156461</v>
+        <v>28.11266240156456</v>
       </c>
       <c r="G7" t="n">
-        <v>28.09730132066444</v>
+        <v>28.09730132066458</v>
       </c>
       <c r="H7" t="n">
-        <v>28.09445233963537</v>
+        <v>28.09445233963516</v>
       </c>
       <c r="I7" t="n">
-        <v>28.11266539537585</v>
+        <v>28.11266539537583</v>
       </c>
       <c r="J7" t="n">
-        <v>28.09445233963537</v>
+        <v>28.09445233963516</v>
       </c>
       <c r="K7" t="n">
-        <v>25.0304124360565</v>
+        <v>21.43558030192423</v>
       </c>
       <c r="L7" t="n">
-        <v>28.09445233963537</v>
+        <v>28.09445233963516</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.6260146688738</v>
+        <v>172.6260146688737</v>
       </c>
       <c r="C8" t="n">
-        <v>172.7003326788734</v>
+        <v>172.7003326788732</v>
       </c>
       <c r="D8" t="n">
         <v>164.4412651735375</v>
       </c>
       <c r="E8" t="n">
-        <v>172.7003326788734</v>
+        <v>172.7003326788732</v>
       </c>
       <c r="F8" t="n">
-        <v>172.7003326788734</v>
+        <v>172.7003326788732</v>
       </c>
       <c r="G8" t="n">
-        <v>166.6208664003755</v>
+        <v>166.6208664003756</v>
       </c>
       <c r="H8" t="n">
         <v>167.0851416156287</v>
       </c>
       <c r="I8" t="n">
-        <v>172.7003326788734</v>
+        <v>172.7003326788732</v>
       </c>
       <c r="J8" t="n">
-        <v>160.5122489163816</v>
+        <v>160.5122489163815</v>
       </c>
       <c r="K8" t="n">
         <v>169.4172092786861</v>
       </c>
       <c r="L8" t="n">
-        <v>171.3266555529513</v>
+        <v>161.2649657974194</v>
       </c>
     </row>
     <row r="9">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170.3099916168247</v>
+        <v>170.3099916168246</v>
       </c>
       <c r="C9" t="n">
         <v>173.1793492051212</v>
@@ -7938,22 +7938,22 @@
         <v>173.1793492051212</v>
       </c>
       <c r="G9" t="n">
-        <v>167.8587543615065</v>
+        <v>167.8587543615066</v>
       </c>
       <c r="H9" t="n">
-        <v>168.0589666997661</v>
+        <v>168.058966699766</v>
       </c>
       <c r="I9" t="n">
         <v>173.1793492051212</v>
       </c>
       <c r="J9" t="n">
-        <v>165.3809908320638</v>
+        <v>165.3809908320636</v>
       </c>
       <c r="K9" t="n">
         <v>169.0032682454899</v>
       </c>
       <c r="L9" t="n">
-        <v>169.7822048717343</v>
+        <v>165.6917855220081</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen resource use fossils results.xlsx
+++ b/Results/Hydrogen/hydrogen resource use fossils results.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>410.3914677474596</v>
+        <v>410.3914677474598</v>
       </c>
       <c r="C2" t="n">
         <v>433.5097743491357</v>
       </c>
       <c r="D2" t="n">
-        <v>516.9436849857864</v>
+        <v>516.9436849857872</v>
       </c>
       <c r="E2" t="n">
         <v>433.5097743491357</v>
@@ -530,22 +530,22 @@
         <v>433.5097743491357</v>
       </c>
       <c r="G2" t="n">
-        <v>540.2280851423961</v>
+        <v>540.2280851423956</v>
       </c>
       <c r="H2" t="n">
-        <v>1077.656843516059</v>
+        <v>1077.656843516058</v>
       </c>
       <c r="I2" t="n">
         <v>433.5097743491357</v>
       </c>
       <c r="J2" t="n">
-        <v>833.6352089603465</v>
+        <v>833.635208960349</v>
       </c>
       <c r="K2" t="n">
-        <v>514.8108253616947</v>
+        <v>514.810825361695</v>
       </c>
       <c r="L2" t="n">
-        <v>294.4015286840936</v>
+        <v>953.8447060460213</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.881779997743518</v>
+        <v>6.881779997743494</v>
       </c>
       <c r="C3" t="n">
-        <v>6.720405657890912</v>
+        <v>6.720405657890902</v>
       </c>
       <c r="D3" t="n">
-        <v>6.881779997743518</v>
+        <v>6.881779997743494</v>
       </c>
       <c r="E3" t="n">
-        <v>6.840461302603824</v>
+        <v>6.840461302603813</v>
       </c>
       <c r="F3" t="n">
-        <v>6.840461302603814</v>
+        <v>6.840461302603813</v>
       </c>
       <c r="G3" t="n">
-        <v>6.883312304235101</v>
+        <v>6.883312304235134</v>
       </c>
       <c r="H3" t="n">
-        <v>6.881779997743518</v>
+        <v>6.881779997743494</v>
       </c>
       <c r="I3" t="n">
-        <v>6.89178426526477</v>
+        <v>6.891784265264764</v>
       </c>
       <c r="J3" t="n">
-        <v>6.881779997743518</v>
+        <v>6.881779997743494</v>
       </c>
       <c r="K3" t="n">
-        <v>6.881779997743518</v>
+        <v>6.881779997743494</v>
       </c>
       <c r="L3" t="n">
-        <v>6.881779997743518</v>
+        <v>6.881779997743494</v>
       </c>
     </row>
     <row r="4">
@@ -598,34 +598,34 @@
         <v>732.8382158274557</v>
       </c>
       <c r="C4" t="n">
-        <v>732.7163324346784</v>
+        <v>732.7163324346777</v>
       </c>
       <c r="D4" t="n">
-        <v>732.9204669115744</v>
+        <v>732.9204592843855</v>
       </c>
       <c r="E4" t="n">
-        <v>660.5709690455789</v>
+        <v>660.5709690455781</v>
       </c>
       <c r="F4" t="n">
-        <v>732.8904934557916</v>
+        <v>732.8904934557913</v>
       </c>
       <c r="G4" t="n">
-        <v>878.1749198569258</v>
+        <v>878.174919856926</v>
       </c>
       <c r="H4" t="n">
         <v>878.9973925037941</v>
       </c>
       <c r="I4" t="n">
-        <v>732.8482200949768</v>
+        <v>878.1833918179558</v>
       </c>
       <c r="J4" t="n">
-        <v>770.0290324975963</v>
+        <v>878.5720291885591</v>
       </c>
       <c r="K4" t="n">
-        <v>732.9155438128975</v>
+        <v>732.9155438128971</v>
       </c>
       <c r="L4" t="n">
-        <v>733.0272241740071</v>
+        <v>733.0272241740076</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.63909357296167</v>
+        <v>14.6390935729617</v>
       </c>
       <c r="C5" t="n">
-        <v>14.64909784048299</v>
+        <v>14.64909784048298</v>
       </c>
       <c r="D5" t="n">
-        <v>14.63900801096119</v>
+        <v>14.63900801096118</v>
       </c>
       <c r="E5" t="n">
-        <v>14.6516737225958</v>
+        <v>14.65167372259578</v>
       </c>
       <c r="F5" t="n">
-        <v>14.6516737225958</v>
+        <v>14.65167372259578</v>
       </c>
       <c r="G5" t="n">
-        <v>14.64062587945338</v>
+        <v>14.64062587945334</v>
       </c>
       <c r="H5" t="n">
-        <v>14.63909357296167</v>
+        <v>14.6390935729617</v>
       </c>
       <c r="I5" t="n">
-        <v>14.64909784048299</v>
+        <v>14.64909784048298</v>
       </c>
       <c r="J5" t="n">
-        <v>14.63909357296167</v>
+        <v>14.6390935729617</v>
       </c>
       <c r="K5" t="n">
-        <v>14.63909357296167</v>
+        <v>14.6390935729617</v>
       </c>
       <c r="L5" t="n">
-        <v>14.63909357296167</v>
+        <v>14.6390935729617</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.01000425062157</v>
+        <v>18.01000425062151</v>
       </c>
       <c r="C6" t="n">
-        <v>26.45559065434121</v>
+        <v>26.45559065448522</v>
       </c>
       <c r="D6" t="n">
-        <v>28.18974834266977</v>
+        <v>28.18974834266966</v>
       </c>
       <c r="E6" t="n">
-        <v>24.14927779614814</v>
+        <v>24.14927779614808</v>
       </c>
       <c r="F6" t="n">
-        <v>18.28885957448014</v>
+        <v>18.28885957448013</v>
       </c>
       <c r="G6" t="n">
-        <v>26.44296834345946</v>
+        <v>26.44296834345941</v>
       </c>
       <c r="H6" t="n">
-        <v>26.44143603697068</v>
+        <v>26.44143603697066</v>
       </c>
       <c r="I6" t="n">
-        <v>26.45144030448908</v>
+        <v>26.45144030448903</v>
       </c>
       <c r="J6" t="n">
-        <v>26.44309304288856</v>
+        <v>26.44309304288853</v>
       </c>
       <c r="K6" t="n">
-        <v>17.85338607753869</v>
+        <v>17.8533860775387</v>
       </c>
       <c r="L6" t="n">
-        <v>35.24877155143805</v>
+        <v>35.248771551438</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39.08555736155554</v>
+        <v>39.08555736155551</v>
       </c>
       <c r="C7" t="n">
-        <v>48.59392129914497</v>
+        <v>48.59392129914492</v>
       </c>
       <c r="D7" t="n">
-        <v>48.58391924583067</v>
+        <v>48.58391924583056</v>
       </c>
       <c r="E7" t="n">
-        <v>59.55481331937909</v>
+        <v>59.55481331937904</v>
       </c>
       <c r="F7" t="n">
-        <v>48.59390878485371</v>
+        <v>48.59390878485372</v>
       </c>
       <c r="G7" t="n">
-        <v>48.58544933811537</v>
+        <v>48.5854493381153</v>
       </c>
       <c r="H7" t="n">
-        <v>48.5839170316237</v>
+        <v>48.58391703162366</v>
       </c>
       <c r="I7" t="n">
-        <v>48.59392129914497</v>
+        <v>48.59392129914492</v>
       </c>
       <c r="J7" t="n">
-        <v>48.5839170316237</v>
+        <v>48.58391703162366</v>
       </c>
       <c r="K7" t="n">
-        <v>43.08053106713635</v>
+        <v>36.62378618192854</v>
       </c>
       <c r="L7" t="n">
-        <v>48.5839170316237</v>
+        <v>48.58391703162366</v>
       </c>
     </row>
     <row r="8">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>166.097938701725</v>
+        <v>166.0979387017249</v>
       </c>
       <c r="C8" t="n">
         <v>170.6597270395064</v>
@@ -770,22 +770,22 @@
         <v>170.6597270395064</v>
       </c>
       <c r="G8" t="n">
-        <v>163.8250903738453</v>
+        <v>163.8250903738455</v>
       </c>
       <c r="H8" t="n">
-        <v>154.6666202222292</v>
+        <v>154.6666202222293</v>
       </c>
       <c r="I8" t="n">
         <v>170.6597270395064</v>
       </c>
       <c r="J8" t="n">
-        <v>158.2352607227447</v>
+        <v>158.2352607227446</v>
       </c>
       <c r="K8" t="n">
-        <v>164.1197071452851</v>
+        <v>164.1197071452853</v>
       </c>
       <c r="L8" t="n">
-        <v>169.4770512910057</v>
+        <v>169.4770512910056</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168.6829509667459</v>
+        <v>168.6829509667458</v>
       </c>
       <c r="C9" t="n">
-        <v>173.4167242064194</v>
+        <v>173.4167242064195</v>
       </c>
       <c r="D9" t="n">
-        <v>167.859281848633</v>
+        <v>167.8592818486328</v>
       </c>
       <c r="E9" t="n">
-        <v>173.4167242064194</v>
+        <v>173.4167242064195</v>
       </c>
       <c r="F9" t="n">
-        <v>173.4167242064194</v>
+        <v>173.4167242064195</v>
       </c>
       <c r="G9" t="n">
         <v>167.7497415837515</v>
       </c>
       <c r="H9" t="n">
-        <v>164.0459999666681</v>
+        <v>164.045999966668</v>
       </c>
       <c r="I9" t="n">
-        <v>173.4167242064194</v>
+        <v>173.4167242064195</v>
       </c>
       <c r="J9" t="n">
-        <v>165.4869374399328</v>
+        <v>165.4869374399329</v>
       </c>
       <c r="K9" t="n">
-        <v>167.877806730037</v>
+        <v>167.8778067300369</v>
       </c>
       <c r="L9" t="n">
-        <v>170.063381990991</v>
+        <v>165.2396359446417</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.48809248194744</v>
+        <v>18.48809248194743</v>
       </c>
       <c r="C2" t="n">
-        <v>122.4481448371878</v>
+        <v>122.4481448371879</v>
       </c>
       <c r="D2" t="n">
-        <v>192.547993375553</v>
+        <v>192.5479933755528</v>
       </c>
       <c r="E2" t="n">
-        <v>122.4481448371878</v>
+        <v>122.4481448371879</v>
       </c>
       <c r="F2" t="n">
-        <v>122.4481448371878</v>
+        <v>122.4481448371879</v>
       </c>
       <c r="G2" t="n">
-        <v>181.9048108973663</v>
+        <v>181.9048108973664</v>
       </c>
       <c r="H2" t="n">
-        <v>168.9616817326346</v>
+        <v>168.9616817326349</v>
       </c>
       <c r="I2" t="n">
-        <v>122.4481448371878</v>
+        <v>122.4481448371879</v>
       </c>
       <c r="J2" t="n">
         <v>416.1249985428269</v>
       </c>
       <c r="K2" t="n">
-        <v>91.66042070128542</v>
+        <v>91.66042070128549</v>
       </c>
       <c r="L2" t="n">
-        <v>187.97575428933</v>
+        <v>187.9757542893301</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.280236021455981</v>
+        <v>4.280236021455945</v>
       </c>
       <c r="C3" t="n">
-        <v>4.029122088491798</v>
+        <v>4.029122088491797</v>
       </c>
       <c r="D3" t="n">
-        <v>4.280236021455981</v>
+        <v>4.280236021455945</v>
       </c>
       <c r="E3" t="n">
-        <v>4.108068726987806</v>
+        <v>4.108068726987812</v>
       </c>
       <c r="F3" t="n">
         <v>4.10806872698781</v>
       </c>
       <c r="G3" t="n">
-        <v>4.282695655925256</v>
+        <v>4.282695655925195</v>
       </c>
       <c r="H3" t="n">
-        <v>4.280236021455981</v>
+        <v>4.280236021455945</v>
       </c>
       <c r="I3" t="n">
-        <v>4.29589572993163</v>
+        <v>4.295895729931634</v>
       </c>
       <c r="J3" t="n">
-        <v>4.280236021455981</v>
+        <v>4.280236021455945</v>
       </c>
       <c r="K3" t="n">
-        <v>4.280236021455981</v>
+        <v>4.280236021455945</v>
       </c>
       <c r="L3" t="n">
-        <v>4.280236021455981</v>
+        <v>4.280236021455945</v>
       </c>
     </row>
     <row r="4">
@@ -991,34 +991,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>760.5635690724331</v>
+        <v>635.9478284328961</v>
       </c>
       <c r="C4" t="n">
-        <v>635.8541149848393</v>
+        <v>635.8541149848396</v>
       </c>
       <c r="D4" t="n">
-        <v>760.7401889354423</v>
+        <v>760.7401889354409</v>
       </c>
       <c r="E4" t="n">
-        <v>573.0447007240197</v>
+        <v>573.044700724019</v>
       </c>
       <c r="F4" t="n">
-        <v>635.9747000441066</v>
+        <v>635.9747000441067</v>
       </c>
       <c r="G4" t="n">
-        <v>635.9502880673654</v>
+        <v>760.5660287069026</v>
       </c>
       <c r="H4" t="n">
-        <v>761.1528852937507</v>
+        <v>761.1528852937508</v>
       </c>
       <c r="I4" t="n">
-        <v>635.9634881413713</v>
+        <v>635.9634881413716</v>
       </c>
       <c r="J4" t="n">
-        <v>760.9355327713204</v>
+        <v>668.2509495167747</v>
       </c>
       <c r="K4" t="n">
-        <v>635.8404015101695</v>
+        <v>635.8404015101705</v>
       </c>
       <c r="L4" t="n">
         <v>635.998839395935</v>
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.100792920163004</v>
+        <v>9.100792920163075</v>
       </c>
       <c r="C5" t="n">
-        <v>9.116452628638649</v>
+        <v>9.116452628638655</v>
       </c>
       <c r="D5" t="n">
-        <v>9.100788468893542</v>
+        <v>9.100788468893636</v>
       </c>
       <c r="E5" t="n">
-        <v>9.07683499431039</v>
+        <v>9.076834994310406</v>
       </c>
       <c r="F5" t="n">
-        <v>9.07683499431039</v>
+        <v>9.076834994310406</v>
       </c>
       <c r="G5" t="n">
-        <v>9.103252554632276</v>
+        <v>9.10325255463227</v>
       </c>
       <c r="H5" t="n">
-        <v>9.100792920163004</v>
+        <v>9.100792920163075</v>
       </c>
       <c r="I5" t="n">
-        <v>9.116452628638649</v>
+        <v>9.116452628638655</v>
       </c>
       <c r="J5" t="n">
-        <v>9.100792920163004</v>
+        <v>9.100792920163075</v>
       </c>
       <c r="K5" t="n">
-        <v>9.100792920163004</v>
+        <v>9.100792920163075</v>
       </c>
       <c r="L5" t="n">
-        <v>9.100792920163004</v>
+        <v>9.100792920163075</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.42350965867985</v>
+        <v>10.42350965867975</v>
       </c>
       <c r="C6" t="n">
-        <v>15.00665389482566</v>
+        <v>15.00665389486645</v>
       </c>
       <c r="D6" t="n">
         <v>15.98282373314828</v>
       </c>
       <c r="E6" t="n">
-        <v>13.75135439748235</v>
+        <v>13.75135439748236</v>
       </c>
       <c r="F6" t="n">
         <v>10.5614948012593</v>
       </c>
       <c r="G6" t="n">
-        <v>15.03050325531073</v>
+        <v>15.0305032553108</v>
       </c>
       <c r="H6" t="n">
-        <v>15.02804362085081</v>
+        <v>15.02804362085089</v>
       </c>
       <c r="I6" t="n">
-        <v>15.0437033293171</v>
+        <v>15.04370332931714</v>
       </c>
       <c r="J6" t="n">
-        <v>15.0289485371964</v>
+        <v>15.02894853719643</v>
       </c>
       <c r="K6" t="n">
-        <v>10.33797807692741</v>
+        <v>10.33797807692752</v>
       </c>
       <c r="L6" t="n">
-        <v>19.83786436313628</v>
+        <v>19.83786436313629</v>
       </c>
     </row>
     <row r="7">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.67388379812844</v>
+        <v>18.67388379812842</v>
       </c>
       <c r="C7" t="n">
         <v>22.97536181629374</v>
@@ -1120,28 +1120,28 @@
         <v>22.95970643722458</v>
       </c>
       <c r="E7" t="n">
-        <v>27.92110668527062</v>
+        <v>27.92110668527064</v>
       </c>
       <c r="F7" t="n">
-        <v>22.97535981623813</v>
+        <v>22.97535981623806</v>
       </c>
       <c r="G7" t="n">
-        <v>22.96216174228737</v>
+        <v>22.96216174228742</v>
       </c>
       <c r="H7" t="n">
-        <v>22.95970210781812</v>
+        <v>22.95970210781816</v>
       </c>
       <c r="I7" t="n">
         <v>22.97536181629374</v>
       </c>
       <c r="J7" t="n">
-        <v>22.95970210781812</v>
+        <v>22.95970210781816</v>
       </c>
       <c r="K7" t="n">
-        <v>20.47648396840806</v>
+        <v>20.47648396840809</v>
       </c>
       <c r="L7" t="n">
-        <v>22.95970210781812</v>
+        <v>22.95970210781816</v>
       </c>
     </row>
     <row r="8">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.2359515778761</v>
+        <v>172.235951577876</v>
       </c>
       <c r="C8" t="n">
         <v>174.292336715524</v>
@@ -1166,22 +1166,22 @@
         <v>174.292336715524</v>
       </c>
       <c r="G8" t="n">
-        <v>168.0524757064851</v>
+        <v>168.0524757064848</v>
       </c>
       <c r="H8" t="n">
-        <v>168.7837654211999</v>
+        <v>168.7837654211997</v>
       </c>
       <c r="I8" t="n">
         <v>174.292336715524</v>
       </c>
       <c r="J8" t="n">
-        <v>162.9282439966442</v>
+        <v>162.9282439966443</v>
       </c>
       <c r="K8" t="n">
-        <v>170.2049880577377</v>
+        <v>170.2049880577374</v>
       </c>
       <c r="L8" t="n">
-        <v>168.6190307920876</v>
+        <v>168.6190307920871</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.7700747465041</v>
+        <v>169.770074746504</v>
       </c>
       <c r="C9" t="n">
-        <v>173.3789468212092</v>
+        <v>173.3789468212091</v>
       </c>
       <c r="D9" t="n">
-        <v>167.8680312848982</v>
+        <v>167.8680312848981</v>
       </c>
       <c r="E9" t="n">
-        <v>173.3789468212092</v>
+        <v>173.3789468212091</v>
       </c>
       <c r="F9" t="n">
-        <v>173.3789468212092</v>
+        <v>173.3789468212091</v>
       </c>
       <c r="G9" t="n">
         <v>168.0590775364415</v>
       </c>
       <c r="H9" t="n">
-        <v>168.3675675572776</v>
+        <v>168.3675675572773</v>
       </c>
       <c r="I9" t="n">
-        <v>173.3789468212092</v>
+        <v>173.3789468212091</v>
       </c>
       <c r="J9" t="n">
-        <v>165.982791965191</v>
+        <v>165.9827919651909</v>
       </c>
       <c r="K9" t="n">
-        <v>168.9430025530729</v>
+        <v>168.9430025530727</v>
       </c>
       <c r="L9" t="n">
-        <v>169.0237648154994</v>
+        <v>168.2999360122569</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>179.2920817887911</v>
+        <v>179.2920817887908</v>
       </c>
       <c r="C2" t="n">
-        <v>175.0762117277262</v>
+        <v>175.0762117277259</v>
       </c>
       <c r="D2" t="n">
-        <v>314.0101212438434</v>
+        <v>314.0101212438432</v>
       </c>
       <c r="E2" t="n">
-        <v>268.7089523503525</v>
+        <v>268.7089523503524</v>
       </c>
       <c r="F2" t="n">
-        <v>268.7089523503525</v>
+        <v>268.7089523503524</v>
       </c>
       <c r="G2" t="n">
-        <v>317.1512962838814</v>
+        <v>317.1512962838817</v>
       </c>
       <c r="H2" t="n">
-        <v>521.788295597116</v>
+        <v>521.7882955971161</v>
       </c>
       <c r="I2" t="n">
-        <v>268.7089523503525</v>
+        <v>268.7089523503524</v>
       </c>
       <c r="J2" t="n">
-        <v>520.8070941645258</v>
+        <v>520.807094164525</v>
       </c>
       <c r="K2" t="n">
-        <v>295.649642231156</v>
+        <v>295.6496422311553</v>
       </c>
       <c r="L2" t="n">
-        <v>291.3728714991367</v>
+        <v>291.3728714991366</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.548362515101058</v>
+        <v>5.548362515101052</v>
       </c>
       <c r="C3" t="n">
-        <v>5.142961417072006</v>
+        <v>5.142961417071982</v>
       </c>
       <c r="D3" t="n">
-        <v>5.548362515101058</v>
+        <v>5.548362515101051</v>
       </c>
       <c r="E3" t="n">
-        <v>5.444198230014987</v>
+        <v>5.444198230014983</v>
       </c>
       <c r="F3" t="n">
-        <v>5.444198230014988</v>
+        <v>5.444198230014983</v>
       </c>
       <c r="G3" t="n">
-        <v>5.540662554093154</v>
+        <v>5.540662554093179</v>
       </c>
       <c r="H3" t="n">
-        <v>5.548362515101058</v>
+        <v>5.548362515101052</v>
       </c>
       <c r="I3" t="n">
-        <v>5.496501766652287</v>
+        <v>5.496501766652293</v>
       </c>
       <c r="J3" t="n">
-        <v>5.548362515101058</v>
+        <v>5.548362515101052</v>
       </c>
       <c r="K3" t="n">
-        <v>5.548362515101058</v>
+        <v>5.548362515101051</v>
       </c>
       <c r="L3" t="n">
-        <v>5.548362515101058</v>
+        <v>5.548362515101051</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>672.8663679934546</v>
+        <v>805.5474111790148</v>
       </c>
       <c r="C4" t="n">
-        <v>672.5649981157984</v>
+        <v>672.5649981157982</v>
       </c>
       <c r="D4" t="n">
-        <v>672.9306706220424</v>
+        <v>672.9306773344751</v>
       </c>
       <c r="E4" t="n">
-        <v>606.3730749276908</v>
+        <v>606.3730749276905</v>
       </c>
       <c r="F4" t="n">
         <v>672.8393026684187</v>
       </c>
       <c r="G4" t="n">
-        <v>805.5397112180067</v>
+        <v>672.8586680324462</v>
       </c>
       <c r="H4" t="n">
-        <v>806.5328949303026</v>
+        <v>806.5328949303025</v>
       </c>
       <c r="I4" t="n">
-        <v>805.4955504305656</v>
+        <v>672.8145072450052</v>
       </c>
       <c r="J4" t="n">
-        <v>805.983117978612</v>
+        <v>805.9831179786117</v>
       </c>
       <c r="K4" t="n">
-        <v>672.8867626481759</v>
+        <v>672.8867626481757</v>
       </c>
       <c r="L4" t="n">
-        <v>672.8950240144785</v>
+        <v>672.895024014479</v>
       </c>
     </row>
     <row r="5">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.94839378560625</v>
+        <v>11.94839378560627</v>
       </c>
       <c r="C5" t="n">
-        <v>11.93715832941094</v>
+        <v>11.93715832941095</v>
       </c>
       <c r="D5" t="n">
-        <v>11.94838721209421</v>
+        <v>11.94838721209419</v>
       </c>
       <c r="E5" t="n">
         <v>11.89839331301318</v>
@@ -1445,19 +1445,19 @@
         <v>11.94069382459834</v>
       </c>
       <c r="H5" t="n">
-        <v>11.94839378560625</v>
+        <v>11.94839378560627</v>
       </c>
       <c r="I5" t="n">
         <v>11.89653303715748</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94839378560625</v>
+        <v>11.94839378560627</v>
       </c>
       <c r="K5" t="n">
-        <v>11.94839378560625</v>
+        <v>11.94839378560627</v>
       </c>
       <c r="L5" t="n">
-        <v>11.94839378560625</v>
+        <v>11.94839378560627</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.51517986777366</v>
+        <v>14.51517986777365</v>
       </c>
       <c r="C6" t="n">
         <v>21.34689143553981</v>
       </c>
       <c r="D6" t="n">
-        <v>22.77336274721333</v>
+        <v>22.7733627472134</v>
       </c>
       <c r="E6" t="n">
-        <v>19.43535805279068</v>
+        <v>19.43535805279071</v>
       </c>
       <c r="F6" t="n">
-        <v>14.68124666803876</v>
+        <v>14.68124666803879</v>
       </c>
       <c r="G6" t="n">
-        <v>21.34736753041465</v>
+        <v>21.34736753041467</v>
       </c>
       <c r="H6" t="n">
-        <v>21.35506749145034</v>
+        <v>21.35506749145032</v>
       </c>
       <c r="I6" t="n">
-        <v>21.30320674297378</v>
+        <v>21.30320674297381</v>
       </c>
       <c r="J6" t="n">
-        <v>21.35641171470282</v>
+        <v>21.35641171470286</v>
       </c>
       <c r="K6" t="n">
-        <v>14.38812544450028</v>
+        <v>14.38812544450031</v>
       </c>
       <c r="L6" t="n">
-        <v>28.49990204656911</v>
+        <v>28.49990204656918</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.80141712480654</v>
+        <v>26.80141712480652</v>
       </c>
       <c r="C7" t="n">
         <v>33.16508374528419</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17632383053106</v>
+        <v>33.17632383053115</v>
       </c>
       <c r="E7" t="n">
-        <v>40.48095852540419</v>
+        <v>40.48095852540418</v>
       </c>
       <c r="F7" t="n">
-        <v>33.12445370189974</v>
+        <v>33.12445370189973</v>
       </c>
       <c r="G7" t="n">
-        <v>33.16861924047158</v>
+        <v>33.16861924047156</v>
       </c>
       <c r="H7" t="n">
-        <v>33.17631920147947</v>
+        <v>33.17631920147951</v>
       </c>
       <c r="I7" t="n">
-        <v>33.12445845303073</v>
+        <v>33.12445845303072</v>
       </c>
       <c r="J7" t="n">
-        <v>33.17631920147947</v>
+        <v>33.17631920147951</v>
       </c>
       <c r="K7" t="n">
         <v>29.48267784904393</v>
       </c>
       <c r="L7" t="n">
-        <v>33.17631920147947</v>
+        <v>33.17631920147951</v>
       </c>
     </row>
     <row r="8">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>163.3501429267516</v>
+        <v>163.3501429267517</v>
       </c>
       <c r="C8" t="n">
         <v>165.3972036468965</v>
@@ -1556,25 +1556,25 @@
         <v>165.6016664516009</v>
       </c>
       <c r="E8" t="n">
-        <v>165.0178081187632</v>
+        <v>165.0178081187631</v>
       </c>
       <c r="F8" t="n">
-        <v>165.0178081187632</v>
+        <v>165.0178081187631</v>
       </c>
       <c r="G8" t="n">
-        <v>164.3242484449758</v>
+        <v>164.3242484449759</v>
       </c>
       <c r="H8" t="n">
-        <v>162.2122347051116</v>
+        <v>162.2122347051115</v>
       </c>
       <c r="I8" t="n">
-        <v>165.0178081187632</v>
+        <v>165.0178081187631</v>
       </c>
       <c r="J8" t="n">
-        <v>172.1008621900337</v>
+        <v>172.1008621900335</v>
       </c>
       <c r="K8" t="n">
-        <v>172.660482550422</v>
+        <v>172.6604825504221</v>
       </c>
       <c r="L8" t="n">
         <v>179.3152408247453</v>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163.0743701340254</v>
+        <v>163.0743701340255</v>
       </c>
       <c r="C9" t="n">
-        <v>165.0464810570723</v>
+        <v>165.0464810570724</v>
       </c>
       <c r="D9" t="n">
         <v>167.1619685237093</v>
@@ -1602,7 +1602,7 @@
         <v>165.9477609757689</v>
       </c>
       <c r="G9" t="n">
-        <v>165.8251161092018</v>
+        <v>165.8251161092019</v>
       </c>
       <c r="H9" t="n">
         <v>165.7911115775445</v>
@@ -1611,13 +1611,13 @@
         <v>165.9477609757689</v>
       </c>
       <c r="J9" t="n">
-        <v>175.9728047334176</v>
+        <v>175.9728047334175</v>
       </c>
       <c r="K9" t="n">
-        <v>173.8492832567793</v>
+        <v>173.8492832567792</v>
       </c>
       <c r="L9" t="n">
-        <v>179.844363725994</v>
+        <v>179.8443637259941</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93.1727480414894</v>
+        <v>93.17274804148927</v>
       </c>
       <c r="C2" t="n">
-        <v>117.0729928456997</v>
+        <v>117.0729928457</v>
       </c>
       <c r="D2" t="n">
-        <v>230.270838286605</v>
+        <v>230.2708382866051</v>
       </c>
       <c r="E2" t="n">
-        <v>133.3116406713084</v>
+        <v>133.3116406713087</v>
       </c>
       <c r="F2" t="n">
-        <v>133.3116406713084</v>
+        <v>133.3116406713087</v>
       </c>
       <c r="G2" t="n">
-        <v>204.4987689914499</v>
+        <v>204.4987689914504</v>
       </c>
       <c r="H2" t="n">
-        <v>286.3411992164336</v>
+        <v>286.3411992164337</v>
       </c>
       <c r="I2" t="n">
-        <v>133.3116406713084</v>
+        <v>133.3116406713087</v>
       </c>
       <c r="J2" t="n">
-        <v>377.2726568119442</v>
+        <v>377.2726568119444</v>
       </c>
       <c r="K2" t="n">
-        <v>143.233009055628</v>
+        <v>143.2330090556279</v>
       </c>
       <c r="L2" t="n">
-        <v>149.5663970054837</v>
+        <v>149.5663970054839</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.654032156819115</v>
+        <v>4.654032156819189</v>
       </c>
       <c r="C3" t="n">
-        <v>4.327819788408807</v>
+        <v>4.327819788408809</v>
       </c>
       <c r="D3" t="n">
-        <v>4.654032156819115</v>
+        <v>4.654032156819188</v>
       </c>
       <c r="E3" t="n">
-        <v>4.50052219049654</v>
+        <v>4.500522190496551</v>
       </c>
       <c r="F3" t="n">
-        <v>4.500522190496547</v>
+        <v>4.500522190496551</v>
       </c>
       <c r="G3" t="n">
-        <v>4.645411735598366</v>
+        <v>4.645411735598413</v>
       </c>
       <c r="H3" t="n">
-        <v>4.654032156819115</v>
+        <v>4.654032156819188</v>
       </c>
       <c r="I3" t="n">
-        <v>4.596127718719708</v>
+        <v>4.596127718719712</v>
       </c>
       <c r="J3" t="n">
-        <v>4.654032156819115</v>
+        <v>4.654032156819189</v>
       </c>
       <c r="K3" t="n">
-        <v>4.654032156819115</v>
+        <v>4.654032156819188</v>
       </c>
       <c r="L3" t="n">
-        <v>4.654032156819115</v>
+        <v>4.654032156819188</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>761.3589314122839</v>
+        <v>761.3589314122829</v>
       </c>
       <c r="C4" t="n">
-        <v>636.1188614623718</v>
+        <v>636.1188614623723</v>
       </c>
       <c r="D4" t="n">
-        <v>761.5675668045438</v>
+        <v>761.5675668045441</v>
       </c>
       <c r="E4" t="n">
-        <v>573.2908886521617</v>
+        <v>573.2908886521616</v>
       </c>
       <c r="F4" t="n">
-        <v>636.2468724138856</v>
+        <v>636.2468724138853</v>
       </c>
       <c r="G4" t="n">
-        <v>636.2938016015568</v>
+        <v>761.3503109910627</v>
       </c>
       <c r="H4" t="n">
         <v>762.1470385037624</v>
       </c>
       <c r="I4" t="n">
-        <v>636.2445175846781</v>
+        <v>636.2445175846776</v>
       </c>
       <c r="J4" t="n">
-        <v>668.5807281776996</v>
+        <v>668.5807281776987</v>
       </c>
       <c r="K4" t="n">
-        <v>636.2371950889305</v>
+        <v>636.2371950889304</v>
       </c>
       <c r="L4" t="n">
-        <v>636.3198821526271</v>
+        <v>636.3198821526277</v>
       </c>
     </row>
     <row r="5">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.08387289981451</v>
+        <v>10.08387289981453</v>
       </c>
       <c r="C5" t="n">
-        <v>10.07468776439312</v>
+        <v>10.07468776439314</v>
       </c>
       <c r="D5" t="n">
-        <v>10.08386934642133</v>
+        <v>10.08386934642124</v>
       </c>
       <c r="E5" t="n">
         <v>10.01955768622231</v>
@@ -1838,22 +1838,22 @@
         <v>10.01955768622231</v>
       </c>
       <c r="G5" t="n">
-        <v>10.07525247859378</v>
+        <v>10.07525247859376</v>
       </c>
       <c r="H5" t="n">
-        <v>10.08387289981451</v>
+        <v>10.08387289981453</v>
       </c>
       <c r="I5" t="n">
-        <v>10.02596846171505</v>
+        <v>10.02596846171506</v>
       </c>
       <c r="J5" t="n">
-        <v>10.08387289981451</v>
+        <v>10.08387289981453</v>
       </c>
       <c r="K5" t="n">
-        <v>10.08387289981451</v>
+        <v>10.08387289981453</v>
       </c>
       <c r="L5" t="n">
-        <v>10.08387289981451</v>
+        <v>10.08387289981453</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.03714459011187</v>
+        <v>12.03714459011206</v>
       </c>
       <c r="C6" t="n">
-        <v>17.63023241642053</v>
+        <v>17.63023241631929</v>
       </c>
       <c r="D6" t="n">
-        <v>18.80722802680982</v>
+        <v>18.80722802680987</v>
       </c>
       <c r="E6" t="n">
-        <v>16.04854786445596</v>
+        <v>16.04854786445597</v>
       </c>
       <c r="F6" t="n">
-        <v>12.15316261322478</v>
+        <v>12.15316261322477</v>
       </c>
       <c r="G6" t="n">
-        <v>17.63588484204398</v>
+        <v>17.635884842044</v>
       </c>
       <c r="H6" t="n">
-        <v>17.64450526328448</v>
+        <v>17.64450526328469</v>
       </c>
       <c r="I6" t="n">
-        <v>17.58660082516523</v>
+        <v>17.58660082516517</v>
       </c>
       <c r="J6" t="n">
-        <v>17.64560726154332</v>
+        <v>17.64560726154343</v>
       </c>
       <c r="K6" t="n">
         <v>11.93298498757819</v>
       </c>
       <c r="L6" t="n">
-        <v>23.50186235811909</v>
+        <v>23.50186235811936</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.40697900961904</v>
+        <v>20.40697900961912</v>
       </c>
       <c r="C7" t="n">
-        <v>25.15313360717934</v>
+        <v>25.15313360717937</v>
       </c>
       <c r="D7" t="n">
-        <v>25.16232288867118</v>
+        <v>25.16232288867123</v>
       </c>
       <c r="E7" t="n">
-        <v>30.59197548370663</v>
+        <v>30.59197548370666</v>
       </c>
       <c r="F7" t="n">
-        <v>25.10441127160049</v>
+        <v>25.10441127160056</v>
       </c>
       <c r="G7" t="n">
-        <v>25.15369832137996</v>
+        <v>25.15369832137998</v>
       </c>
       <c r="H7" t="n">
-        <v>25.1623187426007</v>
+        <v>25.16231874260079</v>
       </c>
       <c r="I7" t="n">
-        <v>25.10441430450127</v>
+        <v>25.1044143045013</v>
       </c>
       <c r="J7" t="n">
-        <v>25.1623187426007</v>
+        <v>25.16231874260079</v>
       </c>
       <c r="K7" t="n">
-        <v>22.40705796947208</v>
+        <v>22.40705796947205</v>
       </c>
       <c r="L7" t="n">
-        <v>25.1623187426007</v>
+        <v>25.16231874260079</v>
       </c>
     </row>
     <row r="8">
@@ -1946,34 +1946,34 @@
         <v>164.6376622185687</v>
       </c>
       <c r="C8" t="n">
-        <v>166.1166456253175</v>
+        <v>166.1166456253177</v>
       </c>
       <c r="D8" t="n">
         <v>166.1673071425723</v>
       </c>
       <c r="E8" t="n">
-        <v>167.1570913551207</v>
+        <v>167.1570913551208</v>
       </c>
       <c r="F8" t="n">
-        <v>167.1570913551207</v>
+        <v>167.1570913551208</v>
       </c>
       <c r="G8" t="n">
-        <v>166.1259830746846</v>
+        <v>166.1259830746845</v>
       </c>
       <c r="H8" t="n">
-        <v>165.6137950311643</v>
+        <v>165.6137950311644</v>
       </c>
       <c r="I8" t="n">
         <v>167.1570913551207</v>
       </c>
       <c r="J8" t="n">
-        <v>173.9393196470937</v>
+        <v>173.9393196470938</v>
       </c>
       <c r="K8" t="n">
-        <v>175.1481084081326</v>
+        <v>175.1481084081327</v>
       </c>
       <c r="L8" t="n">
-        <v>181.423371642873</v>
+        <v>181.4233716428731</v>
       </c>
     </row>
     <row r="9">
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163.2982484286498</v>
+        <v>163.2982484286497</v>
       </c>
       <c r="C9" t="n">
-        <v>165.0896772918421</v>
+        <v>165.089677291842</v>
       </c>
       <c r="D9" t="n">
         <v>166.7764085020979</v>
       </c>
       <c r="E9" t="n">
-        <v>166.3671850357485</v>
+        <v>166.3671850357486</v>
       </c>
       <c r="F9" t="n">
-        <v>166.3671850357485</v>
+        <v>166.3671850357486</v>
       </c>
       <c r="G9" t="n">
         <v>166.2905118839965</v>
@@ -2004,13 +2004,13 @@
         <v>166.5564876508731</v>
       </c>
       <c r="I9" t="n">
-        <v>166.3671850357485</v>
+        <v>166.3671850357486</v>
       </c>
       <c r="J9" t="n">
-        <v>176.2334407230928</v>
+        <v>176.233440723093</v>
       </c>
       <c r="K9" t="n">
-        <v>174.3829473298672</v>
+        <v>174.3829473298671</v>
       </c>
       <c r="L9" t="n">
         <v>180.3811599867713</v>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.90281054143465</v>
+        <v>41.90281054143438</v>
       </c>
       <c r="C2" t="n">
-        <v>75.62186661499562</v>
+        <v>75.62186661498893</v>
       </c>
       <c r="D2" t="n">
-        <v>179.750979649901</v>
+        <v>179.750979649891</v>
       </c>
       <c r="E2" t="n">
-        <v>47.59177106935247</v>
+        <v>47.59177106935259</v>
       </c>
       <c r="F2" t="n">
-        <v>47.59177106935247</v>
+        <v>47.59177106935259</v>
       </c>
       <c r="G2" t="n">
-        <v>136.690873778271</v>
+        <v>136.6908737782671</v>
       </c>
       <c r="H2" t="n">
-        <v>173.390160117372</v>
+        <v>173.3901601173728</v>
       </c>
       <c r="I2" t="n">
-        <v>47.59177106935247</v>
+        <v>47.59177106935259</v>
       </c>
       <c r="J2" t="n">
-        <v>284.3814951317976</v>
+        <v>284.3814951317994</v>
       </c>
       <c r="K2" t="n">
-        <v>60.37286861775041</v>
+        <v>60.37286861775022</v>
       </c>
       <c r="L2" t="n">
-        <v>71.43816753738896</v>
+        <v>71.43816753738825</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.033430896842621</v>
+        <v>4.033430896842567</v>
       </c>
       <c r="C3" t="n">
-        <v>3.792653835049977</v>
+        <v>3.792653835049975</v>
       </c>
       <c r="D3" t="n">
-        <v>4.033430896842622</v>
+        <v>4.033430896842566</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8209658820942</v>
+        <v>3.820965882094183</v>
       </c>
       <c r="F3" t="n">
-        <v>3.820965882094202</v>
+        <v>3.820965882094186</v>
       </c>
       <c r="G3" t="n">
-        <v>4.024148004457774</v>
+        <v>4.024148004457778</v>
       </c>
       <c r="H3" t="n">
-        <v>4.033430896842622</v>
+        <v>4.033430896842566</v>
       </c>
       <c r="I3" t="n">
-        <v>3.971152062712598</v>
+        <v>3.971152062712592</v>
       </c>
       <c r="J3" t="n">
-        <v>4.033430896842621</v>
+        <v>4.033430896842566</v>
       </c>
       <c r="K3" t="n">
-        <v>4.033430896842622</v>
+        <v>4.033430896842566</v>
       </c>
       <c r="L3" t="n">
-        <v>4.033430896842622</v>
+        <v>4.033430896842566</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.333953495126</v>
+        <v>635.3339534951252</v>
       </c>
       <c r="C4" t="n">
-        <v>635.2157570335353</v>
+        <v>635.2157570335359</v>
       </c>
       <c r="D4" t="n">
-        <v>635.4862881666839</v>
+        <v>635.4862774741762</v>
       </c>
       <c r="E4" t="n">
-        <v>572.3050697076369</v>
+        <v>572.3050697076366</v>
       </c>
       <c r="F4" t="n">
-        <v>635.2566451833879</v>
+        <v>635.2566451833881</v>
       </c>
       <c r="G4" t="n">
-        <v>759.9137738162481</v>
+        <v>759.9137738162474</v>
       </c>
       <c r="H4" t="n">
-        <v>760.5663447728617</v>
+        <v>760.5663447728616</v>
       </c>
       <c r="I4" t="n">
-        <v>759.8607778745026</v>
+        <v>759.8607778745024</v>
       </c>
       <c r="J4" t="n">
-        <v>760.2578805838834</v>
+        <v>760.2578805838838</v>
       </c>
       <c r="K4" t="n">
-        <v>635.2340297995697</v>
+        <v>635.2340297995694</v>
       </c>
       <c r="L4" t="n">
-        <v>635.348441968062</v>
+        <v>635.3484419680616</v>
       </c>
     </row>
     <row r="5">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.994890379058573</v>
+        <v>8.994890379058537</v>
       </c>
       <c r="C5" t="n">
-        <v>8.987021207959403</v>
+        <v>8.987021207959431</v>
       </c>
       <c r="D5" t="n">
-        <v>8.994882019361253</v>
+        <v>8.994882019361244</v>
       </c>
       <c r="E5" t="n">
         <v>8.913490612020004</v>
@@ -2234,22 +2234,22 @@
         <v>8.913490612020004</v>
       </c>
       <c r="G5" t="n">
-        <v>8.985607486673723</v>
+        <v>8.985607486673743</v>
       </c>
       <c r="H5" t="n">
-        <v>8.994890379058573</v>
+        <v>8.994890379058537</v>
       </c>
       <c r="I5" t="n">
-        <v>8.932611544928582</v>
+        <v>8.932611544928561</v>
       </c>
       <c r="J5" t="n">
-        <v>8.994890379058573</v>
+        <v>8.994890379058537</v>
       </c>
       <c r="K5" t="n">
-        <v>8.994890379058573</v>
+        <v>8.994890379058537</v>
       </c>
       <c r="L5" t="n">
-        <v>8.994890379058573</v>
+        <v>8.994890379058537</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.57088262809954</v>
+        <v>10.57088262809953</v>
       </c>
       <c r="C6" t="n">
-        <v>15.46994079159981</v>
+        <v>15.46994079168753</v>
       </c>
       <c r="D6" t="n">
-        <v>16.51625629870694</v>
+        <v>16.5162562987069</v>
       </c>
       <c r="E6" t="n">
-        <v>14.07067416570983</v>
+        <v>14.07067416570981</v>
       </c>
       <c r="F6" t="n">
-        <v>10.65329461153436</v>
+        <v>10.65329461153432</v>
       </c>
       <c r="G6" t="n">
         <v>15.48588978609794</v>
       </c>
       <c r="H6" t="n">
-        <v>15.49517267849279</v>
+        <v>15.49517267849283</v>
       </c>
       <c r="I6" t="n">
-        <v>15.43289384435282</v>
+        <v>15.43289384435275</v>
       </c>
       <c r="J6" t="n">
-        <v>15.49614043549112</v>
+        <v>15.49614043549106</v>
       </c>
       <c r="K6" t="n">
-        <v>10.47941141292248</v>
+        <v>10.47941141292243</v>
       </c>
       <c r="L6" t="n">
-        <v>20.6390053919737</v>
+        <v>20.63900539197371</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.90810999663429</v>
+        <v>16.90810999663439</v>
       </c>
       <c r="C7" t="n">
-        <v>20.79614452025038</v>
+        <v>20.79614452025049</v>
       </c>
       <c r="D7" t="n">
-        <v>20.80401715849939</v>
+        <v>20.80401715849964</v>
       </c>
       <c r="E7" t="n">
-        <v>25.2375251697961</v>
+        <v>25.23752516979606</v>
       </c>
       <c r="F7" t="n">
-        <v>20.74173239413653</v>
+        <v>20.74173239413705</v>
       </c>
       <c r="G7" t="n">
-        <v>20.7947307989649</v>
+        <v>20.7947307989648</v>
       </c>
       <c r="H7" t="n">
-        <v>20.80401369134982</v>
+        <v>20.80401369134962</v>
       </c>
       <c r="I7" t="n">
-        <v>20.74173485721957</v>
+        <v>20.74173485721962</v>
       </c>
       <c r="J7" t="n">
-        <v>20.80401369134982</v>
+        <v>20.80401369134962</v>
       </c>
       <c r="K7" t="n">
-        <v>15.89837462474266</v>
+        <v>18.45513157747684</v>
       </c>
       <c r="L7" t="n">
-        <v>20.80401369134982</v>
+        <v>20.80401369134962</v>
       </c>
     </row>
     <row r="8">
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>165.4862733937213</v>
+        <v>165.4862733937211</v>
       </c>
       <c r="C8" t="n">
-        <v>166.7777969210055</v>
+        <v>166.7777969210056</v>
       </c>
       <c r="D8" t="n">
-        <v>166.5581959537062</v>
+        <v>166.5581959537059</v>
       </c>
       <c r="E8" t="n">
         <v>168.7046078054658</v>
@@ -2354,7 +2354,7 @@
         <v>168.7046078054658</v>
       </c>
       <c r="G8" t="n">
-        <v>167.5039677338928</v>
+        <v>167.5039677338927</v>
       </c>
       <c r="H8" t="n">
         <v>167.2037694869492</v>
@@ -2363,10 +2363,10 @@
         <v>168.7046078054658</v>
       </c>
       <c r="J8" t="n">
-        <v>175.3465556616989</v>
+        <v>175.3465556616987</v>
       </c>
       <c r="K8" t="n">
-        <v>177.0805907819434</v>
+        <v>177.0805907819432</v>
       </c>
       <c r="L8" t="n">
         <v>182.6090944023933</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163.4375417826225</v>
+        <v>163.4375417826226</v>
       </c>
       <c r="C9" t="n">
         <v>165.1765634717208</v>
@@ -2409,7 +2409,7 @@
         <v>175.1275041280697</v>
       </c>
       <c r="L9" t="n">
-        <v>180.5994611207727</v>
+        <v>180.5994611207726</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94.35419197869672</v>
+        <v>94.35419197869599</v>
       </c>
       <c r="C2" t="n">
-        <v>39.61709796133784</v>
+        <v>39.61709796133675</v>
       </c>
       <c r="D2" t="n">
-        <v>212.3513906828592</v>
+        <v>212.3513906828526</v>
       </c>
       <c r="E2" t="n">
-        <v>178.3728855687187</v>
+        <v>178.3728855687161</v>
       </c>
       <c r="F2" t="n">
-        <v>178.3728855687187</v>
+        <v>178.3728855687161</v>
       </c>
       <c r="G2" t="n">
-        <v>228.5169528456253</v>
+        <v>228.5169528456169</v>
       </c>
       <c r="H2" t="n">
-        <v>462.7769158990602</v>
+        <v>462.7769158990593</v>
       </c>
       <c r="I2" t="n">
-        <v>178.3728855687187</v>
+        <v>178.3728855687161</v>
       </c>
       <c r="J2" t="n">
-        <v>482.0952792099491</v>
+        <v>482.0952792099474</v>
       </c>
       <c r="K2" t="n">
         <v>218.4135435433685</v>
       </c>
       <c r="L2" t="n">
-        <v>216.0365139386748</v>
+        <v>216.0365139386737</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.950917465302438</v>
+        <v>4.950917465302408</v>
       </c>
       <c r="C3" t="n">
-        <v>4.491131008564323</v>
+        <v>4.491131008564277</v>
       </c>
       <c r="D3" t="n">
-        <v>4.950917465302438</v>
+        <v>4.950917465302408</v>
       </c>
       <c r="E3" t="n">
-        <v>4.814511809198767</v>
+        <v>4.81451180919876</v>
       </c>
       <c r="F3" t="n">
-        <v>4.814511809198768</v>
+        <v>4.81451180919876</v>
       </c>
       <c r="G3" t="n">
-        <v>4.943425219573128</v>
+        <v>4.943425219573129</v>
       </c>
       <c r="H3" t="n">
-        <v>4.950917465302438</v>
+        <v>4.950917465302408</v>
       </c>
       <c r="I3" t="n">
-        <v>4.900438303293964</v>
+        <v>4.900438303293948</v>
       </c>
       <c r="J3" t="n">
-        <v>4.950917465302438</v>
+        <v>4.950917465302408</v>
       </c>
       <c r="K3" t="n">
-        <v>4.950917465302438</v>
+        <v>4.950917465302408</v>
       </c>
       <c r="L3" t="n">
-        <v>4.950917465302438</v>
+        <v>4.950917465302408</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>671.8823159171984</v>
+        <v>671.8823159171977</v>
       </c>
       <c r="C4" t="n">
-        <v>671.4847386258182</v>
+        <v>671.4847386258176</v>
       </c>
       <c r="D4" t="n">
-        <v>671.9145504719751</v>
+        <v>671.9145404012957</v>
       </c>
       <c r="E4" t="n">
-        <v>605.397904511913</v>
+        <v>605.3979045119113</v>
       </c>
       <c r="F4" t="n">
-        <v>671.8521436927873</v>
+        <v>671.8521436927867</v>
       </c>
       <c r="G4" t="n">
-        <v>671.8748236714696</v>
+        <v>671.8748236714691</v>
       </c>
       <c r="H4" t="n">
-        <v>805.0336973200033</v>
+        <v>805.0336973200039</v>
       </c>
       <c r="I4" t="n">
-        <v>671.8318367551897</v>
+        <v>804.0071677562046</v>
       </c>
       <c r="J4" t="n">
-        <v>804.4783920828395</v>
+        <v>706.0008811261487</v>
       </c>
       <c r="K4" t="n">
-        <v>671.9229190371918</v>
+        <v>671.9229190371911</v>
       </c>
       <c r="L4" t="n">
-        <v>671.9164913473567</v>
+        <v>671.9164913473558</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.8747159502987</v>
+        <v>10.87471595029862</v>
       </c>
       <c r="C5" t="n">
         <v>10.8627403307138</v>
       </c>
       <c r="D5" t="n">
-        <v>10.87472225877037</v>
+        <v>10.87472225877024</v>
       </c>
       <c r="E5" t="n">
-        <v>10.81836696555451</v>
+        <v>10.81836696555443</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81836696555451</v>
+        <v>10.81836696555443</v>
       </c>
       <c r="G5" t="n">
-        <v>10.86722370456941</v>
+        <v>10.86722370456933</v>
       </c>
       <c r="H5" t="n">
-        <v>10.8747159502987</v>
+        <v>10.87471595029862</v>
       </c>
       <c r="I5" t="n">
-        <v>10.82423678829025</v>
+        <v>10.82423678829015</v>
       </c>
       <c r="J5" t="n">
-        <v>10.8747159502987</v>
+        <v>10.87471595029862</v>
       </c>
       <c r="K5" t="n">
-        <v>10.8747159502987</v>
+        <v>10.87471595029862</v>
       </c>
       <c r="L5" t="n">
-        <v>10.8747159502987</v>
+        <v>10.87471595029862</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.11850900200021</v>
+        <v>13.11850900200016</v>
       </c>
       <c r="C6" t="n">
-        <v>19.34988864308504</v>
+        <v>19.34988864321053</v>
       </c>
       <c r="D6" t="n">
-        <v>20.66185219817975</v>
+        <v>20.66185219817963</v>
       </c>
       <c r="E6" t="n">
-        <v>17.60320185635516</v>
+        <v>17.60320185635501</v>
       </c>
       <c r="F6" t="n">
-        <v>13.2625706172879</v>
+        <v>13.26257061728786</v>
       </c>
       <c r="G6" t="n">
-        <v>19.35883428734184</v>
+        <v>19.35883428734172</v>
       </c>
       <c r="H6" t="n">
-        <v>19.36632653309879</v>
+        <v>19.3663265330987</v>
       </c>
       <c r="I6" t="n">
-        <v>19.31584737106271</v>
+        <v>19.31584737106255</v>
       </c>
       <c r="J6" t="n">
-        <v>19.36755439751738</v>
+        <v>19.36755439751729</v>
       </c>
       <c r="K6" t="n">
-        <v>13.00245258466844</v>
+        <v>13.00245258466839</v>
       </c>
       <c r="L6" t="n">
-        <v>25.8926943683389</v>
+        <v>25.89269436833884</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.56508642736583</v>
+        <v>23.56508642736604</v>
       </c>
       <c r="C7" t="n">
-        <v>29.16154621998511</v>
+        <v>29.16154621998501</v>
       </c>
       <c r="D7" t="n">
-        <v>29.17352525324904</v>
+        <v>29.17352525324816</v>
       </c>
       <c r="E7" t="n">
-        <v>35.59505600852175</v>
+        <v>35.59505600852163</v>
       </c>
       <c r="F7" t="n">
-        <v>29.12303843550102</v>
+        <v>29.12303843550051</v>
       </c>
       <c r="G7" t="n">
-        <v>29.16602959384025</v>
+        <v>29.16602959384057</v>
       </c>
       <c r="H7" t="n">
-        <v>29.17352183956983</v>
+        <v>29.17352183956985</v>
       </c>
       <c r="I7" t="n">
-        <v>29.12304267756166</v>
+        <v>29.12304267756137</v>
       </c>
       <c r="J7" t="n">
-        <v>29.17352183956983</v>
+        <v>29.17352183956985</v>
       </c>
       <c r="K7" t="n">
-        <v>22.11149966867396</v>
+        <v>25.9239737714933</v>
       </c>
       <c r="L7" t="n">
-        <v>29.17352183956983</v>
+        <v>29.17352183956985</v>
       </c>
     </row>
     <row r="8">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>159.208283881411</v>
+        <v>159.2082838814113</v>
       </c>
       <c r="C8" t="n">
         <v>167.7646917008386</v>
       </c>
       <c r="D8" t="n">
-        <v>167.1738009350294</v>
+        <v>167.17380093503</v>
       </c>
       <c r="E8" t="n">
         <v>166.4415408791667</v>
@@ -2750,7 +2750,7 @@
         <v>166.4415408791667</v>
       </c>
       <c r="G8" t="n">
-        <v>165.2514057182711</v>
+        <v>165.2514057182714</v>
       </c>
       <c r="H8" t="n">
         <v>162.6391275551879</v>
@@ -2762,7 +2762,7 @@
         <v>172.4600929918982</v>
       </c>
       <c r="K8" t="n">
-        <v>173.5141624099637</v>
+        <v>173.5141624099639</v>
       </c>
       <c r="L8" t="n">
         <v>180.3865360521725</v>
@@ -2781,7 +2781,7 @@
         <v>165.6242077267931</v>
       </c>
       <c r="D9" t="n">
-        <v>167.3588370944451</v>
+        <v>167.3588370944452</v>
       </c>
       <c r="E9" t="n">
         <v>166.1615605125498</v>
@@ -2802,7 +2802,7 @@
         <v>175.8407248644211</v>
       </c>
       <c r="K9" t="n">
-        <v>173.6689055426259</v>
+        <v>173.6689055426258</v>
       </c>
       <c r="L9" t="n">
         <v>180.0333863328626</v>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.8833736512843</v>
+        <v>38.88337365128431</v>
       </c>
       <c r="C2" t="n">
-        <v>15.97818552545488</v>
+        <v>15.97818552545496</v>
       </c>
       <c r="D2" t="n">
-        <v>89.14882729394085</v>
+        <v>89.14882729394088</v>
       </c>
       <c r="E2" t="n">
-        <v>66.38358347312729</v>
+        <v>66.38358347312709</v>
       </c>
       <c r="F2" t="n">
-        <v>66.38358347312729</v>
+        <v>66.38358347312709</v>
       </c>
       <c r="G2" t="n">
-        <v>84.29988258805173</v>
+        <v>84.29988258805051</v>
       </c>
       <c r="H2" t="n">
-        <v>182.5678933623369</v>
+        <v>182.5678933623367</v>
       </c>
       <c r="I2" t="n">
-        <v>66.38358347312729</v>
+        <v>66.38358347312709</v>
       </c>
       <c r="J2" t="n">
-        <v>213.3979686179301</v>
+        <v>213.3979686179302</v>
       </c>
       <c r="K2" t="n">
-        <v>58.74005408497111</v>
+        <v>58.74005408497105</v>
       </c>
       <c r="L2" t="n">
-        <v>46.41916111726326</v>
+        <v>46.41916111726327</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.100153940537505</v>
+        <v>4.100153940537465</v>
       </c>
       <c r="C3" t="n">
-        <v>3.733332373093398</v>
+        <v>3.733332373093426</v>
       </c>
       <c r="D3" t="n">
-        <v>4.100153940537505</v>
+        <v>4.100153940537465</v>
       </c>
       <c r="E3" t="n">
-        <v>3.976689586979303</v>
+        <v>3.976689586979306</v>
       </c>
       <c r="F3" t="n">
-        <v>3.976689586979303</v>
+        <v>3.976689586979306</v>
       </c>
       <c r="G3" t="n">
-        <v>4.093837882289714</v>
+        <v>4.093837882289751</v>
       </c>
       <c r="H3" t="n">
-        <v>4.100153940537505</v>
+        <v>4.100153940537465</v>
       </c>
       <c r="I3" t="n">
         <v>4.057043847464437</v>
       </c>
       <c r="J3" t="n">
-        <v>4.100153940537505</v>
+        <v>4.100153940537465</v>
       </c>
       <c r="K3" t="n">
-        <v>4.100153940537505</v>
+        <v>4.100153940537465</v>
       </c>
       <c r="L3" t="n">
-        <v>4.100153940537505</v>
+        <v>4.100153940537465</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.384969886856</v>
+        <v>635.384969886857</v>
       </c>
       <c r="C4" t="n">
         <v>635.1980208022017</v>
       </c>
       <c r="D4" t="n">
-        <v>635.4170416519902</v>
+        <v>760.0575075649191</v>
       </c>
       <c r="E4" t="n">
-        <v>572.4685304161827</v>
+        <v>572.4685304161831</v>
       </c>
       <c r="F4" t="n">
-        <v>635.3464584545233</v>
+        <v>635.3464584545242</v>
       </c>
       <c r="G4" t="n">
-        <v>759.8606180200685</v>
+        <v>635.3786538286088</v>
       </c>
       <c r="H4" t="n">
-        <v>760.7026177637032</v>
+        <v>760.7026177637041</v>
       </c>
       <c r="I4" t="n">
-        <v>759.8238239852435</v>
+        <v>759.8238239852443</v>
       </c>
       <c r="J4" t="n">
-        <v>667.605757809358</v>
+        <v>760.2327068855521</v>
       </c>
       <c r="K4" t="n">
-        <v>635.3515812425295</v>
+        <v>635.3515812425302</v>
       </c>
       <c r="L4" t="n">
-        <v>635.3875420276706</v>
+        <v>635.3875420276703</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.909716740258695</v>
+        <v>8.909716740258677</v>
       </c>
       <c r="C5" t="n">
-        <v>8.902446820574438</v>
+        <v>8.902446820574466</v>
       </c>
       <c r="D5" t="n">
-        <v>8.909735293927245</v>
+        <v>8.909735293927218</v>
       </c>
       <c r="E5" t="n">
-        <v>8.857181489983239</v>
+        <v>8.85718148998323</v>
       </c>
       <c r="F5" t="n">
-        <v>8.857181489983239</v>
+        <v>8.85718148998323</v>
       </c>
       <c r="G5" t="n">
-        <v>8.903400682010988</v>
+        <v>8.903400682010975</v>
       </c>
       <c r="H5" t="n">
-        <v>8.909716740258695</v>
+        <v>8.909716740258677</v>
       </c>
       <c r="I5" t="n">
-        <v>8.866606647185668</v>
+        <v>8.866606647185671</v>
       </c>
       <c r="J5" t="n">
-        <v>8.909716740258695</v>
+        <v>8.909716740258677</v>
       </c>
       <c r="K5" t="n">
-        <v>8.909716740258695</v>
+        <v>8.909716740258677</v>
       </c>
       <c r="L5" t="n">
-        <v>8.909716740258695</v>
+        <v>8.909716740258677</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.42659120529155</v>
+        <v>10.42659120529153</v>
       </c>
       <c r="C6" t="n">
-        <v>15.25863066327085</v>
+        <v>15.25863066317601</v>
       </c>
       <c r="D6" t="n">
-        <v>16.27920497077702</v>
+        <v>16.27920497077704</v>
       </c>
       <c r="E6" t="n">
-        <v>13.89798576413126</v>
+        <v>13.89798576413125</v>
       </c>
       <c r="F6" t="n">
-        <v>10.53150451863472</v>
+        <v>10.53150451863471</v>
       </c>
       <c r="G6" t="n">
-        <v>15.26773627087255</v>
+        <v>15.26773627087254</v>
       </c>
       <c r="H6" t="n">
-        <v>15.27405232915451</v>
+        <v>15.2740523291545</v>
       </c>
       <c r="I6" t="n">
         <v>15.23094223604723</v>
       </c>
       <c r="J6" t="n">
-        <v>15.27500498451141</v>
+        <v>15.27500498451139</v>
       </c>
       <c r="K6" t="n">
-        <v>10.33654712708653</v>
+        <v>10.33654712708658</v>
       </c>
       <c r="L6" t="n">
-        <v>20.3376308021113</v>
+        <v>20.33763080211135</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.94303941550414</v>
+        <v>16.94303941550416</v>
       </c>
       <c r="C7" t="n">
-        <v>20.84779883769766</v>
+        <v>20.84779883769763</v>
       </c>
       <c r="D7" t="n">
-        <v>20.8550709471601</v>
+        <v>20.85507094716012</v>
       </c>
       <c r="E7" t="n">
-        <v>25.3263570655724</v>
+        <v>25.32635706557238</v>
       </c>
       <c r="F7" t="n">
         <v>20.81195667202446</v>
       </c>
       <c r="G7" t="n">
-        <v>20.84875269913413</v>
+        <v>20.84875269913415</v>
       </c>
       <c r="H7" t="n">
-        <v>20.85506875738187</v>
+        <v>20.85506875738186</v>
       </c>
       <c r="I7" t="n">
         <v>20.81195866430885</v>
       </c>
       <c r="J7" t="n">
-        <v>20.85506875738187</v>
+        <v>20.85506875738186</v>
       </c>
       <c r="K7" t="n">
-        <v>15.92912495364678</v>
+        <v>18.5884245139853</v>
       </c>
       <c r="L7" t="n">
-        <v>20.85506875738187</v>
+        <v>20.85506875738186</v>
       </c>
     </row>
     <row r="8">
@@ -3131,19 +3131,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157.7414760657433</v>
+        <v>157.7414760657431</v>
       </c>
       <c r="C8" t="n">
-        <v>167.86632105107</v>
+        <v>167.8663210510701</v>
       </c>
       <c r="D8" t="n">
         <v>168.8539789700452</v>
       </c>
       <c r="E8" t="n">
-        <v>168.0781724920832</v>
+        <v>168.0781724920833</v>
       </c>
       <c r="F8" t="n">
-        <v>168.0781724920832</v>
+        <v>168.0781724920833</v>
       </c>
       <c r="G8" t="n">
         <v>167.5443998807485</v>
@@ -3152,13 +3152,13 @@
         <v>167.0915614054946</v>
       </c>
       <c r="I8" t="n">
-        <v>168.0781724920832</v>
+        <v>168.0781724920833</v>
       </c>
       <c r="J8" t="n">
-        <v>177.0713915612116</v>
+        <v>177.0713915612118</v>
       </c>
       <c r="K8" t="n">
-        <v>175.9115431136735</v>
+        <v>175.9115431136733</v>
       </c>
       <c r="L8" t="n">
         <v>183.1115777791237</v>
@@ -3177,7 +3177,7 @@
         <v>165.4318276807246</v>
       </c>
       <c r="D9" t="n">
-        <v>167.4388736808459</v>
+        <v>167.4388736808458</v>
       </c>
       <c r="E9" t="n">
         <v>166.3460007402072</v>
@@ -3186,7 +3186,7 @@
         <v>166.3460007402072</v>
       </c>
       <c r="G9" t="n">
-        <v>166.048222595517</v>
+        <v>166.0482225955169</v>
       </c>
       <c r="H9" t="n">
         <v>166.7245874331483</v>
@@ -3195,10 +3195,10 @@
         <v>166.3460007402072</v>
       </c>
       <c r="J9" t="n">
-        <v>177.1290454299028</v>
+        <v>177.1290454299029</v>
       </c>
       <c r="K9" t="n">
-        <v>173.9545459963024</v>
+        <v>173.9545459963023</v>
       </c>
       <c r="L9" t="n">
         <v>180.7897585872014</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.96581352492507</v>
+        <v>20.96581352492467</v>
       </c>
       <c r="C2" t="n">
-        <v>11.67518110329364</v>
+        <v>11.67518110329363</v>
       </c>
       <c r="D2" t="n">
         <v>78.44566520480981</v>
       </c>
       <c r="E2" t="n">
-        <v>26.12022231020545</v>
+        <v>26.12022231020516</v>
       </c>
       <c r="F2" t="n">
-        <v>26.12022231020545</v>
+        <v>26.12022231020516</v>
       </c>
       <c r="G2" t="n">
-        <v>44.75472862379282</v>
+        <v>44.75472862379219</v>
       </c>
       <c r="H2" t="n">
-        <v>124.9384103100264</v>
+        <v>124.938410310026</v>
       </c>
       <c r="I2" t="n">
-        <v>26.12022231020545</v>
+        <v>26.12022231020516</v>
       </c>
       <c r="J2" t="n">
-        <v>80.00509154785871</v>
+        <v>80.00509154785904</v>
       </c>
       <c r="K2" t="n">
-        <v>17.49936814418119</v>
+        <v>17.49936814418139</v>
       </c>
       <c r="L2" t="n">
-        <v>13.2135181744545</v>
+        <v>13.21351817445447</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.577126551821705</v>
+        <v>3.577126551821347</v>
       </c>
       <c r="C3" t="n">
-        <v>3.245569032837281</v>
+        <v>3.245569032837282</v>
       </c>
       <c r="D3" t="n">
-        <v>3.577126551821705</v>
+        <v>3.577126551821347</v>
       </c>
       <c r="E3" t="n">
-        <v>3.417275828195275</v>
+        <v>3.417275828195279</v>
       </c>
       <c r="F3" t="n">
-        <v>3.417275828195276</v>
+        <v>3.417275828195279</v>
       </c>
       <c r="G3" t="n">
-        <v>3.57085460841741</v>
+        <v>3.570854608416782</v>
       </c>
       <c r="H3" t="n">
-        <v>3.577126551821705</v>
+        <v>3.577126551821346</v>
       </c>
       <c r="I3" t="n">
-        <v>3.534162566131825</v>
+        <v>3.534162566131514</v>
       </c>
       <c r="J3" t="n">
-        <v>3.577126551821705</v>
+        <v>3.577126551821346</v>
       </c>
       <c r="K3" t="n">
-        <v>3.577126551821705</v>
+        <v>3.577126551821347</v>
       </c>
       <c r="L3" t="n">
-        <v>3.577126551821705</v>
+        <v>3.577126551821347</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>758.756989876209</v>
+        <v>758.7569898762086</v>
       </c>
       <c r="C4" t="n">
-        <v>634.5205044659804</v>
+        <v>634.5205044659799</v>
       </c>
       <c r="D4" t="n">
-        <v>634.7285468302888</v>
+        <v>634.728546830289</v>
       </c>
       <c r="E4" t="n">
-        <v>571.7394412108603</v>
+        <v>571.7394412108605</v>
       </c>
       <c r="F4" t="n">
-        <v>634.5927613105715</v>
+        <v>634.5927613105713</v>
       </c>
       <c r="G4" t="n">
-        <v>758.7507179328036</v>
+        <v>758.7507179328043</v>
       </c>
       <c r="H4" t="n">
-        <v>759.4837006525111</v>
+        <v>634.6799842477197</v>
       </c>
       <c r="I4" t="n">
-        <v>634.5983682858728</v>
+        <v>758.7140258905189</v>
       </c>
       <c r="J4" t="n">
-        <v>759.0882810772071</v>
+        <v>666.8039185661185</v>
       </c>
       <c r="K4" t="n">
-        <v>634.5896377999177</v>
+        <v>634.5896377999278</v>
       </c>
       <c r="L4" t="n">
-        <v>634.6404883013613</v>
+        <v>634.640488301361</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.966227511815243</v>
+        <v>7.966227511815119</v>
       </c>
       <c r="C5" t="n">
-        <v>7.960573003186357</v>
+        <v>7.960573003186351</v>
       </c>
       <c r="D5" t="n">
-        <v>7.966251021504561</v>
+        <v>7.966251021504368</v>
       </c>
       <c r="E5" t="n">
-        <v>7.902363342675264</v>
+        <v>7.902363342675267</v>
       </c>
       <c r="F5" t="n">
-        <v>7.902363342675264</v>
+        <v>7.902363342675267</v>
       </c>
       <c r="G5" t="n">
-        <v>7.959955568410578</v>
+        <v>7.959955568410379</v>
       </c>
       <c r="H5" t="n">
-        <v>7.966227511815243</v>
+        <v>7.966227511815119</v>
       </c>
       <c r="I5" t="n">
-        <v>7.923263526125027</v>
+        <v>7.923263526125052</v>
       </c>
       <c r="J5" t="n">
-        <v>7.966227511815243</v>
+        <v>7.966227511815119</v>
       </c>
       <c r="K5" t="n">
-        <v>7.966227511815243</v>
+        <v>7.966227511815119</v>
       </c>
       <c r="L5" t="n">
-        <v>7.966227511815243</v>
+        <v>7.966227511815119</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.112675711765212</v>
+        <v>9.112675711765172</v>
       </c>
       <c r="C6" t="n">
-        <v>13.28046781928149</v>
+        <v>13.28046781934361</v>
       </c>
       <c r="D6" t="n">
-        <v>14.17477073480945</v>
+        <v>14.17477073480934</v>
       </c>
       <c r="E6" t="n">
-        <v>12.09860537909304</v>
+        <v>12.09860537909302</v>
       </c>
       <c r="F6" t="n">
-        <v>9.190132146597209</v>
+        <v>9.190132146597199</v>
       </c>
       <c r="G6" t="n">
-        <v>13.2991131820263</v>
+        <v>13.29911318202634</v>
       </c>
       <c r="H6" t="n">
-        <v>13.30538512546546</v>
+        <v>13.30538512546536</v>
       </c>
       <c r="I6" t="n">
-        <v>13.26242113974081</v>
+        <v>13.26242113974078</v>
       </c>
       <c r="J6" t="n">
-        <v>13.30620910514129</v>
+        <v>13.30620910514099</v>
       </c>
       <c r="K6" t="n">
-        <v>9.034793982581103</v>
+        <v>9.034793982580913</v>
       </c>
       <c r="L6" t="n">
-        <v>17.68502068931025</v>
+        <v>17.68502068931031</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.46628913794601</v>
+        <v>14.46628913794584</v>
       </c>
       <c r="C7" t="n">
         <v>17.76609383590695</v>
       </c>
       <c r="D7" t="n">
-        <v>17.77174979587902</v>
+        <v>17.771749795879</v>
       </c>
       <c r="E7" t="n">
-        <v>21.54321327458037</v>
+        <v>21.54321327458051</v>
       </c>
       <c r="F7" t="n">
-        <v>17.72878257196839</v>
+        <v>17.72878257196838</v>
       </c>
       <c r="G7" t="n">
-        <v>17.76547640113116</v>
+        <v>17.76547640113114</v>
       </c>
       <c r="H7" t="n">
-        <v>17.7717483445358</v>
+        <v>17.77174834453562</v>
       </c>
       <c r="I7" t="n">
-        <v>17.72878435884572</v>
+        <v>17.72878435884565</v>
       </c>
       <c r="J7" t="n">
-        <v>17.7717483445358</v>
+        <v>17.77174834453562</v>
       </c>
       <c r="K7" t="n">
-        <v>15.77885095217556</v>
+        <v>15.85655290912708</v>
       </c>
       <c r="L7" t="n">
-        <v>17.7717483445358</v>
+        <v>17.77174834453562</v>
       </c>
     </row>
     <row r="8">
@@ -3530,10 +3530,10 @@
         <v>154.1516047794871</v>
       </c>
       <c r="C8" t="n">
-        <v>167.8177593128153</v>
+        <v>167.8177593128154</v>
       </c>
       <c r="D8" t="n">
-        <v>168.507501998222</v>
+        <v>168.5075019982219</v>
       </c>
       <c r="E8" t="n">
         <v>168.6961632596245</v>
@@ -3545,13 +3545,13 @@
         <v>168.0855687954221</v>
       </c>
       <c r="H8" t="n">
-        <v>167.7249434046072</v>
+        <v>167.7249434046071</v>
       </c>
       <c r="I8" t="n">
         <v>168.6961632596245</v>
       </c>
       <c r="J8" t="n">
-        <v>179.4140955470432</v>
+        <v>179.4140955470431</v>
       </c>
       <c r="K8" t="n">
         <v>177.2718222416554</v>
@@ -3570,7 +3570,7 @@
         <v>151.9971797689409</v>
       </c>
       <c r="C9" t="n">
-        <v>165.3279913628164</v>
+        <v>165.3279913628166</v>
       </c>
       <c r="D9" t="n">
         <v>166.950287456705</v>
@@ -3585,19 +3585,19 @@
         <v>166.0433094381085</v>
       </c>
       <c r="H9" t="n">
-        <v>166.6339507622188</v>
+        <v>166.6339507622187</v>
       </c>
       <c r="I9" t="n">
         <v>166.3962240747646</v>
       </c>
       <c r="J9" t="n">
-        <v>177.6537589125202</v>
+        <v>177.6537589125204</v>
       </c>
       <c r="K9" t="n">
         <v>174.7184147590548</v>
       </c>
       <c r="L9" t="n">
-        <v>180.6945521391107</v>
+        <v>180.6945521391106</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.57775513306632</v>
+        <v>79.57775513306706</v>
       </c>
       <c r="C2" t="n">
-        <v>25.07411827772989</v>
+        <v>25.07411827772972</v>
       </c>
       <c r="D2" t="n">
-        <v>128.2756330762655</v>
+        <v>128.2756330762591</v>
       </c>
       <c r="E2" t="n">
-        <v>150.8821779887758</v>
+        <v>150.8821779887728</v>
       </c>
       <c r="F2" t="n">
-        <v>150.8821779887758</v>
+        <v>150.8821779887728</v>
       </c>
       <c r="G2" t="n">
-        <v>161.7614436835527</v>
+        <v>161.761443683549</v>
       </c>
       <c r="H2" t="n">
-        <v>398.6381048524841</v>
+        <v>398.6381048524848</v>
       </c>
       <c r="I2" t="n">
-        <v>150.8821779887758</v>
+        <v>150.8821779887728</v>
       </c>
       <c r="J2" t="n">
-        <v>322.1565127440264</v>
+        <v>322.1565127440151</v>
       </c>
       <c r="K2" t="n">
-        <v>148.7508583278887</v>
+        <v>148.7508583279007</v>
       </c>
       <c r="L2" t="n">
-        <v>168.4965463535912</v>
+        <v>168.4965463535916</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.691139572988048</v>
+        <v>4.691139572988281</v>
       </c>
       <c r="C3" t="n">
-        <v>4.278018885682595</v>
+        <v>4.278018885682593</v>
       </c>
       <c r="D3" t="n">
-        <v>4.691139572988048</v>
+        <v>4.691139572988281</v>
       </c>
       <c r="E3" t="n">
-        <v>4.583376414147607</v>
+        <v>4.583376414147587</v>
       </c>
       <c r="F3" t="n">
-        <v>4.583376414147607</v>
+        <v>4.583376414147591</v>
       </c>
       <c r="G3" t="n">
-        <v>4.68517953061391</v>
+        <v>4.685179530613843</v>
       </c>
       <c r="H3" t="n">
-        <v>4.691139572988048</v>
+        <v>4.691139572988281</v>
       </c>
       <c r="I3" t="n">
-        <v>4.650436806301339</v>
+        <v>4.650436806301353</v>
       </c>
       <c r="J3" t="n">
-        <v>4.691139572988048</v>
+        <v>4.691139572988281</v>
       </c>
       <c r="K3" t="n">
-        <v>4.691139572988048</v>
+        <v>4.691139572988281</v>
       </c>
       <c r="L3" t="n">
-        <v>4.691139572988048</v>
+        <v>4.691139572988281</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>671.4017095096924</v>
+        <v>671.4017095096931</v>
       </c>
       <c r="C4" t="n">
-        <v>671.088235939243</v>
+        <v>671.0882359392418</v>
       </c>
       <c r="D4" t="n">
-        <v>671.3682906259861</v>
+        <v>671.3682906259853</v>
       </c>
       <c r="E4" t="n">
         <v>604.9948366489941</v>
       </c>
       <c r="F4" t="n">
-        <v>671.3823961697976</v>
+        <v>671.3823961697964</v>
       </c>
       <c r="G4" t="n">
-        <v>803.2543169135646</v>
+        <v>671.395749467318</v>
       </c>
       <c r="H4" t="n">
-        <v>804.222665023934</v>
+        <v>804.2226650239342</v>
       </c>
       <c r="I4" t="n">
-        <v>803.2195741892518</v>
+        <v>671.3610067430066</v>
       </c>
       <c r="J4" t="n">
-        <v>803.6666258256945</v>
+        <v>705.456605977034</v>
       </c>
       <c r="K4" t="n">
-        <v>671.4043627515857</v>
+        <v>671.4043627516251</v>
       </c>
       <c r="L4" t="n">
-        <v>671.4268492574671</v>
+        <v>671.4268492574658</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.25822312751425</v>
+        <v>10.25822312751433</v>
       </c>
       <c r="C5" t="n">
         <v>10.24861595955486</v>
       </c>
       <c r="D5" t="n">
-        <v>10.25823033888261</v>
+        <v>10.25823033888281</v>
       </c>
       <c r="E5" t="n">
-        <v>10.21095280556371</v>
+        <v>10.21095280556368</v>
       </c>
       <c r="F5" t="n">
-        <v>10.21095280556371</v>
+        <v>10.21095280556368</v>
       </c>
       <c r="G5" t="n">
-        <v>10.25226308513986</v>
+        <v>10.25226308514003</v>
       </c>
       <c r="H5" t="n">
-        <v>10.25822312751425</v>
+        <v>10.25822312751433</v>
       </c>
       <c r="I5" t="n">
-        <v>10.21752036082737</v>
+        <v>10.2175203608274</v>
       </c>
       <c r="J5" t="n">
-        <v>10.25822312751425</v>
+        <v>10.25822312751433</v>
       </c>
       <c r="K5" t="n">
-        <v>10.25822312751425</v>
+        <v>10.25822312751433</v>
       </c>
       <c r="L5" t="n">
-        <v>10.25822312751425</v>
+        <v>10.25822312751433</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.23075921582324</v>
+        <v>12.23075921582335</v>
       </c>
       <c r="C6" t="n">
-        <v>17.9913331887439</v>
+        <v>17.99133318862068</v>
       </c>
       <c r="D6" t="n">
-        <v>19.20372820721187</v>
+        <v>19.203728207212</v>
       </c>
       <c r="E6" t="n">
-        <v>16.38133390412051</v>
+        <v>16.38133390412042</v>
       </c>
       <c r="F6" t="n">
-        <v>12.36920560730758</v>
+        <v>12.36920560730752</v>
       </c>
       <c r="G6" t="n">
-        <v>18.00020097809357</v>
+        <v>18.00020097809385</v>
       </c>
       <c r="H6" t="n">
-        <v>18.0061610204969</v>
+        <v>18.00616102049691</v>
       </c>
       <c r="I6" t="n">
-        <v>17.9654582537811</v>
+        <v>17.96545825378099</v>
       </c>
       <c r="J6" t="n">
-        <v>18.00729604188044</v>
+        <v>18.00729604188057</v>
       </c>
       <c r="K6" t="n">
-        <v>12.12347816313081</v>
+        <v>12.12347816313082</v>
       </c>
       <c r="L6" t="n">
-        <v>24.03905112690422</v>
+        <v>24.03905112690438</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.56288835132144</v>
+        <v>21.56288835132167</v>
       </c>
       <c r="C7" t="n">
-        <v>26.64789102333421</v>
+        <v>26.64789102333413</v>
       </c>
       <c r="D7" t="n">
-        <v>26.65750021947695</v>
+        <v>26.65750021947699</v>
       </c>
       <c r="E7" t="n">
-        <v>32.49586425030315</v>
+        <v>32.49586425030289</v>
       </c>
       <c r="F7" t="n">
-        <v>26.61679163269609</v>
+        <v>26.61679163269603</v>
       </c>
       <c r="G7" t="n">
-        <v>26.65153814891919</v>
+        <v>26.651538148919</v>
       </c>
       <c r="H7" t="n">
-        <v>26.65749819129353</v>
+        <v>26.65749819129366</v>
       </c>
       <c r="I7" t="n">
-        <v>26.61679542460672</v>
+        <v>26.61679542460659</v>
       </c>
       <c r="J7" t="n">
-        <v>26.65749819129353</v>
+        <v>26.65749819129366</v>
       </c>
       <c r="K7" t="n">
-        <v>23.70566209498309</v>
+        <v>23.70566209498315</v>
       </c>
       <c r="L7" t="n">
-        <v>26.65749819129353</v>
+        <v>26.65749819129366</v>
       </c>
     </row>
     <row r="8">
@@ -3923,34 +3923,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157.4141933423799</v>
+        <v>157.4141933423801</v>
       </c>
       <c r="C8" t="n">
         <v>167.252891463649</v>
       </c>
       <c r="D8" t="n">
-        <v>168.7612203629309</v>
+        <v>168.761220362931</v>
       </c>
       <c r="E8" t="n">
-        <v>166.7185249690422</v>
+        <v>166.7185249690421</v>
       </c>
       <c r="F8" t="n">
-        <v>166.7185249690422</v>
+        <v>166.7185249690421</v>
       </c>
       <c r="G8" t="n">
-        <v>166.1342365704932</v>
+        <v>166.1342365704935</v>
       </c>
       <c r="H8" t="n">
         <v>163.5912511901874</v>
       </c>
       <c r="I8" t="n">
-        <v>166.7185249690422</v>
+        <v>166.7185249690421</v>
       </c>
       <c r="J8" t="n">
-        <v>175.5029919916132</v>
+        <v>175.5029919916133</v>
       </c>
       <c r="K8" t="n">
-        <v>174.2394155929076</v>
+        <v>174.2394155929078</v>
       </c>
       <c r="L8" t="n">
         <v>181.0904687764512</v>
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155.9476625004235</v>
+        <v>155.9476625004239</v>
       </c>
       <c r="C9" t="n">
         <v>164.9329545799289</v>
       </c>
       <c r="D9" t="n">
-        <v>167.8015490759853</v>
+        <v>167.8015490759855</v>
       </c>
       <c r="E9" t="n">
-        <v>166.0728395479861</v>
+        <v>166.072839547986</v>
       </c>
       <c r="F9" t="n">
-        <v>166.0728395479861</v>
+        <v>166.072839547986</v>
       </c>
       <c r="G9" t="n">
         <v>165.6009038671066</v>
       </c>
       <c r="H9" t="n">
-        <v>165.7032710279779</v>
+        <v>165.7032710279781</v>
       </c>
       <c r="I9" t="n">
-        <v>166.0728395479861</v>
+        <v>166.072839547986</v>
       </c>
       <c r="J9" t="n">
-        <v>176.8109573828065</v>
+        <v>176.8109573828067</v>
       </c>
       <c r="K9" t="n">
-        <v>173.4590157473391</v>
+        <v>173.4590157473393</v>
       </c>
       <c r="L9" t="n">
-        <v>180.1785779312252</v>
+        <v>180.1785779312253</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.9812281382748</v>
+        <v>35.98122813827482</v>
       </c>
       <c r="C2" t="n">
-        <v>15.10419504429626</v>
+        <v>15.10419504429629</v>
       </c>
       <c r="D2" t="n">
-        <v>93.78777186637267</v>
+        <v>93.78777186637328</v>
       </c>
       <c r="E2" t="n">
-        <v>57.56636978825627</v>
+        <v>57.56636978825838</v>
       </c>
       <c r="F2" t="n">
-        <v>57.56636978825627</v>
+        <v>57.56636978825838</v>
       </c>
       <c r="G2" t="n">
-        <v>67.24666116460536</v>
+        <v>67.24666116460567</v>
       </c>
       <c r="H2" t="n">
-        <v>150.9867725342007</v>
+        <v>150.9867725342009</v>
       </c>
       <c r="I2" t="n">
-        <v>57.56636978825627</v>
+        <v>57.56636978825838</v>
       </c>
       <c r="J2" t="n">
-        <v>108.4141494893389</v>
+        <v>108.4141494893438</v>
       </c>
       <c r="K2" t="n">
         <v>43.69594633337608</v>
       </c>
       <c r="L2" t="n">
-        <v>15.81241838808091</v>
+        <v>15.812418388081</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.891114899935738</v>
+        <v>3.891114899935724</v>
       </c>
       <c r="C3" t="n">
-        <v>3.562740872424731</v>
+        <v>3.562740872424677</v>
       </c>
       <c r="D3" t="n">
-        <v>3.891114899935738</v>
+        <v>3.891114899935724</v>
       </c>
       <c r="E3" t="n">
-        <v>3.76769588295975</v>
+        <v>3.767695882959758</v>
       </c>
       <c r="F3" t="n">
-        <v>3.767695882959751</v>
+        <v>3.767695882959758</v>
       </c>
       <c r="G3" t="n">
-        <v>3.885998812272014</v>
+        <v>3.88599881227202</v>
       </c>
       <c r="H3" t="n">
-        <v>3.891114899935738</v>
+        <v>3.891114899935724</v>
       </c>
       <c r="I3" t="n">
-        <v>3.855849284448283</v>
+        <v>3.855849284448292</v>
       </c>
       <c r="J3" t="n">
-        <v>3.891114899935738</v>
+        <v>3.891114899935724</v>
       </c>
       <c r="K3" t="n">
-        <v>3.891114899935738</v>
+        <v>3.891114899935724</v>
       </c>
       <c r="L3" t="n">
-        <v>3.891114899935738</v>
+        <v>3.891114899935724</v>
       </c>
     </row>
     <row r="4">
@@ -4159,34 +4159,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.0533787217905</v>
+        <v>759.3726103755046</v>
       </c>
       <c r="C4" t="n">
-        <v>634.8982157565908</v>
+        <v>634.8982157565911</v>
       </c>
       <c r="D4" t="n">
-        <v>635.1199924345856</v>
+        <v>635.1200073649131</v>
       </c>
       <c r="E4" t="n">
-        <v>572.169511788058</v>
+        <v>572.1695117880588</v>
       </c>
       <c r="F4" t="n">
-        <v>635.0210307859066</v>
+        <v>635.0210307859071</v>
       </c>
       <c r="G4" t="n">
-        <v>635.0482626341264</v>
+        <v>635.0482626341268</v>
       </c>
       <c r="H4" t="n">
-        <v>760.1874482620156</v>
+        <v>760.1874482620158</v>
       </c>
       <c r="I4" t="n">
-        <v>759.3373447600183</v>
+        <v>759.3373447600176</v>
       </c>
       <c r="J4" t="n">
-        <v>759.7233385758896</v>
+        <v>667.2287975903157</v>
       </c>
       <c r="K4" t="n">
-        <v>635.0072499962016</v>
+        <v>635.0072499962014</v>
       </c>
       <c r="L4" t="n">
         <v>635.0492678975947</v>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.449333672326199</v>
+        <v>8.449333672326244</v>
       </c>
       <c r="C5" t="n">
-        <v>8.443013885141214</v>
+        <v>8.443013885141168</v>
       </c>
       <c r="D5" t="n">
-        <v>8.44934794363623</v>
+        <v>8.449347943636202</v>
       </c>
       <c r="E5" t="n">
-        <v>8.400464022989953</v>
+        <v>8.400464022989944</v>
       </c>
       <c r="F5" t="n">
-        <v>8.400464022989953</v>
+        <v>8.400464022989944</v>
       </c>
       <c r="G5" t="n">
-        <v>8.444217584662475</v>
+        <v>8.444217584662443</v>
       </c>
       <c r="H5" t="n">
-        <v>8.449333672326199</v>
+        <v>8.449333672326244</v>
       </c>
       <c r="I5" t="n">
-        <v>8.414068056838756</v>
+        <v>8.414068056838753</v>
       </c>
       <c r="J5" t="n">
-        <v>8.449333672326199</v>
+        <v>8.449333672326244</v>
       </c>
       <c r="K5" t="n">
-        <v>8.449333672326199</v>
+        <v>8.449333672326244</v>
       </c>
       <c r="L5" t="n">
-        <v>8.449333672326199</v>
+        <v>8.449333672326244</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.745025342104464</v>
+        <v>9.745025342104483</v>
       </c>
       <c r="C6" t="n">
         <v>14.19820083847179</v>
       </c>
       <c r="D6" t="n">
-        <v>15.14397126130214</v>
+        <v>15.14397126130211</v>
       </c>
       <c r="E6" t="n">
         <v>12.94764199129913</v>
       </c>
       <c r="F6" t="n">
-        <v>9.84338199419312</v>
+        <v>9.843381994193129</v>
       </c>
       <c r="G6" t="n">
-        <v>14.21161736668478</v>
+        <v>14.21161736668476</v>
       </c>
       <c r="H6" t="n">
-        <v>14.21673345438756</v>
+        <v>14.21673345438751</v>
       </c>
       <c r="I6" t="n">
         <v>14.18146783886107</v>
       </c>
       <c r="J6" t="n">
-        <v>14.21761226429293</v>
+        <v>14.21761226429292</v>
       </c>
       <c r="K6" t="n">
-        <v>9.661961068940615</v>
+        <v>9.661961068940581</v>
       </c>
       <c r="L6" t="n">
-        <v>18.88780648750054</v>
+        <v>18.88780648750058</v>
       </c>
     </row>
     <row r="7">
@@ -4282,34 +4282,34 @@
         <v>16.16889186888723</v>
       </c>
       <c r="C7" t="n">
-        <v>19.88544989703525</v>
+        <v>19.88544989703529</v>
       </c>
       <c r="D7" t="n">
-        <v>19.89177163110036</v>
+        <v>19.89177163110033</v>
       </c>
       <c r="E7" t="n">
         <v>24.15262584005139</v>
       </c>
       <c r="F7" t="n">
-        <v>19.85650242893024</v>
+        <v>19.85650242893023</v>
       </c>
       <c r="G7" t="n">
-        <v>19.88665359655653</v>
+        <v>19.8866535965565</v>
       </c>
       <c r="H7" t="n">
-        <v>19.89176968422026</v>
+        <v>19.89176968422029</v>
       </c>
       <c r="I7" t="n">
-        <v>19.85650406873279</v>
+        <v>19.85650406873283</v>
       </c>
       <c r="J7" t="n">
-        <v>19.89176968422026</v>
+        <v>19.89176968422029</v>
       </c>
       <c r="K7" t="n">
-        <v>17.73472047599701</v>
+        <v>15.20400147878707</v>
       </c>
       <c r="L7" t="n">
-        <v>19.89176968422026</v>
+        <v>19.89176968422029</v>
       </c>
     </row>
     <row r="8">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>138.284122224884</v>
+        <v>138.2841222248841</v>
       </c>
       <c r="C8" t="n">
-        <v>166.5566317158751</v>
+        <v>166.5566317158752</v>
       </c>
       <c r="D8" t="n">
         <v>168.4674026071028</v>
@@ -4331,7 +4331,7 @@
         <v>167.562393960894</v>
       </c>
       <c r="F8" t="n">
-        <v>167.5623939608941</v>
+        <v>167.562393960894</v>
       </c>
       <c r="G8" t="n">
         <v>165.607321818474</v>
@@ -4340,13 +4340,13 @@
         <v>167.4980581397496</v>
       </c>
       <c r="I8" t="n">
-        <v>167.5623939608941</v>
+        <v>167.562393960894</v>
       </c>
       <c r="J8" t="n">
         <v>179.0578103295421</v>
       </c>
       <c r="K8" t="n">
-        <v>174.0769404675183</v>
+        <v>174.0769404675182</v>
       </c>
       <c r="L8" t="n">
         <v>183.5464368708612</v>
@@ -4359,10 +4359,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136.5810625287657</v>
+        <v>136.5810625287658</v>
       </c>
       <c r="C9" t="n">
-        <v>164.1314335102907</v>
+        <v>164.1314335102909</v>
       </c>
       <c r="D9" t="n">
         <v>167.1246982474525</v>
@@ -4386,7 +4386,7 @@
         <v>177.6810623645385</v>
       </c>
       <c r="K9" t="n">
-        <v>171.9387421881016</v>
+        <v>171.9387421881015</v>
       </c>
       <c r="L9" t="n">
         <v>180.8455949270466</v>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.73383667465116</v>
+        <v>20.73383667465117</v>
       </c>
       <c r="C2" t="n">
-        <v>11.34440422524625</v>
+        <v>11.34440422524623</v>
       </c>
       <c r="D2" t="n">
-        <v>93.4421603639458</v>
+        <v>93.44216036394555</v>
       </c>
       <c r="E2" t="n">
-        <v>21.35183556280407</v>
+        <v>21.35183556280405</v>
       </c>
       <c r="F2" t="n">
-        <v>21.35183556280407</v>
+        <v>21.35183556280405</v>
       </c>
       <c r="G2" t="n">
-        <v>46.04419400599361</v>
+        <v>46.04419400599355</v>
       </c>
       <c r="H2" t="n">
-        <v>114.6745016967521</v>
+        <v>114.674501696752</v>
       </c>
       <c r="I2" t="n">
-        <v>21.35183556280407</v>
+        <v>21.35183556280405</v>
       </c>
       <c r="J2" t="n">
-        <v>63.73476159041789</v>
+        <v>63.73476159041786</v>
       </c>
       <c r="K2" t="n">
-        <v>19.87471466096459</v>
+        <v>19.87471466096461</v>
       </c>
       <c r="L2" t="n">
-        <v>12.44592307208802</v>
+        <v>12.44592307208805</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.352573259842935</v>
+        <v>3.352573259842949</v>
       </c>
       <c r="C3" t="n">
-        <v>3.062108742018052</v>
+        <v>3.06210874201805</v>
       </c>
       <c r="D3" t="n">
-        <v>3.352573259842935</v>
+        <v>3.352573259842949</v>
       </c>
       <c r="E3" t="n">
-        <v>3.231237136263355</v>
+        <v>3.23123713626335</v>
       </c>
       <c r="F3" t="n">
-        <v>3.231237136263356</v>
+        <v>3.23123713626335</v>
       </c>
       <c r="G3" t="n">
-        <v>3.350016733967897</v>
+        <v>3.350016733967903</v>
       </c>
       <c r="H3" t="n">
-        <v>3.352573259842935</v>
+        <v>3.352573259842949</v>
       </c>
       <c r="I3" t="n">
-        <v>3.334340937255822</v>
+        <v>3.334340937255819</v>
       </c>
       <c r="J3" t="n">
-        <v>3.352573259842935</v>
+        <v>3.352573259842949</v>
       </c>
       <c r="K3" t="n">
-        <v>3.352573259842935</v>
+        <v>3.352573259842949</v>
       </c>
       <c r="L3" t="n">
-        <v>3.352573259842935</v>
+        <v>3.352573259842949</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>634.3368085006531</v>
+        <v>758.3168363328424</v>
       </c>
       <c r="C4" t="n">
-        <v>634.2220350742103</v>
+        <v>634.2220350742105</v>
       </c>
       <c r="D4" t="n">
-        <v>634.4450739538123</v>
+        <v>634.4450596530085</v>
       </c>
       <c r="E4" t="n">
-        <v>571.4687593975458</v>
+        <v>571.4687593975461</v>
       </c>
       <c r="F4" t="n">
-        <v>634.3115547975868</v>
+        <v>634.3115547975866</v>
       </c>
       <c r="G4" t="n">
-        <v>758.314279806967</v>
+        <v>634.3342519747782</v>
       </c>
       <c r="H4" t="n">
-        <v>759.0102398169186</v>
+        <v>759.0102398169182</v>
       </c>
       <c r="I4" t="n">
-        <v>758.2986040102548</v>
+        <v>634.3185761780659</v>
       </c>
       <c r="J4" t="n">
-        <v>666.480468061166</v>
+        <v>758.6281463452608</v>
       </c>
       <c r="K4" t="n">
-        <v>634.2847461594481</v>
+        <v>634.2847461594478</v>
       </c>
       <c r="L4" t="n">
-        <v>634.3358272898602</v>
+        <v>634.3358272898593</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.547078111224542</v>
+        <v>7.547078111224549</v>
       </c>
       <c r="C5" t="n">
-        <v>7.541876157291278</v>
+        <v>7.541876157291276</v>
       </c>
       <c r="D5" t="n">
-        <v>7.547090954723383</v>
+        <v>7.547090954723436</v>
       </c>
       <c r="E5" t="n">
-        <v>7.512111439248045</v>
+        <v>7.512111439248047</v>
       </c>
       <c r="F5" t="n">
-        <v>7.512111439248045</v>
+        <v>7.512111439248047</v>
       </c>
       <c r="G5" t="n">
-        <v>7.544521585349502</v>
+        <v>7.544521585349524</v>
       </c>
       <c r="H5" t="n">
-        <v>7.547078111224542</v>
+        <v>7.547078111224549</v>
       </c>
       <c r="I5" t="n">
-        <v>7.528845788637431</v>
+        <v>7.528845788637427</v>
       </c>
       <c r="J5" t="n">
-        <v>7.547078111224542</v>
+        <v>7.547078111224549</v>
       </c>
       <c r="K5" t="n">
-        <v>7.547078111224542</v>
+        <v>7.547078111224549</v>
       </c>
       <c r="L5" t="n">
-        <v>7.547078111224542</v>
+        <v>7.547078111224549</v>
       </c>
     </row>
     <row r="6">
@@ -4635,22 +4635,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.490300581310317</v>
+        <v>8.490300581310326</v>
       </c>
       <c r="C6" t="n">
-        <v>12.32475319943163</v>
+        <v>12.32475319937806</v>
       </c>
       <c r="D6" t="n">
-        <v>13.14463935327345</v>
+        <v>13.14463935327346</v>
       </c>
       <c r="E6" t="n">
-        <v>11.25911114962814</v>
+        <v>11.25911114962811</v>
       </c>
       <c r="F6" t="n">
-        <v>8.584274755982399</v>
+        <v>8.58427475598239</v>
       </c>
       <c r="G6" t="n">
-        <v>12.34272700115274</v>
+        <v>12.34272700115277</v>
       </c>
       <c r="H6" t="n">
         <v>12.3452835270652</v>
@@ -4659,13 +4659,13 @@
         <v>12.32705120444067</v>
       </c>
       <c r="J6" t="n">
-        <v>12.34604113521831</v>
+        <v>12.34604113521829</v>
       </c>
       <c r="K6" t="n">
-        <v>8.418692294529675</v>
+        <v>8.418692294529672</v>
       </c>
       <c r="L6" t="n">
-        <v>16.37213555623944</v>
+        <v>16.37213555623946</v>
       </c>
     </row>
     <row r="7">
@@ -4678,34 +4678,34 @@
         <v>13.99929701972374</v>
       </c>
       <c r="C7" t="n">
-        <v>17.19552952731749</v>
+        <v>17.19552952731748</v>
       </c>
       <c r="D7" t="n">
-        <v>17.20073299210802</v>
+        <v>17.20073299210799</v>
       </c>
       <c r="E7" t="n">
-        <v>20.876886005022</v>
+        <v>20.87688600502197</v>
       </c>
       <c r="F7" t="n">
-        <v>17.18249755334288</v>
+        <v>17.1824975533429</v>
       </c>
       <c r="G7" t="n">
-        <v>17.19817495537574</v>
+        <v>17.19817495537572</v>
       </c>
       <c r="H7" t="n">
-        <v>17.20073148125076</v>
+        <v>17.20073148125077</v>
       </c>
       <c r="I7" t="n">
         <v>17.18249915866362</v>
       </c>
       <c r="J7" t="n">
-        <v>17.20073148125076</v>
+        <v>17.20073148125077</v>
       </c>
       <c r="K7" t="n">
-        <v>15.27055178355444</v>
+        <v>15.27055178355448</v>
       </c>
       <c r="L7" t="n">
-        <v>17.20073148125076</v>
+        <v>17.20073148125077</v>
       </c>
     </row>
     <row r="8">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.94153299843899</v>
+        <v>84.9415329984391</v>
       </c>
       <c r="C8" t="n">
         <v>166.0241795584537</v>
@@ -4739,10 +4739,10 @@
         <v>168.3253492753852</v>
       </c>
       <c r="J8" t="n">
-        <v>179.3720552412973</v>
+        <v>179.3720552412972</v>
       </c>
       <c r="K8" t="n">
-        <v>175.7727656767247</v>
+        <v>175.7727656767248</v>
       </c>
       <c r="L8" t="n">
         <v>183.2458491362292</v>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.86836588048051</v>
+        <v>83.8683658804806</v>
       </c>
       <c r="C9" t="n">
-        <v>163.5588814006607</v>
+        <v>163.5588814006608</v>
       </c>
       <c r="D9" t="n">
         <v>166.5482308966538</v>
@@ -4779,13 +4779,13 @@
         <v>165.9655220970119</v>
       </c>
       <c r="J9" t="n">
-        <v>177.3958365527734</v>
+        <v>177.3958365527733</v>
       </c>
       <c r="K9" t="n">
-        <v>173.2772924797814</v>
+        <v>173.2772924797816</v>
       </c>
       <c r="L9" t="n">
-        <v>180.5113773618771</v>
+        <v>180.5113773618772</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>305.6860047247388</v>
+        <v>305.6860047247418</v>
       </c>
       <c r="C2" t="n">
-        <v>359.4913397268894</v>
+        <v>359.4913397268886</v>
       </c>
       <c r="D2" t="n">
-        <v>452.3271091309342</v>
+        <v>452.3271091309336</v>
       </c>
       <c r="E2" t="n">
-        <v>359.4913397268894</v>
+        <v>359.4913397268886</v>
       </c>
       <c r="F2" t="n">
-        <v>359.4913397268894</v>
+        <v>359.4913397268886</v>
       </c>
       <c r="G2" t="n">
-        <v>469.0465593164394</v>
+        <v>469.0465593164404</v>
       </c>
       <c r="H2" t="n">
-        <v>914.04726427429</v>
+        <v>914.0472642742866</v>
       </c>
       <c r="I2" t="n">
-        <v>359.4913397268894</v>
+        <v>359.4913397268886</v>
       </c>
       <c r="J2" t="n">
-        <v>775.90369078054</v>
+        <v>775.9036907805402</v>
       </c>
       <c r="K2" t="n">
-        <v>419.8657180231308</v>
+        <v>419.8657180231315</v>
       </c>
       <c r="L2" t="n">
-        <v>278.4957696128072</v>
+        <v>278.4957696128074</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.393019524793012</v>
+        <v>6.393019524793154</v>
       </c>
       <c r="C3" t="n">
-        <v>6.264945026727172</v>
+        <v>6.264945026727178</v>
       </c>
       <c r="D3" t="n">
-        <v>6.393019524793012</v>
+        <v>6.393019524793154</v>
       </c>
       <c r="E3" t="n">
-        <v>6.368416706125283</v>
+        <v>6.368416706125288</v>
       </c>
       <c r="F3" t="n">
-        <v>6.368416706125283</v>
+        <v>6.368416706125287</v>
       </c>
       <c r="G3" t="n">
-        <v>6.39458604258712</v>
+        <v>6.394586042587207</v>
       </c>
       <c r="H3" t="n">
-        <v>6.393019524793012</v>
+        <v>6.393019524793154</v>
       </c>
       <c r="I3" t="n">
         <v>6.403189469656192</v>
       </c>
       <c r="J3" t="n">
-        <v>6.393019524793012</v>
+        <v>6.393019524793154</v>
       </c>
       <c r="K3" t="n">
-        <v>6.393019524793012</v>
+        <v>6.393019524793154</v>
       </c>
       <c r="L3" t="n">
-        <v>6.393019524793012</v>
+        <v>6.393019524793154</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>821.2786513019782</v>
+        <v>685.5614675598325</v>
       </c>
       <c r="C4" t="n">
         <v>685.4445364719261</v>
       </c>
       <c r="D4" t="n">
-        <v>685.6140073834143</v>
+        <v>685.6139990044384</v>
       </c>
       <c r="E4" t="n">
-        <v>617.9462738964679</v>
+        <v>617.9462738964672</v>
       </c>
       <c r="F4" t="n">
-        <v>685.6029214128637</v>
+        <v>685.6029214128635</v>
       </c>
       <c r="G4" t="n">
-        <v>821.2802178197719</v>
+        <v>685.5630340776268</v>
       </c>
       <c r="H4" t="n">
-        <v>822.0188530314774</v>
+        <v>822.0188530314772</v>
       </c>
       <c r="I4" t="n">
-        <v>821.2888212468414</v>
+        <v>821.288821246842</v>
       </c>
       <c r="J4" t="n">
-        <v>821.638753489887</v>
+        <v>720.3515711451504</v>
       </c>
       <c r="K4" t="n">
-        <v>685.5787170139841</v>
+        <v>685.5787170139843</v>
       </c>
       <c r="L4" t="n">
-        <v>685.7344109721663</v>
+        <v>685.7344109721664</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.33270605228193</v>
+        <v>13.3327060522819</v>
       </c>
       <c r="C5" t="n">
-        <v>13.34287599714509</v>
+        <v>13.3428759971451</v>
       </c>
       <c r="D5" t="n">
-        <v>13.33262820661591</v>
+        <v>13.33262820661601</v>
       </c>
       <c r="E5" t="n">
-        <v>13.34956461645898</v>
+        <v>13.34956461645899</v>
       </c>
       <c r="F5" t="n">
-        <v>13.34956461645898</v>
+        <v>13.34956461645899</v>
       </c>
       <c r="G5" t="n">
-        <v>13.33427257007603</v>
+        <v>13.33427257007609</v>
       </c>
       <c r="H5" t="n">
-        <v>13.33270605228193</v>
+        <v>13.3327060522819</v>
       </c>
       <c r="I5" t="n">
-        <v>13.34287599714509</v>
+        <v>13.3428759971451</v>
       </c>
       <c r="J5" t="n">
-        <v>13.33270605228193</v>
+        <v>13.3327060522819</v>
       </c>
       <c r="K5" t="n">
-        <v>13.33270605228193</v>
+        <v>13.3327060522819</v>
       </c>
       <c r="L5" t="n">
-        <v>13.33270605228193</v>
+        <v>13.3327060522819</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.22319002203983</v>
+        <v>16.22319002203989</v>
       </c>
       <c r="C6" t="n">
-        <v>23.67457693977576</v>
+        <v>23.67457693990069</v>
       </c>
       <c r="D6" t="n">
-        <v>25.19787620005394</v>
+        <v>25.197876200054</v>
       </c>
       <c r="E6" t="n">
-        <v>21.64083667799321</v>
+        <v>21.6408366779932</v>
       </c>
       <c r="F6" t="n">
-        <v>16.47302175906847</v>
+        <v>16.47302175906846</v>
       </c>
       <c r="G6" t="n">
-        <v>23.65809215513722</v>
+        <v>23.65809215513731</v>
       </c>
       <c r="H6" t="n">
-        <v>23.65652563734986</v>
+        <v>23.65652563734997</v>
       </c>
       <c r="I6" t="n">
-        <v>23.66669558220626</v>
+        <v>23.66669558220625</v>
       </c>
       <c r="J6" t="n">
-        <v>23.65798649030989</v>
+        <v>23.65798649030994</v>
       </c>
       <c r="K6" t="n">
-        <v>16.08511199762015</v>
+        <v>16.0851119976202</v>
       </c>
       <c r="L6" t="n">
-        <v>31.42126624317233</v>
+        <v>31.4212662431723</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.42465025647586</v>
+        <v>32.42465025647585</v>
       </c>
       <c r="C7" t="n">
-        <v>40.15079967008781</v>
+        <v>40.15079967008784</v>
       </c>
       <c r="D7" t="n">
-        <v>40.14063210255203</v>
+        <v>40.14063210255215</v>
       </c>
       <c r="E7" t="n">
-        <v>49.05486524177363</v>
+        <v>49.05486524177365</v>
       </c>
       <c r="F7" t="n">
-        <v>40.15078904679788</v>
+        <v>40.15078904679792</v>
       </c>
       <c r="G7" t="n">
-        <v>40.14219624301883</v>
+        <v>40.14219624301884</v>
       </c>
       <c r="H7" t="n">
-        <v>40.14062972522471</v>
+        <v>40.14062972522467</v>
       </c>
       <c r="I7" t="n">
-        <v>40.15079967008781</v>
+        <v>40.15079967008784</v>
       </c>
       <c r="J7" t="n">
-        <v>40.14062972522471</v>
+        <v>40.14062972522467</v>
       </c>
       <c r="K7" t="n">
-        <v>35.66996191793683</v>
+        <v>35.66996191793682</v>
       </c>
       <c r="L7" t="n">
-        <v>40.14062972522471</v>
+        <v>40.14062972522467</v>
       </c>
     </row>
     <row r="8">
@@ -5111,34 +5111,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>167.556862430852</v>
+        <v>167.5568624308522</v>
       </c>
       <c r="C8" t="n">
-        <v>171.0339059979306</v>
+        <v>171.0339059979305</v>
       </c>
       <c r="D8" t="n">
-        <v>164.3470894822649</v>
+        <v>164.347089482265</v>
       </c>
       <c r="E8" t="n">
-        <v>171.0339059979306</v>
+        <v>171.0339059979305</v>
       </c>
       <c r="F8" t="n">
-        <v>171.0339059979306</v>
+        <v>171.0339059979305</v>
       </c>
       <c r="G8" t="n">
-        <v>164.1999810996376</v>
+        <v>164.1999810996375</v>
       </c>
       <c r="H8" t="n">
-        <v>156.1327962007702</v>
+        <v>156.1327962007703</v>
       </c>
       <c r="I8" t="n">
-        <v>171.0339059979306</v>
+        <v>171.0339059979305</v>
       </c>
       <c r="J8" t="n">
         <v>157.98081840302</v>
       </c>
       <c r="K8" t="n">
-        <v>165.1156865523961</v>
+        <v>165.1156865523965</v>
       </c>
       <c r="L8" t="n">
         <v>169.0691798020906</v>
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.0761472287817</v>
+        <v>169.0761472287816</v>
       </c>
       <c r="C9" t="n">
-        <v>173.3478161035096</v>
+        <v>173.3478161035097</v>
       </c>
       <c r="D9" t="n">
         <v>167.7691012376136</v>
       </c>
       <c r="E9" t="n">
-        <v>173.3478161035096</v>
+        <v>173.3478161035097</v>
       </c>
       <c r="F9" t="n">
-        <v>173.3478161035096</v>
+        <v>173.3478161035097</v>
       </c>
       <c r="G9" t="n">
         <v>167.701229492574</v>
       </c>
       <c r="H9" t="n">
-        <v>164.440462760649</v>
+        <v>164.4404627606492</v>
       </c>
       <c r="I9" t="n">
-        <v>173.3478161035096</v>
+        <v>173.3478161035097</v>
       </c>
       <c r="J9" t="n">
-        <v>165.1822556200745</v>
+        <v>165.1822556200746</v>
       </c>
       <c r="K9" t="n">
-        <v>168.0823777026625</v>
+        <v>168.0823777026626</v>
       </c>
       <c r="L9" t="n">
-        <v>169.6962905164547</v>
+        <v>165.1138795785788</v>
       </c>
     </row>
   </sheetData>
@@ -5267,31 +5267,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>234.8504957905396</v>
+        <v>234.8504957905395</v>
       </c>
       <c r="C2" t="n">
-        <v>314.625013446726</v>
+        <v>314.6250134467257</v>
       </c>
       <c r="D2" t="n">
-        <v>391.2931990020682</v>
+        <v>391.2931990020704</v>
       </c>
       <c r="E2" t="n">
-        <v>314.625013446726</v>
+        <v>314.6250134467257</v>
       </c>
       <c r="F2" t="n">
-        <v>314.625013446726</v>
+        <v>314.6250134467257</v>
       </c>
       <c r="G2" t="n">
-        <v>403.2068908755313</v>
+        <v>403.2068908755325</v>
       </c>
       <c r="H2" t="n">
-        <v>759.0247025789193</v>
+        <v>759.0247025789174</v>
       </c>
       <c r="I2" t="n">
-        <v>314.625013446726</v>
+        <v>314.6250134467257</v>
       </c>
       <c r="J2" t="n">
-        <v>622.744216119884</v>
+        <v>622.7442161198846</v>
       </c>
       <c r="K2" t="n">
         <v>315.8294433826154</v>
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.803489097629615</v>
+        <v>5.803489097629571</v>
       </c>
       <c r="C3" t="n">
-        <v>5.619173032330088</v>
+        <v>5.619173032330086</v>
       </c>
       <c r="D3" t="n">
-        <v>5.803489097629619</v>
+        <v>5.803489097629562</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711289625537544</v>
+        <v>5.711289625537539</v>
       </c>
       <c r="F3" t="n">
-        <v>5.711289625537544</v>
+        <v>5.711289625537541</v>
       </c>
       <c r="G3" t="n">
-        <v>5.805396815265095</v>
+        <v>5.805396815265119</v>
       </c>
       <c r="H3" t="n">
-        <v>5.803489097629619</v>
+        <v>5.803489097629562</v>
       </c>
       <c r="I3" t="n">
-        <v>5.815789563676556</v>
+        <v>5.815789563676553</v>
       </c>
       <c r="J3" t="n">
-        <v>5.803489097629619</v>
+        <v>5.803489097629562</v>
       </c>
       <c r="K3" t="n">
-        <v>5.803489097629619</v>
+        <v>5.803489097629562</v>
       </c>
       <c r="L3" t="n">
-        <v>5.803489097629619</v>
+        <v>5.803489097629562</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>764.6097616453008</v>
+        <v>638.4926161528122</v>
       </c>
       <c r="C4" t="n">
         <v>638.4027566683181</v>
       </c>
       <c r="D4" t="n">
-        <v>638.5551621612939</v>
+        <v>638.5551621612947</v>
       </c>
       <c r="E4" t="n">
-        <v>575.5274528078405</v>
+        <v>575.5274528078402</v>
       </c>
       <c r="F4" t="n">
-        <v>638.5368178237597</v>
+        <v>638.5368178237596</v>
       </c>
       <c r="G4" t="n">
-        <v>764.6116693629366</v>
+        <v>638.4945238704471</v>
       </c>
       <c r="H4" t="n">
         <v>765.2864784525019</v>
       </c>
       <c r="I4" t="n">
-        <v>764.6220621113478</v>
+        <v>764.6220621113487</v>
       </c>
       <c r="J4" t="n">
-        <v>764.9563340984697</v>
+        <v>670.8754224779382</v>
       </c>
       <c r="K4" t="n">
-        <v>638.4633752209605</v>
+        <v>638.4633752209608</v>
       </c>
       <c r="L4" t="n">
-        <v>638.6523050249688</v>
+        <v>638.6523050249689</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.882822535787</v>
+        <v>11.88282253578706</v>
       </c>
       <c r="C5" t="n">
-        <v>11.89512300183397</v>
+        <v>11.89512300183396</v>
       </c>
       <c r="D5" t="n">
-        <v>11.88277782592244</v>
+        <v>11.88277782592242</v>
       </c>
       <c r="E5" t="n">
-        <v>11.87852778265381</v>
+        <v>11.8785277826538</v>
       </c>
       <c r="F5" t="n">
-        <v>11.87852778265381</v>
+        <v>11.8785277826538</v>
       </c>
       <c r="G5" t="n">
-        <v>11.88473025342251</v>
+        <v>11.88473025342246</v>
       </c>
       <c r="H5" t="n">
-        <v>11.88282253578701</v>
+        <v>11.88282253578706</v>
       </c>
       <c r="I5" t="n">
-        <v>11.89512300183397</v>
+        <v>11.89512300183396</v>
       </c>
       <c r="J5" t="n">
-        <v>11.88282253578701</v>
+        <v>11.88282253578706</v>
       </c>
       <c r="K5" t="n">
-        <v>11.88282253578701</v>
+        <v>11.88282253578706</v>
       </c>
       <c r="L5" t="n">
-        <v>11.88282253578701</v>
+        <v>11.88282253578706</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.27236109126942</v>
+        <v>14.27236109126945</v>
       </c>
       <c r="C6" t="n">
-        <v>20.63823169662226</v>
+        <v>20.63823169662228</v>
       </c>
       <c r="D6" t="n">
-        <v>21.9610557038819</v>
+        <v>21.96105570388189</v>
       </c>
       <c r="E6" t="n">
-        <v>18.89819363377377</v>
+        <v>18.8981936337738</v>
       </c>
       <c r="F6" t="n">
-        <v>14.47665066706828</v>
+        <v>14.47665066706832</v>
       </c>
       <c r="G6" t="n">
-        <v>20.64247448932037</v>
+        <v>20.64247448932035</v>
       </c>
       <c r="H6" t="n">
-        <v>20.64056677169813</v>
+        <v>20.64056677169814</v>
       </c>
       <c r="I6" t="n">
-        <v>20.65286723773182</v>
+        <v>20.65286723773183</v>
       </c>
       <c r="J6" t="n">
-        <v>20.64181829815297</v>
+        <v>20.64181829815301</v>
       </c>
       <c r="K6" t="n">
         <v>14.15406840206161</v>
       </c>
       <c r="L6" t="n">
-        <v>27.29269009771594</v>
+        <v>27.29269009771595</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.10997852465947</v>
+        <v>27.10997852465951</v>
       </c>
       <c r="C7" t="n">
-        <v>33.44436905660414</v>
+        <v>33.4443690566042</v>
       </c>
       <c r="D7" t="n">
-        <v>33.43207097389111</v>
+        <v>33.43207097389109</v>
       </c>
       <c r="E7" t="n">
-        <v>40.73991811256916</v>
+        <v>40.73991811256921</v>
       </c>
       <c r="F7" t="n">
-        <v>33.44436026892232</v>
+        <v>33.44436026892235</v>
       </c>
       <c r="G7" t="n">
-        <v>33.43397630819272</v>
+        <v>33.43397630819274</v>
       </c>
       <c r="H7" t="n">
-        <v>33.43206859055721</v>
+        <v>33.43206859055727</v>
       </c>
       <c r="I7" t="n">
-        <v>33.44436905660414</v>
+        <v>33.4443690566042</v>
       </c>
       <c r="J7" t="n">
-        <v>33.43206859055721</v>
+        <v>33.43206859055727</v>
       </c>
       <c r="K7" t="n">
-        <v>25.4714280907976</v>
+        <v>29.76902578003367</v>
       </c>
       <c r="L7" t="n">
-        <v>33.43206859055721</v>
+        <v>33.43206859055727</v>
       </c>
     </row>
     <row r="8">
@@ -5507,13 +5507,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>168.4516714278703</v>
+        <v>168.4516714278704</v>
       </c>
       <c r="C8" t="n">
         <v>170.9572358032791</v>
       </c>
       <c r="D8" t="n">
-        <v>164.4534021574637</v>
+        <v>164.4534021574636</v>
       </c>
       <c r="E8" t="n">
         <v>170.9572358032791</v>
@@ -5525,19 +5525,19 @@
         <v>164.4110449669012</v>
       </c>
       <c r="H8" t="n">
-        <v>157.7134557229642</v>
+        <v>157.7134557229641</v>
       </c>
       <c r="I8" t="n">
         <v>170.9572358032791</v>
       </c>
       <c r="J8" t="n">
-        <v>159.8379139760527</v>
+        <v>159.8379139760528</v>
       </c>
       <c r="K8" t="n">
-        <v>165.9901220750931</v>
+        <v>165.990122075093</v>
       </c>
       <c r="L8" t="n">
-        <v>167.7000486797229</v>
+        <v>167.7000486797228</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.1617536877661</v>
+        <v>169.1617536877662</v>
       </c>
       <c r="C9" t="n">
-        <v>173.0329961491226</v>
+        <v>173.0329961491225</v>
       </c>
       <c r="D9" t="n">
-        <v>167.5335425887049</v>
+        <v>167.533542588705</v>
       </c>
       <c r="E9" t="n">
-        <v>173.0329961491226</v>
+        <v>173.0329961491225</v>
       </c>
       <c r="F9" t="n">
-        <v>173.0329961491226</v>
+        <v>173.0329961491225</v>
       </c>
       <c r="G9" t="n">
-        <v>167.5093246465939</v>
+        <v>167.5093246465938</v>
       </c>
       <c r="H9" t="n">
         <v>164.803493038796</v>
       </c>
       <c r="I9" t="n">
-        <v>173.0329961491226</v>
+        <v>173.0329961491225</v>
       </c>
       <c r="J9" t="n">
-        <v>165.658903503404</v>
+        <v>165.6589035034039</v>
       </c>
       <c r="K9" t="n">
-        <v>168.1596144994332</v>
+        <v>168.1596144994333</v>
       </c>
       <c r="L9" t="n">
-        <v>168.860472018113</v>
+        <v>165.1096157147679</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>211.5089467282458</v>
+        <v>211.5089467282466</v>
       </c>
       <c r="C2" t="n">
-        <v>281.0989276554192</v>
+        <v>281.0989276554193</v>
       </c>
       <c r="D2" t="n">
-        <v>348.4969734715206</v>
+        <v>348.4969734715209</v>
       </c>
       <c r="E2" t="n">
-        <v>281.0989276554192</v>
+        <v>281.0989276554193</v>
       </c>
       <c r="F2" t="n">
-        <v>281.0989276554192</v>
+        <v>281.0989276554193</v>
       </c>
       <c r="G2" t="n">
-        <v>361.8634637409376</v>
+        <v>361.8634637409385</v>
       </c>
       <c r="H2" t="n">
-        <v>655.1574525448239</v>
+        <v>655.1574525448232</v>
       </c>
       <c r="I2" t="n">
-        <v>281.0989276554192</v>
+        <v>281.0989276554193</v>
       </c>
       <c r="J2" t="n">
-        <v>577.4402553467671</v>
+        <v>577.4402553467677</v>
       </c>
       <c r="K2" t="n">
-        <v>220.7772391376409</v>
+        <v>220.7772391376407</v>
       </c>
       <c r="L2" t="n">
-        <v>676.2593697945763</v>
+        <v>220.4823720380224</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.414732734499733</v>
+        <v>5.414732734500095</v>
       </c>
       <c r="C3" t="n">
-        <v>5.118513738462823</v>
+        <v>5.118513738462831</v>
       </c>
       <c r="D3" t="n">
-        <v>5.414732734499734</v>
+        <v>5.414732734500095</v>
       </c>
       <c r="E3" t="n">
-        <v>5.213324080369569</v>
+        <v>5.213324080369565</v>
       </c>
       <c r="F3" t="n">
-        <v>5.213324080369566</v>
+        <v>5.213324080369563</v>
       </c>
       <c r="G3" t="n">
-        <v>5.416564734255883</v>
+        <v>5.416564734255917</v>
       </c>
       <c r="H3" t="n">
-        <v>5.414732734499734</v>
+        <v>5.414732734500095</v>
       </c>
       <c r="I3" t="n">
-        <v>5.426556475908</v>
+        <v>5.426556475908002</v>
       </c>
       <c r="J3" t="n">
-        <v>5.414732734499734</v>
+        <v>5.414732734500095</v>
       </c>
       <c r="K3" t="n">
-        <v>5.414732734499734</v>
+        <v>5.414732734500095</v>
       </c>
       <c r="L3" t="n">
-        <v>5.414732734499734</v>
+        <v>5.414732734500095</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>637.8933897211321</v>
+        <v>637.8933897211318</v>
       </c>
       <c r="C4" t="n">
-        <v>637.810654108298</v>
+        <v>637.8106541082983</v>
       </c>
       <c r="D4" t="n">
-        <v>763.8878732799783</v>
+        <v>637.9868177493559</v>
       </c>
       <c r="E4" t="n">
-        <v>574.9533037842054</v>
+        <v>574.9533037842062</v>
       </c>
       <c r="F4" t="n">
-        <v>637.9496126672088</v>
+        <v>637.9496126672086</v>
       </c>
       <c r="G4" t="n">
-        <v>637.8952217208885</v>
+        <v>763.7256749296491</v>
       </c>
       <c r="H4" t="n">
-        <v>764.4166472274939</v>
+        <v>764.4166472274934</v>
       </c>
       <c r="I4" t="n">
-        <v>763.7356666713004</v>
+        <v>637.9052134625402</v>
       </c>
       <c r="J4" t="n">
-        <v>670.278844987645</v>
+        <v>764.0896214672905</v>
       </c>
       <c r="K4" t="n">
-        <v>637.7781037846438</v>
+        <v>637.778103784644</v>
       </c>
       <c r="L4" t="n">
-        <v>638.0653605053975</v>
+        <v>638.0653605053976</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.22630093006511</v>
+        <v>11.22630093006521</v>
       </c>
       <c r="C5" t="n">
-        <v>11.23812467147337</v>
+        <v>11.23812467147338</v>
       </c>
       <c r="D5" t="n">
-        <v>11.22628357731547</v>
+        <v>11.22628357731556</v>
       </c>
       <c r="E5" t="n">
-        <v>11.19042374670139</v>
+        <v>11.19042374670141</v>
       </c>
       <c r="F5" t="n">
-        <v>11.19042374670139</v>
+        <v>11.19042374670141</v>
       </c>
       <c r="G5" t="n">
-        <v>11.22813292982125</v>
+        <v>11.22813292982129</v>
       </c>
       <c r="H5" t="n">
-        <v>11.2263009300651</v>
+        <v>11.22630093006521</v>
       </c>
       <c r="I5" t="n">
-        <v>11.23812467147337</v>
+        <v>11.23812467147338</v>
       </c>
       <c r="J5" t="n">
-        <v>11.2263009300651</v>
+        <v>11.22630093006521</v>
       </c>
       <c r="K5" t="n">
-        <v>11.2263009300651</v>
+        <v>11.22630093006521</v>
       </c>
       <c r="L5" t="n">
-        <v>11.2263009300651</v>
+        <v>11.22630093006521</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.39695351108848</v>
+        <v>13.39695351108864</v>
       </c>
       <c r="C6" t="n">
-        <v>19.34920457029845</v>
+        <v>19.34920457029849</v>
       </c>
       <c r="D6" t="n">
-        <v>20.6228867567056</v>
+        <v>20.62288675670552</v>
       </c>
       <c r="E6" t="n">
-        <v>17.71717029320102</v>
+        <v>17.71717029320105</v>
       </c>
       <c r="F6" t="n">
-        <v>13.5700444432102</v>
+        <v>13.57004444321022</v>
       </c>
       <c r="G6" t="n">
-        <v>19.38370641866639</v>
+        <v>19.38370641866654</v>
       </c>
       <c r="H6" t="n">
-        <v>19.38187441892632</v>
+        <v>19.38187441892642</v>
       </c>
       <c r="I6" t="n">
-        <v>19.39369816031851</v>
+        <v>19.39369816031855</v>
       </c>
       <c r="J6" t="n">
-        <v>19.38305061977987</v>
+        <v>19.38305061978015</v>
       </c>
       <c r="K6" t="n">
-        <v>13.28578053323016</v>
+        <v>13.28578053323023</v>
       </c>
       <c r="L6" t="n">
-        <v>25.63362475101866</v>
+        <v>25.63362475101885</v>
       </c>
     </row>
     <row r="7">
@@ -5863,34 +5863,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.31996547969077</v>
+        <v>24.31996547969102</v>
       </c>
       <c r="C7" t="n">
-        <v>29.95755940982545</v>
+        <v>29.95755940982546</v>
       </c>
       <c r="D7" t="n">
-        <v>29.945738007084</v>
+        <v>29.94573800708406</v>
       </c>
       <c r="E7" t="n">
-        <v>36.44957096835981</v>
+        <v>36.44957096835982</v>
       </c>
       <c r="F7" t="n">
-        <v>29.95755135561301</v>
+        <v>29.95755135561308</v>
       </c>
       <c r="G7" t="n">
-        <v>29.94756766817337</v>
+        <v>29.9475676681734</v>
       </c>
       <c r="H7" t="n">
         <v>29.94573566841716</v>
       </c>
       <c r="I7" t="n">
-        <v>29.95755940982545</v>
+        <v>29.95755940982546</v>
       </c>
       <c r="J7" t="n">
         <v>29.94573566841716</v>
       </c>
       <c r="K7" t="n">
-        <v>26.68614331059909</v>
+        <v>26.6861433105992</v>
       </c>
       <c r="L7" t="n">
         <v>29.94573566841716</v>
@@ -5903,34 +5903,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>168.4291506132149</v>
+        <v>168.4291506132147</v>
       </c>
       <c r="C8" t="n">
-        <v>171.3558151439407</v>
+        <v>171.3558151439406</v>
       </c>
       <c r="D8" t="n">
         <v>164.7879589536109</v>
       </c>
       <c r="E8" t="n">
-        <v>171.3558151439407</v>
+        <v>171.3558151439406</v>
       </c>
       <c r="F8" t="n">
-        <v>171.3558151439407</v>
+        <v>171.3558151439406</v>
       </c>
       <c r="G8" t="n">
-        <v>164.7647330200325</v>
+        <v>164.7647330200324</v>
       </c>
       <c r="H8" t="n">
         <v>158.9005609108997</v>
       </c>
       <c r="I8" t="n">
-        <v>171.3558151439407</v>
+        <v>171.3558151439406</v>
       </c>
       <c r="J8" t="n">
         <v>160.4796804260006</v>
       </c>
       <c r="K8" t="n">
-        <v>167.7432096036154</v>
+        <v>167.7432096036153</v>
       </c>
       <c r="L8" t="n">
         <v>159.4761573502741</v>
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168.9038857210302</v>
+        <v>168.9038857210301</v>
       </c>
       <c r="C9" t="n">
-        <v>172.9569925073838</v>
+        <v>172.9569925073837</v>
       </c>
       <c r="D9" t="n">
         <v>167.4210898239196</v>
       </c>
       <c r="E9" t="n">
-        <v>172.9569925073838</v>
+        <v>172.9569925073837</v>
       </c>
       <c r="F9" t="n">
-        <v>172.9569925073838</v>
+        <v>172.9569925073837</v>
       </c>
       <c r="G9" t="n">
-        <v>167.4041695795844</v>
+        <v>167.4041695795842</v>
       </c>
       <c r="H9" t="n">
-        <v>165.0367942314375</v>
+        <v>165.0367942314374</v>
       </c>
       <c r="I9" t="n">
-        <v>172.9569925073838</v>
+        <v>172.9569925073837</v>
       </c>
       <c r="J9" t="n">
-        <v>165.6711873059517</v>
+        <v>165.6711873059516</v>
       </c>
       <c r="K9" t="n">
-        <v>168.6248251219161</v>
+        <v>168.624825121916</v>
       </c>
       <c r="L9" t="n">
-        <v>165.2682151304431</v>
+        <v>165.2682151304429</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.05768912061903</v>
+        <v>73.05768912061936</v>
       </c>
       <c r="C2" t="n">
-        <v>300.7677103846681</v>
+        <v>300.7677103846679</v>
       </c>
       <c r="D2" t="n">
-        <v>231.55638697186</v>
+        <v>231.5563869718602</v>
       </c>
       <c r="E2" t="n">
-        <v>300.7677103846681</v>
+        <v>300.7677103846679</v>
       </c>
       <c r="F2" t="n">
-        <v>300.7677103846681</v>
+        <v>300.7677103846679</v>
       </c>
       <c r="G2" t="n">
-        <v>281.9878043972368</v>
+        <v>281.9878043972367</v>
       </c>
       <c r="H2" t="n">
         <v>383.5767044631112</v>
       </c>
       <c r="I2" t="n">
-        <v>300.7677103846681</v>
+        <v>300.7677103846679</v>
       </c>
       <c r="J2" t="n">
-        <v>820.640492550769</v>
+        <v>820.6404925507686</v>
       </c>
       <c r="K2" t="n">
-        <v>274.0372077716466</v>
+        <v>274.037207771647</v>
       </c>
       <c r="L2" t="n">
-        <v>510.6925341865314</v>
+        <v>510.6925341865315</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.47596814444473</v>
+        <v>5.475968144444742</v>
       </c>
       <c r="C3" t="n">
-        <v>5.318284639216489</v>
+        <v>5.318284639216484</v>
       </c>
       <c r="D3" t="n">
-        <v>5.47596814444473</v>
+        <v>5.475968144444742</v>
       </c>
       <c r="E3" t="n">
-        <v>5.416488831082416</v>
+        <v>5.416488831082402</v>
       </c>
       <c r="F3" t="n">
-        <v>5.416488831082418</v>
+        <v>5.4164888310824</v>
       </c>
       <c r="G3" t="n">
-        <v>5.481443351691945</v>
+        <v>5.481443351691944</v>
       </c>
       <c r="H3" t="n">
-        <v>5.47596814444473</v>
+        <v>5.475968144444742</v>
       </c>
       <c r="I3" t="n">
-        <v>5.511038847544608</v>
+        <v>5.511038847544598</v>
       </c>
       <c r="J3" t="n">
-        <v>5.47596814444473</v>
+        <v>5.475968144444742</v>
       </c>
       <c r="K3" t="n">
-        <v>5.47596814444473</v>
+        <v>5.475968144444742</v>
       </c>
       <c r="L3" t="n">
-        <v>5.47596814444473</v>
+        <v>5.475968144444742</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>684.1844525236561</v>
+        <v>818.6034491965382</v>
       </c>
       <c r="C4" t="n">
-        <v>684.240846286668</v>
+        <v>684.2408462866675</v>
       </c>
       <c r="D4" t="n">
-        <v>818.7827579837133</v>
+        <v>818.7827579837126</v>
       </c>
       <c r="E4" t="n">
-        <v>616.7727567525817</v>
+        <v>616.7727567525819</v>
       </c>
       <c r="F4" t="n">
-        <v>684.2615505532018</v>
+        <v>684.2615505532016</v>
       </c>
       <c r="G4" t="n">
-        <v>684.1899277309044</v>
+        <v>818.6089244037848</v>
       </c>
       <c r="H4" t="n">
-        <v>819.3169477219468</v>
+        <v>684.2545566818231</v>
       </c>
       <c r="I4" t="n">
-        <v>684.2195232267572</v>
+        <v>818.6385198996373</v>
       </c>
       <c r="J4" t="n">
-        <v>819.0120731419154</v>
+        <v>819.0120731419156</v>
       </c>
       <c r="K4" t="n">
-        <v>684.2101511598296</v>
+        <v>684.2101511598293</v>
       </c>
       <c r="L4" t="n">
-        <v>684.2840796779967</v>
+        <v>684.2840796779965</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.32842056291677</v>
+        <v>11.32842056291675</v>
       </c>
       <c r="C5" t="n">
-        <v>11.36349126601664</v>
+        <v>11.36349126601661</v>
       </c>
       <c r="D5" t="n">
         <v>11.32839095601244</v>
       </c>
       <c r="E5" t="n">
-        <v>11.33530438149657</v>
+        <v>11.33530438149655</v>
       </c>
       <c r="F5" t="n">
-        <v>11.33530438149657</v>
+        <v>11.33530438149655</v>
       </c>
       <c r="G5" t="n">
-        <v>11.33389577016396</v>
+        <v>11.33389577016395</v>
       </c>
       <c r="H5" t="n">
-        <v>11.32842056291677</v>
+        <v>11.32842056291675</v>
       </c>
       <c r="I5" t="n">
-        <v>11.36349126601664</v>
+        <v>11.36349126601661</v>
       </c>
       <c r="J5" t="n">
-        <v>11.32842056291677</v>
+        <v>11.32842056291675</v>
       </c>
       <c r="K5" t="n">
-        <v>11.32842056291677</v>
+        <v>11.32842056291675</v>
       </c>
       <c r="L5" t="n">
-        <v>11.32842056291677</v>
+        <v>11.32842056291675</v>
       </c>
     </row>
     <row r="6">
@@ -6222,34 +6222,34 @@
         <v>13.2927596824789</v>
       </c>
       <c r="C6" t="n">
-        <v>19.20653449648836</v>
+        <v>19.20653449648834</v>
       </c>
       <c r="D6" t="n">
-        <v>20.42164118405633</v>
+        <v>20.42164118405634</v>
       </c>
       <c r="E6" t="n">
-        <v>17.59450041981172</v>
+        <v>17.59450041981171</v>
       </c>
       <c r="F6" t="n">
-        <v>13.49819792132516</v>
+        <v>13.49819792132512</v>
       </c>
       <c r="G6" t="n">
-        <v>19.20277213061335</v>
+        <v>19.20277213061332</v>
       </c>
       <c r="H6" t="n">
-        <v>19.19729692337479</v>
+        <v>19.19729692337478</v>
       </c>
       <c r="I6" t="n">
-        <v>19.23236762646602</v>
+        <v>19.232367626466</v>
       </c>
       <c r="J6" t="n">
-        <v>19.19845732520298</v>
+        <v>19.19845732520295</v>
       </c>
       <c r="K6" t="n">
-        <v>13.18307987258566</v>
+        <v>13.18307987258565</v>
       </c>
       <c r="L6" t="n">
-        <v>25.36507979258058</v>
+        <v>25.36507979258057</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.84693286367268</v>
+        <v>26.84693286367271</v>
       </c>
       <c r="C7" t="n">
         <v>33.2004461644616</v>
       </c>
       <c r="D7" t="n">
-        <v>33.16537910498745</v>
+        <v>33.16537910498747</v>
       </c>
       <c r="E7" t="n">
         <v>40.49179299084972</v>
       </c>
       <c r="F7" t="n">
-        <v>33.20044196247624</v>
+        <v>33.20044196247625</v>
       </c>
       <c r="G7" t="n">
         <v>33.17085066860894</v>
       </c>
       <c r="H7" t="n">
-        <v>33.16537546136173</v>
+        <v>33.16537546136174</v>
       </c>
       <c r="I7" t="n">
         <v>33.2004461644616</v>
       </c>
       <c r="J7" t="n">
-        <v>33.16537546136173</v>
+        <v>33.16537546136174</v>
       </c>
       <c r="K7" t="n">
-        <v>29.5044465383166</v>
+        <v>29.50444653831662</v>
       </c>
       <c r="L7" t="n">
-        <v>33.16537546136173</v>
+        <v>33.16537546136174</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.0102313130304</v>
+        <v>172.0102313130303</v>
       </c>
       <c r="C8" t="n">
-        <v>171.4452028116781</v>
+        <v>171.445202811678</v>
       </c>
       <c r="D8" t="n">
-        <v>167.8535267143937</v>
+        <v>167.8535267143936</v>
       </c>
       <c r="E8" t="n">
-        <v>171.4452028116781</v>
+        <v>171.445202811678</v>
       </c>
       <c r="F8" t="n">
-        <v>171.4452028116781</v>
+        <v>171.445202811678</v>
       </c>
       <c r="G8" t="n">
-        <v>166.9786491847111</v>
+        <v>166.978649184711</v>
       </c>
       <c r="H8" t="n">
-        <v>165.0367597437984</v>
+        <v>165.0367597437983</v>
       </c>
       <c r="I8" t="n">
-        <v>171.4452028116781</v>
+        <v>171.445202811678</v>
       </c>
       <c r="J8" t="n">
-        <v>155.9340385252217</v>
+        <v>155.9340385252218</v>
       </c>
       <c r="K8" t="n">
-        <v>166.9872135807211</v>
+        <v>166.987213580721</v>
       </c>
       <c r="L8" t="n">
-        <v>170.9811421751772</v>
+        <v>163.2792014811771</v>
       </c>
     </row>
     <row r="9">
@@ -6342,34 +6342,34 @@
         <v>170.2788250504325</v>
       </c>
       <c r="C9" t="n">
-        <v>172.9596292856736</v>
+        <v>172.9596292856737</v>
       </c>
       <c r="D9" t="n">
-        <v>168.5859788918748</v>
+        <v>168.5859788918749</v>
       </c>
       <c r="E9" t="n">
-        <v>172.9596292856736</v>
+        <v>172.9596292856737</v>
       </c>
       <c r="F9" t="n">
-        <v>172.9596292856736</v>
+        <v>172.9596292856737</v>
       </c>
       <c r="G9" t="n">
-        <v>168.2314846006709</v>
+        <v>168.231484600671</v>
       </c>
       <c r="H9" t="n">
-        <v>167.446571906796</v>
+        <v>167.4465719067959</v>
       </c>
       <c r="I9" t="n">
-        <v>172.9596292856736</v>
+        <v>172.9596292856737</v>
       </c>
       <c r="J9" t="n">
-        <v>163.7378443115297</v>
+        <v>163.7378443115296</v>
       </c>
       <c r="K9" t="n">
         <v>168.2333331469633</v>
       </c>
       <c r="L9" t="n">
-        <v>166.7305704126944</v>
+        <v>166.7305704126943</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.3562465189001</v>
+        <v>23.35624651890013</v>
       </c>
       <c r="C2" t="n">
-        <v>203.7080562314733</v>
+        <v>203.7080562314734</v>
       </c>
       <c r="D2" t="n">
-        <v>175.161305664024</v>
+        <v>175.1613056640239</v>
       </c>
       <c r="E2" t="n">
-        <v>203.7080562314733</v>
+        <v>203.7080562314734</v>
       </c>
       <c r="F2" t="n">
-        <v>203.7080562314733</v>
+        <v>203.7080562314734</v>
       </c>
       <c r="G2" t="n">
-        <v>185.2819746375578</v>
+        <v>185.2819746375586</v>
       </c>
       <c r="H2" t="n">
         <v>129.5966377805293</v>
       </c>
       <c r="I2" t="n">
-        <v>203.7080562314733</v>
+        <v>203.7080562314734</v>
       </c>
       <c r="J2" t="n">
-        <v>451.9055817030423</v>
+        <v>451.9055817030426</v>
       </c>
       <c r="K2" t="n">
         <v>118.6935159272517</v>
       </c>
       <c r="L2" t="n">
-        <v>43.03751382128457</v>
+        <v>43.03751382128469</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.62437772984206</v>
+        <v>4.624377729842</v>
       </c>
       <c r="C3" t="n">
-        <v>4.482830058134606</v>
+        <v>4.482830058134609</v>
       </c>
       <c r="D3" t="n">
-        <v>4.62437772984206</v>
+        <v>4.624377729842</v>
       </c>
       <c r="E3" t="n">
-        <v>4.55737129155174</v>
+        <v>4.557371291551743</v>
       </c>
       <c r="F3" t="n">
         <v>4.557371291551745</v>
       </c>
       <c r="G3" t="n">
-        <v>4.629881182953985</v>
+        <v>4.629881182954056</v>
       </c>
       <c r="H3" t="n">
-        <v>4.62437772984206</v>
+        <v>4.624377729842</v>
       </c>
       <c r="I3" t="n">
-        <v>4.659449890699057</v>
+        <v>4.659449890699065</v>
       </c>
       <c r="J3" t="n">
-        <v>4.62437772984206</v>
+        <v>4.624377729842</v>
       </c>
       <c r="K3" t="n">
-        <v>4.62437772984206</v>
+        <v>4.624377729842</v>
       </c>
       <c r="L3" t="n">
-        <v>4.62437772984206</v>
+        <v>4.624377729842</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>761.2124839580674</v>
+        <v>761.2124839580673</v>
       </c>
       <c r="C4" t="n">
-        <v>636.5847472894977</v>
+        <v>636.5847472894978</v>
       </c>
       <c r="D4" t="n">
-        <v>636.533928783074</v>
+        <v>636.5339286196424</v>
       </c>
       <c r="E4" t="n">
-        <v>573.7622949581266</v>
+        <v>573.7622949581269</v>
       </c>
       <c r="F4" t="n">
-        <v>636.5904263738786</v>
+        <v>636.5904263738785</v>
       </c>
       <c r="G4" t="n">
-        <v>636.5115746942774</v>
+        <v>761.2179874111797</v>
       </c>
       <c r="H4" t="n">
-        <v>636.5293377704467</v>
+        <v>761.7292938424418</v>
       </c>
       <c r="I4" t="n">
-        <v>636.5411434020227</v>
+        <v>761.2475561189248</v>
       </c>
       <c r="J4" t="n">
-        <v>761.5718092781718</v>
+        <v>668.8325825627127</v>
       </c>
       <c r="K4" t="n">
-        <v>636.3944404170486</v>
+        <v>636.3944404170489</v>
       </c>
       <c r="L4" t="n">
-        <v>636.5882030650396</v>
+        <v>636.5882030650399</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.495515880461129</v>
+        <v>9.495515880461134</v>
       </c>
       <c r="C5" t="n">
-        <v>9.530588041318184</v>
+        <v>9.530588041318193</v>
       </c>
       <c r="D5" t="n">
         <v>9.49549787642761</v>
       </c>
       <c r="E5" t="n">
-        <v>9.500153436516467</v>
+        <v>9.500153436516465</v>
       </c>
       <c r="F5" t="n">
-        <v>9.500153436516467</v>
+        <v>9.500153436516465</v>
       </c>
       <c r="G5" t="n">
-        <v>9.501019333573185</v>
+        <v>9.501019333573177</v>
       </c>
       <c r="H5" t="n">
-        <v>9.495515880461129</v>
+        <v>9.495515880461134</v>
       </c>
       <c r="I5" t="n">
-        <v>9.530588041318184</v>
+        <v>9.530588041318193</v>
       </c>
       <c r="J5" t="n">
-        <v>9.495515880461129</v>
+        <v>9.495515880461134</v>
       </c>
       <c r="K5" t="n">
-        <v>9.495515880461129</v>
+        <v>9.495515880461134</v>
       </c>
       <c r="L5" t="n">
-        <v>9.495515880461129</v>
+        <v>9.495515880461134</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.78005252547426</v>
+        <v>10.78005252547425</v>
       </c>
       <c r="C6" t="n">
         <v>15.39734947121002</v>
       </c>
       <c r="D6" t="n">
-        <v>16.34653922932251</v>
+        <v>16.34653922932263</v>
       </c>
       <c r="E6" t="n">
-        <v>14.13948779675214</v>
+        <v>14.13948779675216</v>
       </c>
       <c r="F6" t="n">
-        <v>10.94312464141113</v>
+        <v>10.94312464141115</v>
       </c>
       <c r="G6" t="n">
         <v>15.39603071241727</v>
       </c>
       <c r="H6" t="n">
-        <v>15.39052725930323</v>
+        <v>15.39052725930326</v>
       </c>
       <c r="I6" t="n">
-        <v>15.42559942016229</v>
+        <v>15.42559942016228</v>
       </c>
       <c r="J6" t="n">
-        <v>15.3914333432549</v>
+        <v>15.39143334325496</v>
       </c>
       <c r="K6" t="n">
-        <v>10.69441059082482</v>
+        <v>10.69441059082485</v>
       </c>
       <c r="L6" t="n">
-        <v>20.20655363443908</v>
+        <v>20.20655363443922</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.67691141639246</v>
+        <v>20.67691141639247</v>
       </c>
       <c r="C7" t="n">
-        <v>25.4557313008018</v>
+        <v>25.45573130080183</v>
       </c>
       <c r="D7" t="n">
-        <v>25.42066351426281</v>
+        <v>25.42066351426297</v>
       </c>
       <c r="E7" t="n">
-        <v>30.92991814996808</v>
+        <v>30.92991814996814</v>
       </c>
       <c r="F7" t="n">
-        <v>25.45573018527799</v>
+        <v>25.45573018527803</v>
       </c>
       <c r="G7" t="n">
-        <v>25.42616259305676</v>
+        <v>25.42616259305683</v>
       </c>
       <c r="H7" t="n">
-        <v>25.42065913994463</v>
+        <v>25.42065913994475</v>
       </c>
       <c r="I7" t="n">
-        <v>25.4557313008018</v>
+        <v>25.45573130080183</v>
       </c>
       <c r="J7" t="n">
-        <v>25.42065913994463</v>
+        <v>25.42065913994475</v>
       </c>
       <c r="K7" t="n">
-        <v>22.56060283014227</v>
+        <v>22.67211491860477</v>
       </c>
       <c r="L7" t="n">
-        <v>25.42065913994463</v>
+        <v>25.42065913994475</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.2793143277125</v>
+        <v>172.2793143277126</v>
       </c>
       <c r="C8" t="n">
-        <v>172.3757941877958</v>
+        <v>172.3757941877959</v>
       </c>
       <c r="D8" t="n">
-        <v>167.927634873833</v>
+        <v>167.9276348738329</v>
       </c>
       <c r="E8" t="n">
-        <v>172.3757941877958</v>
+        <v>172.3757941877959</v>
       </c>
       <c r="F8" t="n">
-        <v>172.3757941877958</v>
+        <v>172.3757941877959</v>
       </c>
       <c r="G8" t="n">
-        <v>167.9544567808544</v>
+        <v>167.9544567808545</v>
       </c>
       <c r="H8" t="n">
         <v>169.5232477262695</v>
       </c>
       <c r="I8" t="n">
-        <v>172.3757941877958</v>
+        <v>172.3757941877959</v>
       </c>
       <c r="J8" t="n">
-        <v>161.6305152875138</v>
+        <v>161.6305152875139</v>
       </c>
       <c r="K8" t="n">
-        <v>169.6939127074645</v>
+        <v>169.6939127074646</v>
       </c>
       <c r="L8" t="n">
-        <v>166.0558843623427</v>
+        <v>171.8549486326253</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.8788617552626</v>
+        <v>169.8788617552628</v>
       </c>
       <c r="C9" t="n">
-        <v>172.7981612541917</v>
+        <v>172.7981612541918</v>
       </c>
       <c r="D9" t="n">
-        <v>168.1065783191064</v>
+        <v>168.1065783191065</v>
       </c>
       <c r="E9" t="n">
-        <v>172.7981612541917</v>
+        <v>172.7981612541918</v>
       </c>
       <c r="F9" t="n">
-        <v>172.7981612541917</v>
+        <v>172.7981612541918</v>
       </c>
       <c r="G9" t="n">
-        <v>168.1191069519913</v>
+        <v>168.1191069519915</v>
       </c>
       <c r="H9" t="n">
         <v>168.7593367651579</v>
       </c>
       <c r="I9" t="n">
-        <v>172.7981612541917</v>
+        <v>172.7981612541918</v>
       </c>
       <c r="J9" t="n">
-        <v>165.5459157371505</v>
+        <v>165.5459157371506</v>
       </c>
       <c r="K9" t="n">
-        <v>168.826005760733</v>
+        <v>168.8260057607332</v>
       </c>
       <c r="L9" t="n">
-        <v>167.3491684362777</v>
+        <v>169.706687819464</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.69630697769957</v>
+        <v>21.69630697769956</v>
       </c>
       <c r="C2" t="n">
-        <v>144.180700654242</v>
+        <v>144.1807006542421</v>
       </c>
       <c r="D2" t="n">
-        <v>110.2551592780781</v>
+        <v>110.2551592780782</v>
       </c>
       <c r="E2" t="n">
-        <v>144.180700654242</v>
+        <v>144.1807006542421</v>
       </c>
       <c r="F2" t="n">
-        <v>144.180700654242</v>
+        <v>144.1807006542421</v>
       </c>
       <c r="G2" t="n">
-        <v>136.3697864401665</v>
+        <v>136.3697864401663</v>
       </c>
       <c r="H2" t="n">
-        <v>134.9204580178757</v>
+        <v>134.9204580178755</v>
       </c>
       <c r="I2" t="n">
-        <v>144.180700654242</v>
+        <v>144.1807006542421</v>
       </c>
       <c r="J2" t="n">
-        <v>276.9622823912787</v>
+        <v>276.9622823912782</v>
       </c>
       <c r="K2" t="n">
-        <v>58.11921457723713</v>
+        <v>58.11921457723702</v>
       </c>
       <c r="L2" t="n">
-        <v>262.9024968540979</v>
+        <v>68.47163475217479</v>
       </c>
     </row>
     <row r="3">
@@ -6891,31 +6891,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.153643134711057</v>
+        <v>4.153643134711056</v>
       </c>
       <c r="C3" t="n">
-        <v>3.997550746337672</v>
+        <v>3.997550746337666</v>
       </c>
       <c r="D3" t="n">
         <v>4.153643134711057</v>
       </c>
       <c r="E3" t="n">
-        <v>4.065393212876855</v>
+        <v>4.06539321287685</v>
       </c>
       <c r="F3" t="n">
-        <v>4.065393212876852</v>
+        <v>4.065393212876851</v>
       </c>
       <c r="G3" t="n">
-        <v>4.158690180722157</v>
+        <v>4.158690180722161</v>
       </c>
       <c r="H3" t="n">
         <v>4.153643134711057</v>
       </c>
       <c r="I3" t="n">
-        <v>4.185720998562402</v>
+        <v>4.185720998562391</v>
       </c>
       <c r="J3" t="n">
-        <v>4.153643134711057</v>
+        <v>4.153643134711056</v>
       </c>
       <c r="K3" t="n">
         <v>4.153643134711057</v>
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.6706864026596</v>
+        <v>635.670686402659</v>
       </c>
       <c r="C4" t="n">
-        <v>635.7200110014758</v>
+        <v>635.720011001476</v>
       </c>
       <c r="D4" t="n">
-        <v>635.6543819012978</v>
+        <v>635.6543819012979</v>
       </c>
       <c r="E4" t="n">
         <v>572.9250182385711</v>
       </c>
       <c r="F4" t="n">
-        <v>635.7413919370121</v>
+        <v>635.7413919370123</v>
       </c>
       <c r="G4" t="n">
-        <v>760.0894326357819</v>
+        <v>635.6757334486708</v>
       </c>
       <c r="H4" t="n">
         <v>760.5392574583368</v>
       </c>
       <c r="I4" t="n">
-        <v>635.7027642665111</v>
+        <v>635.7027642665105</v>
       </c>
       <c r="J4" t="n">
-        <v>760.404810253703</v>
+        <v>667.9267294349162</v>
       </c>
       <c r="K4" t="n">
-        <v>635.5427548006643</v>
+        <v>635.5427548006649</v>
       </c>
       <c r="L4" t="n">
-        <v>635.7551932434864</v>
+        <v>635.7551932434868</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.693812630791729</v>
+        <v>8.693812630791738</v>
       </c>
       <c r="C5" t="n">
-        <v>8.725890494643068</v>
+        <v>8.725890494643053</v>
       </c>
       <c r="D5" t="n">
-        <v>8.693803778236967</v>
+        <v>8.693803778236981</v>
       </c>
       <c r="E5" t="n">
-        <v>8.693100217210571</v>
+        <v>8.693100217210553</v>
       </c>
       <c r="F5" t="n">
-        <v>8.693100217210571</v>
+        <v>8.693100217210553</v>
       </c>
       <c r="G5" t="n">
-        <v>8.69885967680284</v>
+        <v>8.698859676802815</v>
       </c>
       <c r="H5" t="n">
-        <v>8.693812630791729</v>
+        <v>8.693812630791738</v>
       </c>
       <c r="I5" t="n">
-        <v>8.725890494643068</v>
+        <v>8.725890494643053</v>
       </c>
       <c r="J5" t="n">
-        <v>8.693812630791729</v>
+        <v>8.693812630791738</v>
       </c>
       <c r="K5" t="n">
-        <v>8.693812630791729</v>
+        <v>8.693812630791738</v>
       </c>
       <c r="L5" t="n">
-        <v>8.693812630791729</v>
+        <v>8.693812630791738</v>
       </c>
     </row>
     <row r="6">
@@ -7014,10 +7014,10 @@
         <v>9.686032244097621</v>
       </c>
       <c r="C6" t="n">
-        <v>13.81324133258957</v>
+        <v>13.81324133258959</v>
       </c>
       <c r="D6" t="n">
-        <v>14.66727224376595</v>
+        <v>14.66727224376591</v>
       </c>
       <c r="E6" t="n">
         <v>12.68820296605154</v>
@@ -7029,19 +7029,19 @@
         <v>13.81682006402259</v>
       </c>
       <c r="H6" t="n">
-        <v>13.81177301800423</v>
+        <v>13.8117730180042</v>
       </c>
       <c r="I6" t="n">
-        <v>13.84385088186284</v>
+        <v>13.84385088186281</v>
       </c>
       <c r="J6" t="n">
-        <v>13.81258383878836</v>
+        <v>13.81258383878834</v>
       </c>
       <c r="K6" t="n">
-        <v>9.609394491532269</v>
+        <v>9.609394491532273</v>
       </c>
       <c r="L6" t="n">
-        <v>18.12145424010372</v>
+        <v>18.12145424010366</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.64680788441681</v>
+        <v>17.64680788441679</v>
       </c>
       <c r="C7" t="n">
-        <v>21.67621920360147</v>
+        <v>21.67621920360141</v>
       </c>
       <c r="D7" t="n">
-        <v>21.64414415008796</v>
+        <v>21.64414415008797</v>
       </c>
       <c r="E7" t="n">
-        <v>26.28905789050662</v>
+        <v>26.28905789050656</v>
       </c>
       <c r="F7" t="n">
-        <v>21.67621768050147</v>
+        <v>21.67621768050142</v>
       </c>
       <c r="G7" t="n">
-        <v>21.64918838576123</v>
+        <v>21.64918838576119</v>
       </c>
       <c r="H7" t="n">
-        <v>21.64414133975012</v>
+        <v>21.64414133975009</v>
       </c>
       <c r="I7" t="n">
-        <v>21.67621920360147</v>
+        <v>21.67621920360141</v>
       </c>
       <c r="J7" t="n">
-        <v>21.64414133975012</v>
+        <v>21.64414133975009</v>
       </c>
       <c r="K7" t="n">
-        <v>19.234105838898</v>
+        <v>19.23410583889796</v>
       </c>
       <c r="L7" t="n">
-        <v>21.64414133975012</v>
+        <v>21.64414133975009</v>
       </c>
     </row>
     <row r="8">
@@ -7091,19 +7091,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>171.7934853478498</v>
+        <v>171.7934853478497</v>
       </c>
       <c r="C8" t="n">
-        <v>173.4753101058409</v>
+        <v>173.4753101058408</v>
       </c>
       <c r="D8" t="n">
         <v>169.4039654778224</v>
       </c>
       <c r="E8" t="n">
-        <v>173.4753101058409</v>
+        <v>173.4753101058408</v>
       </c>
       <c r="F8" t="n">
-        <v>173.4753101058409</v>
+        <v>173.4753101058408</v>
       </c>
       <c r="G8" t="n">
         <v>168.8355537660291</v>
@@ -7112,16 +7112,16 @@
         <v>169.1402978879384</v>
       </c>
       <c r="I8" t="n">
-        <v>173.4753101058409</v>
+        <v>173.4753101058408</v>
       </c>
       <c r="J8" t="n">
         <v>165.595753026944</v>
       </c>
       <c r="K8" t="n">
-        <v>170.7721952078501</v>
+        <v>170.77219520785</v>
       </c>
       <c r="L8" t="n">
-        <v>170.740483137861</v>
+        <v>166.5428725732038</v>
       </c>
     </row>
     <row r="9">
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.3826488564067</v>
+        <v>169.3826488564068</v>
       </c>
       <c r="C9" t="n">
         <v>172.9002735605054</v>
@@ -7146,7 +7146,7 @@
         <v>172.9002735605054</v>
       </c>
       <c r="G9" t="n">
-        <v>168.1780890457875</v>
+        <v>168.1780890457874</v>
       </c>
       <c r="H9" t="n">
         <v>168.3049044215459</v>
@@ -7158,10 +7158,10 @@
         <v>166.8608852704675</v>
       </c>
       <c r="K9" t="n">
-        <v>168.9667613145539</v>
+        <v>168.9667613145538</v>
       </c>
       <c r="L9" t="n">
-        <v>167.2484199957098</v>
+        <v>167.2484199957099</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>209.2554450735241</v>
+        <v>209.2554450735239</v>
       </c>
       <c r="C2" t="n">
-        <v>347.1066907474911</v>
+        <v>347.1066907474914</v>
       </c>
       <c r="D2" t="n">
-        <v>419.7047469670048</v>
+        <v>419.7047469670043</v>
       </c>
       <c r="E2" t="n">
-        <v>347.1066907474911</v>
+        <v>347.1066907474914</v>
       </c>
       <c r="F2" t="n">
-        <v>347.1066907474911</v>
+        <v>347.1066907474914</v>
       </c>
       <c r="G2" t="n">
-        <v>412.2738247660015</v>
+        <v>412.2738247660007</v>
       </c>
       <c r="H2" t="n">
-        <v>818.814829767769</v>
+        <v>818.8148297677694</v>
       </c>
       <c r="I2" t="n">
-        <v>347.1066907474911</v>
+        <v>347.1066907474914</v>
       </c>
       <c r="J2" t="n">
-        <v>780.6101405224009</v>
+        <v>780.6101405223998</v>
       </c>
       <c r="K2" t="n">
-        <v>370.5363191480636</v>
+        <v>370.536319148063</v>
       </c>
       <c r="L2" t="n">
-        <v>782.1467505618538</v>
+        <v>219.5569386356866</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.116027450505943</v>
+        <v>6.116027450505908</v>
       </c>
       <c r="C3" t="n">
-        <v>5.967899912943421</v>
+        <v>5.967899912943417</v>
       </c>
       <c r="D3" t="n">
-        <v>6.116027450505943</v>
+        <v>6.116027450505908</v>
       </c>
       <c r="E3" t="n">
-        <v>6.07109475310739</v>
+        <v>6.071094753107386</v>
       </c>
       <c r="F3" t="n">
-        <v>6.07109475310739</v>
+        <v>6.071094753107364</v>
       </c>
       <c r="G3" t="n">
         <v>6.118710984388352</v>
       </c>
       <c r="H3" t="n">
-        <v>6.116027450505943</v>
+        <v>6.116027450505908</v>
       </c>
       <c r="I3" t="n">
-        <v>6.133303606429272</v>
+        <v>6.13330360642926</v>
       </c>
       <c r="J3" t="n">
-        <v>6.116027450505943</v>
+        <v>6.116027450505908</v>
       </c>
       <c r="K3" t="n">
-        <v>6.116027450505943</v>
+        <v>6.116027450505908</v>
       </c>
       <c r="L3" t="n">
-        <v>6.116027450505943</v>
+        <v>6.116027450505908</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685.180914636004</v>
+        <v>685.1809146360032</v>
       </c>
       <c r="C4" t="n">
-        <v>685.1217623073815</v>
+        <v>685.1217623073821</v>
       </c>
       <c r="D4" t="n">
         <v>685.2787644461835</v>
       </c>
       <c r="E4" t="n">
-        <v>617.6323547644757</v>
+        <v>617.6323547644744</v>
       </c>
       <c r="F4" t="n">
-        <v>685.23915445071</v>
+        <v>685.2391544507103</v>
       </c>
       <c r="G4" t="n">
-        <v>820.5276561826007</v>
+        <v>820.5276561826005</v>
       </c>
       <c r="H4" t="n">
-        <v>821.2870037832761</v>
+        <v>821.2870037832765</v>
       </c>
       <c r="I4" t="n">
-        <v>820.542248804642</v>
+        <v>820.5422488046421</v>
       </c>
       <c r="J4" t="n">
-        <v>820.912905590616</v>
+        <v>820.9129055906166</v>
       </c>
       <c r="K4" t="n">
         <v>685.1930306767127</v>
       </c>
       <c r="L4" t="n">
-        <v>685.3421533395093</v>
+        <v>685.3421533395087</v>
       </c>
     </row>
     <row r="5">
@@ -7370,25 +7370,25 @@
         <v>12.6526811708047</v>
       </c>
       <c r="C5" t="n">
-        <v>12.66995732672803</v>
+        <v>12.66995732672801</v>
       </c>
       <c r="D5" t="n">
-        <v>12.65262098206368</v>
+        <v>12.65262098206365</v>
       </c>
       <c r="E5" t="n">
-        <v>12.66356419467177</v>
+        <v>12.66356419467174</v>
       </c>
       <c r="F5" t="n">
-        <v>12.66356419467177</v>
+        <v>12.66356419467174</v>
       </c>
       <c r="G5" t="n">
-        <v>12.65536470468711</v>
+        <v>12.65536470468705</v>
       </c>
       <c r="H5" t="n">
         <v>12.6526811708047</v>
       </c>
       <c r="I5" t="n">
-        <v>12.66995732672803</v>
+        <v>12.66995732672801</v>
       </c>
       <c r="J5" t="n">
         <v>12.6526811708047</v>
@@ -7410,34 +7410,34 @@
         <v>15.21258570635869</v>
       </c>
       <c r="C6" t="n">
-        <v>22.10622366091033</v>
+        <v>22.10622366080017</v>
       </c>
       <c r="D6" t="n">
-        <v>23.52055307477728</v>
+        <v>23.52055307477703</v>
       </c>
       <c r="E6" t="n">
-        <v>20.22485615331576</v>
+        <v>20.22485615331568</v>
       </c>
       <c r="F6" t="n">
-        <v>15.44420489967665</v>
+        <v>15.44420489967659</v>
       </c>
       <c r="G6" t="n">
-        <v>22.0963911542317</v>
+        <v>22.09639115423155</v>
       </c>
       <c r="H6" t="n">
-        <v>22.09370762035471</v>
+        <v>22.09370762035461</v>
       </c>
       <c r="I6" t="n">
-        <v>22.11098377627262</v>
+        <v>22.11098377627251</v>
       </c>
       <c r="J6" t="n">
-        <v>22.09505994788211</v>
+        <v>22.09505994788205</v>
       </c>
       <c r="K6" t="n">
-        <v>15.08476533490729</v>
+        <v>15.08476533490724</v>
       </c>
       <c r="L6" t="n">
-        <v>29.281614840168</v>
+        <v>29.28161484016784</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.879681585698</v>
+        <v>30.87968158569789</v>
       </c>
       <c r="C7" t="n">
-        <v>38.22480409958558</v>
+        <v>38.22480409958549</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20752927872336</v>
+        <v>38.20752927872326</v>
       </c>
       <c r="E7" t="n">
-        <v>46.68097194443095</v>
+        <v>46.68097194443088</v>
       </c>
       <c r="F7" t="n">
-        <v>38.22479395264804</v>
+        <v>38.22479395264797</v>
       </c>
       <c r="G7" t="n">
-        <v>38.21021147754463</v>
+        <v>38.21021147754443</v>
       </c>
       <c r="H7" t="n">
-        <v>38.20752794366225</v>
+        <v>38.20752794366214</v>
       </c>
       <c r="I7" t="n">
-        <v>38.22480409958558</v>
+        <v>38.22480409958549</v>
       </c>
       <c r="J7" t="n">
-        <v>38.20752794366225</v>
+        <v>38.20752794366214</v>
       </c>
       <c r="K7" t="n">
-        <v>33.96174554670612</v>
+        <v>33.96174554670601</v>
       </c>
       <c r="L7" t="n">
-        <v>38.20752794366225</v>
+        <v>38.20752794366214</v>
       </c>
     </row>
     <row r="8">
@@ -7487,34 +7487,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>169.4649912777723</v>
+        <v>169.4649912777722</v>
       </c>
       <c r="C8" t="n">
-        <v>170.9666710066142</v>
+        <v>170.9666710066144</v>
       </c>
       <c r="D8" t="n">
-        <v>164.2944725063375</v>
+        <v>164.2944725063373</v>
       </c>
       <c r="E8" t="n">
-        <v>170.9666710066142</v>
+        <v>170.9666710066144</v>
       </c>
       <c r="F8" t="n">
-        <v>170.9666710066142</v>
+        <v>170.9666710066144</v>
       </c>
       <c r="G8" t="n">
-        <v>164.8506391760572</v>
+        <v>164.8506391760573</v>
       </c>
       <c r="H8" t="n">
-        <v>156.2218583229033</v>
+        <v>156.2218583229034</v>
       </c>
       <c r="I8" t="n">
-        <v>170.9666710066142</v>
+        <v>170.9666710066144</v>
       </c>
       <c r="J8" t="n">
         <v>157.5164491198476</v>
       </c>
       <c r="K8" t="n">
-        <v>165.6770475304354</v>
+        <v>165.6770475304355</v>
       </c>
       <c r="L8" t="n">
         <v>159.0288026519805</v>
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169.6495660846568</v>
+        <v>169.6495660846567</v>
       </c>
       <c r="C9" t="n">
-        <v>173.1311875816268</v>
+        <v>173.1311875816269</v>
       </c>
       <c r="D9" t="n">
-        <v>167.5439128712753</v>
+        <v>167.5439128712752</v>
       </c>
       <c r="E9" t="n">
-        <v>173.1311875816268</v>
+        <v>173.1311875816269</v>
       </c>
       <c r="F9" t="n">
-        <v>173.1311875816268</v>
+        <v>173.1311875816269</v>
       </c>
       <c r="G9" t="n">
-        <v>167.7653934767317</v>
+        <v>167.7653934767318</v>
       </c>
       <c r="H9" t="n">
         <v>164.2725779881565</v>
       </c>
       <c r="I9" t="n">
-        <v>173.1311875816268</v>
+        <v>173.1311875816269</v>
       </c>
       <c r="J9" t="n">
         <v>164.7894144780929</v>
       </c>
       <c r="K9" t="n">
-        <v>168.1072183133282</v>
+        <v>168.1072183133283</v>
       </c>
       <c r="L9" t="n">
-        <v>165.4105608834736</v>
+        <v>169.8407352326215</v>
       </c>
     </row>
   </sheetData>
@@ -7646,34 +7646,34 @@
         <v>29.70289843105977</v>
       </c>
       <c r="C2" t="n">
-        <v>210.4159433237724</v>
+        <v>210.4159433237725</v>
       </c>
       <c r="D2" t="n">
-        <v>328.9336053313745</v>
+        <v>328.9336053313743</v>
       </c>
       <c r="E2" t="n">
-        <v>210.4159433237724</v>
+        <v>210.4159433237725</v>
       </c>
       <c r="F2" t="n">
-        <v>210.4159433237724</v>
+        <v>210.4159433237725</v>
       </c>
       <c r="G2" t="n">
-        <v>261.5706787711161</v>
+        <v>261.5706787711156</v>
       </c>
       <c r="H2" t="n">
-        <v>258.2960407722234</v>
+        <v>258.2960407722238</v>
       </c>
       <c r="I2" t="n">
-        <v>210.4159433237724</v>
+        <v>210.4159433237725</v>
       </c>
       <c r="J2" t="n">
-        <v>552.0751121092048</v>
+        <v>552.0751121092056</v>
       </c>
       <c r="K2" t="n">
-        <v>148.3853257188756</v>
+        <v>148.3853257188758</v>
       </c>
       <c r="L2" t="n">
-        <v>89.14113660583185</v>
+        <v>557.6878014776809</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.970664711016122</v>
+        <v>4.970664711016147</v>
       </c>
       <c r="C3" t="n">
-        <v>4.789416540477657</v>
+        <v>4.789416540477665</v>
       </c>
       <c r="D3" t="n">
-        <v>4.970664711016122</v>
+        <v>4.970664711016147</v>
       </c>
       <c r="E3" t="n">
-        <v>4.872284262234992</v>
+        <v>4.872284262234994</v>
       </c>
       <c r="F3" t="n">
-        <v>4.872284262234991</v>
+        <v>4.872284262234994</v>
       </c>
       <c r="G3" t="n">
-        <v>4.973513692045545</v>
+        <v>4.973513692045548</v>
       </c>
       <c r="H3" t="n">
-        <v>4.970664711016122</v>
+        <v>4.970664711016147</v>
       </c>
       <c r="I3" t="n">
         <v>4.988877766756772</v>
       </c>
       <c r="J3" t="n">
-        <v>4.970664711016122</v>
+        <v>4.970664711016147</v>
       </c>
       <c r="K3" t="n">
-        <v>4.970664711016122</v>
+        <v>4.970664711016147</v>
       </c>
       <c r="L3" t="n">
-        <v>4.970664711016122</v>
+        <v>4.970664711016147</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>762.3455331340629</v>
+        <v>762.3455331340626</v>
       </c>
       <c r="C4" t="n">
         <v>637.0511875181369</v>
       </c>
       <c r="D4" t="n">
-        <v>637.3393319232659</v>
+        <v>637.3393315469383</v>
       </c>
       <c r="E4" t="n">
-        <v>574.2085370840417</v>
+        <v>574.2085370840422</v>
       </c>
       <c r="F4" t="n">
-        <v>637.1494377171093</v>
+        <v>637.1494377171086</v>
       </c>
       <c r="G4" t="n">
-        <v>637.1096261406681</v>
+        <v>762.3483821150926</v>
       </c>
       <c r="H4" t="n">
-        <v>762.9530973604982</v>
+        <v>762.9530973604981</v>
       </c>
       <c r="I4" t="n">
-        <v>762.3637461898034</v>
+        <v>762.3637461898031</v>
       </c>
       <c r="J4" t="n">
-        <v>669.457483507405</v>
+        <v>669.4574835074056</v>
       </c>
       <c r="K4" t="n">
-        <v>636.9583517212758</v>
+        <v>636.9583517212761</v>
       </c>
       <c r="L4" t="n">
-        <v>637.2441024631651</v>
+        <v>637.2441024631647</v>
       </c>
     </row>
     <row r="5">
@@ -7778,7 +7778,7 @@
         <v>10.25223910823254</v>
       </c>
       <c r="G5" t="n">
-        <v>10.25894916002601</v>
+        <v>10.258949160026</v>
       </c>
       <c r="H5" t="n">
         <v>10.25610017899659</v>
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.99576467836347</v>
+        <v>11.99576467836348</v>
       </c>
       <c r="C6" t="n">
-        <v>17.27491319868625</v>
+        <v>17.27491319868624</v>
       </c>
       <c r="D6" t="n">
-        <v>18.37186967046584</v>
+        <v>18.37186967046586</v>
       </c>
       <c r="E6" t="n">
-        <v>15.83278881392586</v>
+        <v>15.83278881392584</v>
       </c>
       <c r="F6" t="n">
         <v>12.16822662451316</v>
       </c>
       <c r="G6" t="n">
-        <v>17.27965941237147</v>
+        <v>17.27965941237142</v>
       </c>
       <c r="H6" t="n">
-        <v>17.27681043135023</v>
+        <v>17.27681043135021</v>
       </c>
       <c r="I6" t="n">
-        <v>17.2950234870827</v>
+        <v>17.29502348708267</v>
       </c>
       <c r="J6" t="n">
-        <v>17.27784830066388</v>
+        <v>17.27784830066386</v>
       </c>
       <c r="K6" t="n">
-        <v>11.89766654286724</v>
+        <v>11.89766654286723</v>
       </c>
       <c r="L6" t="n">
-        <v>22.7933043072153</v>
+        <v>22.79330430721528</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.80618643562444</v>
+        <v>22.80618643562445</v>
       </c>
       <c r="C7" t="n">
-        <v>28.11266539537583</v>
+        <v>28.11266539537586</v>
       </c>
       <c r="D7" t="n">
-        <v>28.09445740346669</v>
+        <v>28.09445740346672</v>
       </c>
       <c r="E7" t="n">
         <v>34.21521295458713</v>
       </c>
       <c r="F7" t="n">
-        <v>28.11266240156456</v>
+        <v>28.11266240156459</v>
       </c>
       <c r="G7" t="n">
         <v>28.09730132066458</v>
       </c>
       <c r="H7" t="n">
-        <v>28.09445233963516</v>
+        <v>28.09445233963518</v>
       </c>
       <c r="I7" t="n">
-        <v>28.11266539537583</v>
+        <v>28.11266539537586</v>
       </c>
       <c r="J7" t="n">
-        <v>28.09445233963516</v>
+        <v>28.09445233963518</v>
       </c>
       <c r="K7" t="n">
-        <v>21.43558030192423</v>
+        <v>25.03041243605633</v>
       </c>
       <c r="L7" t="n">
-        <v>28.09445233963516</v>
+        <v>28.09445233963518</v>
       </c>
     </row>
     <row r="8">
@@ -7886,25 +7886,25 @@
         <v>172.6260146688737</v>
       </c>
       <c r="C8" t="n">
-        <v>172.7003326788732</v>
+        <v>172.7003326788731</v>
       </c>
       <c r="D8" t="n">
         <v>164.4412651735375</v>
       </c>
       <c r="E8" t="n">
-        <v>172.7003326788732</v>
+        <v>172.7003326788731</v>
       </c>
       <c r="F8" t="n">
-        <v>172.7003326788732</v>
+        <v>172.7003326788731</v>
       </c>
       <c r="G8" t="n">
-        <v>166.6208664003756</v>
+        <v>166.6208664003757</v>
       </c>
       <c r="H8" t="n">
         <v>167.0851416156287</v>
       </c>
       <c r="I8" t="n">
-        <v>172.7003326788732</v>
+        <v>172.7003326788731</v>
       </c>
       <c r="J8" t="n">
         <v>160.5122489163815</v>
@@ -7923,31 +7923,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170.3099916168246</v>
+        <v>170.3099916168245</v>
       </c>
       <c r="C9" t="n">
-        <v>173.1793492051212</v>
+        <v>173.179349205121</v>
       </c>
       <c r="D9" t="n">
         <v>166.9766288540941</v>
       </c>
       <c r="E9" t="n">
-        <v>173.1793492051212</v>
+        <v>173.179349205121</v>
       </c>
       <c r="F9" t="n">
-        <v>173.1793492051212</v>
+        <v>173.179349205121</v>
       </c>
       <c r="G9" t="n">
         <v>167.8587543615066</v>
       </c>
       <c r="H9" t="n">
-        <v>168.058966699766</v>
+        <v>168.0589666997661</v>
       </c>
       <c r="I9" t="n">
-        <v>173.1793492051212</v>
+        <v>173.179349205121</v>
       </c>
       <c r="J9" t="n">
-        <v>165.3809908320636</v>
+        <v>165.3809908320638</v>
       </c>
       <c r="K9" t="n">
         <v>169.0032682454899</v>

--- a/Results/Hydrogen/hydrogen resource use fossils results.xlsx
+++ b/Results/Hydrogen/hydrogen resource use fossils results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>410.3914677474598</v>
+        <v>172.7427504075003</v>
       </c>
       <c r="C2" t="n">
-        <v>433.5097743491357</v>
+        <v>177.6685180785343</v>
       </c>
       <c r="D2" t="n">
-        <v>516.9436849857872</v>
+        <v>172.8395578923377</v>
       </c>
       <c r="E2" t="n">
-        <v>433.5097743491357</v>
+        <v>177.6685180785343</v>
       </c>
       <c r="F2" t="n">
-        <v>433.5097743491357</v>
+        <v>177.6685180785343</v>
       </c>
       <c r="G2" t="n">
-        <v>540.2280851423956</v>
+        <v>172.8359181038174</v>
       </c>
       <c r="H2" t="n">
-        <v>1077.656843516058</v>
+        <v>173.3070857450437</v>
       </c>
       <c r="I2" t="n">
-        <v>433.5097743491357</v>
+        <v>177.6685180785343</v>
       </c>
       <c r="J2" t="n">
-        <v>833.635208960349</v>
+        <v>173.1242804179911</v>
       </c>
       <c r="K2" t="n">
-        <v>514.810825361695</v>
+        <v>172.8377078332214</v>
       </c>
       <c r="L2" t="n">
-        <v>953.8447060460213</v>
+        <v>172.5856744350296</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.881779997743494</v>
+        <v>175.0205123417236</v>
       </c>
       <c r="C3" t="n">
-        <v>6.720405657890902</v>
+        <v>180.0042635072955</v>
       </c>
       <c r="D3" t="n">
-        <v>6.881779997743494</v>
+        <v>175.0205123417236</v>
       </c>
       <c r="E3" t="n">
-        <v>6.840461302603813</v>
+        <v>180.0042635072955</v>
       </c>
       <c r="F3" t="n">
-        <v>6.840461302603813</v>
+        <v>180.0042635072955</v>
       </c>
       <c r="G3" t="n">
-        <v>6.883312304235134</v>
+        <v>175.0034220152444</v>
       </c>
       <c r="H3" t="n">
-        <v>6.881779997743494</v>
+        <v>175.0205123417236</v>
       </c>
       <c r="I3" t="n">
-        <v>6.891784265264764</v>
+        <v>180.0042635072955</v>
       </c>
       <c r="J3" t="n">
-        <v>6.881779997743494</v>
+        <v>175.0205123417236</v>
       </c>
       <c r="K3" t="n">
-        <v>6.881779997743494</v>
+        <v>175.0205123417236</v>
       </c>
       <c r="L3" t="n">
-        <v>6.881779997743494</v>
+        <v>175.0205123417236</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>732.8382158274557</v>
+        <v>410.3914677474606</v>
       </c>
       <c r="C4" t="n">
-        <v>732.7163324346777</v>
+        <v>433.5097743491368</v>
       </c>
       <c r="D4" t="n">
-        <v>732.9204592843855</v>
+        <v>516.9436849857874</v>
       </c>
       <c r="E4" t="n">
-        <v>660.5709690455781</v>
+        <v>433.5097743491368</v>
       </c>
       <c r="F4" t="n">
-        <v>732.8904934557913</v>
+        <v>433.5097743491368</v>
       </c>
       <c r="G4" t="n">
-        <v>878.174919856926</v>
+        <v>540.228085142395</v>
       </c>
       <c r="H4" t="n">
-        <v>878.9973925037941</v>
+        <v>1077.656843516058</v>
       </c>
       <c r="I4" t="n">
-        <v>878.1833918179558</v>
+        <v>433.5097743491368</v>
       </c>
       <c r="J4" t="n">
-        <v>878.5720291885591</v>
+        <v>833.6352089603487</v>
       </c>
       <c r="K4" t="n">
-        <v>732.9155438128971</v>
+        <v>514.8108253616954</v>
       </c>
       <c r="L4" t="n">
-        <v>733.0272241740076</v>
+        <v>953.8447060460232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.6390935729617</v>
+        <v>6.881779997743496</v>
       </c>
       <c r="C5" t="n">
-        <v>14.64909784048298</v>
+        <v>6.720405657890911</v>
       </c>
       <c r="D5" t="n">
-        <v>14.63900801096118</v>
+        <v>6.881779997743496</v>
       </c>
       <c r="E5" t="n">
-        <v>14.65167372259578</v>
+        <v>6.840461302603813</v>
       </c>
       <c r="F5" t="n">
-        <v>14.65167372259578</v>
+        <v>6.84046130260381</v>
       </c>
       <c r="G5" t="n">
-        <v>14.64062587945334</v>
+        <v>6.883312304235139</v>
       </c>
       <c r="H5" t="n">
-        <v>14.6390935729617</v>
+        <v>6.881779997743496</v>
       </c>
       <c r="I5" t="n">
-        <v>14.64909784048298</v>
+        <v>6.891784265264763</v>
       </c>
       <c r="J5" t="n">
-        <v>14.6390935729617</v>
+        <v>6.881779997743496</v>
       </c>
       <c r="K5" t="n">
-        <v>14.6390935729617</v>
+        <v>6.881779997743496</v>
       </c>
       <c r="L5" t="n">
-        <v>14.6390935729617</v>
+        <v>6.881779997743496</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.01000425062151</v>
+        <v>732.8382158274568</v>
       </c>
       <c r="C6" t="n">
-        <v>26.45559065448522</v>
+        <v>732.7163324346774</v>
       </c>
       <c r="D6" t="n">
-        <v>28.18974834266966</v>
+        <v>732.9204592843857</v>
       </c>
       <c r="E6" t="n">
-        <v>24.14927779614808</v>
+        <v>660.5709690455783</v>
       </c>
       <c r="F6" t="n">
-        <v>18.28885957448013</v>
+        <v>732.8904934557925</v>
       </c>
       <c r="G6" t="n">
-        <v>26.44296834345941</v>
+        <v>878.1749198569264</v>
       </c>
       <c r="H6" t="n">
-        <v>26.44143603697066</v>
+        <v>878.9973925037945</v>
       </c>
       <c r="I6" t="n">
-        <v>26.45144030448903</v>
+        <v>878.1833918179551</v>
       </c>
       <c r="J6" t="n">
-        <v>26.44309304288853</v>
+        <v>878.5720291885592</v>
       </c>
       <c r="K6" t="n">
-        <v>17.8533860775387</v>
+        <v>732.9155438128976</v>
       </c>
       <c r="L6" t="n">
-        <v>35.248771551438</v>
+        <v>733.0272241740076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39.08555736155551</v>
+        <v>14.63909357296171</v>
       </c>
       <c r="C7" t="n">
-        <v>48.59392129914492</v>
+        <v>14.64909784048297</v>
       </c>
       <c r="D7" t="n">
-        <v>48.58391924583056</v>
+        <v>14.63900801096118</v>
       </c>
       <c r="E7" t="n">
-        <v>59.55481331937904</v>
+        <v>14.65167372259579</v>
       </c>
       <c r="F7" t="n">
-        <v>48.59390878485372</v>
+        <v>14.65167372259579</v>
       </c>
       <c r="G7" t="n">
-        <v>48.5854493381153</v>
+        <v>14.64062587945335</v>
       </c>
       <c r="H7" t="n">
-        <v>48.58391703162366</v>
+        <v>14.63909357296171</v>
       </c>
       <c r="I7" t="n">
-        <v>48.59392129914492</v>
+        <v>14.64909784048297</v>
       </c>
       <c r="J7" t="n">
-        <v>48.58391703162366</v>
+        <v>14.63909357296171</v>
       </c>
       <c r="K7" t="n">
-        <v>36.62378618192854</v>
+        <v>14.63909357296171</v>
       </c>
       <c r="L7" t="n">
-        <v>48.58391703162366</v>
+        <v>14.63909357296171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>166.0979387017249</v>
+        <v>18.01000425062151</v>
       </c>
       <c r="C8" t="n">
-        <v>170.6597270395064</v>
+        <v>26.45559065448525</v>
       </c>
       <c r="D8" t="n">
-        <v>164.0749273698661</v>
+        <v>28.18974834266969</v>
       </c>
       <c r="E8" t="n">
-        <v>170.6597270395064</v>
+        <v>24.14927779614808</v>
       </c>
       <c r="F8" t="n">
-        <v>170.6597270395064</v>
+        <v>18.28885957448011</v>
       </c>
       <c r="G8" t="n">
-        <v>163.8250903738455</v>
+        <v>26.44296834345943</v>
       </c>
       <c r="H8" t="n">
-        <v>154.6666202222293</v>
+        <v>26.44143603697069</v>
       </c>
       <c r="I8" t="n">
-        <v>170.6597270395064</v>
+        <v>26.45144030448903</v>
       </c>
       <c r="J8" t="n">
-        <v>158.2352607227446</v>
+        <v>26.44309304288855</v>
       </c>
       <c r="K8" t="n">
-        <v>164.1197071452853</v>
+        <v>17.85338607753869</v>
       </c>
       <c r="L8" t="n">
-        <v>169.4770512910056</v>
+        <v>35.24877155143803</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>39.08555736155552</v>
+      </c>
+      <c r="C9" t="n">
+        <v>48.59392129914495</v>
+      </c>
+      <c r="D9" t="n">
+        <v>48.58391924583056</v>
+      </c>
+      <c r="E9" t="n">
+        <v>59.55481331937905</v>
+      </c>
+      <c r="F9" t="n">
+        <v>48.59390878485374</v>
+      </c>
+      <c r="G9" t="n">
+        <v>48.58544933811531</v>
+      </c>
+      <c r="H9" t="n">
+        <v>48.58391703162369</v>
+      </c>
+      <c r="I9" t="n">
+        <v>48.59392129914495</v>
+      </c>
+      <c r="J9" t="n">
+        <v>48.58391703162369</v>
+      </c>
+      <c r="K9" t="n">
+        <v>36.62378618192857</v>
+      </c>
+      <c r="L9" t="n">
+        <v>48.58391703162369</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>166.0979387017251</v>
+      </c>
+      <c r="C10" t="n">
+        <v>170.6597270395065</v>
+      </c>
+      <c r="D10" t="n">
+        <v>164.0749273698662</v>
+      </c>
+      <c r="E10" t="n">
+        <v>170.6597270395065</v>
+      </c>
+      <c r="F10" t="n">
+        <v>170.6597270395065</v>
+      </c>
+      <c r="G10" t="n">
+        <v>163.8250903738456</v>
+      </c>
+      <c r="H10" t="n">
+        <v>154.6666202222294</v>
+      </c>
+      <c r="I10" t="n">
+        <v>170.6597270395065</v>
+      </c>
+      <c r="J10" t="n">
+        <v>158.2352607227447</v>
+      </c>
+      <c r="K10" t="n">
+        <v>164.1197071452853</v>
+      </c>
+      <c r="L10" t="n">
+        <v>169.4770512910058</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>168.6829509667458</v>
-      </c>
-      <c r="C9" t="n">
-        <v>173.4167242064195</v>
-      </c>
-      <c r="D9" t="n">
-        <v>167.8592818486328</v>
-      </c>
-      <c r="E9" t="n">
-        <v>173.4167242064195</v>
-      </c>
-      <c r="F9" t="n">
-        <v>173.4167242064195</v>
-      </c>
-      <c r="G9" t="n">
-        <v>167.7497415837515</v>
-      </c>
-      <c r="H9" t="n">
-        <v>164.045999966668</v>
-      </c>
-      <c r="I9" t="n">
-        <v>173.4167242064195</v>
-      </c>
-      <c r="J9" t="n">
-        <v>165.4869374399329</v>
-      </c>
-      <c r="K9" t="n">
-        <v>167.8778067300369</v>
-      </c>
-      <c r="L9" t="n">
-        <v>165.2396359446417</v>
+      <c r="B11" t="n">
+        <v>168.6829509667459</v>
+      </c>
+      <c r="C11" t="n">
+        <v>173.4167242064196</v>
+      </c>
+      <c r="D11" t="n">
+        <v>167.8592818486331</v>
+      </c>
+      <c r="E11" t="n">
+        <v>173.4167242064196</v>
+      </c>
+      <c r="F11" t="n">
+        <v>173.4167242064196</v>
+      </c>
+      <c r="G11" t="n">
+        <v>167.7497415837517</v>
+      </c>
+      <c r="H11" t="n">
+        <v>164.0459999666682</v>
+      </c>
+      <c r="I11" t="n">
+        <v>173.4167242064196</v>
+      </c>
+      <c r="J11" t="n">
+        <v>165.486937439933</v>
+      </c>
+      <c r="K11" t="n">
+        <v>167.877806730037</v>
+      </c>
+      <c r="L11" t="n">
+        <v>165.2396359446418</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.48809248194743</v>
+        <v>169.9315525939236</v>
       </c>
       <c r="C2" t="n">
-        <v>122.4481448371879</v>
+        <v>174.7902680805899</v>
       </c>
       <c r="D2" t="n">
-        <v>192.5479933755528</v>
+        <v>170.1545030945346</v>
       </c>
       <c r="E2" t="n">
-        <v>122.4481448371879</v>
+        <v>174.7902680805899</v>
       </c>
       <c r="F2" t="n">
-        <v>122.4481448371879</v>
+        <v>174.7902680805899</v>
       </c>
       <c r="G2" t="n">
-        <v>181.9048108973664</v>
+        <v>170.1177842286455</v>
       </c>
       <c r="H2" t="n">
-        <v>168.9616817326349</v>
+        <v>170.0998011074491</v>
       </c>
       <c r="I2" t="n">
-        <v>122.4481448371879</v>
+        <v>174.7902680805899</v>
       </c>
       <c r="J2" t="n">
-        <v>416.1249985428269</v>
+        <v>170.3793064239752</v>
       </c>
       <c r="K2" t="n">
-        <v>91.66042070128549</v>
+        <v>170.028575274452</v>
       </c>
       <c r="L2" t="n">
-        <v>187.9757542893301</v>
+        <v>170.0208026907763</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.280236021455945</v>
+        <v>172.5908454601613</v>
       </c>
       <c r="C3" t="n">
-        <v>4.029122088491797</v>
+        <v>177.3941199563681</v>
       </c>
       <c r="D3" t="n">
-        <v>4.280236021455945</v>
+        <v>172.5908454601613</v>
       </c>
       <c r="E3" t="n">
-        <v>4.108068726987812</v>
+        <v>177.3941199563681</v>
       </c>
       <c r="F3" t="n">
-        <v>4.10806872698781</v>
+        <v>177.3941199563681</v>
       </c>
       <c r="G3" t="n">
-        <v>4.282695655925195</v>
+        <v>172.5770741090441</v>
       </c>
       <c r="H3" t="n">
-        <v>4.280236021455945</v>
+        <v>172.5908454601613</v>
       </c>
       <c r="I3" t="n">
-        <v>4.295895729931634</v>
+        <v>177.3941199563681</v>
       </c>
       <c r="J3" t="n">
-        <v>4.280236021455945</v>
+        <v>172.5908454601613</v>
       </c>
       <c r="K3" t="n">
-        <v>4.280236021455945</v>
+        <v>172.5908454601613</v>
       </c>
       <c r="L3" t="n">
-        <v>4.280236021455945</v>
+        <v>172.5908454601613</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.9478284328961</v>
+        <v>18.48809248194736</v>
       </c>
       <c r="C4" t="n">
-        <v>635.8541149848396</v>
+        <v>122.448144837188</v>
       </c>
       <c r="D4" t="n">
-        <v>760.7401889354409</v>
+        <v>192.5479933755528</v>
       </c>
       <c r="E4" t="n">
-        <v>573.044700724019</v>
+        <v>122.448144837188</v>
       </c>
       <c r="F4" t="n">
-        <v>635.9747000441067</v>
+        <v>122.448144837188</v>
       </c>
       <c r="G4" t="n">
-        <v>760.5660287069026</v>
+        <v>181.9048108973666</v>
       </c>
       <c r="H4" t="n">
-        <v>761.1528852937508</v>
+        <v>168.9616817326349</v>
       </c>
       <c r="I4" t="n">
-        <v>635.9634881413716</v>
+        <v>122.448144837188</v>
       </c>
       <c r="J4" t="n">
-        <v>668.2509495167747</v>
+        <v>416.1249985428259</v>
       </c>
       <c r="K4" t="n">
-        <v>635.8404015101705</v>
+        <v>91.66042070128537</v>
       </c>
       <c r="L4" t="n">
-        <v>635.998839395935</v>
+        <v>187.9757542893302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.100792920163075</v>
+        <v>4.280236021455959</v>
       </c>
       <c r="C5" t="n">
-        <v>9.116452628638655</v>
+        <v>4.0291220884918</v>
       </c>
       <c r="D5" t="n">
-        <v>9.100788468893636</v>
+        <v>4.280236021455959</v>
       </c>
       <c r="E5" t="n">
-        <v>9.076834994310406</v>
+        <v>4.10806872698781</v>
       </c>
       <c r="F5" t="n">
-        <v>9.076834994310406</v>
+        <v>4.10806872698781</v>
       </c>
       <c r="G5" t="n">
-        <v>9.10325255463227</v>
+        <v>4.282695655925235</v>
       </c>
       <c r="H5" t="n">
-        <v>9.100792920163075</v>
+        <v>4.280236021455959</v>
       </c>
       <c r="I5" t="n">
-        <v>9.116452628638655</v>
+        <v>4.295895729931637</v>
       </c>
       <c r="J5" t="n">
-        <v>9.100792920163075</v>
+        <v>4.280236021455959</v>
       </c>
       <c r="K5" t="n">
-        <v>9.100792920163075</v>
+        <v>4.280236021455959</v>
       </c>
       <c r="L5" t="n">
-        <v>9.100792920163075</v>
+        <v>4.280236021455959</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.42350965867975</v>
+        <v>635.9478284328957</v>
       </c>
       <c r="C6" t="n">
-        <v>15.00665389486645</v>
+        <v>635.8541149848394</v>
       </c>
       <c r="D6" t="n">
-        <v>15.98282373314828</v>
+        <v>760.740188935441</v>
       </c>
       <c r="E6" t="n">
-        <v>13.75135439748236</v>
+        <v>573.0447007240199</v>
       </c>
       <c r="F6" t="n">
-        <v>10.5614948012593</v>
+        <v>635.9747000441063</v>
       </c>
       <c r="G6" t="n">
-        <v>15.0305032553108</v>
+        <v>760.5660287069024</v>
       </c>
       <c r="H6" t="n">
-        <v>15.02804362085089</v>
+        <v>761.1528852937508</v>
       </c>
       <c r="I6" t="n">
-        <v>15.04370332931714</v>
+        <v>635.9634881413716</v>
       </c>
       <c r="J6" t="n">
-        <v>15.02894853719643</v>
+        <v>668.250949516774</v>
       </c>
       <c r="K6" t="n">
-        <v>10.33797807692752</v>
+        <v>635.8404015101704</v>
       </c>
       <c r="L6" t="n">
-        <v>19.83786436313629</v>
+        <v>635.998839395935</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.67388379812842</v>
+        <v>9.100792920162972</v>
       </c>
       <c r="C7" t="n">
-        <v>22.97536181629374</v>
+        <v>9.116452628638665</v>
       </c>
       <c r="D7" t="n">
-        <v>22.95970643722458</v>
+        <v>9.100788468893519</v>
       </c>
       <c r="E7" t="n">
-        <v>27.92110668527064</v>
+        <v>9.076834994310405</v>
       </c>
       <c r="F7" t="n">
-        <v>22.97535981623806</v>
+        <v>9.076834994310405</v>
       </c>
       <c r="G7" t="n">
-        <v>22.96216174228742</v>
+        <v>9.103252554632286</v>
       </c>
       <c r="H7" t="n">
-        <v>22.95970210781816</v>
+        <v>9.100792920162972</v>
       </c>
       <c r="I7" t="n">
-        <v>22.97536181629374</v>
+        <v>9.116452628638665</v>
       </c>
       <c r="J7" t="n">
-        <v>22.95970210781816</v>
+        <v>9.100792920162972</v>
       </c>
       <c r="K7" t="n">
-        <v>20.47648396840809</v>
+        <v>9.100792920162972</v>
       </c>
       <c r="L7" t="n">
-        <v>22.95970210781816</v>
+        <v>9.100792920162972</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.235951577876</v>
+        <v>10.42350965867985</v>
       </c>
       <c r="C8" t="n">
-        <v>174.292336715524</v>
+        <v>15.00665389486648</v>
       </c>
       <c r="D8" t="n">
-        <v>167.5656678879732</v>
+        <v>15.98282373314824</v>
       </c>
       <c r="E8" t="n">
-        <v>174.292336715524</v>
+        <v>13.75135439748238</v>
       </c>
       <c r="F8" t="n">
-        <v>174.292336715524</v>
+        <v>10.56149480125932</v>
       </c>
       <c r="G8" t="n">
-        <v>168.0524757064848</v>
+        <v>15.03050325531073</v>
       </c>
       <c r="H8" t="n">
-        <v>168.7837654211997</v>
+        <v>15.02804362085079</v>
       </c>
       <c r="I8" t="n">
-        <v>174.292336715524</v>
+        <v>15.04370332931715</v>
       </c>
       <c r="J8" t="n">
-        <v>162.9282439966443</v>
+        <v>15.0289485371964</v>
       </c>
       <c r="K8" t="n">
-        <v>170.2049880577374</v>
+        <v>10.33797807692738</v>
       </c>
       <c r="L8" t="n">
-        <v>168.6190307920871</v>
+        <v>19.8378643631363</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18.6738837981284</v>
+      </c>
+      <c r="C9" t="n">
+        <v>22.97536181629376</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22.95970643722455</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27.92110668527065</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22.97535981623812</v>
+      </c>
+      <c r="G9" t="n">
+        <v>22.96216174228736</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22.95970210781809</v>
+      </c>
+      <c r="I9" t="n">
+        <v>22.97536181629376</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.95970210781809</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20.47648396840802</v>
+      </c>
+      <c r="L9" t="n">
+        <v>22.95970210781809</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>172.235951577876</v>
+      </c>
+      <c r="C10" t="n">
+        <v>174.292336715524</v>
+      </c>
+      <c r="D10" t="n">
+        <v>167.5656678879732</v>
+      </c>
+      <c r="E10" t="n">
+        <v>174.292336715524</v>
+      </c>
+      <c r="F10" t="n">
+        <v>174.292336715524</v>
+      </c>
+      <c r="G10" t="n">
+        <v>168.0524757064851</v>
+      </c>
+      <c r="H10" t="n">
+        <v>168.7837654211999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>174.292336715524</v>
+      </c>
+      <c r="J10" t="n">
+        <v>162.9282439966442</v>
+      </c>
+      <c r="K10" t="n">
+        <v>170.2049880577375</v>
+      </c>
+      <c r="L10" t="n">
+        <v>168.6190307920874</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>169.770074746504</v>
-      </c>
-      <c r="C9" t="n">
-        <v>173.3789468212091</v>
-      </c>
-      <c r="D9" t="n">
-        <v>167.8680312848981</v>
-      </c>
-      <c r="E9" t="n">
-        <v>173.3789468212091</v>
-      </c>
-      <c r="F9" t="n">
-        <v>173.3789468212091</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>169.7700747465042</v>
+      </c>
+      <c r="C11" t="n">
+        <v>173.3789468212092</v>
+      </c>
+      <c r="D11" t="n">
+        <v>167.8680312848983</v>
+      </c>
+      <c r="E11" t="n">
+        <v>173.3789468212092</v>
+      </c>
+      <c r="F11" t="n">
+        <v>173.3789468212092</v>
+      </c>
+      <c r="G11" t="n">
         <v>168.0590775364415</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>168.3675675572773</v>
       </c>
-      <c r="I9" t="n">
-        <v>173.3789468212091</v>
-      </c>
-      <c r="J9" t="n">
-        <v>165.9827919651909</v>
-      </c>
-      <c r="K9" t="n">
-        <v>168.9430025530727</v>
-      </c>
-      <c r="L9" t="n">
-        <v>168.2999360122569</v>
+      <c r="I11" t="n">
+        <v>173.3789468212092</v>
+      </c>
+      <c r="J11" t="n">
+        <v>165.982791965191</v>
+      </c>
+      <c r="K11" t="n">
+        <v>168.9430025530728</v>
+      </c>
+      <c r="L11" t="n">
+        <v>168.2999360122571</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>179.2920817887908</v>
+        <v>164.8478684824732</v>
       </c>
       <c r="C2" t="n">
-        <v>175.0762117277259</v>
+        <v>166.7861635349084</v>
       </c>
       <c r="D2" t="n">
-        <v>314.0101212438432</v>
+        <v>170.4114828573969</v>
       </c>
       <c r="E2" t="n">
-        <v>268.7089523503524</v>
+        <v>168.693136746805</v>
       </c>
       <c r="F2" t="n">
-        <v>268.7089523503524</v>
+        <v>168.693136746805</v>
       </c>
       <c r="G2" t="n">
-        <v>317.1512962838817</v>
+        <v>169.0109637086192</v>
       </c>
       <c r="H2" t="n">
-        <v>521.7882955971161</v>
+        <v>170.5828281573628</v>
       </c>
       <c r="I2" t="n">
-        <v>268.7089523503524</v>
+        <v>168.693136746805</v>
       </c>
       <c r="J2" t="n">
-        <v>520.807094164525</v>
+        <v>181.1218287358147</v>
       </c>
       <c r="K2" t="n">
-        <v>295.6496422311553</v>
+        <v>176.8928524693961</v>
       </c>
       <c r="L2" t="n">
-        <v>291.3728714991366</v>
+        <v>182.4466070752856</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.548362515101052</v>
+        <v>167.2479141948564</v>
       </c>
       <c r="C3" t="n">
-        <v>5.142961417071982</v>
+        <v>169.2206548407867</v>
       </c>
       <c r="D3" t="n">
-        <v>5.548362515101051</v>
+        <v>172.7434061753669</v>
       </c>
       <c r="E3" t="n">
-        <v>5.444198230014983</v>
+        <v>171.05155876187</v>
       </c>
       <c r="F3" t="n">
-        <v>5.444198230014983</v>
+        <v>171.05155876187</v>
       </c>
       <c r="G3" t="n">
-        <v>5.540662554093179</v>
+        <v>171.3260622602741</v>
       </c>
       <c r="H3" t="n">
-        <v>5.548362515101052</v>
+        <v>172.7434061753669</v>
       </c>
       <c r="I3" t="n">
-        <v>5.496501766652293</v>
+        <v>171.05155876187</v>
       </c>
       <c r="J3" t="n">
-        <v>5.548362515101052</v>
+        <v>183.4173191987995</v>
       </c>
       <c r="K3" t="n">
-        <v>5.548362515101051</v>
+        <v>179.349598804638</v>
       </c>
       <c r="L3" t="n">
-        <v>5.548362515101051</v>
+        <v>185.034416920039</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>805.5474111790148</v>
+        <v>179.2920817887911</v>
       </c>
       <c r="C4" t="n">
-        <v>672.5649981157982</v>
+        <v>175.0762117277266</v>
       </c>
       <c r="D4" t="n">
-        <v>672.9306773344751</v>
+        <v>314.0101212438434</v>
       </c>
       <c r="E4" t="n">
-        <v>606.3730749276905</v>
+        <v>268.7089523503521</v>
       </c>
       <c r="F4" t="n">
-        <v>672.8393026684187</v>
+        <v>268.7089523503521</v>
       </c>
       <c r="G4" t="n">
-        <v>672.8586680324462</v>
+        <v>317.1512962838822</v>
       </c>
       <c r="H4" t="n">
-        <v>806.5328949303025</v>
+        <v>521.7882955971163</v>
       </c>
       <c r="I4" t="n">
-        <v>672.8145072450052</v>
+        <v>268.7089523503521</v>
       </c>
       <c r="J4" t="n">
-        <v>805.9831179786117</v>
+        <v>520.8070941645248</v>
       </c>
       <c r="K4" t="n">
-        <v>672.8867626481757</v>
+        <v>295.6496422311556</v>
       </c>
       <c r="L4" t="n">
-        <v>672.895024014479</v>
+        <v>291.3728714991366</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.94839378560627</v>
+        <v>5.548362515101062</v>
       </c>
       <c r="C5" t="n">
-        <v>11.93715832941095</v>
+        <v>5.142961417072041</v>
       </c>
       <c r="D5" t="n">
-        <v>11.94838721209419</v>
+        <v>5.548362515101064</v>
       </c>
       <c r="E5" t="n">
-        <v>11.89839331301318</v>
+        <v>5.444198230014977</v>
       </c>
       <c r="F5" t="n">
-        <v>11.89839331301318</v>
+        <v>5.44419823001498</v>
       </c>
       <c r="G5" t="n">
-        <v>11.94069382459834</v>
+        <v>5.540662554093155</v>
       </c>
       <c r="H5" t="n">
-        <v>11.94839378560627</v>
+        <v>5.548362515101064</v>
       </c>
       <c r="I5" t="n">
-        <v>11.89653303715748</v>
+        <v>5.496501766652286</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94839378560627</v>
+        <v>5.548362515101062</v>
       </c>
       <c r="K5" t="n">
-        <v>11.94839378560627</v>
+        <v>5.548362515101064</v>
       </c>
       <c r="L5" t="n">
-        <v>11.94839378560627</v>
+        <v>5.548362515101064</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.51517986777365</v>
+        <v>805.5474111790146</v>
       </c>
       <c r="C6" t="n">
-        <v>21.34689143553981</v>
+        <v>672.5649981157989</v>
       </c>
       <c r="D6" t="n">
-        <v>22.7733627472134</v>
+        <v>672.930677334475</v>
       </c>
       <c r="E6" t="n">
-        <v>19.43535805279071</v>
+        <v>606.3730749276911</v>
       </c>
       <c r="F6" t="n">
-        <v>14.68124666803879</v>
+        <v>672.8393026684191</v>
       </c>
       <c r="G6" t="n">
-        <v>21.34736753041467</v>
+        <v>672.8586680324468</v>
       </c>
       <c r="H6" t="n">
-        <v>21.35506749145032</v>
+        <v>806.5328949303026</v>
       </c>
       <c r="I6" t="n">
-        <v>21.30320674297381</v>
+        <v>672.8145072450063</v>
       </c>
       <c r="J6" t="n">
-        <v>21.35641171470286</v>
+        <v>805.9831179786115</v>
       </c>
       <c r="K6" t="n">
-        <v>14.38812544450031</v>
+        <v>672.8867626481759</v>
       </c>
       <c r="L6" t="n">
-        <v>28.49990204656918</v>
+        <v>672.8950240144783</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.80141712480652</v>
+        <v>11.94839378560628</v>
       </c>
       <c r="C7" t="n">
-        <v>33.16508374528419</v>
+        <v>11.93715832941097</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17632383053115</v>
+        <v>11.9483872120942</v>
       </c>
       <c r="E7" t="n">
-        <v>40.48095852540418</v>
+        <v>11.89839331301318</v>
       </c>
       <c r="F7" t="n">
-        <v>33.12445370189973</v>
+        <v>11.89839331301318</v>
       </c>
       <c r="G7" t="n">
-        <v>33.16861924047156</v>
+        <v>11.94069382459835</v>
       </c>
       <c r="H7" t="n">
-        <v>33.17631920147951</v>
+        <v>11.94839378560628</v>
       </c>
       <c r="I7" t="n">
-        <v>33.12445845303072</v>
+        <v>11.89653303715749</v>
       </c>
       <c r="J7" t="n">
-        <v>33.17631920147951</v>
+        <v>11.94839378560628</v>
       </c>
       <c r="K7" t="n">
-        <v>29.48267784904393</v>
+        <v>11.94839378560628</v>
       </c>
       <c r="L7" t="n">
-        <v>33.17631920147951</v>
+        <v>11.94839378560628</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>163.3501429267517</v>
+        <v>14.51517986777368</v>
       </c>
       <c r="C8" t="n">
-        <v>165.3972036468965</v>
+        <v>21.34689143553981</v>
       </c>
       <c r="D8" t="n">
-        <v>165.6016664516009</v>
+        <v>22.77336274721334</v>
       </c>
       <c r="E8" t="n">
-        <v>165.0178081187631</v>
+        <v>19.4353580527907</v>
       </c>
       <c r="F8" t="n">
-        <v>165.0178081187631</v>
+        <v>14.68124666803876</v>
       </c>
       <c r="G8" t="n">
-        <v>164.3242484449759</v>
+        <v>21.34736753041467</v>
       </c>
       <c r="H8" t="n">
-        <v>162.2122347051115</v>
+        <v>21.35506749145031</v>
       </c>
       <c r="I8" t="n">
-        <v>165.0178081187631</v>
+        <v>21.30320674297381</v>
       </c>
       <c r="J8" t="n">
-        <v>172.1008621900335</v>
+        <v>21.35641171470288</v>
       </c>
       <c r="K8" t="n">
-        <v>172.6604825504221</v>
+        <v>14.38812544450033</v>
       </c>
       <c r="L8" t="n">
-        <v>179.3152408247453</v>
+        <v>28.49990204656916</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>26.80141712480658</v>
+      </c>
+      <c r="C9" t="n">
+        <v>33.16508374528415</v>
+      </c>
+      <c r="D9" t="n">
+        <v>33.17632383053109</v>
+      </c>
+      <c r="E9" t="n">
+        <v>40.48095852540423</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33.12445370189978</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33.16861924047162</v>
+      </c>
+      <c r="H9" t="n">
+        <v>33.17631920147951</v>
+      </c>
+      <c r="I9" t="n">
+        <v>33.12445845303075</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33.17631920147951</v>
+      </c>
+      <c r="K9" t="n">
+        <v>29.48267784904392</v>
+      </c>
+      <c r="L9" t="n">
+        <v>33.17631920147951</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>163.3501429267519</v>
+      </c>
+      <c r="C10" t="n">
+        <v>165.3972036468965</v>
+      </c>
+      <c r="D10" t="n">
+        <v>165.6016664516009</v>
+      </c>
+      <c r="E10" t="n">
+        <v>165.0178081187632</v>
+      </c>
+      <c r="F10" t="n">
+        <v>165.0178081187632</v>
+      </c>
+      <c r="G10" t="n">
+        <v>164.3242484449758</v>
+      </c>
+      <c r="H10" t="n">
+        <v>162.2122347051115</v>
+      </c>
+      <c r="I10" t="n">
+        <v>165.0178081187632</v>
+      </c>
+      <c r="J10" t="n">
+        <v>172.1008621900336</v>
+      </c>
+      <c r="K10" t="n">
+        <v>172.660482550422</v>
+      </c>
+      <c r="L10" t="n">
+        <v>179.3152408247453</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>163.0743701340255</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>165.0464810570724</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>167.1619685237093</v>
       </c>
-      <c r="E9" t="n">
-        <v>165.9477609757689</v>
-      </c>
-      <c r="F9" t="n">
-        <v>165.9477609757689</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E11" t="n">
+        <v>165.947760975769</v>
+      </c>
+      <c r="F11" t="n">
+        <v>165.947760975769</v>
+      </c>
+      <c r="G11" t="n">
         <v>165.8251161092019</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>165.7911115775445</v>
       </c>
-      <c r="I9" t="n">
-        <v>165.9477609757689</v>
-      </c>
-      <c r="J9" t="n">
-        <v>175.9728047334175</v>
-      </c>
-      <c r="K9" t="n">
-        <v>173.8492832567792</v>
-      </c>
-      <c r="L9" t="n">
-        <v>179.8443637259941</v>
+      <c r="I11" t="n">
+        <v>165.947760975769</v>
+      </c>
+      <c r="J11" t="n">
+        <v>175.9728047334176</v>
+      </c>
+      <c r="K11" t="n">
+        <v>173.849283256779</v>
+      </c>
+      <c r="L11" t="n">
+        <v>179.844363725994</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93.17274804148927</v>
+        <v>164.252353931908</v>
       </c>
       <c r="C2" t="n">
-        <v>117.0729928457</v>
+        <v>166.3082607223817</v>
       </c>
       <c r="D2" t="n">
-        <v>230.2708382866051</v>
+        <v>169.2859665969922</v>
       </c>
       <c r="E2" t="n">
-        <v>133.3116406713087</v>
+        <v>167.7863003555545</v>
       </c>
       <c r="F2" t="n">
-        <v>133.3116406713087</v>
+        <v>167.7863003555545</v>
       </c>
       <c r="G2" t="n">
-        <v>204.4987689914504</v>
+        <v>168.448424592663</v>
       </c>
       <c r="H2" t="n">
-        <v>286.3411992164337</v>
+        <v>169.3178955203965</v>
       </c>
       <c r="I2" t="n">
-        <v>133.3116406713087</v>
+        <v>167.7863003555545</v>
       </c>
       <c r="J2" t="n">
-        <v>377.2726568119444</v>
+        <v>180.1649430067598</v>
       </c>
       <c r="K2" t="n">
-        <v>143.2330090556279</v>
+        <v>175.9197186432228</v>
       </c>
       <c r="L2" t="n">
-        <v>149.5663970054839</v>
+        <v>181.7751502782727</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.654032156819189</v>
+        <v>166.734582703776</v>
       </c>
       <c r="C3" t="n">
-        <v>4.327819788408809</v>
+        <v>168.7948322091979</v>
       </c>
       <c r="D3" t="n">
-        <v>4.654032156819188</v>
+        <v>171.6827808087757</v>
       </c>
       <c r="E3" t="n">
-        <v>4.500522190496551</v>
+        <v>170.2760042791215</v>
       </c>
       <c r="F3" t="n">
-        <v>4.500522190496551</v>
+        <v>170.2760042791215</v>
       </c>
       <c r="G3" t="n">
-        <v>4.645411735598413</v>
+        <v>170.868615151157</v>
       </c>
       <c r="H3" t="n">
-        <v>4.654032156819188</v>
+        <v>171.6827808087757</v>
       </c>
       <c r="I3" t="n">
-        <v>4.596127718719712</v>
+        <v>170.2760042791215</v>
       </c>
       <c r="J3" t="n">
-        <v>4.654032156819189</v>
+        <v>182.5799234881842</v>
       </c>
       <c r="K3" t="n">
-        <v>4.654032156819188</v>
+        <v>178.5256041222324</v>
       </c>
       <c r="L3" t="n">
-        <v>4.654032156819188</v>
+        <v>184.4870651112022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>761.3589314122829</v>
+        <v>93.17274804148943</v>
       </c>
       <c r="C4" t="n">
-        <v>636.1188614623723</v>
+        <v>117.0729928457</v>
       </c>
       <c r="D4" t="n">
-        <v>761.5675668045441</v>
+        <v>230.2708382866056</v>
       </c>
       <c r="E4" t="n">
-        <v>573.2908886521616</v>
+        <v>133.3116406713086</v>
       </c>
       <c r="F4" t="n">
-        <v>636.2468724138853</v>
+        <v>133.3116406713086</v>
       </c>
       <c r="G4" t="n">
-        <v>761.3503109910627</v>
+        <v>204.4987689914503</v>
       </c>
       <c r="H4" t="n">
-        <v>762.1470385037624</v>
+        <v>286.3411992164336</v>
       </c>
       <c r="I4" t="n">
-        <v>636.2445175846776</v>
+        <v>133.3116406713086</v>
       </c>
       <c r="J4" t="n">
-        <v>668.5807281776987</v>
+        <v>377.2726568119437</v>
       </c>
       <c r="K4" t="n">
-        <v>636.2371950889304</v>
+        <v>143.2330090556281</v>
       </c>
       <c r="L4" t="n">
-        <v>636.3198821526277</v>
+        <v>149.5663970054841</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.08387289981453</v>
+        <v>4.654032156819092</v>
       </c>
       <c r="C5" t="n">
-        <v>10.07468776439314</v>
+        <v>4.327819788408811</v>
       </c>
       <c r="D5" t="n">
-        <v>10.08386934642124</v>
+        <v>4.654032156819092</v>
       </c>
       <c r="E5" t="n">
-        <v>10.01955768622231</v>
+        <v>4.500522190496548</v>
       </c>
       <c r="F5" t="n">
-        <v>10.01955768622231</v>
+        <v>4.500522190496542</v>
       </c>
       <c r="G5" t="n">
-        <v>10.07525247859376</v>
+        <v>4.645411735598389</v>
       </c>
       <c r="H5" t="n">
-        <v>10.08387289981453</v>
+        <v>4.654032156819092</v>
       </c>
       <c r="I5" t="n">
-        <v>10.02596846171506</v>
+        <v>4.59612771871971</v>
       </c>
       <c r="J5" t="n">
-        <v>10.08387289981453</v>
+        <v>4.654032156819092</v>
       </c>
       <c r="K5" t="n">
-        <v>10.08387289981453</v>
+        <v>4.654032156819092</v>
       </c>
       <c r="L5" t="n">
-        <v>10.08387289981453</v>
+        <v>4.654032156819092</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.03714459011206</v>
+        <v>761.3589314122842</v>
       </c>
       <c r="C6" t="n">
-        <v>17.63023241631929</v>
+        <v>636.118861462372</v>
       </c>
       <c r="D6" t="n">
-        <v>18.80722802680987</v>
+        <v>761.5675668045442</v>
       </c>
       <c r="E6" t="n">
-        <v>16.04854786445597</v>
+        <v>573.2908886521617</v>
       </c>
       <c r="F6" t="n">
-        <v>12.15316261322477</v>
+        <v>636.2468724138847</v>
       </c>
       <c r="G6" t="n">
-        <v>17.635884842044</v>
+        <v>761.3503109910633</v>
       </c>
       <c r="H6" t="n">
-        <v>17.64450526328469</v>
+        <v>762.1470385037622</v>
       </c>
       <c r="I6" t="n">
-        <v>17.58660082516517</v>
+        <v>636.2445175846776</v>
       </c>
       <c r="J6" t="n">
-        <v>17.64560726154343</v>
+        <v>668.5807281776985</v>
       </c>
       <c r="K6" t="n">
-        <v>11.93298498757819</v>
+        <v>636.2371950889303</v>
       </c>
       <c r="L6" t="n">
-        <v>23.50186235811936</v>
+        <v>636.3198821526278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.40697900961912</v>
+        <v>10.08387289981454</v>
       </c>
       <c r="C7" t="n">
-        <v>25.15313360717937</v>
+        <v>10.07468776439313</v>
       </c>
       <c r="D7" t="n">
-        <v>25.16232288867123</v>
+        <v>10.08386934642126</v>
       </c>
       <c r="E7" t="n">
-        <v>30.59197548370666</v>
+        <v>10.01955768622232</v>
       </c>
       <c r="F7" t="n">
-        <v>25.10441127160056</v>
+        <v>10.01955768622232</v>
       </c>
       <c r="G7" t="n">
-        <v>25.15369832137998</v>
+        <v>10.0752524785937</v>
       </c>
       <c r="H7" t="n">
-        <v>25.16231874260079</v>
+        <v>10.08387289981454</v>
       </c>
       <c r="I7" t="n">
-        <v>25.1044143045013</v>
+        <v>10.02596846171505</v>
       </c>
       <c r="J7" t="n">
-        <v>25.16231874260079</v>
+        <v>10.08387289981454</v>
       </c>
       <c r="K7" t="n">
-        <v>22.40705796947205</v>
+        <v>10.08387289981454</v>
       </c>
       <c r="L7" t="n">
-        <v>25.16231874260079</v>
+        <v>10.08387289981454</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>164.6376622185687</v>
+        <v>12.03714459011192</v>
       </c>
       <c r="C8" t="n">
-        <v>166.1166456253177</v>
+        <v>17.63023241631917</v>
       </c>
       <c r="D8" t="n">
-        <v>166.1673071425723</v>
+        <v>18.80722802680985</v>
       </c>
       <c r="E8" t="n">
-        <v>167.1570913551208</v>
+        <v>16.048547864456</v>
       </c>
       <c r="F8" t="n">
-        <v>167.1570913551208</v>
+        <v>12.15316261322478</v>
       </c>
       <c r="G8" t="n">
-        <v>166.1259830746845</v>
+        <v>17.63588484204395</v>
       </c>
       <c r="H8" t="n">
-        <v>165.6137950311644</v>
+        <v>17.64450526328449</v>
       </c>
       <c r="I8" t="n">
-        <v>167.1570913551207</v>
+        <v>17.58660082516523</v>
       </c>
       <c r="J8" t="n">
-        <v>173.9393196470938</v>
+        <v>17.64560726154341</v>
       </c>
       <c r="K8" t="n">
-        <v>175.1481084081327</v>
+        <v>11.9329849875783</v>
       </c>
       <c r="L8" t="n">
-        <v>181.4233716428731</v>
+        <v>23.50186235811918</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>20.40697900961906</v>
+      </c>
+      <c r="C9" t="n">
+        <v>25.15313360717931</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25.16232288867121</v>
+      </c>
+      <c r="E9" t="n">
+        <v>30.59197548370661</v>
+      </c>
+      <c r="F9" t="n">
+        <v>25.1044112716005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25.15369832137986</v>
+      </c>
+      <c r="H9" t="n">
+        <v>25.16231874260073</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25.10441430450129</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.16231874260073</v>
+      </c>
+      <c r="K9" t="n">
+        <v>22.40705796947198</v>
+      </c>
+      <c r="L9" t="n">
+        <v>25.16231874260073</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>164.6376622185688</v>
+      </c>
+      <c r="C10" t="n">
+        <v>166.1166456253177</v>
+      </c>
+      <c r="D10" t="n">
+        <v>166.1673071425722</v>
+      </c>
+      <c r="E10" t="n">
+        <v>167.1570913551207</v>
+      </c>
+      <c r="F10" t="n">
+        <v>167.1570913551207</v>
+      </c>
+      <c r="G10" t="n">
+        <v>166.1259830746846</v>
+      </c>
+      <c r="H10" t="n">
+        <v>165.6137950311643</v>
+      </c>
+      <c r="I10" t="n">
+        <v>167.1570913551207</v>
+      </c>
+      <c r="J10" t="n">
+        <v>173.9393196470938</v>
+      </c>
+      <c r="K10" t="n">
+        <v>175.1481084081327</v>
+      </c>
+      <c r="L10" t="n">
+        <v>181.4233716428731</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>163.2982484286497</v>
-      </c>
-      <c r="C9" t="n">
-        <v>165.089677291842</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>163.2982484286495</v>
+      </c>
+      <c r="C11" t="n">
+        <v>165.0896772918419</v>
+      </c>
+      <c r="D11" t="n">
         <v>166.7764085020979</v>
       </c>
-      <c r="E9" t="n">
-        <v>166.3671850357486</v>
-      </c>
-      <c r="F9" t="n">
-        <v>166.3671850357486</v>
-      </c>
-      <c r="G9" t="n">
-        <v>166.2905118839965</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="E11" t="n">
+        <v>166.3671850357485</v>
+      </c>
+      <c r="F11" t="n">
+        <v>166.3671850357485</v>
+      </c>
+      <c r="G11" t="n">
+        <v>166.2905118839964</v>
+      </c>
+      <c r="H11" t="n">
         <v>166.5564876508731</v>
       </c>
-      <c r="I9" t="n">
-        <v>166.3671850357486</v>
-      </c>
-      <c r="J9" t="n">
-        <v>176.233440723093</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="I11" t="n">
+        <v>166.3671850357485</v>
+      </c>
+      <c r="J11" t="n">
+        <v>176.2334407230929</v>
+      </c>
+      <c r="K11" t="n">
         <v>174.3829473298671</v>
       </c>
-      <c r="L9" t="n">
-        <v>180.3811599867713</v>
+      <c r="L11" t="n">
+        <v>180.3811599867714</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,320 +2415,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.90281054143438</v>
+        <v>163.845447450952</v>
       </c>
       <c r="C2" t="n">
-        <v>75.62186661498893</v>
+        <v>165.9530587959866</v>
       </c>
       <c r="D2" t="n">
-        <v>179.750979649891</v>
+        <v>168.4084458683526</v>
       </c>
       <c r="E2" t="n">
-        <v>47.59177106935259</v>
+        <v>167.1825809296042</v>
       </c>
       <c r="F2" t="n">
-        <v>47.59177106935259</v>
+        <v>167.1825809296042</v>
       </c>
       <c r="G2" t="n">
-        <v>136.6908737782671</v>
+        <v>168.1566787943761</v>
       </c>
       <c r="H2" t="n">
-        <v>173.3901601173728</v>
+        <v>168.3809434590875</v>
       </c>
       <c r="I2" t="n">
-        <v>47.59177106935259</v>
+        <v>167.1825809296042</v>
       </c>
       <c r="J2" t="n">
-        <v>284.3814951317994</v>
+        <v>179.3379449183965</v>
       </c>
       <c r="K2" t="n">
-        <v>60.37286861775022</v>
+        <v>175.7539317906886</v>
       </c>
       <c r="L2" t="n">
-        <v>71.43816753738825</v>
+        <v>181.2487010954483</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.033430896842567</v>
+        <v>166.3827630890753</v>
       </c>
       <c r="C3" t="n">
-        <v>3.792653835049975</v>
+        <v>168.4843680984696</v>
       </c>
       <c r="D3" t="n">
-        <v>4.033430896842566</v>
+        <v>170.8535557096652</v>
       </c>
       <c r="E3" t="n">
-        <v>3.820965882094183</v>
+        <v>169.7658514443491</v>
       </c>
       <c r="F3" t="n">
-        <v>3.820965882094186</v>
+        <v>169.7658514443491</v>
       </c>
       <c r="G3" t="n">
-        <v>4.024148004457778</v>
+        <v>170.6529850588103</v>
       </c>
       <c r="H3" t="n">
-        <v>4.033430896842566</v>
+        <v>170.8535557096652</v>
       </c>
       <c r="I3" t="n">
-        <v>3.971152062712592</v>
+        <v>169.7658514443491</v>
       </c>
       <c r="J3" t="n">
-        <v>4.033430896842566</v>
+        <v>181.8474345963829</v>
       </c>
       <c r="K3" t="n">
-        <v>4.033430896842566</v>
+        <v>178.4573452328507</v>
       </c>
       <c r="L3" t="n">
-        <v>4.033430896842566</v>
+        <v>184.0359854517201</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.3339534951252</v>
+        <v>41.90281054143443</v>
       </c>
       <c r="C4" t="n">
-        <v>635.2157570335359</v>
+        <v>75.62186661498905</v>
       </c>
       <c r="D4" t="n">
-        <v>635.4862774741762</v>
+        <v>179.7509796498909</v>
       </c>
       <c r="E4" t="n">
-        <v>572.3050697076366</v>
+        <v>47.59177106935256</v>
       </c>
       <c r="F4" t="n">
-        <v>635.2566451833881</v>
+        <v>47.59177106935256</v>
       </c>
       <c r="G4" t="n">
-        <v>759.9137738162474</v>
+        <v>136.6908737782668</v>
       </c>
       <c r="H4" t="n">
-        <v>760.5663447728616</v>
+        <v>173.3901601173733</v>
       </c>
       <c r="I4" t="n">
-        <v>759.8607778745024</v>
+        <v>47.59177106935256</v>
       </c>
       <c r="J4" t="n">
-        <v>760.2578805838838</v>
+        <v>284.3814951317995</v>
       </c>
       <c r="K4" t="n">
-        <v>635.2340297995694</v>
+        <v>60.37286861775033</v>
       </c>
       <c r="L4" t="n">
-        <v>635.3484419680616</v>
+        <v>71.43816753738834</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.994890379058537</v>
+        <v>4.03343089684258</v>
       </c>
       <c r="C5" t="n">
-        <v>8.987021207959431</v>
+        <v>3.792653835049976</v>
       </c>
       <c r="D5" t="n">
-        <v>8.994882019361244</v>
+        <v>4.03343089684258</v>
       </c>
       <c r="E5" t="n">
-        <v>8.913490612020004</v>
+        <v>3.820965882094195</v>
       </c>
       <c r="F5" t="n">
-        <v>8.913490612020004</v>
+        <v>3.820965882094196</v>
       </c>
       <c r="G5" t="n">
-        <v>8.985607486673743</v>
+        <v>4.02414800445778</v>
       </c>
       <c r="H5" t="n">
-        <v>8.994890379058537</v>
+        <v>4.03343089684258</v>
       </c>
       <c r="I5" t="n">
-        <v>8.932611544928561</v>
+        <v>3.971152062712601</v>
       </c>
       <c r="J5" t="n">
-        <v>8.994890379058537</v>
+        <v>4.03343089684258</v>
       </c>
       <c r="K5" t="n">
-        <v>8.994890379058537</v>
+        <v>4.03343089684258</v>
       </c>
       <c r="L5" t="n">
-        <v>8.994890379058537</v>
+        <v>4.03343089684258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.57088262809953</v>
+        <v>635.3339534951264</v>
       </c>
       <c r="C6" t="n">
-        <v>15.46994079168753</v>
+        <v>635.2157570335363</v>
       </c>
       <c r="D6" t="n">
-        <v>16.5162562987069</v>
+        <v>635.486277474177</v>
       </c>
       <c r="E6" t="n">
-        <v>14.07067416570981</v>
+        <v>572.3050697076368</v>
       </c>
       <c r="F6" t="n">
-        <v>10.65329461153432</v>
+        <v>635.2566451833887</v>
       </c>
       <c r="G6" t="n">
-        <v>15.48588978609794</v>
+        <v>759.9137738162475</v>
       </c>
       <c r="H6" t="n">
-        <v>15.49517267849283</v>
+        <v>760.566344772862</v>
       </c>
       <c r="I6" t="n">
-        <v>15.43289384435275</v>
+        <v>759.8607778745021</v>
       </c>
       <c r="J6" t="n">
-        <v>15.49614043549106</v>
+        <v>760.2578805838834</v>
       </c>
       <c r="K6" t="n">
-        <v>10.47941141292243</v>
+        <v>635.2340297995704</v>
       </c>
       <c r="L6" t="n">
-        <v>20.63900539197371</v>
+        <v>635.3484419680624</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.90810999663439</v>
+        <v>8.994890379058551</v>
       </c>
       <c r="C7" t="n">
-        <v>20.79614452025049</v>
+        <v>8.98702120795944</v>
       </c>
       <c r="D7" t="n">
-        <v>20.80401715849964</v>
+        <v>8.994882019361253</v>
       </c>
       <c r="E7" t="n">
-        <v>25.23752516979606</v>
+        <v>8.91349061202002</v>
       </c>
       <c r="F7" t="n">
-        <v>20.74173239413705</v>
+        <v>8.91349061202002</v>
       </c>
       <c r="G7" t="n">
-        <v>20.7947307989648</v>
+        <v>8.985607486673754</v>
       </c>
       <c r="H7" t="n">
-        <v>20.80401369134962</v>
+        <v>8.994890379058551</v>
       </c>
       <c r="I7" t="n">
-        <v>20.74173485721962</v>
+        <v>8.932611544928571</v>
       </c>
       <c r="J7" t="n">
-        <v>20.80401369134962</v>
+        <v>8.994890379058551</v>
       </c>
       <c r="K7" t="n">
-        <v>18.45513157747684</v>
+        <v>8.994890379058551</v>
       </c>
       <c r="L7" t="n">
-        <v>20.80401369134962</v>
+        <v>8.994890379058551</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>165.4862733937211</v>
+        <v>10.57088262809955</v>
       </c>
       <c r="C8" t="n">
-        <v>166.7777969210056</v>
+        <v>15.46994079168753</v>
       </c>
       <c r="D8" t="n">
-        <v>166.5581959537059</v>
+        <v>16.51625629870689</v>
       </c>
       <c r="E8" t="n">
-        <v>168.7046078054658</v>
+        <v>14.07067416570983</v>
       </c>
       <c r="F8" t="n">
-        <v>168.7046078054658</v>
+        <v>10.65329461153432</v>
       </c>
       <c r="G8" t="n">
-        <v>167.5039677338927</v>
+        <v>15.48588978609794</v>
       </c>
       <c r="H8" t="n">
-        <v>167.2037694869492</v>
+        <v>15.49517267849282</v>
       </c>
       <c r="I8" t="n">
-        <v>168.7046078054658</v>
+        <v>15.43289384435278</v>
       </c>
       <c r="J8" t="n">
-        <v>175.3465556616987</v>
+        <v>15.49614043549107</v>
       </c>
       <c r="K8" t="n">
-        <v>177.0805907819432</v>
+        <v>10.47941141292244</v>
       </c>
       <c r="L8" t="n">
-        <v>182.6090944023933</v>
+        <v>20.63900539197373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16.9081099966344</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20.79614452025052</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20.80401715849965</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25.23752516979609</v>
+      </c>
+      <c r="F9" t="n">
+        <v>20.74173239413707</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20.79473079896484</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20.80401369134962</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20.74173485721964</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.80401369134962</v>
+      </c>
+      <c r="K9" t="n">
+        <v>18.45513157747687</v>
+      </c>
+      <c r="L9" t="n">
+        <v>20.80401369134962</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>165.4862733937213</v>
+      </c>
+      <c r="C10" t="n">
+        <v>166.7777969210054</v>
+      </c>
+      <c r="D10" t="n">
+        <v>166.558195953706</v>
+      </c>
+      <c r="E10" t="n">
+        <v>168.7046078054659</v>
+      </c>
+      <c r="F10" t="n">
+        <v>168.7046078054659</v>
+      </c>
+      <c r="G10" t="n">
+        <v>167.5039677338928</v>
+      </c>
+      <c r="H10" t="n">
+        <v>167.2037694869492</v>
+      </c>
+      <c r="I10" t="n">
+        <v>168.7046078054659</v>
+      </c>
+      <c r="J10" t="n">
+        <v>175.3465556616988</v>
+      </c>
+      <c r="K10" t="n">
+        <v>177.0805907819433</v>
+      </c>
+      <c r="L10" t="n">
+        <v>182.6090944023933</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>163.4375417826226</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>163.4375417826227</v>
+      </c>
+      <c r="C11" t="n">
         <v>165.1765634717208</v>
       </c>
-      <c r="D9" t="n">
-        <v>166.4540434908918</v>
-      </c>
-      <c r="E9" t="n">
-        <v>166.6997116919294</v>
-      </c>
-      <c r="F9" t="n">
-        <v>166.6997116919294</v>
-      </c>
-      <c r="G9" t="n">
-        <v>166.7238658762157</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="D11" t="n">
+        <v>166.4540434908917</v>
+      </c>
+      <c r="E11" t="n">
+        <v>166.6997116919296</v>
+      </c>
+      <c r="F11" t="n">
+        <v>166.6997116919296</v>
+      </c>
+      <c r="G11" t="n">
+        <v>166.7238658762156</v>
+      </c>
+      <c r="H11" t="n">
         <v>166.7202790965732</v>
       </c>
-      <c r="I9" t="n">
-        <v>166.6997116919294</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="I11" t="n">
+        <v>166.6997116919296</v>
+      </c>
+      <c r="J11" t="n">
         <v>176.3800242860432</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>175.1275041280697</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>180.5994611207726</v>
       </c>
     </row>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,320 +2891,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94.35419197869599</v>
+        <v>158.8179850511418</v>
       </c>
       <c r="C2" t="n">
-        <v>39.61709796133675</v>
+        <v>165.984575988897</v>
       </c>
       <c r="D2" t="n">
-        <v>212.3513906828526</v>
+        <v>169.5455493096513</v>
       </c>
       <c r="E2" t="n">
-        <v>178.3728855687161</v>
+        <v>167.9728020052474</v>
       </c>
       <c r="F2" t="n">
-        <v>178.3728855687161</v>
+        <v>167.9728020052474</v>
       </c>
       <c r="G2" t="n">
-        <v>228.5169528456169</v>
+        <v>167.8821394324875</v>
       </c>
       <c r="H2" t="n">
-        <v>462.7769158990593</v>
+        <v>169.7704804627782</v>
       </c>
       <c r="I2" t="n">
-        <v>178.3728855687161</v>
+        <v>167.9728020052474</v>
       </c>
       <c r="J2" t="n">
-        <v>482.0952792099474</v>
+        <v>180.6091899444756</v>
       </c>
       <c r="K2" t="n">
-        <v>218.4135435433685</v>
+        <v>175.9098757380087</v>
       </c>
       <c r="L2" t="n">
-        <v>216.0365139386737</v>
+        <v>181.9562623550867</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.950917465302408</v>
+        <v>161.2169320510115</v>
       </c>
       <c r="C3" t="n">
-        <v>4.491131008564277</v>
+        <v>168.556704312068</v>
       </c>
       <c r="D3" t="n">
-        <v>4.950917465302408</v>
+        <v>171.9797281869522</v>
       </c>
       <c r="E3" t="n">
-        <v>4.81451180919876</v>
+        <v>170.4222635316662</v>
       </c>
       <c r="F3" t="n">
-        <v>4.81451180919876</v>
+        <v>170.4222635316662</v>
       </c>
       <c r="G3" t="n">
-        <v>4.943425219573129</v>
+        <v>170.2782509061437</v>
       </c>
       <c r="H3" t="n">
-        <v>4.950917465302408</v>
+        <v>171.9797281869522</v>
       </c>
       <c r="I3" t="n">
-        <v>4.900438303293948</v>
+        <v>170.4222635316662</v>
       </c>
       <c r="J3" t="n">
-        <v>4.950917465302408</v>
+        <v>182.9401626227865</v>
       </c>
       <c r="K3" t="n">
-        <v>4.950917465302408</v>
+        <v>178.4393371347604</v>
       </c>
       <c r="L3" t="n">
-        <v>4.950917465302408</v>
+        <v>184.612607600597</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>671.8823159171977</v>
+        <v>94.35419197869615</v>
       </c>
       <c r="C4" t="n">
-        <v>671.4847386258176</v>
+        <v>39.61709796133677</v>
       </c>
       <c r="D4" t="n">
-        <v>671.9145404012957</v>
+        <v>212.3513906828526</v>
       </c>
       <c r="E4" t="n">
-        <v>605.3979045119113</v>
+        <v>178.3728855687169</v>
       </c>
       <c r="F4" t="n">
-        <v>671.8521436927867</v>
+        <v>178.3728855687169</v>
       </c>
       <c r="G4" t="n">
-        <v>671.8748236714691</v>
+        <v>228.5169528456168</v>
       </c>
       <c r="H4" t="n">
-        <v>805.0336973200039</v>
+        <v>462.7769158990594</v>
       </c>
       <c r="I4" t="n">
-        <v>804.0071677562046</v>
+        <v>178.3728855687169</v>
       </c>
       <c r="J4" t="n">
-        <v>706.0008811261487</v>
+        <v>482.0952792099479</v>
       </c>
       <c r="K4" t="n">
-        <v>671.9229190371911</v>
+        <v>218.4135435433684</v>
       </c>
       <c r="L4" t="n">
-        <v>671.9164913473558</v>
+        <v>216.0365139386737</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.87471595029862</v>
+        <v>4.950917465302413</v>
       </c>
       <c r="C5" t="n">
-        <v>10.8627403307138</v>
+        <v>4.491131008564276</v>
       </c>
       <c r="D5" t="n">
-        <v>10.87472225877024</v>
+        <v>4.950917465302413</v>
       </c>
       <c r="E5" t="n">
-        <v>10.81836696555443</v>
+        <v>4.814511809198768</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81836696555443</v>
+        <v>4.814511809198767</v>
       </c>
       <c r="G5" t="n">
-        <v>10.86722370456933</v>
+        <v>4.943425219573135</v>
       </c>
       <c r="H5" t="n">
-        <v>10.87471595029862</v>
+        <v>4.950917465302413</v>
       </c>
       <c r="I5" t="n">
-        <v>10.82423678829015</v>
+        <v>4.900438303293955</v>
       </c>
       <c r="J5" t="n">
-        <v>10.87471595029862</v>
+        <v>4.950917465302413</v>
       </c>
       <c r="K5" t="n">
-        <v>10.87471595029862</v>
+        <v>4.950917465302413</v>
       </c>
       <c r="L5" t="n">
-        <v>10.87471595029862</v>
+        <v>4.950917465302413</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.11850900200016</v>
+        <v>671.8823159171994</v>
       </c>
       <c r="C6" t="n">
-        <v>19.34988864321053</v>
+        <v>671.4847386258184</v>
       </c>
       <c r="D6" t="n">
-        <v>20.66185219817963</v>
+        <v>671.914540401296</v>
       </c>
       <c r="E6" t="n">
-        <v>17.60320185635501</v>
+        <v>605.3979045119119</v>
       </c>
       <c r="F6" t="n">
-        <v>13.26257061728786</v>
+        <v>671.8521436927878</v>
       </c>
       <c r="G6" t="n">
-        <v>19.35883428734172</v>
+        <v>671.8748236714704</v>
       </c>
       <c r="H6" t="n">
-        <v>19.3663265330987</v>
+        <v>805.0336973200042</v>
       </c>
       <c r="I6" t="n">
-        <v>19.31584737106255</v>
+        <v>804.0071677562041</v>
       </c>
       <c r="J6" t="n">
-        <v>19.36755439751729</v>
+        <v>706.0008811261492</v>
       </c>
       <c r="K6" t="n">
-        <v>13.00245258466839</v>
+        <v>671.9229190371921</v>
       </c>
       <c r="L6" t="n">
-        <v>25.89269436833884</v>
+        <v>671.916491347356</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.56508642736604</v>
+        <v>10.87471595029864</v>
       </c>
       <c r="C7" t="n">
-        <v>29.16154621998501</v>
+        <v>10.86274033071383</v>
       </c>
       <c r="D7" t="n">
-        <v>29.17352525324816</v>
+        <v>10.87472225877027</v>
       </c>
       <c r="E7" t="n">
-        <v>35.59505600852163</v>
+        <v>10.81836696555447</v>
       </c>
       <c r="F7" t="n">
-        <v>29.12303843550051</v>
+        <v>10.81836696555447</v>
       </c>
       <c r="G7" t="n">
-        <v>29.16602959384057</v>
+        <v>10.86722370456936</v>
       </c>
       <c r="H7" t="n">
-        <v>29.17352183956985</v>
+        <v>10.87471595029864</v>
       </c>
       <c r="I7" t="n">
-        <v>29.12304267756137</v>
+        <v>10.82423678829017</v>
       </c>
       <c r="J7" t="n">
-        <v>29.17352183956985</v>
+        <v>10.87471595029864</v>
       </c>
       <c r="K7" t="n">
-        <v>25.9239737714933</v>
+        <v>10.87471595029864</v>
       </c>
       <c r="L7" t="n">
-        <v>29.17352183956985</v>
+        <v>10.87471595029864</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>159.2082838814113</v>
+        <v>13.11850900200018</v>
       </c>
       <c r="C8" t="n">
-        <v>167.7646917008386</v>
+        <v>19.34988864321059</v>
       </c>
       <c r="D8" t="n">
-        <v>167.17380093503</v>
+        <v>20.66185219817969</v>
       </c>
       <c r="E8" t="n">
-        <v>166.4415408791667</v>
+        <v>17.60320185635504</v>
       </c>
       <c r="F8" t="n">
-        <v>166.4415408791667</v>
+        <v>13.26257061728788</v>
       </c>
       <c r="G8" t="n">
-        <v>165.2514057182714</v>
+        <v>19.35883428734176</v>
       </c>
       <c r="H8" t="n">
-        <v>162.6391275551879</v>
+        <v>19.36632653309874</v>
       </c>
       <c r="I8" t="n">
-        <v>166.4415408791667</v>
+        <v>19.31584737106258</v>
       </c>
       <c r="J8" t="n">
-        <v>172.4600929918982</v>
+        <v>19.36755439751735</v>
       </c>
       <c r="K8" t="n">
-        <v>173.5141624099639</v>
+        <v>13.00245258466842</v>
       </c>
       <c r="L8" t="n">
-        <v>180.3865360521725</v>
+        <v>25.8926943683389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>23.56508642736611</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29.16154621998511</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29.17352525324825</v>
+      </c>
+      <c r="E9" t="n">
+        <v>35.59505600852178</v>
+      </c>
+      <c r="F9" t="n">
+        <v>29.12303843550059</v>
+      </c>
+      <c r="G9" t="n">
+        <v>29.16602959384065</v>
+      </c>
+      <c r="H9" t="n">
+        <v>29.17352183956994</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29.12304267756146</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.17352183956994</v>
+      </c>
+      <c r="K9" t="n">
+        <v>25.92397377149337</v>
+      </c>
+      <c r="L9" t="n">
+        <v>29.17352183956994</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>159.2082838814111</v>
+      </c>
+      <c r="C10" t="n">
+        <v>167.7646917008386</v>
+      </c>
+      <c r="D10" t="n">
+        <v>167.17380093503</v>
+      </c>
+      <c r="E10" t="n">
+        <v>166.4415408791668</v>
+      </c>
+      <c r="F10" t="n">
+        <v>166.4415408791668</v>
+      </c>
+      <c r="G10" t="n">
+        <v>165.2514057182713</v>
+      </c>
+      <c r="H10" t="n">
+        <v>162.6391275551879</v>
+      </c>
+      <c r="I10" t="n">
+        <v>166.4415408791668</v>
+      </c>
+      <c r="J10" t="n">
+        <v>172.4600929918984</v>
+      </c>
+      <c r="K10" t="n">
+        <v>173.5141624099639</v>
+      </c>
+      <c r="L10" t="n">
+        <v>180.3865360521726</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>157.9040437327918</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>157.9040437327917</v>
+      </c>
+      <c r="C11" t="n">
         <v>165.6242077267931</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>167.3588370944452</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>166.1615605125498</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>166.1615605125498</v>
       </c>
-      <c r="G9" t="n">
-        <v>165.5949088524006</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>165.5949088524005</v>
+      </c>
+      <c r="H11" t="n">
         <v>165.5204774085975</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>166.1615605125498</v>
       </c>
-      <c r="J9" t="n">
-        <v>175.8407248644211</v>
-      </c>
-      <c r="K9" t="n">
-        <v>173.6689055426258</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J11" t="n">
+        <v>175.8407248644212</v>
+      </c>
+      <c r="K11" t="n">
+        <v>173.668905542626</v>
+      </c>
+      <c r="L11" t="n">
         <v>180.0333863328626</v>
       </c>
     </row>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,320 +3367,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.88337365128431</v>
+        <v>156.1483505204604</v>
       </c>
       <c r="C2" t="n">
-        <v>15.97818552545496</v>
+        <v>165.5651302985513</v>
       </c>
       <c r="D2" t="n">
-        <v>89.14882729394088</v>
+        <v>168.3881192881794</v>
       </c>
       <c r="E2" t="n">
-        <v>66.38358347312709</v>
+        <v>167.0358376578299</v>
       </c>
       <c r="F2" t="n">
-        <v>66.38358347312709</v>
+        <v>167.0358376578299</v>
       </c>
       <c r="G2" t="n">
-        <v>84.29988258805051</v>
+        <v>166.9171405960864</v>
       </c>
       <c r="H2" t="n">
-        <v>182.5678933623367</v>
+        <v>168.475738648844</v>
       </c>
       <c r="I2" t="n">
-        <v>66.38358347312709</v>
+        <v>167.0358376578299</v>
       </c>
       <c r="J2" t="n">
-        <v>213.3979686179302</v>
+        <v>179.3394924671522</v>
       </c>
       <c r="K2" t="n">
-        <v>58.74005408497105</v>
+        <v>174.5636074091769</v>
       </c>
       <c r="L2" t="n">
-        <v>46.41916111726327</v>
+        <v>181.1995191850277</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.100153940537465</v>
+        <v>158.5669042973954</v>
       </c>
       <c r="C3" t="n">
-        <v>3.733332373093426</v>
+        <v>168.159291785541</v>
       </c>
       <c r="D3" t="n">
-        <v>4.100153940537465</v>
+        <v>170.9402184401178</v>
       </c>
       <c r="E3" t="n">
-        <v>3.976689586979306</v>
+        <v>169.5942869669244</v>
       </c>
       <c r="F3" t="n">
-        <v>3.976689586979306</v>
+        <v>169.5942869669244</v>
       </c>
       <c r="G3" t="n">
-        <v>4.093837882289751</v>
+        <v>169.4540963966333</v>
       </c>
       <c r="H3" t="n">
-        <v>4.100153940537465</v>
+        <v>170.9402184401178</v>
       </c>
       <c r="I3" t="n">
-        <v>4.057043847464437</v>
+        <v>169.5942869669244</v>
       </c>
       <c r="J3" t="n">
-        <v>4.100153940537465</v>
+        <v>181.9294828918288</v>
       </c>
       <c r="K3" t="n">
-        <v>4.100153940537465</v>
+        <v>177.2501302500482</v>
       </c>
       <c r="L3" t="n">
-        <v>4.100153940537465</v>
+        <v>184.0121442140497</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.384969886857</v>
+        <v>38.88337365128413</v>
       </c>
       <c r="C4" t="n">
-        <v>635.1980208022017</v>
+        <v>15.97818552545484</v>
       </c>
       <c r="D4" t="n">
-        <v>760.0575075649191</v>
+        <v>89.14882729394066</v>
       </c>
       <c r="E4" t="n">
-        <v>572.4685304161831</v>
+        <v>66.38358347312705</v>
       </c>
       <c r="F4" t="n">
-        <v>635.3464584545242</v>
+        <v>66.38358347312705</v>
       </c>
       <c r="G4" t="n">
-        <v>635.3786538286088</v>
+        <v>84.29988258805048</v>
       </c>
       <c r="H4" t="n">
-        <v>760.7026177637041</v>
+        <v>182.5678933623366</v>
       </c>
       <c r="I4" t="n">
-        <v>759.8238239852443</v>
+        <v>66.38358347312705</v>
       </c>
       <c r="J4" t="n">
-        <v>760.2327068855521</v>
+        <v>213.3979686179298</v>
       </c>
       <c r="K4" t="n">
-        <v>635.3515812425302</v>
+        <v>58.74005408496826</v>
       </c>
       <c r="L4" t="n">
-        <v>635.3875420276703</v>
+        <v>46.41916111726314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.909716740258677</v>
+        <v>4.100153940537521</v>
       </c>
       <c r="C5" t="n">
-        <v>8.902446820574466</v>
+        <v>3.73333237309339</v>
       </c>
       <c r="D5" t="n">
-        <v>8.909735293927218</v>
+        <v>4.10015394053752</v>
       </c>
       <c r="E5" t="n">
-        <v>8.85718148998323</v>
+        <v>3.97668958697931</v>
       </c>
       <c r="F5" t="n">
-        <v>8.85718148998323</v>
+        <v>3.97668958697931</v>
       </c>
       <c r="G5" t="n">
-        <v>8.903400682010975</v>
+        <v>4.093837882289636</v>
       </c>
       <c r="H5" t="n">
-        <v>8.909716740258677</v>
+        <v>4.100153940537521</v>
       </c>
       <c r="I5" t="n">
-        <v>8.866606647185671</v>
+        <v>4.057043847464441</v>
       </c>
       <c r="J5" t="n">
-        <v>8.909716740258677</v>
+        <v>4.100153940537521</v>
       </c>
       <c r="K5" t="n">
-        <v>8.909716740258677</v>
+        <v>4.100153940537521</v>
       </c>
       <c r="L5" t="n">
-        <v>8.909716740258677</v>
+        <v>4.100153940537521</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.42659120529153</v>
+        <v>635.3849698868569</v>
       </c>
       <c r="C6" t="n">
-        <v>15.25863066317601</v>
+        <v>635.198020802202</v>
       </c>
       <c r="D6" t="n">
-        <v>16.27920497077704</v>
+        <v>760.0575075649194</v>
       </c>
       <c r="E6" t="n">
-        <v>13.89798576413125</v>
+        <v>572.4685304161828</v>
       </c>
       <c r="F6" t="n">
-        <v>10.53150451863471</v>
+        <v>635.3464584545238</v>
       </c>
       <c r="G6" t="n">
-        <v>15.26773627087254</v>
+        <v>635.3786538286087</v>
       </c>
       <c r="H6" t="n">
-        <v>15.2740523291545</v>
+        <v>760.7026177637033</v>
       </c>
       <c r="I6" t="n">
-        <v>15.23094223604723</v>
+        <v>759.8238239852448</v>
       </c>
       <c r="J6" t="n">
-        <v>15.27500498451139</v>
+        <v>760.2327068855523</v>
       </c>
       <c r="K6" t="n">
-        <v>10.33654712708658</v>
+        <v>635.3515812425668</v>
       </c>
       <c r="L6" t="n">
-        <v>20.33763080211135</v>
+        <v>635.3875420276707</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.94303941550416</v>
+        <v>8.909716740258659</v>
       </c>
       <c r="C7" t="n">
-        <v>20.84779883769763</v>
+        <v>8.902446820574433</v>
       </c>
       <c r="D7" t="n">
-        <v>20.85507094716012</v>
+        <v>8.909735293927138</v>
       </c>
       <c r="E7" t="n">
-        <v>25.32635706557238</v>
+        <v>8.857181489983212</v>
       </c>
       <c r="F7" t="n">
-        <v>20.81195667202446</v>
+        <v>8.857181489983212</v>
       </c>
       <c r="G7" t="n">
-        <v>20.84875269913415</v>
+        <v>8.903400682010854</v>
       </c>
       <c r="H7" t="n">
-        <v>20.85506875738186</v>
+        <v>8.909716740258659</v>
       </c>
       <c r="I7" t="n">
-        <v>20.81195866430885</v>
+        <v>8.866606647185648</v>
       </c>
       <c r="J7" t="n">
-        <v>20.85506875738186</v>
+        <v>8.909716740258659</v>
       </c>
       <c r="K7" t="n">
-        <v>18.5884245139853</v>
+        <v>8.909716740258659</v>
       </c>
       <c r="L7" t="n">
-        <v>20.85506875738186</v>
+        <v>8.909716740258659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157.7414760657431</v>
+        <v>10.4265912052914</v>
       </c>
       <c r="C8" t="n">
-        <v>167.8663210510701</v>
+        <v>15.25863066317592</v>
       </c>
       <c r="D8" t="n">
-        <v>168.8539789700452</v>
+        <v>16.27920497077679</v>
       </c>
       <c r="E8" t="n">
-        <v>168.0781724920833</v>
+        <v>13.8979857641312</v>
       </c>
       <c r="F8" t="n">
-        <v>168.0781724920833</v>
+        <v>10.53150451863466</v>
       </c>
       <c r="G8" t="n">
-        <v>167.5443998807485</v>
+        <v>15.26773627087226</v>
       </c>
       <c r="H8" t="n">
-        <v>167.0915614054946</v>
+        <v>15.27405232915418</v>
       </c>
       <c r="I8" t="n">
-        <v>168.0781724920833</v>
+        <v>15.23094223604716</v>
       </c>
       <c r="J8" t="n">
-        <v>177.0713915612118</v>
+        <v>15.27500498451127</v>
       </c>
       <c r="K8" t="n">
-        <v>175.9115431136733</v>
+        <v>10.3365471270864</v>
       </c>
       <c r="L8" t="n">
-        <v>183.1115777791237</v>
+        <v>20.33763080211103</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16.94303941550404</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20.84779883769762</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20.85507094715998</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25.32635706557233</v>
+      </c>
+      <c r="F9" t="n">
+        <v>20.81195667202445</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20.8487526991341</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20.85506875738189</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20.81195866430881</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.85506875738189</v>
+      </c>
+      <c r="K9" t="n">
+        <v>18.58842451398527</v>
+      </c>
+      <c r="L9" t="n">
+        <v>20.85506875738189</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>157.7414760657431</v>
+      </c>
+      <c r="C10" t="n">
+        <v>167.8663210510701</v>
+      </c>
+      <c r="D10" t="n">
+        <v>168.8539789700452</v>
+      </c>
+      <c r="E10" t="n">
+        <v>168.0781724920832</v>
+      </c>
+      <c r="F10" t="n">
+        <v>168.0781724920832</v>
+      </c>
+      <c r="G10" t="n">
+        <v>167.5443998807485</v>
+      </c>
+      <c r="H10" t="n">
+        <v>167.0915614054946</v>
+      </c>
+      <c r="I10" t="n">
+        <v>168.0781724920832</v>
+      </c>
+      <c r="J10" t="n">
+        <v>177.0713915612115</v>
+      </c>
+      <c r="K10" t="n">
+        <v>175.9115431136732</v>
+      </c>
+      <c r="L10" t="n">
+        <v>183.1115777791236</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>155.7727780445751</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>155.7727780445749</v>
+      </c>
+      <c r="C11" t="n">
         <v>165.4318276807246</v>
       </c>
-      <c r="D9" t="n">
-        <v>167.4388736808458</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>167.4388736808457</v>
+      </c>
+      <c r="E11" t="n">
+        <v>166.3460007402071</v>
+      </c>
+      <c r="F11" t="n">
         <v>166.3460007402072</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G11" t="n">
+        <v>166.0482225955171</v>
+      </c>
+      <c r="H11" t="n">
+        <v>166.7245874331483</v>
+      </c>
+      <c r="I11" t="n">
         <v>166.3460007402072</v>
       </c>
-      <c r="G9" t="n">
-        <v>166.0482225955169</v>
-      </c>
-      <c r="H9" t="n">
-        <v>166.7245874331483</v>
-      </c>
-      <c r="I9" t="n">
-        <v>166.3460007402072</v>
-      </c>
-      <c r="J9" t="n">
-        <v>177.1290454299029</v>
-      </c>
-      <c r="K9" t="n">
-        <v>173.9545459963023</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J11" t="n">
+        <v>177.1290454299027</v>
+      </c>
+      <c r="K11" t="n">
+        <v>173.9545459963021</v>
+      </c>
+      <c r="L11" t="n">
         <v>180.7897585872014</v>
       </c>
     </row>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.96581352492467</v>
+        <v>152.1838685527595</v>
       </c>
       <c r="C2" t="n">
-        <v>11.67518110329363</v>
+        <v>165.4189173547984</v>
       </c>
       <c r="D2" t="n">
-        <v>78.44566520480981</v>
+        <v>167.785010456019</v>
       </c>
       <c r="E2" t="n">
-        <v>26.12022231020516</v>
+        <v>166.6478824372508</v>
       </c>
       <c r="F2" t="n">
-        <v>26.12022231020516</v>
+        <v>166.6478824372508</v>
       </c>
       <c r="G2" t="n">
-        <v>44.75472862379219</v>
+        <v>166.4902981471428</v>
       </c>
       <c r="H2" t="n">
-        <v>124.938410310026</v>
+        <v>167.8247404154939</v>
       </c>
       <c r="I2" t="n">
-        <v>26.12022231020516</v>
+        <v>166.6478824372508</v>
       </c>
       <c r="J2" t="n">
-        <v>80.00509154785904</v>
+        <v>178.4624162135597</v>
       </c>
       <c r="K2" t="n">
-        <v>17.49936814418139</v>
+        <v>174.8758424861707</v>
       </c>
       <c r="L2" t="n">
-        <v>13.21351817445447</v>
+        <v>180.7894493610519</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.577126551821347</v>
+        <v>154.5619069251204</v>
       </c>
       <c r="C3" t="n">
-        <v>3.245569032837282</v>
+        <v>168.017595258184</v>
       </c>
       <c r="D3" t="n">
-        <v>3.577126551821347</v>
+        <v>170.3420451915666</v>
       </c>
       <c r="E3" t="n">
-        <v>3.417275828195279</v>
+        <v>169.2492546879503</v>
       </c>
       <c r="F3" t="n">
-        <v>3.417275828195279</v>
+        <v>169.2492546879503</v>
       </c>
       <c r="G3" t="n">
-        <v>3.570854608416782</v>
+        <v>169.0679546819194</v>
       </c>
       <c r="H3" t="n">
-        <v>3.577126551821346</v>
+        <v>170.3420451915666</v>
       </c>
       <c r="I3" t="n">
-        <v>3.534162566131514</v>
+        <v>169.2492546879503</v>
       </c>
       <c r="J3" t="n">
-        <v>3.577126551821346</v>
+        <v>181.1913518926681</v>
       </c>
       <c r="K3" t="n">
-        <v>3.577126551821347</v>
+        <v>177.6178148229806</v>
       </c>
       <c r="L3" t="n">
-        <v>3.577126551821347</v>
+        <v>183.6319745379649</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>758.7569898762086</v>
+        <v>20.96581352492508</v>
       </c>
       <c r="C4" t="n">
-        <v>634.5205044659799</v>
+        <v>11.67518110329365</v>
       </c>
       <c r="D4" t="n">
-        <v>634.728546830289</v>
+        <v>78.4456652048102</v>
       </c>
       <c r="E4" t="n">
-        <v>571.7394412108605</v>
+        <v>26.12022231020526</v>
       </c>
       <c r="F4" t="n">
-        <v>634.5927613105713</v>
+        <v>26.12022231020526</v>
       </c>
       <c r="G4" t="n">
-        <v>758.7507179328043</v>
+        <v>44.75472862379227</v>
       </c>
       <c r="H4" t="n">
-        <v>634.6799842477197</v>
+        <v>124.9384103100266</v>
       </c>
       <c r="I4" t="n">
-        <v>758.7140258905189</v>
+        <v>26.12022231020526</v>
       </c>
       <c r="J4" t="n">
-        <v>666.8039185661185</v>
+        <v>80.00509154785935</v>
       </c>
       <c r="K4" t="n">
-        <v>634.5896377999278</v>
+        <v>17.49936814418183</v>
       </c>
       <c r="L4" t="n">
-        <v>634.640488301361</v>
+        <v>13.21351817445451</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.966227511815119</v>
+        <v>3.577126551821721</v>
       </c>
       <c r="C5" t="n">
-        <v>7.960573003186351</v>
+        <v>3.245569032837229</v>
       </c>
       <c r="D5" t="n">
-        <v>7.966251021504368</v>
+        <v>3.577126551821721</v>
       </c>
       <c r="E5" t="n">
-        <v>7.902363342675267</v>
+        <v>3.417275828195289</v>
       </c>
       <c r="F5" t="n">
-        <v>7.902363342675267</v>
+        <v>3.417275828195293</v>
       </c>
       <c r="G5" t="n">
-        <v>7.959955568410379</v>
+        <v>3.570854608417036</v>
       </c>
       <c r="H5" t="n">
-        <v>7.966227511815119</v>
+        <v>3.577126551821721</v>
       </c>
       <c r="I5" t="n">
-        <v>7.923263526125052</v>
+        <v>3.5341625661315</v>
       </c>
       <c r="J5" t="n">
-        <v>7.966227511815119</v>
+        <v>3.577126551821721</v>
       </c>
       <c r="K5" t="n">
-        <v>7.966227511815119</v>
+        <v>3.577126551821721</v>
       </c>
       <c r="L5" t="n">
-        <v>7.966227511815119</v>
+        <v>3.577126551821721</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.112675711765172</v>
+        <v>758.7569898762096</v>
       </c>
       <c r="C6" t="n">
-        <v>13.28046781934361</v>
+        <v>634.5205044659805</v>
       </c>
       <c r="D6" t="n">
-        <v>14.17477073480934</v>
+        <v>634.7285468302894</v>
       </c>
       <c r="E6" t="n">
-        <v>12.09860537909302</v>
+        <v>571.7394412108605</v>
       </c>
       <c r="F6" t="n">
-        <v>9.190132146597199</v>
+        <v>634.5927613105713</v>
       </c>
       <c r="G6" t="n">
-        <v>13.29911318202634</v>
+        <v>758.7507179328053</v>
       </c>
       <c r="H6" t="n">
-        <v>13.30538512546536</v>
+        <v>634.6799842477202</v>
       </c>
       <c r="I6" t="n">
-        <v>13.26242113974078</v>
+        <v>758.7140258905185</v>
       </c>
       <c r="J6" t="n">
-        <v>13.30620910514099</v>
+        <v>666.8039185661186</v>
       </c>
       <c r="K6" t="n">
-        <v>9.034793982580913</v>
+        <v>634.5896377999286</v>
       </c>
       <c r="L6" t="n">
-        <v>17.68502068931031</v>
+        <v>634.640488301362</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.46628913794584</v>
+        <v>7.966227511815255</v>
       </c>
       <c r="C7" t="n">
-        <v>17.76609383590695</v>
+        <v>7.960573003186343</v>
       </c>
       <c r="D7" t="n">
-        <v>17.771749795879</v>
+        <v>7.966251021504571</v>
       </c>
       <c r="E7" t="n">
-        <v>21.54321327458051</v>
+        <v>7.902363342675267</v>
       </c>
       <c r="F7" t="n">
-        <v>17.72878257196838</v>
+        <v>7.902363342675267</v>
       </c>
       <c r="G7" t="n">
-        <v>17.76547640113114</v>
+        <v>7.959955568410582</v>
       </c>
       <c r="H7" t="n">
-        <v>17.77174834453562</v>
+        <v>7.966227511815255</v>
       </c>
       <c r="I7" t="n">
-        <v>17.72878435884565</v>
+        <v>7.923263526125037</v>
       </c>
       <c r="J7" t="n">
-        <v>17.77174834453562</v>
+        <v>7.966227511815255</v>
       </c>
       <c r="K7" t="n">
-        <v>15.85655290912708</v>
+        <v>7.966227511815255</v>
       </c>
       <c r="L7" t="n">
-        <v>17.77174834453562</v>
+        <v>7.966227511815255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>154.1516047794871</v>
+        <v>9.112675711765204</v>
       </c>
       <c r="C8" t="n">
-        <v>167.8177593128154</v>
+        <v>13.28046781934362</v>
       </c>
       <c r="D8" t="n">
-        <v>168.5075019982219</v>
+        <v>14.17477073480943</v>
       </c>
       <c r="E8" t="n">
-        <v>168.6961632596245</v>
+        <v>12.09860537909303</v>
       </c>
       <c r="F8" t="n">
-        <v>168.6961632596245</v>
+        <v>9.190132146597202</v>
       </c>
       <c r="G8" t="n">
-        <v>168.0855687954221</v>
+        <v>13.29911318202632</v>
       </c>
       <c r="H8" t="n">
-        <v>167.7249434046071</v>
+        <v>13.30538512546545</v>
       </c>
       <c r="I8" t="n">
-        <v>168.6961632596245</v>
+        <v>13.26242113974079</v>
       </c>
       <c r="J8" t="n">
-        <v>179.4140955470431</v>
+        <v>13.30620910514128</v>
       </c>
       <c r="K8" t="n">
-        <v>177.2718222416554</v>
+        <v>9.034793982581109</v>
       </c>
       <c r="L8" t="n">
-        <v>183.4234106757945</v>
+        <v>17.68502068931024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14.466289137946</v>
+      </c>
+      <c r="C9" t="n">
+        <v>17.76609383590698</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17.77174979587892</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21.54321327458053</v>
+      </c>
+      <c r="F9" t="n">
+        <v>17.72878257196843</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17.7654764011312</v>
+      </c>
+      <c r="H9" t="n">
+        <v>17.77174834453589</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17.72878435884567</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17.77174834453589</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.85655290912686</v>
+      </c>
+      <c r="L9" t="n">
+        <v>17.77174834453589</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>154.1516047794873</v>
+      </c>
+      <c r="C10" t="n">
+        <v>167.8177593128153</v>
+      </c>
+      <c r="D10" t="n">
+        <v>168.507501998222</v>
+      </c>
+      <c r="E10" t="n">
+        <v>168.6961632596245</v>
+      </c>
+      <c r="F10" t="n">
+        <v>168.6961632596245</v>
+      </c>
+      <c r="G10" t="n">
+        <v>168.0855687954223</v>
+      </c>
+      <c r="H10" t="n">
+        <v>167.7249434046072</v>
+      </c>
+      <c r="I10" t="n">
+        <v>168.6961632596245</v>
+      </c>
+      <c r="J10" t="n">
+        <v>179.4140955470432</v>
+      </c>
+      <c r="K10" t="n">
+        <v>177.2718222416553</v>
+      </c>
+      <c r="L10" t="n">
+        <v>183.4234106757945</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>151.9971797689409</v>
-      </c>
-      <c r="C9" t="n">
-        <v>165.3279913628166</v>
-      </c>
-      <c r="D9" t="n">
-        <v>166.950287456705</v>
-      </c>
-      <c r="E9" t="n">
-        <v>166.3962240747646</v>
-      </c>
-      <c r="F9" t="n">
-        <v>166.3962240747646</v>
-      </c>
-      <c r="G9" t="n">
-        <v>166.0433094381085</v>
-      </c>
-      <c r="H9" t="n">
-        <v>166.6339507622187</v>
-      </c>
-      <c r="I9" t="n">
-        <v>166.3962240747646</v>
-      </c>
-      <c r="J9" t="n">
-        <v>177.6537589125204</v>
-      </c>
-      <c r="K9" t="n">
-        <v>174.7184147590548</v>
-      </c>
-      <c r="L9" t="n">
-        <v>180.6945521391106</v>
+      <c r="B11" t="n">
+        <v>151.997179768941</v>
+      </c>
+      <c r="C11" t="n">
+        <v>165.3279913628164</v>
+      </c>
+      <c r="D11" t="n">
+        <v>166.9502874567049</v>
+      </c>
+      <c r="E11" t="n">
+        <v>166.3962240747647</v>
+      </c>
+      <c r="F11" t="n">
+        <v>166.3962240747647</v>
+      </c>
+      <c r="G11" t="n">
+        <v>166.0433094381086</v>
+      </c>
+      <c r="H11" t="n">
+        <v>166.6339507622188</v>
+      </c>
+      <c r="I11" t="n">
+        <v>166.3962240747647</v>
+      </c>
+      <c r="J11" t="n">
+        <v>177.6537589125205</v>
+      </c>
+      <c r="K11" t="n">
+        <v>174.7184147590547</v>
+      </c>
+      <c r="L11" t="n">
+        <v>180.6945521391108</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.57775513306706</v>
+        <v>156.7129622397586</v>
       </c>
       <c r="C2" t="n">
-        <v>25.07411827772972</v>
+        <v>165.1469644837362</v>
       </c>
       <c r="D2" t="n">
-        <v>128.2756330762591</v>
+        <v>169.1067106251844</v>
       </c>
       <c r="E2" t="n">
-        <v>150.8821779887728</v>
+        <v>167.6003632050239</v>
       </c>
       <c r="F2" t="n">
-        <v>150.8821779887728</v>
+        <v>167.6003632050239</v>
       </c>
       <c r="G2" t="n">
-        <v>161.761443683549</v>
+        <v>167.209264300871</v>
       </c>
       <c r="H2" t="n">
-        <v>398.6381048524848</v>
+        <v>169.3607850264896</v>
       </c>
       <c r="I2" t="n">
-        <v>150.8821779887728</v>
+        <v>167.6003632050239</v>
       </c>
       <c r="J2" t="n">
-        <v>322.1565127440151</v>
+        <v>179.9852117395225</v>
       </c>
       <c r="K2" t="n">
-        <v>148.7508583279007</v>
+        <v>174.9730644810971</v>
       </c>
       <c r="L2" t="n">
-        <v>168.4965463535916</v>
+        <v>181.6715870300411</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.691139572988281</v>
+        <v>159.0961590110134</v>
       </c>
       <c r="C3" t="n">
-        <v>4.278018885682593</v>
+        <v>167.7232396062793</v>
       </c>
       <c r="D3" t="n">
-        <v>4.691139572988281</v>
+        <v>171.6296871935631</v>
       </c>
       <c r="E3" t="n">
-        <v>4.583376414147587</v>
+        <v>170.0756963061138</v>
       </c>
       <c r="F3" t="n">
-        <v>4.583376414147591</v>
+        <v>170.0756963061138</v>
       </c>
       <c r="G3" t="n">
-        <v>4.685179530613843</v>
+        <v>169.6690699087771</v>
       </c>
       <c r="H3" t="n">
-        <v>4.691139572988281</v>
+        <v>171.6296871935631</v>
       </c>
       <c r="I3" t="n">
-        <v>4.650436806301353</v>
+        <v>170.0756963061138</v>
       </c>
       <c r="J3" t="n">
-        <v>4.691139572988281</v>
+        <v>182.4793263310803</v>
       </c>
       <c r="K3" t="n">
-        <v>4.691139572988281</v>
+        <v>177.5669719214029</v>
       </c>
       <c r="L3" t="n">
-        <v>4.691139572988281</v>
+        <v>184.371784472898</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>671.4017095096931</v>
+        <v>79.57775513306649</v>
       </c>
       <c r="C4" t="n">
-        <v>671.0882359392418</v>
+        <v>25.07411827772994</v>
       </c>
       <c r="D4" t="n">
-        <v>671.3682906259853</v>
+        <v>128.275633076266</v>
       </c>
       <c r="E4" t="n">
-        <v>604.9948366489941</v>
+        <v>150.8821779887765</v>
       </c>
       <c r="F4" t="n">
-        <v>671.3823961697964</v>
+        <v>150.8821779887765</v>
       </c>
       <c r="G4" t="n">
-        <v>671.395749467318</v>
+        <v>161.7614436835533</v>
       </c>
       <c r="H4" t="n">
-        <v>804.2226650239342</v>
+        <v>398.6381048524842</v>
       </c>
       <c r="I4" t="n">
-        <v>671.3610067430066</v>
+        <v>150.8821779887765</v>
       </c>
       <c r="J4" t="n">
-        <v>705.456605977034</v>
+        <v>322.1565127440269</v>
       </c>
       <c r="K4" t="n">
-        <v>671.4043627516251</v>
+        <v>148.750858327884</v>
       </c>
       <c r="L4" t="n">
-        <v>671.4268492574658</v>
+        <v>168.4965463535916</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.25822312751433</v>
+        <v>4.691139572988235</v>
       </c>
       <c r="C5" t="n">
-        <v>10.24861595955486</v>
+        <v>4.278018885682663</v>
       </c>
       <c r="D5" t="n">
-        <v>10.25823033888281</v>
+        <v>4.691139572988235</v>
       </c>
       <c r="E5" t="n">
-        <v>10.21095280556368</v>
+        <v>4.583376414147591</v>
       </c>
       <c r="F5" t="n">
-        <v>10.21095280556368</v>
+        <v>4.583376414147605</v>
       </c>
       <c r="G5" t="n">
-        <v>10.25226308514003</v>
+        <v>4.685179530613962</v>
       </c>
       <c r="H5" t="n">
-        <v>10.25822312751433</v>
+        <v>4.691139572988235</v>
       </c>
       <c r="I5" t="n">
-        <v>10.2175203608274</v>
+        <v>4.650436806301355</v>
       </c>
       <c r="J5" t="n">
-        <v>10.25822312751433</v>
+        <v>4.691139572988235</v>
       </c>
       <c r="K5" t="n">
-        <v>10.25822312751433</v>
+        <v>4.691139572988235</v>
       </c>
       <c r="L5" t="n">
-        <v>10.25822312751433</v>
+        <v>4.691139572988235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.23075921582335</v>
+        <v>671.4017095096928</v>
       </c>
       <c r="C6" t="n">
-        <v>17.99133318862068</v>
+        <v>671.0882359392422</v>
       </c>
       <c r="D6" t="n">
-        <v>19.203728207212</v>
+        <v>671.368290625986</v>
       </c>
       <c r="E6" t="n">
-        <v>16.38133390412042</v>
+        <v>604.9948366489942</v>
       </c>
       <c r="F6" t="n">
-        <v>12.36920560730752</v>
+        <v>671.3823961697982</v>
       </c>
       <c r="G6" t="n">
-        <v>18.00020097809385</v>
+        <v>671.3957494673191</v>
       </c>
       <c r="H6" t="n">
-        <v>18.00616102049691</v>
+        <v>804.2226650239336</v>
       </c>
       <c r="I6" t="n">
-        <v>17.96545825378099</v>
+        <v>671.3610067430066</v>
       </c>
       <c r="J6" t="n">
-        <v>18.00729604188057</v>
+        <v>705.4566059770324</v>
       </c>
       <c r="K6" t="n">
-        <v>12.12347816313082</v>
+        <v>671.4043627516044</v>
       </c>
       <c r="L6" t="n">
-        <v>24.03905112690438</v>
+        <v>671.4268492574683</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.56288835132167</v>
+        <v>10.25822312751427</v>
       </c>
       <c r="C7" t="n">
-        <v>26.64789102333413</v>
+        <v>10.24861595955485</v>
       </c>
       <c r="D7" t="n">
-        <v>26.65750021947699</v>
+        <v>10.25823033888279</v>
       </c>
       <c r="E7" t="n">
-        <v>32.49586425030289</v>
+        <v>10.2109528055637</v>
       </c>
       <c r="F7" t="n">
-        <v>26.61679163269603</v>
+        <v>10.2109528055637</v>
       </c>
       <c r="G7" t="n">
-        <v>26.651538148919</v>
+        <v>10.25226308513998</v>
       </c>
       <c r="H7" t="n">
-        <v>26.65749819129366</v>
+        <v>10.25822312751427</v>
       </c>
       <c r="I7" t="n">
-        <v>26.61679542460659</v>
+        <v>10.21752036082736</v>
       </c>
       <c r="J7" t="n">
-        <v>26.65749819129366</v>
+        <v>10.25822312751427</v>
       </c>
       <c r="K7" t="n">
-        <v>23.70566209498315</v>
+        <v>10.25822312751427</v>
       </c>
       <c r="L7" t="n">
-        <v>26.65749819129366</v>
+        <v>10.25822312751427</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157.4141933423801</v>
+        <v>12.23075921582341</v>
       </c>
       <c r="C8" t="n">
-        <v>167.252891463649</v>
+        <v>17.99133318862084</v>
       </c>
       <c r="D8" t="n">
-        <v>168.761220362931</v>
+        <v>19.20372820721211</v>
       </c>
       <c r="E8" t="n">
-        <v>166.7185249690421</v>
+        <v>16.38133390412048</v>
       </c>
       <c r="F8" t="n">
-        <v>166.7185249690421</v>
+        <v>12.36920560730755</v>
       </c>
       <c r="G8" t="n">
-        <v>166.1342365704935</v>
+        <v>18.00020097809369</v>
       </c>
       <c r="H8" t="n">
-        <v>163.5912511901874</v>
+        <v>18.00616102049694</v>
       </c>
       <c r="I8" t="n">
-        <v>166.7185249690421</v>
+        <v>17.96545825378111</v>
       </c>
       <c r="J8" t="n">
-        <v>175.5029919916133</v>
+        <v>18.00729604188052</v>
       </c>
       <c r="K8" t="n">
-        <v>174.2394155929078</v>
+        <v>12.12347816313092</v>
       </c>
       <c r="L8" t="n">
-        <v>181.0904687764512</v>
+        <v>24.03905112690426</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>21.56288835132166</v>
+      </c>
+      <c r="C9" t="n">
+        <v>26.64789102333414</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26.65750021947695</v>
+      </c>
+      <c r="E9" t="n">
+        <v>32.49586425030311</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26.61679163269597</v>
+      </c>
+      <c r="G9" t="n">
+        <v>26.65153814891917</v>
+      </c>
+      <c r="H9" t="n">
+        <v>26.65749819129353</v>
+      </c>
+      <c r="I9" t="n">
+        <v>26.6167954246066</v>
+      </c>
+      <c r="J9" t="n">
+        <v>26.65749819129353</v>
+      </c>
+      <c r="K9" t="n">
+        <v>23.70566209498319</v>
+      </c>
+      <c r="L9" t="n">
+        <v>26.65749819129353</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>157.41419334238</v>
+      </c>
+      <c r="C10" t="n">
+        <v>167.252891463649</v>
+      </c>
+      <c r="D10" t="n">
+        <v>168.7612203629311</v>
+      </c>
+      <c r="E10" t="n">
+        <v>166.7185249690421</v>
+      </c>
+      <c r="F10" t="n">
+        <v>166.7185249690421</v>
+      </c>
+      <c r="G10" t="n">
+        <v>166.1342365704932</v>
+      </c>
+      <c r="H10" t="n">
+        <v>163.5912511901874</v>
+      </c>
+      <c r="I10" t="n">
+        <v>166.7185249690421</v>
+      </c>
+      <c r="J10" t="n">
+        <v>175.5029919916133</v>
+      </c>
+      <c r="K10" t="n">
+        <v>174.239415592908</v>
+      </c>
+      <c r="L10" t="n">
+        <v>181.0904687764512</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>155.9476625004239</v>
-      </c>
-      <c r="C9" t="n">
-        <v>164.9329545799289</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>155.9476625004237</v>
+      </c>
+      <c r="C11" t="n">
+        <v>164.9329545799287</v>
+      </c>
+      <c r="D11" t="n">
         <v>167.8015490759855</v>
       </c>
-      <c r="E9" t="n">
-        <v>166.072839547986</v>
-      </c>
-      <c r="F9" t="n">
-        <v>166.072839547986</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E11" t="n">
+        <v>166.0728395479859</v>
+      </c>
+      <c r="F11" t="n">
+        <v>166.0728395479859</v>
+      </c>
+      <c r="G11" t="n">
         <v>165.6009038671066</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>165.7032710279781</v>
       </c>
-      <c r="I9" t="n">
-        <v>166.072839547986</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="I11" t="n">
+        <v>166.0728395479859</v>
+      </c>
+      <c r="J11" t="n">
         <v>176.8109573828067</v>
       </c>
-      <c r="K9" t="n">
-        <v>173.4590157473393</v>
-      </c>
-      <c r="L9" t="n">
-        <v>180.1785779312253</v>
+      <c r="K11" t="n">
+        <v>173.4590157473391</v>
+      </c>
+      <c r="L11" t="n">
+        <v>180.1785779312254</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,320 +4795,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.98122813827482</v>
+        <v>136.9267220730476</v>
       </c>
       <c r="C2" t="n">
-        <v>15.10419504429629</v>
+        <v>164.2566835918919</v>
       </c>
       <c r="D2" t="n">
-        <v>93.78777186637328</v>
+        <v>168.127046363144</v>
       </c>
       <c r="E2" t="n">
-        <v>57.56636978825838</v>
+        <v>166.3108235000142</v>
       </c>
       <c r="F2" t="n">
-        <v>57.56636978825838</v>
+        <v>166.3108235000143</v>
       </c>
       <c r="G2" t="n">
-        <v>67.24666116460567</v>
+        <v>164.5960148147709</v>
       </c>
       <c r="H2" t="n">
-        <v>150.9867725342009</v>
+        <v>168.1761960128414</v>
       </c>
       <c r="I2" t="n">
-        <v>57.56636978825838</v>
+        <v>166.3108235000142</v>
       </c>
       <c r="J2" t="n">
-        <v>108.4141494893438</v>
+        <v>178.7865612697238</v>
       </c>
       <c r="K2" t="n">
-        <v>43.69594633337608</v>
+        <v>172.3830862753441</v>
       </c>
       <c r="L2" t="n">
-        <v>15.812418388081</v>
+        <v>180.9630571056967</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.891114899935724</v>
+        <v>139.0438082101726</v>
       </c>
       <c r="C3" t="n">
-        <v>3.562740872424677</v>
+        <v>166.8319046924865</v>
       </c>
       <c r="D3" t="n">
-        <v>3.891114899935724</v>
+        <v>170.6703500693328</v>
       </c>
       <c r="E3" t="n">
-        <v>3.767695882959758</v>
+        <v>168.8688686892303</v>
       </c>
       <c r="F3" t="n">
-        <v>3.767695882959758</v>
+        <v>168.8688686892303</v>
       </c>
       <c r="G3" t="n">
-        <v>3.88599881227202</v>
+        <v>167.1165556881016</v>
       </c>
       <c r="H3" t="n">
-        <v>3.891114899935724</v>
+        <v>170.6703500693328</v>
       </c>
       <c r="I3" t="n">
-        <v>3.855849284448292</v>
+        <v>168.8688686892303</v>
       </c>
       <c r="J3" t="n">
-        <v>3.891114899935724</v>
+        <v>181.4874612357997</v>
       </c>
       <c r="K3" t="n">
-        <v>3.891114899935724</v>
+        <v>175.0535140391386</v>
       </c>
       <c r="L3" t="n">
-        <v>3.891114899935724</v>
+        <v>183.8045936971315</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>759.3726103755046</v>
+        <v>35.9812281382749</v>
       </c>
       <c r="C4" t="n">
-        <v>634.8982157565911</v>
+        <v>15.10419504429616</v>
       </c>
       <c r="D4" t="n">
-        <v>635.1200073649131</v>
+        <v>93.78777186637261</v>
       </c>
       <c r="E4" t="n">
-        <v>572.1695117880588</v>
+        <v>57.5663697882563</v>
       </c>
       <c r="F4" t="n">
-        <v>635.0210307859071</v>
+        <v>57.5663697882563</v>
       </c>
       <c r="G4" t="n">
-        <v>635.0482626341268</v>
+        <v>67.24666116460516</v>
       </c>
       <c r="H4" t="n">
-        <v>760.1874482620158</v>
+        <v>150.9867725342009</v>
       </c>
       <c r="I4" t="n">
-        <v>759.3373447600176</v>
+        <v>57.5663697882563</v>
       </c>
       <c r="J4" t="n">
-        <v>667.2287975903157</v>
+        <v>108.4141494893388</v>
       </c>
       <c r="K4" t="n">
-        <v>635.0072499962014</v>
+        <v>43.69594633337604</v>
       </c>
       <c r="L4" t="n">
-        <v>635.0492678975947</v>
+        <v>15.81241838808101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.449333672326244</v>
+        <v>3.891114899935796</v>
       </c>
       <c r="C5" t="n">
-        <v>8.443013885141168</v>
+        <v>3.562740872424615</v>
       </c>
       <c r="D5" t="n">
-        <v>8.449347943636202</v>
+        <v>3.891114899935796</v>
       </c>
       <c r="E5" t="n">
-        <v>8.400464022989944</v>
+        <v>3.767695882959754</v>
       </c>
       <c r="F5" t="n">
-        <v>8.400464022989944</v>
+        <v>3.767695882959754</v>
       </c>
       <c r="G5" t="n">
-        <v>8.444217584662443</v>
+        <v>3.885998812271981</v>
       </c>
       <c r="H5" t="n">
-        <v>8.449333672326244</v>
+        <v>3.891114899935796</v>
       </c>
       <c r="I5" t="n">
-        <v>8.414068056838753</v>
+        <v>3.855849284448287</v>
       </c>
       <c r="J5" t="n">
-        <v>8.449333672326244</v>
+        <v>3.891114899935789</v>
       </c>
       <c r="K5" t="n">
-        <v>8.449333672326244</v>
+        <v>3.891114899935796</v>
       </c>
       <c r="L5" t="n">
-        <v>8.449333672326244</v>
+        <v>3.891114899935796</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.745025342104483</v>
+        <v>759.3726103755049</v>
       </c>
       <c r="C6" t="n">
-        <v>14.19820083847179</v>
+        <v>634.89821575659</v>
       </c>
       <c r="D6" t="n">
-        <v>15.14397126130211</v>
+        <v>635.1200073649127</v>
       </c>
       <c r="E6" t="n">
-        <v>12.94764199129913</v>
+        <v>572.169511788058</v>
       </c>
       <c r="F6" t="n">
-        <v>9.843381994193129</v>
+        <v>635.0210307859063</v>
       </c>
       <c r="G6" t="n">
-        <v>14.21161736668476</v>
+        <v>635.0482626341264</v>
       </c>
       <c r="H6" t="n">
-        <v>14.21673345438751</v>
+        <v>760.1874482620148</v>
       </c>
       <c r="I6" t="n">
-        <v>14.18146783886107</v>
+        <v>759.3373447600175</v>
       </c>
       <c r="J6" t="n">
-        <v>14.21761226429292</v>
+        <v>667.228797590315</v>
       </c>
       <c r="K6" t="n">
-        <v>9.661961068940581</v>
+        <v>635.0072499962017</v>
       </c>
       <c r="L6" t="n">
-        <v>18.88780648750058</v>
+        <v>635.0492678975937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.16889186888723</v>
+        <v>8.449333672326135</v>
       </c>
       <c r="C7" t="n">
-        <v>19.88544989703529</v>
+        <v>8.443013885141147</v>
       </c>
       <c r="D7" t="n">
-        <v>19.89177163110033</v>
+        <v>8.44934794363626</v>
       </c>
       <c r="E7" t="n">
-        <v>24.15262584005139</v>
+        <v>8.400464022989944</v>
       </c>
       <c r="F7" t="n">
-        <v>19.85650242893023</v>
+        <v>8.400464022989944</v>
       </c>
       <c r="G7" t="n">
-        <v>19.8866535965565</v>
+        <v>8.444217584662459</v>
       </c>
       <c r="H7" t="n">
-        <v>19.89176968422029</v>
+        <v>8.449333672326135</v>
       </c>
       <c r="I7" t="n">
-        <v>19.85650406873283</v>
+        <v>8.414068056838742</v>
       </c>
       <c r="J7" t="n">
-        <v>19.89176968422029</v>
+        <v>8.449333672326135</v>
       </c>
       <c r="K7" t="n">
-        <v>15.20400147878707</v>
+        <v>8.449333672326135</v>
       </c>
       <c r="L7" t="n">
-        <v>19.89176968422029</v>
+        <v>8.449333672326135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>138.2841222248841</v>
+        <v>9.745025342104356</v>
       </c>
       <c r="C8" t="n">
-        <v>166.5566317158752</v>
+        <v>14.19820083847147</v>
       </c>
       <c r="D8" t="n">
-        <v>168.4674026071028</v>
+        <v>15.14397126130211</v>
       </c>
       <c r="E8" t="n">
-        <v>167.562393960894</v>
+        <v>12.94764199129911</v>
       </c>
       <c r="F8" t="n">
-        <v>167.562393960894</v>
+        <v>9.843381994193116</v>
       </c>
       <c r="G8" t="n">
-        <v>165.607321818474</v>
+        <v>14.21161736668479</v>
       </c>
       <c r="H8" t="n">
-        <v>167.4980581397496</v>
+        <v>14.21673345438758</v>
       </c>
       <c r="I8" t="n">
-        <v>167.562393960894</v>
+        <v>14.18146783886106</v>
       </c>
       <c r="J8" t="n">
-        <v>179.0578103295421</v>
+        <v>14.21761226429291</v>
       </c>
       <c r="K8" t="n">
-        <v>174.0769404675182</v>
+        <v>9.661961068940615</v>
       </c>
       <c r="L8" t="n">
-        <v>183.5464368708612</v>
+        <v>18.88780648750058</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16.16889186888709</v>
+      </c>
+      <c r="C9" t="n">
+        <v>19.88544989703519</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19.8917716311003</v>
+      </c>
+      <c r="E9" t="n">
+        <v>24.15262584005135</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19.85650242893022</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19.88665359655651</v>
+      </c>
+      <c r="H9" t="n">
+        <v>19.89176968422025</v>
+      </c>
+      <c r="I9" t="n">
+        <v>19.8565040687328</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19.89176968422025</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.20400147878692</v>
+      </c>
+      <c r="L9" t="n">
+        <v>19.89176968422025</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>138.2841222248842</v>
+      </c>
+      <c r="C10" t="n">
+        <v>166.5566317158753</v>
+      </c>
+      <c r="D10" t="n">
+        <v>168.4674026071028</v>
+      </c>
+      <c r="E10" t="n">
+        <v>167.562393960894</v>
+      </c>
+      <c r="F10" t="n">
+        <v>167.562393960894</v>
+      </c>
+      <c r="G10" t="n">
+        <v>165.6073218184738</v>
+      </c>
+      <c r="H10" t="n">
+        <v>167.4980581397497</v>
+      </c>
+      <c r="I10" t="n">
+        <v>167.562393960894</v>
+      </c>
+      <c r="J10" t="n">
+        <v>179.0578103295421</v>
+      </c>
+      <c r="K10" t="n">
+        <v>174.0769404675182</v>
+      </c>
+      <c r="L10" t="n">
+        <v>183.5464368708612</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>136.5810625287658</v>
       </c>
-      <c r="C9" t="n">
-        <v>164.1314335102909</v>
-      </c>
-      <c r="D9" t="n">
-        <v>167.1246982474525</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C11" t="n">
+        <v>164.1314335102907</v>
+      </c>
+      <c r="D11" t="n">
+        <v>167.1246982474524</v>
+      </c>
+      <c r="E11" t="n">
         <v>165.7163733351333</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>165.7163733351333</v>
       </c>
-      <c r="G9" t="n">
-        <v>163.9093085944475</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>163.9093085944473</v>
+      </c>
+      <c r="H11" t="n">
         <v>166.7327930753866</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>165.7163733351333</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>177.6810623645385</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>171.9387421881015</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>180.8455949270466</v>
       </c>
     </row>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.73383667465117</v>
+        <v>84.05389122454169</v>
       </c>
       <c r="C2" t="n">
-        <v>11.34440422524623</v>
+        <v>163.6474938387528</v>
       </c>
       <c r="D2" t="n">
-        <v>93.44216036394555</v>
+        <v>167.5508961919819</v>
       </c>
       <c r="E2" t="n">
-        <v>21.35183556280405</v>
+        <v>166.1659528761823</v>
       </c>
       <c r="F2" t="n">
-        <v>21.35183556280405</v>
+        <v>166.1659528761824</v>
       </c>
       <c r="G2" t="n">
-        <v>46.04419400599355</v>
+        <v>159.7637627842801</v>
       </c>
       <c r="H2" t="n">
-        <v>114.674501696752</v>
+        <v>167.5624052624803</v>
       </c>
       <c r="I2" t="n">
-        <v>21.35183556280405</v>
+        <v>166.1659528761823</v>
       </c>
       <c r="J2" t="n">
-        <v>63.73476159041786</v>
+        <v>178.0344044904033</v>
       </c>
       <c r="K2" t="n">
-        <v>19.87471466096461</v>
+        <v>173.4624295590791</v>
       </c>
       <c r="L2" t="n">
-        <v>12.44592307208805</v>
+        <v>180.6001992345942</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.352573259842949</v>
+        <v>85.3492781515257</v>
       </c>
       <c r="C3" t="n">
-        <v>3.06210874201805</v>
+        <v>166.2189308056115</v>
       </c>
       <c r="D3" t="n">
-        <v>3.352573259842949</v>
+        <v>170.0869970949408</v>
       </c>
       <c r="E3" t="n">
-        <v>3.23123713626335</v>
+        <v>168.7658533970713</v>
       </c>
       <c r="F3" t="n">
-        <v>3.23123713626335</v>
+        <v>168.7658533970713</v>
       </c>
       <c r="G3" t="n">
-        <v>3.350016733967903</v>
+        <v>162.2335137278755</v>
       </c>
       <c r="H3" t="n">
-        <v>3.352573259842949</v>
+        <v>170.0869970949408</v>
       </c>
       <c r="I3" t="n">
-        <v>3.334340937255819</v>
+        <v>168.7658533970713</v>
       </c>
       <c r="J3" t="n">
-        <v>3.352573259842949</v>
+        <v>180.7754914284272</v>
       </c>
       <c r="K3" t="n">
-        <v>3.352573259842949</v>
+        <v>176.1796575066371</v>
       </c>
       <c r="L3" t="n">
-        <v>3.352573259842949</v>
+        <v>183.441060676042</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>758.3168363328424</v>
+        <v>20.73383667465114</v>
       </c>
       <c r="C4" t="n">
-        <v>634.2220350742105</v>
+        <v>11.34440422524624</v>
       </c>
       <c r="D4" t="n">
-        <v>634.4450596530085</v>
+        <v>93.44216036394577</v>
       </c>
       <c r="E4" t="n">
-        <v>571.4687593975461</v>
+        <v>21.35183556280406</v>
       </c>
       <c r="F4" t="n">
-        <v>634.3115547975866</v>
+        <v>21.35183556280406</v>
       </c>
       <c r="G4" t="n">
-        <v>634.3342519747782</v>
+        <v>46.04419400599397</v>
       </c>
       <c r="H4" t="n">
-        <v>759.0102398169182</v>
+        <v>114.674501696752</v>
       </c>
       <c r="I4" t="n">
-        <v>634.3185761780659</v>
+        <v>21.35183556280406</v>
       </c>
       <c r="J4" t="n">
-        <v>758.6281463452608</v>
+        <v>63.73476159041792</v>
       </c>
       <c r="K4" t="n">
-        <v>634.2847461594478</v>
+        <v>19.87471466096459</v>
       </c>
       <c r="L4" t="n">
-        <v>634.3358272898593</v>
+        <v>12.44592307208811</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.547078111224549</v>
+        <v>3.352573259842926</v>
       </c>
       <c r="C5" t="n">
-        <v>7.541876157291276</v>
+        <v>3.062108742018101</v>
       </c>
       <c r="D5" t="n">
-        <v>7.547090954723436</v>
+        <v>3.352573259842926</v>
       </c>
       <c r="E5" t="n">
-        <v>7.512111439248047</v>
+        <v>3.231237136263346</v>
       </c>
       <c r="F5" t="n">
-        <v>7.512111439248047</v>
+        <v>3.231237136263346</v>
       </c>
       <c r="G5" t="n">
-        <v>7.544521585349524</v>
+        <v>3.350016733967884</v>
       </c>
       <c r="H5" t="n">
-        <v>7.547078111224549</v>
+        <v>3.352573259842926</v>
       </c>
       <c r="I5" t="n">
-        <v>7.528845788637427</v>
+        <v>3.334340937255811</v>
       </c>
       <c r="J5" t="n">
-        <v>7.547078111224549</v>
+        <v>3.352573259842926</v>
       </c>
       <c r="K5" t="n">
-        <v>7.547078111224549</v>
+        <v>3.352573259842926</v>
       </c>
       <c r="L5" t="n">
-        <v>7.547078111224549</v>
+        <v>3.352573259842926</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.490300581310326</v>
+        <v>758.3168363328421</v>
       </c>
       <c r="C6" t="n">
-        <v>12.32475319937806</v>
+        <v>634.2220350742106</v>
       </c>
       <c r="D6" t="n">
-        <v>13.14463935327346</v>
+        <v>634.4450596530082</v>
       </c>
       <c r="E6" t="n">
-        <v>11.25911114962811</v>
+        <v>571.4687593975461</v>
       </c>
       <c r="F6" t="n">
-        <v>8.58427475598239</v>
+        <v>634.3115547975877</v>
       </c>
       <c r="G6" t="n">
-        <v>12.34272700115277</v>
+        <v>634.3342519747782</v>
       </c>
       <c r="H6" t="n">
-        <v>12.3452835270652</v>
+        <v>759.0102398169186</v>
       </c>
       <c r="I6" t="n">
-        <v>12.32705120444067</v>
+        <v>634.3185761780662</v>
       </c>
       <c r="J6" t="n">
-        <v>12.34604113521829</v>
+        <v>758.6281463452613</v>
       </c>
       <c r="K6" t="n">
-        <v>8.418692294529672</v>
+        <v>634.284746159448</v>
       </c>
       <c r="L6" t="n">
-        <v>16.37213555623946</v>
+        <v>634.3358272898598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.99929701972374</v>
+        <v>7.547078111224534</v>
       </c>
       <c r="C7" t="n">
-        <v>17.19552952731748</v>
+        <v>7.541876157291291</v>
       </c>
       <c r="D7" t="n">
-        <v>17.20073299210799</v>
+        <v>7.547090954723385</v>
       </c>
       <c r="E7" t="n">
-        <v>20.87688600502197</v>
+        <v>7.512111439248053</v>
       </c>
       <c r="F7" t="n">
-        <v>17.1824975533429</v>
+        <v>7.512111439248053</v>
       </c>
       <c r="G7" t="n">
-        <v>17.19817495537572</v>
+        <v>7.544521585349509</v>
       </c>
       <c r="H7" t="n">
-        <v>17.20073148125077</v>
+        <v>7.547078111224534</v>
       </c>
       <c r="I7" t="n">
-        <v>17.18249915866362</v>
+        <v>7.528845788637438</v>
       </c>
       <c r="J7" t="n">
-        <v>17.20073148125077</v>
+        <v>7.547078111224534</v>
       </c>
       <c r="K7" t="n">
-        <v>15.27055178355448</v>
+        <v>7.547078111224534</v>
       </c>
       <c r="L7" t="n">
-        <v>17.20073148125077</v>
+        <v>7.547078111224534</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.9415329984391</v>
+        <v>8.490300581310304</v>
       </c>
       <c r="C8" t="n">
-        <v>166.0241795584537</v>
+        <v>12.32475319937803</v>
       </c>
       <c r="D8" t="n">
-        <v>167.8833525394915</v>
+        <v>13.14463935327343</v>
       </c>
       <c r="E8" t="n">
-        <v>168.3253492753852</v>
+        <v>11.25911114962811</v>
       </c>
       <c r="F8" t="n">
-        <v>168.3253492753852</v>
+        <v>8.58427475598239</v>
       </c>
       <c r="G8" t="n">
-        <v>161.2175722584881</v>
+        <v>12.34272700115274</v>
       </c>
       <c r="H8" t="n">
-        <v>167.6878697767208</v>
+        <v>12.34528352706518</v>
       </c>
       <c r="I8" t="n">
-        <v>168.3253492753852</v>
+        <v>12.32705120444067</v>
       </c>
       <c r="J8" t="n">
-        <v>179.3720552412972</v>
+        <v>12.34604113521829</v>
       </c>
       <c r="K8" t="n">
-        <v>175.7727656767248</v>
+        <v>8.418692294529677</v>
       </c>
       <c r="L8" t="n">
-        <v>183.2458491362292</v>
+        <v>16.37213555623944</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13.99929701972374</v>
+      </c>
+      <c r="C9" t="n">
+        <v>17.19552952731756</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17.20073299210802</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20.87688600502201</v>
+      </c>
+      <c r="F9" t="n">
+        <v>17.18249755334292</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17.19817495537572</v>
+      </c>
+      <c r="H9" t="n">
+        <v>17.20073148125076</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17.18249915866366</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17.20073148125076</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.27055178355447</v>
+      </c>
+      <c r="L9" t="n">
+        <v>17.20073148125076</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>84.9415329984391</v>
+      </c>
+      <c r="C10" t="n">
+        <v>166.0241795584537</v>
+      </c>
+      <c r="D10" t="n">
+        <v>167.8833525394915</v>
+      </c>
+      <c r="E10" t="n">
+        <v>168.3253492753853</v>
+      </c>
+      <c r="F10" t="n">
+        <v>168.3253492753853</v>
+      </c>
+      <c r="G10" t="n">
+        <v>161.2175722584882</v>
+      </c>
+      <c r="H10" t="n">
+        <v>167.6878697767208</v>
+      </c>
+      <c r="I10" t="n">
+        <v>168.3253492753853</v>
+      </c>
+      <c r="J10" t="n">
+        <v>179.3720552412973</v>
+      </c>
+      <c r="K10" t="n">
+        <v>175.7727656767248</v>
+      </c>
+      <c r="L10" t="n">
+        <v>183.2458491362292</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>83.8683658804806</v>
-      </c>
-      <c r="C9" t="n">
-        <v>163.5588814006608</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>83.8683658804805</v>
+      </c>
+      <c r="C11" t="n">
+        <v>163.5588814006607</v>
+      </c>
+      <c r="D11" t="n">
         <v>166.5482308966538</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>165.9655220970119</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>165.9655220970119</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>159.3015061780957</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>166.470794687125</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>165.9655220970119</v>
       </c>
-      <c r="J9" t="n">
-        <v>177.3958365527733</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>177.3958365527734</v>
+      </c>
+      <c r="K11" t="n">
         <v>173.2772924797816</v>
       </c>
-      <c r="L9" t="n">
-        <v>180.5113773618772</v>
+      <c r="L11" t="n">
+        <v>180.5113773618771</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>305.6860047247418</v>
+        <v>172.3147072750344</v>
       </c>
       <c r="C2" t="n">
-        <v>359.4913397268886</v>
+        <v>177.255978010906</v>
       </c>
       <c r="D2" t="n">
-        <v>452.3271091309336</v>
+        <v>172.4681182044132</v>
       </c>
       <c r="E2" t="n">
-        <v>359.4913397268886</v>
+        <v>177.255978010906</v>
       </c>
       <c r="F2" t="n">
-        <v>359.4913397268886</v>
+        <v>177.255978010906</v>
       </c>
       <c r="G2" t="n">
-        <v>469.0465593164404</v>
+        <v>172.4593909054083</v>
       </c>
       <c r="H2" t="n">
-        <v>914.0472642742866</v>
+        <v>172.877009347928</v>
       </c>
       <c r="I2" t="n">
-        <v>359.4913397268886</v>
+        <v>177.255978010906</v>
       </c>
       <c r="J2" t="n">
-        <v>775.9036907805402</v>
+        <v>172.7779462160325</v>
       </c>
       <c r="K2" t="n">
-        <v>419.8657180231315</v>
+        <v>172.4316805531787</v>
       </c>
       <c r="L2" t="n">
-        <v>278.4957696128074</v>
+        <v>172.2467413393244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.393019524793154</v>
+        <v>174.6745269662409</v>
       </c>
       <c r="C3" t="n">
-        <v>6.264945026727178</v>
+        <v>179.6232126680408</v>
       </c>
       <c r="D3" t="n">
-        <v>6.393019524793154</v>
+        <v>174.6745269662409</v>
       </c>
       <c r="E3" t="n">
-        <v>6.368416706125288</v>
+        <v>179.6232126680408</v>
       </c>
       <c r="F3" t="n">
-        <v>6.368416706125287</v>
+        <v>179.6232126680408</v>
       </c>
       <c r="G3" t="n">
-        <v>6.394586042587207</v>
+        <v>174.6574054666712</v>
       </c>
       <c r="H3" t="n">
-        <v>6.393019524793154</v>
+        <v>174.6745269662409</v>
       </c>
       <c r="I3" t="n">
-        <v>6.403189469656192</v>
+        <v>179.6232126680408</v>
       </c>
       <c r="J3" t="n">
-        <v>6.393019524793154</v>
+        <v>174.6745269662409</v>
       </c>
       <c r="K3" t="n">
-        <v>6.393019524793154</v>
+        <v>174.6745269662409</v>
       </c>
       <c r="L3" t="n">
-        <v>6.393019524793154</v>
+        <v>174.6745269662409</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685.5614675598325</v>
+        <v>305.6860047247263</v>
       </c>
       <c r="C4" t="n">
-        <v>685.4445364719261</v>
+        <v>359.4913397268858</v>
       </c>
       <c r="D4" t="n">
-        <v>685.6139990044384</v>
+        <v>452.3271091309302</v>
       </c>
       <c r="E4" t="n">
-        <v>617.9462738964672</v>
+        <v>359.4913397268858</v>
       </c>
       <c r="F4" t="n">
-        <v>685.6029214128635</v>
+        <v>359.4913397268858</v>
       </c>
       <c r="G4" t="n">
-        <v>685.5630340776268</v>
+        <v>469.0465593164429</v>
       </c>
       <c r="H4" t="n">
-        <v>822.0188530314772</v>
+        <v>914.0472642742882</v>
       </c>
       <c r="I4" t="n">
-        <v>821.288821246842</v>
+        <v>359.4913397268858</v>
       </c>
       <c r="J4" t="n">
-        <v>720.3515711451504</v>
+        <v>775.90369078054</v>
       </c>
       <c r="K4" t="n">
-        <v>685.5787170139843</v>
+        <v>419.8657180231318</v>
       </c>
       <c r="L4" t="n">
-        <v>685.7344109721664</v>
+        <v>278.4957696128012</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.3327060522819</v>
+        <v>6.393019524793028</v>
       </c>
       <c r="C5" t="n">
-        <v>13.3428759971451</v>
+        <v>6.264945026727142</v>
       </c>
       <c r="D5" t="n">
-        <v>13.33262820661601</v>
+        <v>6.393019524793028</v>
       </c>
       <c r="E5" t="n">
-        <v>13.34956461645899</v>
+        <v>6.368416706125264</v>
       </c>
       <c r="F5" t="n">
-        <v>13.34956461645899</v>
+        <v>6.368416706125275</v>
       </c>
       <c r="G5" t="n">
-        <v>13.33427257007609</v>
+        <v>6.39458604258711</v>
       </c>
       <c r="H5" t="n">
-        <v>13.3327060522819</v>
+        <v>6.393019524793028</v>
       </c>
       <c r="I5" t="n">
-        <v>13.3428759971451</v>
+        <v>6.403189469656169</v>
       </c>
       <c r="J5" t="n">
-        <v>13.3327060522819</v>
+        <v>6.393019524793028</v>
       </c>
       <c r="K5" t="n">
-        <v>13.3327060522819</v>
+        <v>6.393019524793028</v>
       </c>
       <c r="L5" t="n">
-        <v>13.3327060522819</v>
+        <v>6.393019524793028</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.22319002203989</v>
+        <v>685.5614675598324</v>
       </c>
       <c r="C6" t="n">
-        <v>23.67457693990069</v>
+        <v>685.4445364719261</v>
       </c>
       <c r="D6" t="n">
-        <v>25.197876200054</v>
+        <v>685.6139990044384</v>
       </c>
       <c r="E6" t="n">
-        <v>21.6408366779932</v>
+        <v>617.9462738964671</v>
       </c>
       <c r="F6" t="n">
-        <v>16.47302175906846</v>
+        <v>685.6029214128631</v>
       </c>
       <c r="G6" t="n">
-        <v>23.65809215513731</v>
+        <v>685.5630340776269</v>
       </c>
       <c r="H6" t="n">
-        <v>23.65652563734997</v>
+        <v>822.018853031477</v>
       </c>
       <c r="I6" t="n">
-        <v>23.66669558220625</v>
+        <v>821.2888212468421</v>
       </c>
       <c r="J6" t="n">
-        <v>23.65798649030994</v>
+        <v>720.3515711451498</v>
       </c>
       <c r="K6" t="n">
-        <v>16.0851119976202</v>
+        <v>685.5787170139847</v>
       </c>
       <c r="L6" t="n">
-        <v>31.4212662431723</v>
+        <v>685.7344109721655</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.42465025647585</v>
+        <v>13.33270605228187</v>
       </c>
       <c r="C7" t="n">
-        <v>40.15079967008784</v>
+        <v>13.342875997145</v>
       </c>
       <c r="D7" t="n">
-        <v>40.14063210255215</v>
+        <v>13.33262820661585</v>
       </c>
       <c r="E7" t="n">
-        <v>49.05486524177365</v>
+        <v>13.34956461645896</v>
       </c>
       <c r="F7" t="n">
-        <v>40.15078904679792</v>
+        <v>13.34956461645896</v>
       </c>
       <c r="G7" t="n">
-        <v>40.14219624301884</v>
+        <v>13.33427257007593</v>
       </c>
       <c r="H7" t="n">
-        <v>40.14062972522467</v>
+        <v>13.33270605228187</v>
       </c>
       <c r="I7" t="n">
-        <v>40.15079967008784</v>
+        <v>13.342875997145</v>
       </c>
       <c r="J7" t="n">
-        <v>40.14062972522467</v>
+        <v>13.33270605228187</v>
       </c>
       <c r="K7" t="n">
-        <v>35.66996191793682</v>
+        <v>13.33270605228187</v>
       </c>
       <c r="L7" t="n">
-        <v>40.14062972522467</v>
+        <v>13.33270605228187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>167.5568624308522</v>
+        <v>16.22319002203977</v>
       </c>
       <c r="C8" t="n">
-        <v>171.0339059979305</v>
+        <v>23.67457693990057</v>
       </c>
       <c r="D8" t="n">
-        <v>164.347089482265</v>
+        <v>25.19787620005385</v>
       </c>
       <c r="E8" t="n">
-        <v>171.0339059979305</v>
+        <v>21.6408366779932</v>
       </c>
       <c r="F8" t="n">
-        <v>171.0339059979305</v>
+        <v>16.47302175906846</v>
       </c>
       <c r="G8" t="n">
-        <v>164.1999810996375</v>
+        <v>23.6580921551372</v>
       </c>
       <c r="H8" t="n">
-        <v>156.1327962007703</v>
+        <v>23.65652563734976</v>
       </c>
       <c r="I8" t="n">
-        <v>171.0339059979305</v>
+        <v>23.66669558220616</v>
       </c>
       <c r="J8" t="n">
-        <v>157.98081840302</v>
+        <v>23.6579864903098</v>
       </c>
       <c r="K8" t="n">
-        <v>165.1156865523965</v>
+        <v>16.08511199762015</v>
       </c>
       <c r="L8" t="n">
-        <v>169.0691798020906</v>
+        <v>31.42126624317221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>32.42465025647578</v>
+      </c>
+      <c r="C9" t="n">
+        <v>40.15079967008737</v>
+      </c>
+      <c r="D9" t="n">
+        <v>40.14063210255188</v>
+      </c>
+      <c r="E9" t="n">
+        <v>49.05486524177362</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40.15078904679756</v>
+      </c>
+      <c r="G9" t="n">
+        <v>40.14219624301851</v>
+      </c>
+      <c r="H9" t="n">
+        <v>40.14062972522432</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40.15079967008737</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40.14062972522432</v>
+      </c>
+      <c r="K9" t="n">
+        <v>35.66996191793663</v>
+      </c>
+      <c r="L9" t="n">
+        <v>40.14062972522432</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>167.5568624308527</v>
+      </c>
+      <c r="C10" t="n">
+        <v>171.0339059979306</v>
+      </c>
+      <c r="D10" t="n">
+        <v>164.3470894822649</v>
+      </c>
+      <c r="E10" t="n">
+        <v>171.0339059979306</v>
+      </c>
+      <c r="F10" t="n">
+        <v>171.0339059979306</v>
+      </c>
+      <c r="G10" t="n">
+        <v>164.1999810996374</v>
+      </c>
+      <c r="H10" t="n">
+        <v>156.1327962007703</v>
+      </c>
+      <c r="I10" t="n">
+        <v>171.0339059979306</v>
+      </c>
+      <c r="J10" t="n">
+        <v>157.9808184030202</v>
+      </c>
+      <c r="K10" t="n">
+        <v>165.1156865523962</v>
+      </c>
+      <c r="L10" t="n">
+        <v>169.0691798020909</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>169.0761472287816</v>
-      </c>
-      <c r="C9" t="n">
-        <v>173.3478161035097</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>169.0761472287817</v>
+      </c>
+      <c r="C11" t="n">
+        <v>173.3478161035096</v>
+      </c>
+      <c r="D11" t="n">
         <v>167.7691012376136</v>
       </c>
-      <c r="E9" t="n">
-        <v>173.3478161035097</v>
-      </c>
-      <c r="F9" t="n">
-        <v>173.3478161035097</v>
-      </c>
-      <c r="G9" t="n">
-        <v>167.701229492574</v>
-      </c>
-      <c r="H9" t="n">
-        <v>164.4404627606492</v>
-      </c>
-      <c r="I9" t="n">
-        <v>173.3478161035097</v>
-      </c>
-      <c r="J9" t="n">
-        <v>165.1822556200746</v>
-      </c>
-      <c r="K9" t="n">
-        <v>168.0823777026626</v>
-      </c>
-      <c r="L9" t="n">
-        <v>165.1138795785788</v>
+      <c r="E11" t="n">
+        <v>173.3478161035096</v>
+      </c>
+      <c r="F11" t="n">
+        <v>173.3478161035096</v>
+      </c>
+      <c r="G11" t="n">
+        <v>167.7012294925738</v>
+      </c>
+      <c r="H11" t="n">
+        <v>164.440462760649</v>
+      </c>
+      <c r="I11" t="n">
+        <v>173.3478161035096</v>
+      </c>
+      <c r="J11" t="n">
+        <v>165.1822556200744</v>
+      </c>
+      <c r="K11" t="n">
+        <v>168.0823777026625</v>
+      </c>
+      <c r="L11" t="n">
+        <v>165.1138795785787</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>234.8504957905395</v>
+        <v>171.7747203626026</v>
       </c>
       <c r="C2" t="n">
-        <v>314.6250134467257</v>
+        <v>176.7537980759213</v>
       </c>
       <c r="D2" t="n">
-        <v>391.2931990020704</v>
+        <v>171.9657345233045</v>
       </c>
       <c r="E2" t="n">
-        <v>314.6250134467257</v>
+        <v>176.7537980759213</v>
       </c>
       <c r="F2" t="n">
-        <v>314.6250134467257</v>
+        <v>176.7537980759213</v>
       </c>
       <c r="G2" t="n">
-        <v>403.2068908755325</v>
+        <v>171.953871024125</v>
       </c>
       <c r="H2" t="n">
-        <v>759.0247025789174</v>
+        <v>172.3023820800277</v>
       </c>
       <c r="I2" t="n">
-        <v>314.6250134467257</v>
+        <v>176.7537980759213</v>
       </c>
       <c r="J2" t="n">
-        <v>622.7442161198846</v>
+        <v>172.1911572692337</v>
       </c>
       <c r="K2" t="n">
-        <v>315.8294433826154</v>
+        <v>171.8925939742756</v>
       </c>
       <c r="L2" t="n">
-        <v>296.861680101439</v>
+        <v>171.815429438636</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.803489097629571</v>
+        <v>174.194415106548</v>
       </c>
       <c r="C3" t="n">
-        <v>5.619173032330086</v>
+        <v>179.1347651803314</v>
       </c>
       <c r="D3" t="n">
-        <v>5.803489097629562</v>
+        <v>174.194415106548</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711289625537539</v>
+        <v>179.1347651803314</v>
       </c>
       <c r="F3" t="n">
-        <v>5.711289625537541</v>
+        <v>179.1347651803314</v>
       </c>
       <c r="G3" t="n">
-        <v>5.805396815265119</v>
+        <v>174.1792103476377</v>
       </c>
       <c r="H3" t="n">
-        <v>5.803489097629562</v>
+        <v>174.194415106548</v>
       </c>
       <c r="I3" t="n">
-        <v>5.815789563676553</v>
+        <v>179.1347651803314</v>
       </c>
       <c r="J3" t="n">
-        <v>5.803489097629562</v>
+        <v>174.194415106548</v>
       </c>
       <c r="K3" t="n">
-        <v>5.803489097629562</v>
+        <v>174.194415106548</v>
       </c>
       <c r="L3" t="n">
-        <v>5.803489097629562</v>
+        <v>174.194415106548</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>638.4926161528122</v>
+        <v>234.8504957905411</v>
       </c>
       <c r="C4" t="n">
-        <v>638.4027566683181</v>
+        <v>314.6250134467265</v>
       </c>
       <c r="D4" t="n">
-        <v>638.5551621612947</v>
+        <v>391.2931990020707</v>
       </c>
       <c r="E4" t="n">
-        <v>575.5274528078402</v>
+        <v>314.6250134467265</v>
       </c>
       <c r="F4" t="n">
-        <v>638.5368178237596</v>
+        <v>314.6250134467265</v>
       </c>
       <c r="G4" t="n">
-        <v>638.4945238704471</v>
+        <v>403.2068908755329</v>
       </c>
       <c r="H4" t="n">
-        <v>765.2864784525019</v>
+        <v>759.0247025789183</v>
       </c>
       <c r="I4" t="n">
-        <v>764.6220621113487</v>
+        <v>314.6250134467265</v>
       </c>
       <c r="J4" t="n">
-        <v>670.8754224779382</v>
+        <v>622.7442161198841</v>
       </c>
       <c r="K4" t="n">
-        <v>638.4633752209608</v>
+        <v>315.8294433826152</v>
       </c>
       <c r="L4" t="n">
-        <v>638.6523050249689</v>
+        <v>296.8616801014387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.88282253578706</v>
+        <v>5.803489097629621</v>
       </c>
       <c r="C5" t="n">
-        <v>11.89512300183396</v>
+        <v>5.619173032330085</v>
       </c>
       <c r="D5" t="n">
-        <v>11.88277782592242</v>
+        <v>5.803489097629617</v>
       </c>
       <c r="E5" t="n">
-        <v>11.8785277826538</v>
+        <v>5.711289625537533</v>
       </c>
       <c r="F5" t="n">
-        <v>11.8785277826538</v>
+        <v>5.711289625537543</v>
       </c>
       <c r="G5" t="n">
-        <v>11.88473025342246</v>
+        <v>5.805396815265082</v>
       </c>
       <c r="H5" t="n">
-        <v>11.88282253578706</v>
+        <v>5.803489097629617</v>
       </c>
       <c r="I5" t="n">
-        <v>11.89512300183396</v>
+        <v>5.815789563676544</v>
       </c>
       <c r="J5" t="n">
-        <v>11.88282253578706</v>
+        <v>5.803489097629617</v>
       </c>
       <c r="K5" t="n">
-        <v>11.88282253578706</v>
+        <v>5.803489097629617</v>
       </c>
       <c r="L5" t="n">
-        <v>11.88282253578706</v>
+        <v>5.803489097629617</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.27236109126945</v>
+        <v>638.4926161528123</v>
       </c>
       <c r="C6" t="n">
-        <v>20.63823169662228</v>
+        <v>638.4027566683181</v>
       </c>
       <c r="D6" t="n">
-        <v>21.96105570388189</v>
+        <v>638.5551621612943</v>
       </c>
       <c r="E6" t="n">
-        <v>18.8981936337738</v>
+        <v>575.5274528078406</v>
       </c>
       <c r="F6" t="n">
-        <v>14.47665066706832</v>
+        <v>638.5368178237599</v>
       </c>
       <c r="G6" t="n">
-        <v>20.64247448932035</v>
+        <v>638.4945238704474</v>
       </c>
       <c r="H6" t="n">
-        <v>20.64056677169814</v>
+        <v>765.2864784525023</v>
       </c>
       <c r="I6" t="n">
-        <v>20.65286723773183</v>
+        <v>764.6220621113481</v>
       </c>
       <c r="J6" t="n">
-        <v>20.64181829815301</v>
+        <v>670.8754224779379</v>
       </c>
       <c r="K6" t="n">
-        <v>14.15406840206161</v>
+        <v>638.4633752209605</v>
       </c>
       <c r="L6" t="n">
-        <v>27.29269009771595</v>
+        <v>638.6523050249688</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.10997852465951</v>
+        <v>11.88282253578701</v>
       </c>
       <c r="C7" t="n">
-        <v>33.4443690566042</v>
+        <v>11.89512300183397</v>
       </c>
       <c r="D7" t="n">
-        <v>33.43207097389109</v>
+        <v>11.8827778259224</v>
       </c>
       <c r="E7" t="n">
-        <v>40.73991811256921</v>
+        <v>11.8785277826538</v>
       </c>
       <c r="F7" t="n">
-        <v>33.44436026892235</v>
+        <v>11.8785277826538</v>
       </c>
       <c r="G7" t="n">
-        <v>33.43397630819274</v>
+        <v>11.88473025342252</v>
       </c>
       <c r="H7" t="n">
-        <v>33.43206859055727</v>
+        <v>11.88282253578701</v>
       </c>
       <c r="I7" t="n">
-        <v>33.4443690566042</v>
+        <v>11.89512300183397</v>
       </c>
       <c r="J7" t="n">
-        <v>33.43206859055727</v>
+        <v>11.88282253578701</v>
       </c>
       <c r="K7" t="n">
-        <v>29.76902578003367</v>
+        <v>11.88282253578701</v>
       </c>
       <c r="L7" t="n">
-        <v>33.43206859055727</v>
+        <v>11.88282253578701</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>168.4516714278704</v>
+        <v>14.27236109126943</v>
       </c>
       <c r="C8" t="n">
-        <v>170.9572358032791</v>
+        <v>20.63823169662228</v>
       </c>
       <c r="D8" t="n">
-        <v>164.4534021574636</v>
+        <v>21.96105570388193</v>
       </c>
       <c r="E8" t="n">
-        <v>170.9572358032791</v>
+        <v>18.89819363377377</v>
       </c>
       <c r="F8" t="n">
-        <v>170.9572358032791</v>
+        <v>14.47665066706831</v>
       </c>
       <c r="G8" t="n">
-        <v>164.4110449669012</v>
+        <v>20.64247448932035</v>
       </c>
       <c r="H8" t="n">
-        <v>157.7134557229641</v>
+        <v>20.64056677169815</v>
       </c>
       <c r="I8" t="n">
-        <v>170.9572358032791</v>
+        <v>20.65286723773183</v>
       </c>
       <c r="J8" t="n">
-        <v>159.8379139760528</v>
+        <v>20.641818298153</v>
       </c>
       <c r="K8" t="n">
-        <v>165.990122075093</v>
+        <v>14.15406840206159</v>
       </c>
       <c r="L8" t="n">
-        <v>167.7000486797228</v>
+        <v>27.29269009771597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>27.10997852465952</v>
+      </c>
+      <c r="C9" t="n">
+        <v>33.44436905660424</v>
+      </c>
+      <c r="D9" t="n">
+        <v>33.43207097389114</v>
+      </c>
+      <c r="E9" t="n">
+        <v>40.73991811256926</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33.44436026892239</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33.43397630819274</v>
+      </c>
+      <c r="H9" t="n">
+        <v>33.43206859055732</v>
+      </c>
+      <c r="I9" t="n">
+        <v>33.44436905660424</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33.43206859055732</v>
+      </c>
+      <c r="K9" t="n">
+        <v>29.76902578003365</v>
+      </c>
+      <c r="L9" t="n">
+        <v>33.43206859055732</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>168.4516714278703</v>
+      </c>
+      <c r="C10" t="n">
+        <v>170.9572358032791</v>
+      </c>
+      <c r="D10" t="n">
+        <v>164.4534021574636</v>
+      </c>
+      <c r="E10" t="n">
+        <v>170.9572358032791</v>
+      </c>
+      <c r="F10" t="n">
+        <v>170.9572358032791</v>
+      </c>
+      <c r="G10" t="n">
+        <v>164.4110449669012</v>
+      </c>
+      <c r="H10" t="n">
+        <v>157.7134557229641</v>
+      </c>
+      <c r="I10" t="n">
+        <v>170.9572358032791</v>
+      </c>
+      <c r="J10" t="n">
+        <v>159.8379139760527</v>
+      </c>
+      <c r="K10" t="n">
+        <v>165.9901220750929</v>
+      </c>
+      <c r="L10" t="n">
+        <v>167.7000486797228</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>169.1617536877662</v>
-      </c>
-      <c r="C9" t="n">
-        <v>173.0329961491225</v>
-      </c>
-      <c r="D9" t="n">
-        <v>167.533542588705</v>
-      </c>
-      <c r="E9" t="n">
-        <v>173.0329961491225</v>
-      </c>
-      <c r="F9" t="n">
-        <v>173.0329961491225</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>169.161753687766</v>
+      </c>
+      <c r="C11" t="n">
+        <v>173.0329961491226</v>
+      </c>
+      <c r="D11" t="n">
+        <v>167.5335425887047</v>
+      </c>
+      <c r="E11" t="n">
+        <v>173.0329961491226</v>
+      </c>
+      <c r="F11" t="n">
+        <v>173.0329961491226</v>
+      </c>
+      <c r="G11" t="n">
         <v>167.5093246465938</v>
       </c>
-      <c r="H9" t="n">
-        <v>164.803493038796</v>
-      </c>
-      <c r="I9" t="n">
-        <v>173.0329961491225</v>
-      </c>
-      <c r="J9" t="n">
-        <v>165.6589035034039</v>
-      </c>
-      <c r="K9" t="n">
-        <v>168.1596144994333</v>
-      </c>
-      <c r="L9" t="n">
-        <v>165.1096157147679</v>
+      <c r="H11" t="n">
+        <v>164.8034930387958</v>
+      </c>
+      <c r="I11" t="n">
+        <v>173.0329961491226</v>
+      </c>
+      <c r="J11" t="n">
+        <v>165.6589035034038</v>
+      </c>
+      <c r="K11" t="n">
+        <v>168.1596144994331</v>
+      </c>
+      <c r="L11" t="n">
+        <v>165.1096157147678</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>211.5089467282466</v>
+        <v>171.3323363403753</v>
       </c>
       <c r="C2" t="n">
-        <v>281.0989276554193</v>
+        <v>176.3099096022903</v>
       </c>
       <c r="D2" t="n">
-        <v>348.4969734715209</v>
+        <v>171.5062942521738</v>
       </c>
       <c r="E2" t="n">
-        <v>281.0989276554193</v>
+        <v>176.3099096022903</v>
       </c>
       <c r="F2" t="n">
-        <v>281.0989276554193</v>
+        <v>176.3099096022903</v>
       </c>
       <c r="G2" t="n">
-        <v>361.8634637409385</v>
+        <v>171.4927701252296</v>
       </c>
       <c r="H2" t="n">
-        <v>655.1574525448232</v>
+        <v>171.8007835311497</v>
       </c>
       <c r="I2" t="n">
-        <v>281.0989276554193</v>
+        <v>176.3099096022903</v>
       </c>
       <c r="J2" t="n">
-        <v>577.4402553467677</v>
+        <v>171.7166721939377</v>
       </c>
       <c r="K2" t="n">
-        <v>220.7772391376407</v>
+        <v>171.3653810865933</v>
       </c>
       <c r="L2" t="n">
-        <v>220.4823720380224</v>
+        <v>171.770306215923</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.414732734500095</v>
+        <v>173.7663673399064</v>
       </c>
       <c r="C3" t="n">
-        <v>5.118513738462831</v>
+        <v>178.7248120918672</v>
       </c>
       <c r="D3" t="n">
-        <v>5.414732734500095</v>
+        <v>173.7663673399064</v>
       </c>
       <c r="E3" t="n">
-        <v>5.213324080369565</v>
+        <v>178.7248120918672</v>
       </c>
       <c r="F3" t="n">
-        <v>5.213324080369563</v>
+        <v>178.7248120918672</v>
       </c>
       <c r="G3" t="n">
-        <v>5.416564734255917</v>
+        <v>173.7506053483166</v>
       </c>
       <c r="H3" t="n">
-        <v>5.414732734500095</v>
+        <v>173.7663673399064</v>
       </c>
       <c r="I3" t="n">
-        <v>5.426556475908002</v>
+        <v>178.7248120918672</v>
       </c>
       <c r="J3" t="n">
-        <v>5.414732734500095</v>
+        <v>173.7663673399064</v>
       </c>
       <c r="K3" t="n">
-        <v>5.414732734500095</v>
+        <v>173.7663673399064</v>
       </c>
       <c r="L3" t="n">
-        <v>5.414732734500095</v>
+        <v>173.7663673399064</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>637.8933897211318</v>
+        <v>211.5089467282459</v>
       </c>
       <c r="C4" t="n">
-        <v>637.8106541082983</v>
+        <v>281.0989276554197</v>
       </c>
       <c r="D4" t="n">
-        <v>637.9868177493559</v>
+        <v>348.4969734715207</v>
       </c>
       <c r="E4" t="n">
-        <v>574.9533037842062</v>
+        <v>281.0989276554197</v>
       </c>
       <c r="F4" t="n">
-        <v>637.9496126672086</v>
+        <v>281.0989276554197</v>
       </c>
       <c r="G4" t="n">
-        <v>763.7256749296491</v>
+        <v>361.8634637409374</v>
       </c>
       <c r="H4" t="n">
-        <v>764.4166472274934</v>
+        <v>655.1574525448235</v>
       </c>
       <c r="I4" t="n">
-        <v>637.9052134625402</v>
+        <v>281.0989276554197</v>
       </c>
       <c r="J4" t="n">
-        <v>764.0896214672905</v>
+        <v>577.4402553467681</v>
       </c>
       <c r="K4" t="n">
-        <v>637.778103784644</v>
+        <v>220.7772391376409</v>
       </c>
       <c r="L4" t="n">
-        <v>638.0653605053976</v>
+        <v>220.4823720380234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.22630093006521</v>
+        <v>5.414732734499846</v>
       </c>
       <c r="C5" t="n">
-        <v>11.23812467147338</v>
+        <v>5.118513738462824</v>
       </c>
       <c r="D5" t="n">
-        <v>11.22628357731556</v>
+        <v>5.414732734499852</v>
       </c>
       <c r="E5" t="n">
-        <v>11.19042374670141</v>
+        <v>5.213324080369559</v>
       </c>
       <c r="F5" t="n">
-        <v>11.19042374670141</v>
+        <v>5.213324080369558</v>
       </c>
       <c r="G5" t="n">
-        <v>11.22813292982129</v>
+        <v>5.416564734255927</v>
       </c>
       <c r="H5" t="n">
-        <v>11.22630093006521</v>
+        <v>5.414732734499852</v>
       </c>
       <c r="I5" t="n">
-        <v>11.23812467147338</v>
+        <v>5.426556475907997</v>
       </c>
       <c r="J5" t="n">
-        <v>11.22630093006521</v>
+        <v>5.414732734499852</v>
       </c>
       <c r="K5" t="n">
-        <v>11.22630093006521</v>
+        <v>5.414732734499852</v>
       </c>
       <c r="L5" t="n">
-        <v>11.22630093006521</v>
+        <v>5.414732734499852</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.39695351108864</v>
+        <v>637.8933897211321</v>
       </c>
       <c r="C6" t="n">
-        <v>19.34920457029849</v>
+        <v>637.8106541082984</v>
       </c>
       <c r="D6" t="n">
-        <v>20.62288675670552</v>
+        <v>637.9868177493565</v>
       </c>
       <c r="E6" t="n">
-        <v>17.71717029320105</v>
+        <v>574.9533037842052</v>
       </c>
       <c r="F6" t="n">
-        <v>13.57004444321022</v>
+        <v>637.9496126672087</v>
       </c>
       <c r="G6" t="n">
-        <v>19.38370641866654</v>
+        <v>763.7256749296494</v>
       </c>
       <c r="H6" t="n">
-        <v>19.38187441892642</v>
+        <v>764.4166472274942</v>
       </c>
       <c r="I6" t="n">
-        <v>19.39369816031855</v>
+        <v>637.9052134625401</v>
       </c>
       <c r="J6" t="n">
-        <v>19.38305061978015</v>
+        <v>764.0896214672906</v>
       </c>
       <c r="K6" t="n">
-        <v>13.28578053323023</v>
+        <v>637.7781037846443</v>
       </c>
       <c r="L6" t="n">
-        <v>25.63362475101885</v>
+        <v>638.0653605053976</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.31996547969102</v>
+        <v>11.22630093006545</v>
       </c>
       <c r="C7" t="n">
-        <v>29.95755940982546</v>
+        <v>11.2381246714734</v>
       </c>
       <c r="D7" t="n">
-        <v>29.94573800708406</v>
+        <v>11.22628357731564</v>
       </c>
       <c r="E7" t="n">
-        <v>36.44957096835982</v>
+        <v>11.1904237467014</v>
       </c>
       <c r="F7" t="n">
-        <v>29.95755135561308</v>
+        <v>11.1904237467014</v>
       </c>
       <c r="G7" t="n">
-        <v>29.9475676681734</v>
+        <v>11.22813292982143</v>
       </c>
       <c r="H7" t="n">
-        <v>29.94573566841716</v>
+        <v>11.22630093006547</v>
       </c>
       <c r="I7" t="n">
-        <v>29.95755940982546</v>
+        <v>11.2381246714734</v>
       </c>
       <c r="J7" t="n">
-        <v>29.94573566841716</v>
+        <v>11.22630093006547</v>
       </c>
       <c r="K7" t="n">
-        <v>26.6861433105992</v>
+        <v>11.22630093006547</v>
       </c>
       <c r="L7" t="n">
-        <v>29.94573566841716</v>
+        <v>11.22630093006547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>168.4291506132147</v>
+        <v>13.39695351108897</v>
       </c>
       <c r="C8" t="n">
-        <v>171.3558151439406</v>
+        <v>19.34920457029849</v>
       </c>
       <c r="D8" t="n">
-        <v>164.7879589536109</v>
+        <v>20.62288675670591</v>
       </c>
       <c r="E8" t="n">
-        <v>171.3558151439406</v>
+        <v>17.71717029320104</v>
       </c>
       <c r="F8" t="n">
-        <v>171.3558151439406</v>
+        <v>13.57004444321021</v>
       </c>
       <c r="G8" t="n">
-        <v>164.7647330200324</v>
+        <v>19.38370641866656</v>
       </c>
       <c r="H8" t="n">
-        <v>158.9005609108997</v>
+        <v>19.38187441892679</v>
       </c>
       <c r="I8" t="n">
-        <v>171.3558151439406</v>
+        <v>19.39369816031856</v>
       </c>
       <c r="J8" t="n">
-        <v>160.4796804260006</v>
+        <v>19.38305061978031</v>
       </c>
       <c r="K8" t="n">
-        <v>167.7432096036153</v>
+        <v>13.28578053323046</v>
       </c>
       <c r="L8" t="n">
-        <v>159.4761573502741</v>
+        <v>25.63362475101901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>24.3199654796911</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29.95755940982548</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29.94573800708429</v>
+      </c>
+      <c r="E9" t="n">
+        <v>36.44957096835984</v>
+      </c>
+      <c r="F9" t="n">
+        <v>29.95755135561311</v>
+      </c>
+      <c r="G9" t="n">
+        <v>29.94756766817368</v>
+      </c>
+      <c r="H9" t="n">
+        <v>29.94573566841763</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29.95755940982548</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.94573566841763</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26.68614331059933</v>
+      </c>
+      <c r="L9" t="n">
+        <v>29.94573566841763</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>168.4291506132148</v>
+      </c>
+      <c r="C10" t="n">
+        <v>171.3558151439406</v>
+      </c>
+      <c r="D10" t="n">
+        <v>164.7879589536109</v>
+      </c>
+      <c r="E10" t="n">
+        <v>171.3558151439406</v>
+      </c>
+      <c r="F10" t="n">
+        <v>171.3558151439406</v>
+      </c>
+      <c r="G10" t="n">
+        <v>164.7647330200327</v>
+      </c>
+      <c r="H10" t="n">
+        <v>158.9005609108997</v>
+      </c>
+      <c r="I10" t="n">
+        <v>171.3558151439406</v>
+      </c>
+      <c r="J10" t="n">
+        <v>160.4796804260006</v>
+      </c>
+      <c r="K10" t="n">
+        <v>167.7432096036153</v>
+      </c>
+      <c r="L10" t="n">
+        <v>159.4761573502741</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>168.9038857210301</v>
       </c>
-      <c r="C9" t="n">
-        <v>172.9569925073837</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C11" t="n">
+        <v>172.9569925073838</v>
+      </c>
+      <c r="D11" t="n">
         <v>167.4210898239196</v>
       </c>
-      <c r="E9" t="n">
-        <v>172.9569925073837</v>
-      </c>
-      <c r="F9" t="n">
-        <v>172.9569925073837</v>
-      </c>
-      <c r="G9" t="n">
-        <v>167.4041695795842</v>
-      </c>
-      <c r="H9" t="n">
-        <v>165.0367942314374</v>
-      </c>
-      <c r="I9" t="n">
-        <v>172.9569925073837</v>
-      </c>
-      <c r="J9" t="n">
-        <v>165.6711873059516</v>
-      </c>
-      <c r="K9" t="n">
-        <v>168.624825121916</v>
-      </c>
-      <c r="L9" t="n">
-        <v>165.2682151304429</v>
+      <c r="E11" t="n">
+        <v>172.9569925073838</v>
+      </c>
+      <c r="F11" t="n">
+        <v>172.9569925073838</v>
+      </c>
+      <c r="G11" t="n">
+        <v>167.4041695795844</v>
+      </c>
+      <c r="H11" t="n">
+        <v>165.0367942314376</v>
+      </c>
+      <c r="I11" t="n">
+        <v>172.9569925073838</v>
+      </c>
+      <c r="J11" t="n">
+        <v>165.6711873059518</v>
+      </c>
+      <c r="K11" t="n">
+        <v>168.6248251219161</v>
+      </c>
+      <c r="L11" t="n">
+        <v>165.2682151304431</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,320 +7175,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.05768912061936</v>
+        <v>171.0133739663992</v>
       </c>
       <c r="C2" t="n">
-        <v>300.7677103846679</v>
+        <v>176.2460667601148</v>
       </c>
       <c r="D2" t="n">
-        <v>231.5563869718602</v>
+        <v>171.2118416468529</v>
       </c>
       <c r="E2" t="n">
-        <v>300.7677103846679</v>
+        <v>176.2460667601148</v>
       </c>
       <c r="F2" t="n">
-        <v>300.7677103846679</v>
+        <v>176.2460667601148</v>
       </c>
       <c r="G2" t="n">
-        <v>281.9878043972367</v>
+        <v>171.2557452829836</v>
       </c>
       <c r="H2" t="n">
-        <v>383.5767044631112</v>
+        <v>171.3540726098985</v>
       </c>
       <c r="I2" t="n">
-        <v>300.7677103846679</v>
+        <v>176.2460667601148</v>
       </c>
       <c r="J2" t="n">
-        <v>820.6404925507686</v>
+        <v>171.7871121777359</v>
       </c>
       <c r="K2" t="n">
-        <v>274.037207771647</v>
+        <v>171.2533711385384</v>
       </c>
       <c r="L2" t="n">
-        <v>510.6925341865315</v>
+        <v>171.0644462006327</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.475968144444742</v>
+        <v>173.6246132278364</v>
       </c>
       <c r="C3" t="n">
-        <v>5.318284639216484</v>
+        <v>178.668091726975</v>
       </c>
       <c r="D3" t="n">
-        <v>5.475968144444742</v>
+        <v>173.6246132278364</v>
       </c>
       <c r="E3" t="n">
-        <v>5.416488831082402</v>
+        <v>178.668091726975</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4164888310824</v>
+        <v>178.668091726975</v>
       </c>
       <c r="G3" t="n">
-        <v>5.481443351691944</v>
+        <v>173.6253294058091</v>
       </c>
       <c r="H3" t="n">
-        <v>5.475968144444742</v>
+        <v>173.6246132278364</v>
       </c>
       <c r="I3" t="n">
-        <v>5.511038847544598</v>
+        <v>178.668091726975</v>
       </c>
       <c r="J3" t="n">
-        <v>5.475968144444742</v>
+        <v>173.6246132278364</v>
       </c>
       <c r="K3" t="n">
-        <v>5.475968144444742</v>
+        <v>173.6246132278364</v>
       </c>
       <c r="L3" t="n">
-        <v>5.475968144444742</v>
+        <v>173.6246132278364</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>818.6034491965382</v>
+        <v>73.05768912061903</v>
       </c>
       <c r="C4" t="n">
-        <v>684.2408462866675</v>
+        <v>300.7677103846681</v>
       </c>
       <c r="D4" t="n">
-        <v>818.7827579837126</v>
+        <v>231.55638697186</v>
       </c>
       <c r="E4" t="n">
-        <v>616.7727567525819</v>
+        <v>300.7677103846681</v>
       </c>
       <c r="F4" t="n">
-        <v>684.2615505532016</v>
+        <v>300.7677103846681</v>
       </c>
       <c r="G4" t="n">
-        <v>818.6089244037848</v>
+        <v>281.9878043972366</v>
       </c>
       <c r="H4" t="n">
-        <v>684.2545566818231</v>
+        <v>383.576704463111</v>
       </c>
       <c r="I4" t="n">
-        <v>818.6385198996373</v>
+        <v>300.7677103846681</v>
       </c>
       <c r="J4" t="n">
-        <v>819.0120731419156</v>
+        <v>820.64049255077</v>
       </c>
       <c r="K4" t="n">
-        <v>684.2101511598293</v>
+        <v>274.037207771647</v>
       </c>
       <c r="L4" t="n">
-        <v>684.2840796779965</v>
+        <v>510.6925341865305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.32842056291675</v>
+        <v>5.475968144444742</v>
       </c>
       <c r="C5" t="n">
-        <v>11.36349126601661</v>
+        <v>5.318284639216486</v>
       </c>
       <c r="D5" t="n">
-        <v>11.32839095601244</v>
+        <v>5.475968144444742</v>
       </c>
       <c r="E5" t="n">
-        <v>11.33530438149655</v>
+        <v>5.416488831082415</v>
       </c>
       <c r="F5" t="n">
-        <v>11.33530438149655</v>
+        <v>5.416488831082415</v>
       </c>
       <c r="G5" t="n">
-        <v>11.33389577016395</v>
+        <v>5.481443351691952</v>
       </c>
       <c r="H5" t="n">
-        <v>11.32842056291675</v>
+        <v>5.475968144444746</v>
       </c>
       <c r="I5" t="n">
-        <v>11.36349126601661</v>
+        <v>5.511038847544599</v>
       </c>
       <c r="J5" t="n">
-        <v>11.32842056291675</v>
+        <v>5.475968144444744</v>
       </c>
       <c r="K5" t="n">
-        <v>11.32842056291675</v>
+        <v>5.475968144444742</v>
       </c>
       <c r="L5" t="n">
-        <v>11.32842056291675</v>
+        <v>5.475968144444742</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.2927596824789</v>
+        <v>818.6034491965378</v>
       </c>
       <c r="C6" t="n">
-        <v>19.20653449648834</v>
+        <v>684.240846286668</v>
       </c>
       <c r="D6" t="n">
-        <v>20.42164118405634</v>
+        <v>818.7827579837127</v>
       </c>
       <c r="E6" t="n">
-        <v>17.59450041981171</v>
+        <v>616.772756752582</v>
       </c>
       <c r="F6" t="n">
-        <v>13.49819792132512</v>
+        <v>684.2615505532017</v>
       </c>
       <c r="G6" t="n">
-        <v>19.20277213061332</v>
+        <v>818.6089244037853</v>
       </c>
       <c r="H6" t="n">
-        <v>19.19729692337478</v>
+        <v>684.2545566818234</v>
       </c>
       <c r="I6" t="n">
-        <v>19.232367626466</v>
+        <v>818.6385198996378</v>
       </c>
       <c r="J6" t="n">
-        <v>19.19845732520295</v>
+        <v>819.0120731419158</v>
       </c>
       <c r="K6" t="n">
-        <v>13.18307987258565</v>
+        <v>684.2101511598291</v>
       </c>
       <c r="L6" t="n">
-        <v>25.36507979258057</v>
+        <v>684.2840796779965</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.84693286367271</v>
+        <v>11.32842056291677</v>
       </c>
       <c r="C7" t="n">
-        <v>33.2004461644616</v>
+        <v>11.36349126601662</v>
       </c>
       <c r="D7" t="n">
-        <v>33.16537910498747</v>
+        <v>11.32839095601246</v>
       </c>
       <c r="E7" t="n">
-        <v>40.49179299084972</v>
+        <v>11.33530438149657</v>
       </c>
       <c r="F7" t="n">
-        <v>33.20044196247625</v>
+        <v>11.33530438149656</v>
       </c>
       <c r="G7" t="n">
-        <v>33.17085066860894</v>
+        <v>11.33389577016398</v>
       </c>
       <c r="H7" t="n">
-        <v>33.16537546136174</v>
+        <v>11.32842056291677</v>
       </c>
       <c r="I7" t="n">
-        <v>33.2004461644616</v>
+        <v>11.36349126601662</v>
       </c>
       <c r="J7" t="n">
-        <v>33.16537546136174</v>
+        <v>11.32842056291677</v>
       </c>
       <c r="K7" t="n">
-        <v>29.50444653831662</v>
+        <v>11.32842056291677</v>
       </c>
       <c r="L7" t="n">
-        <v>33.16537546136174</v>
+        <v>11.32842056291677</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.0102313130303</v>
+        <v>13.29275968247892</v>
       </c>
       <c r="C8" t="n">
-        <v>171.445202811678</v>
+        <v>19.20653449648835</v>
       </c>
       <c r="D8" t="n">
-        <v>167.8535267143936</v>
+        <v>20.42164118405637</v>
       </c>
       <c r="E8" t="n">
-        <v>171.445202811678</v>
+        <v>17.59450041981173</v>
       </c>
       <c r="F8" t="n">
-        <v>171.445202811678</v>
+        <v>13.49819792132514</v>
       </c>
       <c r="G8" t="n">
-        <v>166.978649184711</v>
+        <v>19.20277213061336</v>
       </c>
       <c r="H8" t="n">
-        <v>165.0367597437983</v>
+        <v>19.19729692337481</v>
       </c>
       <c r="I8" t="n">
-        <v>171.445202811678</v>
+        <v>19.23236762646601</v>
       </c>
       <c r="J8" t="n">
-        <v>155.9340385252218</v>
+        <v>19.19845732520299</v>
       </c>
       <c r="K8" t="n">
-        <v>166.987213580721</v>
+        <v>13.18307987258567</v>
       </c>
       <c r="L8" t="n">
-        <v>163.2792014811771</v>
+        <v>25.36507979258058</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>26.84693286367265</v>
+      </c>
+      <c r="C9" t="n">
+        <v>33.2004461644616</v>
+      </c>
+      <c r="D9" t="n">
+        <v>33.16537910498747</v>
+      </c>
+      <c r="E9" t="n">
+        <v>40.49179299084965</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33.20044196247621</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33.17085066860894</v>
+      </c>
+      <c r="H9" t="n">
+        <v>33.16537546136173</v>
+      </c>
+      <c r="I9" t="n">
+        <v>33.2004461644616</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33.16537546136173</v>
+      </c>
+      <c r="K9" t="n">
+        <v>29.50444653831661</v>
+      </c>
+      <c r="L9" t="n">
+        <v>33.16537546136173</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>172.0102313130303</v>
+      </c>
+      <c r="C10" t="n">
+        <v>171.4452028116781</v>
+      </c>
+      <c r="D10" t="n">
+        <v>167.8535267143936</v>
+      </c>
+      <c r="E10" t="n">
+        <v>171.4452028116781</v>
+      </c>
+      <c r="F10" t="n">
+        <v>171.4452028116781</v>
+      </c>
+      <c r="G10" t="n">
+        <v>166.9786491847112</v>
+      </c>
+      <c r="H10" t="n">
+        <v>165.0367597437983</v>
+      </c>
+      <c r="I10" t="n">
+        <v>171.4452028116781</v>
+      </c>
+      <c r="J10" t="n">
+        <v>155.9340385252216</v>
+      </c>
+      <c r="K10" t="n">
+        <v>166.987213580721</v>
+      </c>
+      <c r="L10" t="n">
+        <v>163.2792014811771</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>170.2788250504325</v>
       </c>
-      <c r="C9" t="n">
-        <v>172.9596292856737</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C11" t="n">
+        <v>172.9596292856736</v>
+      </c>
+      <c r="D11" t="n">
         <v>168.5859788918749</v>
       </c>
-      <c r="E9" t="n">
-        <v>172.9596292856737</v>
-      </c>
-      <c r="F9" t="n">
-        <v>172.9596292856737</v>
-      </c>
-      <c r="G9" t="n">
-        <v>168.231484600671</v>
-      </c>
-      <c r="H9" t="n">
-        <v>167.4465719067959</v>
-      </c>
-      <c r="I9" t="n">
-        <v>172.9596292856737</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="E11" t="n">
+        <v>172.9596292856736</v>
+      </c>
+      <c r="F11" t="n">
+        <v>172.9596292856736</v>
+      </c>
+      <c r="G11" t="n">
+        <v>168.2314846006709</v>
+      </c>
+      <c r="H11" t="n">
+        <v>167.4465719067958</v>
+      </c>
+      <c r="I11" t="n">
+        <v>172.9596292856736</v>
+      </c>
+      <c r="J11" t="n">
         <v>163.7378443115296</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>168.2333331469633</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>166.7305704126943</v>
       </c>
     </row>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.35624651890013</v>
+        <v>170.0917577454184</v>
       </c>
       <c r="C2" t="n">
-        <v>203.7080562314734</v>
+        <v>175.2376689955343</v>
       </c>
       <c r="D2" t="n">
-        <v>175.1613056640239</v>
+        <v>170.2995023287569</v>
       </c>
       <c r="E2" t="n">
-        <v>203.7080562314734</v>
+        <v>175.2376689955343</v>
       </c>
       <c r="F2" t="n">
-        <v>203.7080562314734</v>
+        <v>175.2376689955343</v>
       </c>
       <c r="G2" t="n">
-        <v>185.2819746375586</v>
+        <v>170.3002893675439</v>
       </c>
       <c r="H2" t="n">
-        <v>129.5966377805293</v>
+        <v>170.2262518420332</v>
       </c>
       <c r="I2" t="n">
-        <v>203.7080562314734</v>
+        <v>175.2376689955343</v>
       </c>
       <c r="J2" t="n">
-        <v>451.9055817030426</v>
+        <v>170.6040492263055</v>
       </c>
       <c r="K2" t="n">
-        <v>118.6935159272517</v>
+        <v>170.2152677272876</v>
       </c>
       <c r="L2" t="n">
-        <v>43.03751382128469</v>
+        <v>170.1126715532574</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.624377729842</v>
+        <v>172.7472143256174</v>
       </c>
       <c r="C3" t="n">
-        <v>4.482830058134609</v>
+        <v>177.7373121113094</v>
       </c>
       <c r="D3" t="n">
-        <v>4.624377729842</v>
+        <v>172.7472143256174</v>
       </c>
       <c r="E3" t="n">
-        <v>4.557371291551743</v>
+        <v>177.7373121113094</v>
       </c>
       <c r="F3" t="n">
-        <v>4.557371291551745</v>
+        <v>177.7373121113094</v>
       </c>
       <c r="G3" t="n">
-        <v>4.629881182954056</v>
+        <v>172.7482307120665</v>
       </c>
       <c r="H3" t="n">
-        <v>4.624377729842</v>
+        <v>172.7472143256174</v>
       </c>
       <c r="I3" t="n">
-        <v>4.659449890699065</v>
+        <v>177.7373121113094</v>
       </c>
       <c r="J3" t="n">
-        <v>4.624377729842</v>
+        <v>172.7472143256174</v>
       </c>
       <c r="K3" t="n">
-        <v>4.624377729842</v>
+        <v>172.7472143256174</v>
       </c>
       <c r="L3" t="n">
-        <v>4.624377729842</v>
+        <v>172.7472143256174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>761.2124839580673</v>
+        <v>23.35624651890013</v>
       </c>
       <c r="C4" t="n">
-        <v>636.5847472894978</v>
+        <v>203.7080562314732</v>
       </c>
       <c r="D4" t="n">
-        <v>636.5339286196424</v>
+        <v>175.1613056640237</v>
       </c>
       <c r="E4" t="n">
-        <v>573.7622949581269</v>
+        <v>203.7080562314732</v>
       </c>
       <c r="F4" t="n">
-        <v>636.5904263738785</v>
+        <v>203.7080562314732</v>
       </c>
       <c r="G4" t="n">
-        <v>761.2179874111797</v>
+        <v>185.281974637557</v>
       </c>
       <c r="H4" t="n">
-        <v>761.7292938424418</v>
+        <v>129.5966377805293</v>
       </c>
       <c r="I4" t="n">
-        <v>761.2475561189248</v>
+        <v>203.7080562314732</v>
       </c>
       <c r="J4" t="n">
-        <v>668.8325825627127</v>
+        <v>451.9055817030414</v>
       </c>
       <c r="K4" t="n">
-        <v>636.3944404170489</v>
+        <v>118.6935159272516</v>
       </c>
       <c r="L4" t="n">
-        <v>636.5882030650399</v>
+        <v>43.03751382128461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.495515880461134</v>
+        <v>4.624377729842017</v>
       </c>
       <c r="C5" t="n">
-        <v>9.530588041318193</v>
+        <v>4.482830058134605</v>
       </c>
       <c r="D5" t="n">
-        <v>9.49549787642761</v>
+        <v>4.624377729842017</v>
       </c>
       <c r="E5" t="n">
-        <v>9.500153436516465</v>
+        <v>4.557371291551743</v>
       </c>
       <c r="F5" t="n">
-        <v>9.500153436516465</v>
+        <v>4.557371291551743</v>
       </c>
       <c r="G5" t="n">
-        <v>9.501019333573177</v>
+        <v>4.629881182954068</v>
       </c>
       <c r="H5" t="n">
-        <v>9.495515880461134</v>
+        <v>4.624377729842017</v>
       </c>
       <c r="I5" t="n">
-        <v>9.530588041318193</v>
+        <v>4.65944989069906</v>
       </c>
       <c r="J5" t="n">
-        <v>9.495515880461134</v>
+        <v>4.624377729842017</v>
       </c>
       <c r="K5" t="n">
-        <v>9.495515880461134</v>
+        <v>4.624377729842017</v>
       </c>
       <c r="L5" t="n">
-        <v>9.495515880461134</v>
+        <v>4.624377729842017</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.78005252547425</v>
+        <v>761.2124839580672</v>
       </c>
       <c r="C6" t="n">
-        <v>15.39734947121002</v>
+        <v>636.5847472894983</v>
       </c>
       <c r="D6" t="n">
-        <v>16.34653922932263</v>
+        <v>636.5339286196416</v>
       </c>
       <c r="E6" t="n">
-        <v>14.13948779675216</v>
+        <v>573.7622949581275</v>
       </c>
       <c r="F6" t="n">
-        <v>10.94312464141115</v>
+        <v>636.5904263738792</v>
       </c>
       <c r="G6" t="n">
-        <v>15.39603071241727</v>
+        <v>761.2179874111804</v>
       </c>
       <c r="H6" t="n">
-        <v>15.39052725930326</v>
+        <v>761.7292938424416</v>
       </c>
       <c r="I6" t="n">
-        <v>15.42559942016228</v>
+        <v>761.2475561189243</v>
       </c>
       <c r="J6" t="n">
-        <v>15.39143334325496</v>
+        <v>668.8325825627117</v>
       </c>
       <c r="K6" t="n">
-        <v>10.69441059082485</v>
+        <v>636.3944404170486</v>
       </c>
       <c r="L6" t="n">
-        <v>20.20655363443922</v>
+        <v>636.5882030650387</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.67691141639247</v>
+        <v>9.495515880461133</v>
       </c>
       <c r="C7" t="n">
-        <v>25.45573130080183</v>
+        <v>9.530588041318182</v>
       </c>
       <c r="D7" t="n">
-        <v>25.42066351426297</v>
+        <v>9.495497876427613</v>
       </c>
       <c r="E7" t="n">
-        <v>30.92991814996814</v>
+        <v>9.500153436516463</v>
       </c>
       <c r="F7" t="n">
-        <v>25.45573018527803</v>
+        <v>9.500153436516463</v>
       </c>
       <c r="G7" t="n">
-        <v>25.42616259305683</v>
+        <v>9.501019333573183</v>
       </c>
       <c r="H7" t="n">
-        <v>25.42065913994475</v>
+        <v>9.495515880461133</v>
       </c>
       <c r="I7" t="n">
-        <v>25.45573130080183</v>
+        <v>9.530588041318182</v>
       </c>
       <c r="J7" t="n">
-        <v>25.42065913994475</v>
+        <v>9.495515880461133</v>
       </c>
       <c r="K7" t="n">
-        <v>22.67211491860477</v>
+        <v>9.495515880461133</v>
       </c>
       <c r="L7" t="n">
-        <v>25.42065913994475</v>
+        <v>9.495515880461133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.2793143277126</v>
+        <v>10.78005252547424</v>
       </c>
       <c r="C8" t="n">
-        <v>172.3757941877959</v>
+        <v>15.39734947120998</v>
       </c>
       <c r="D8" t="n">
-        <v>167.9276348738329</v>
+        <v>16.34653922932261</v>
       </c>
       <c r="E8" t="n">
-        <v>172.3757941877959</v>
+        <v>14.13948779675214</v>
       </c>
       <c r="F8" t="n">
-        <v>172.3757941877959</v>
+        <v>10.94312464141112</v>
       </c>
       <c r="G8" t="n">
-        <v>167.9544567808545</v>
+        <v>15.39603071241727</v>
       </c>
       <c r="H8" t="n">
-        <v>169.5232477262695</v>
+        <v>15.39052725930323</v>
       </c>
       <c r="I8" t="n">
-        <v>172.3757941877959</v>
+        <v>15.42559942016225</v>
       </c>
       <c r="J8" t="n">
-        <v>161.6305152875139</v>
+        <v>15.39143334325493</v>
       </c>
       <c r="K8" t="n">
-        <v>169.6939127074646</v>
+        <v>10.69441059082484</v>
       </c>
       <c r="L8" t="n">
-        <v>171.8549486326253</v>
+        <v>20.2065536344392</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>20.67691141639245</v>
+      </c>
+      <c r="C9" t="n">
+        <v>25.45573130080174</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25.42066351426289</v>
+      </c>
+      <c r="E9" t="n">
+        <v>30.92991814996805</v>
+      </c>
+      <c r="F9" t="n">
+        <v>25.45573018527795</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25.42616259305674</v>
+      </c>
+      <c r="H9" t="n">
+        <v>25.42065913994473</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25.45573130080174</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.42065913994473</v>
+      </c>
+      <c r="K9" t="n">
+        <v>22.67211491860473</v>
+      </c>
+      <c r="L9" t="n">
+        <v>25.42065913994473</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>172.2793143277126</v>
+      </c>
+      <c r="C10" t="n">
+        <v>172.3757941877959</v>
+      </c>
+      <c r="D10" t="n">
+        <v>167.9276348738331</v>
+      </c>
+      <c r="E10" t="n">
+        <v>172.3757941877959</v>
+      </c>
+      <c r="F10" t="n">
+        <v>172.3757941877959</v>
+      </c>
+      <c r="G10" t="n">
+        <v>167.9544567808545</v>
+      </c>
+      <c r="H10" t="n">
+        <v>169.5232477262697</v>
+      </c>
+      <c r="I10" t="n">
+        <v>172.3757941877959</v>
+      </c>
+      <c r="J10" t="n">
+        <v>161.630515287514</v>
+      </c>
+      <c r="K10" t="n">
+        <v>169.6939127074645</v>
+      </c>
+      <c r="L10" t="n">
+        <v>171.8549486326253</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>169.8788617552628</v>
-      </c>
-      <c r="C9" t="n">
-        <v>172.7981612541918</v>
-      </c>
-      <c r="D9" t="n">
-        <v>168.1065783191065</v>
-      </c>
-      <c r="E9" t="n">
-        <v>172.7981612541918</v>
-      </c>
-      <c r="F9" t="n">
-        <v>172.7981612541918</v>
-      </c>
-      <c r="G9" t="n">
-        <v>168.1191069519915</v>
-      </c>
-      <c r="H9" t="n">
-        <v>168.7593367651579</v>
-      </c>
-      <c r="I9" t="n">
-        <v>172.7981612541918</v>
-      </c>
-      <c r="J9" t="n">
-        <v>165.5459157371506</v>
-      </c>
-      <c r="K9" t="n">
-        <v>168.8260057607332</v>
-      </c>
-      <c r="L9" t="n">
-        <v>169.706687819464</v>
+      <c r="B11" t="n">
+        <v>169.8788617552629</v>
+      </c>
+      <c r="C11" t="n">
+        <v>172.7981612541917</v>
+      </c>
+      <c r="D11" t="n">
+        <v>168.1065783191066</v>
+      </c>
+      <c r="E11" t="n">
+        <v>172.7981612541917</v>
+      </c>
+      <c r="F11" t="n">
+        <v>172.7981612541917</v>
+      </c>
+      <c r="G11" t="n">
+        <v>168.1191069519914</v>
+      </c>
+      <c r="H11" t="n">
+        <v>168.7593367651581</v>
+      </c>
+      <c r="I11" t="n">
+        <v>172.7981612541917</v>
+      </c>
+      <c r="J11" t="n">
+        <v>165.5459157371507</v>
+      </c>
+      <c r="K11" t="n">
+        <v>168.826005760733</v>
+      </c>
+      <c r="L11" t="n">
+        <v>169.7066878194641</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.69630697769956</v>
+        <v>169.5830684895345</v>
       </c>
       <c r="C2" t="n">
-        <v>144.1807006542421</v>
+        <v>174.5687912829918</v>
       </c>
       <c r="D2" t="n">
-        <v>110.2551592780782</v>
+        <v>169.6971465388172</v>
       </c>
       <c r="E2" t="n">
-        <v>144.1807006542421</v>
+        <v>174.5687912829918</v>
       </c>
       <c r="F2" t="n">
-        <v>144.1807006542421</v>
+        <v>174.5687912829918</v>
       </c>
       <c r="G2" t="n">
-        <v>136.3697864401663</v>
+        <v>169.7239056410102</v>
       </c>
       <c r="H2" t="n">
-        <v>134.9204580178755</v>
+        <v>169.7125328041402</v>
       </c>
       <c r="I2" t="n">
-        <v>144.1807006542421</v>
+        <v>174.5687912829918</v>
       </c>
       <c r="J2" t="n">
-        <v>276.9622823912782</v>
+        <v>169.8812928606085</v>
       </c>
       <c r="K2" t="n">
-        <v>58.11921457723702</v>
+        <v>169.6318712160402</v>
       </c>
       <c r="L2" t="n">
-        <v>68.47163475217479</v>
+        <v>169.6344228932605</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.153643134711056</v>
+        <v>172.2339649729105</v>
       </c>
       <c r="C3" t="n">
-        <v>3.997550746337666</v>
+        <v>177.1423563394743</v>
       </c>
       <c r="D3" t="n">
-        <v>4.153643134711057</v>
+        <v>172.2339649729105</v>
       </c>
       <c r="E3" t="n">
-        <v>4.06539321287685</v>
+        <v>177.1423563394743</v>
       </c>
       <c r="F3" t="n">
-        <v>4.065393212876851</v>
+        <v>177.1423563394743</v>
       </c>
       <c r="G3" t="n">
-        <v>4.158690180722161</v>
+        <v>172.2329290812599</v>
       </c>
       <c r="H3" t="n">
-        <v>4.153643134711057</v>
+        <v>172.2339649729105</v>
       </c>
       <c r="I3" t="n">
-        <v>4.185720998562391</v>
+        <v>177.1423563394743</v>
       </c>
       <c r="J3" t="n">
-        <v>4.153643134711056</v>
+        <v>172.2339649729105</v>
       </c>
       <c r="K3" t="n">
-        <v>4.153643134711057</v>
+        <v>172.2339649729105</v>
       </c>
       <c r="L3" t="n">
-        <v>4.153643134711057</v>
+        <v>172.2339649729105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>635.670686402659</v>
+        <v>21.69630697769956</v>
       </c>
       <c r="C4" t="n">
-        <v>635.720011001476</v>
+        <v>144.1807006542422</v>
       </c>
       <c r="D4" t="n">
-        <v>635.6543819012979</v>
+        <v>110.2551592780781</v>
       </c>
       <c r="E4" t="n">
-        <v>572.9250182385711</v>
+        <v>144.1807006542422</v>
       </c>
       <c r="F4" t="n">
-        <v>635.7413919370123</v>
+        <v>144.1807006542422</v>
       </c>
       <c r="G4" t="n">
-        <v>635.6757334486708</v>
+        <v>136.3697864401666</v>
       </c>
       <c r="H4" t="n">
-        <v>760.5392574583368</v>
+        <v>134.9204580178756</v>
       </c>
       <c r="I4" t="n">
-        <v>635.7027642665105</v>
+        <v>144.1807006542422</v>
       </c>
       <c r="J4" t="n">
-        <v>667.9267294349162</v>
+        <v>276.9622823912787</v>
       </c>
       <c r="K4" t="n">
-        <v>635.5427548006649</v>
+        <v>58.11921457723705</v>
       </c>
       <c r="L4" t="n">
-        <v>635.7551932434868</v>
+        <v>68.47163475217482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.693812630791738</v>
+        <v>4.153643134711048</v>
       </c>
       <c r="C5" t="n">
-        <v>8.725890494643053</v>
+        <v>3.997550746337665</v>
       </c>
       <c r="D5" t="n">
-        <v>8.693803778236981</v>
+        <v>4.153643134711048</v>
       </c>
       <c r="E5" t="n">
-        <v>8.693100217210553</v>
+        <v>4.065393212876844</v>
       </c>
       <c r="F5" t="n">
-        <v>8.693100217210553</v>
+        <v>4.065393212876844</v>
       </c>
       <c r="G5" t="n">
-        <v>8.698859676802815</v>
+        <v>4.158690180722147</v>
       </c>
       <c r="H5" t="n">
-        <v>8.693812630791738</v>
+        <v>4.153643134711048</v>
       </c>
       <c r="I5" t="n">
-        <v>8.725890494643053</v>
+        <v>4.185720998562383</v>
       </c>
       <c r="J5" t="n">
-        <v>8.693812630791738</v>
+        <v>4.153643134711048</v>
       </c>
       <c r="K5" t="n">
-        <v>8.693812630791738</v>
+        <v>4.153643134711048</v>
       </c>
       <c r="L5" t="n">
-        <v>8.693812630791738</v>
+        <v>4.153643134711048</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.686032244097621</v>
+        <v>635.6706864026598</v>
       </c>
       <c r="C6" t="n">
-        <v>13.81324133258959</v>
+        <v>635.7200110014763</v>
       </c>
       <c r="D6" t="n">
-        <v>14.66727224376591</v>
+        <v>635.6543819012975</v>
       </c>
       <c r="E6" t="n">
-        <v>12.68820296605154</v>
+        <v>572.9250182385708</v>
       </c>
       <c r="F6" t="n">
-        <v>9.829334012052181</v>
+        <v>635.7413919370124</v>
       </c>
       <c r="G6" t="n">
-        <v>13.81682006402259</v>
+        <v>635.6757334486701</v>
       </c>
       <c r="H6" t="n">
-        <v>13.8117730180042</v>
+        <v>760.5392574583368</v>
       </c>
       <c r="I6" t="n">
-        <v>13.84385088186281</v>
+        <v>635.7027642665106</v>
       </c>
       <c r="J6" t="n">
-        <v>13.81258383878834</v>
+        <v>667.9267294349157</v>
       </c>
       <c r="K6" t="n">
-        <v>9.609394491532273</v>
+        <v>635.5427548006635</v>
       </c>
       <c r="L6" t="n">
-        <v>18.12145424010366</v>
+        <v>635.7551932434859</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.64680788441679</v>
+        <v>8.69381263079171</v>
       </c>
       <c r="C7" t="n">
-        <v>21.67621920360141</v>
+        <v>8.725890494643053</v>
       </c>
       <c r="D7" t="n">
-        <v>21.64414415008797</v>
+        <v>8.693803778236957</v>
       </c>
       <c r="E7" t="n">
-        <v>26.28905789050656</v>
+        <v>8.693100217210567</v>
       </c>
       <c r="F7" t="n">
-        <v>21.67621768050142</v>
+        <v>8.693100217210567</v>
       </c>
       <c r="G7" t="n">
-        <v>21.64918838576119</v>
+        <v>8.698859676802817</v>
       </c>
       <c r="H7" t="n">
-        <v>21.64414133975009</v>
+        <v>8.69381263079171</v>
       </c>
       <c r="I7" t="n">
-        <v>21.67621920360141</v>
+        <v>8.725890494643053</v>
       </c>
       <c r="J7" t="n">
-        <v>21.64414133975009</v>
+        <v>8.69381263079171</v>
       </c>
       <c r="K7" t="n">
-        <v>19.23410583889796</v>
+        <v>8.69381263079171</v>
       </c>
       <c r="L7" t="n">
-        <v>21.64414133975009</v>
+        <v>8.69381263079171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>171.7934853478497</v>
+        <v>9.686032244097614</v>
       </c>
       <c r="C8" t="n">
-        <v>173.4753101058408</v>
+        <v>13.81324133258956</v>
       </c>
       <c r="D8" t="n">
-        <v>169.4039654778224</v>
+        <v>14.66727224376592</v>
       </c>
       <c r="E8" t="n">
-        <v>173.4753101058408</v>
+        <v>12.68820296605155</v>
       </c>
       <c r="F8" t="n">
-        <v>173.4753101058408</v>
+        <v>9.829334012052183</v>
       </c>
       <c r="G8" t="n">
-        <v>168.8355537660291</v>
+        <v>13.81682006402256</v>
       </c>
       <c r="H8" t="n">
-        <v>169.1402978879384</v>
+        <v>13.81177301800418</v>
       </c>
       <c r="I8" t="n">
-        <v>173.4753101058408</v>
+        <v>13.84385088186284</v>
       </c>
       <c r="J8" t="n">
-        <v>165.595753026944</v>
+        <v>13.81258383878832</v>
       </c>
       <c r="K8" t="n">
-        <v>170.77219520785</v>
+        <v>9.609394491532269</v>
       </c>
       <c r="L8" t="n">
-        <v>166.5428725732038</v>
+        <v>18.12145424010365</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>17.64680788441679</v>
+      </c>
+      <c r="C9" t="n">
+        <v>21.67621920360142</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21.64414415008795</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26.28905789050665</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21.67621768050147</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21.6491883857612</v>
+      </c>
+      <c r="H9" t="n">
+        <v>21.64414133975011</v>
+      </c>
+      <c r="I9" t="n">
+        <v>21.67621920360142</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.64414133975009</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.23410583889795</v>
+      </c>
+      <c r="L9" t="n">
+        <v>21.64414133975009</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>171.7934853478498</v>
+      </c>
+      <c r="C10" t="n">
+        <v>173.475310105841</v>
+      </c>
+      <c r="D10" t="n">
+        <v>169.4039654778224</v>
+      </c>
+      <c r="E10" t="n">
+        <v>173.475310105841</v>
+      </c>
+      <c r="F10" t="n">
+        <v>173.475310105841</v>
+      </c>
+      <c r="G10" t="n">
+        <v>168.8355537660291</v>
+      </c>
+      <c r="H10" t="n">
+        <v>169.1402978879384</v>
+      </c>
+      <c r="I10" t="n">
+        <v>173.475310105841</v>
+      </c>
+      <c r="J10" t="n">
+        <v>165.595753026944</v>
+      </c>
+      <c r="K10" t="n">
+        <v>170.7721952078501</v>
+      </c>
+      <c r="L10" t="n">
+        <v>166.5428725732039</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>169.3826488564068</v>
-      </c>
-      <c r="C9" t="n">
-        <v>172.9002735605054</v>
-      </c>
-      <c r="D9" t="n">
-        <v>168.4094877498789</v>
-      </c>
-      <c r="E9" t="n">
-        <v>172.9002735605054</v>
-      </c>
-      <c r="F9" t="n">
-        <v>172.9002735605054</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>169.3826488564066</v>
+      </c>
+      <c r="C11" t="n">
+        <v>172.9002735605055</v>
+      </c>
+      <c r="D11" t="n">
+        <v>168.4094877498788</v>
+      </c>
+      <c r="E11" t="n">
+        <v>172.9002735605055</v>
+      </c>
+      <c r="F11" t="n">
+        <v>172.9002735605055</v>
+      </c>
+      <c r="G11" t="n">
         <v>168.1780890457874</v>
       </c>
-      <c r="H9" t="n">
-        <v>168.3049044215459</v>
-      </c>
-      <c r="I9" t="n">
-        <v>172.9002735605054</v>
-      </c>
-      <c r="J9" t="n">
-        <v>166.8608852704675</v>
-      </c>
-      <c r="K9" t="n">
-        <v>168.9667613145538</v>
-      </c>
-      <c r="L9" t="n">
-        <v>167.2484199957099</v>
+      <c r="H11" t="n">
+        <v>168.3049044215458</v>
+      </c>
+      <c r="I11" t="n">
+        <v>172.9002735605055</v>
+      </c>
+      <c r="J11" t="n">
+        <v>166.8608852704674</v>
+      </c>
+      <c r="K11" t="n">
+        <v>168.9667613145537</v>
+      </c>
+      <c r="L11" t="n">
+        <v>167.2484199957098</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,320 +8603,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>209.2554450735239</v>
+        <v>171.8604733175245</v>
       </c>
       <c r="C2" t="n">
-        <v>347.1066907474914</v>
+        <v>176.921748353319</v>
       </c>
       <c r="D2" t="n">
-        <v>419.7047469670043</v>
+        <v>172.1074226226115</v>
       </c>
       <c r="E2" t="n">
-        <v>347.1066907474914</v>
+        <v>176.921748353319</v>
       </c>
       <c r="F2" t="n">
-        <v>347.1066907474914</v>
+        <v>176.921748353319</v>
       </c>
       <c r="G2" t="n">
-        <v>412.2738247660007</v>
+        <v>172.0704658406173</v>
       </c>
       <c r="H2" t="n">
-        <v>818.8148297677694</v>
+        <v>172.5091529188503</v>
       </c>
       <c r="I2" t="n">
-        <v>347.1066907474914</v>
+        <v>176.921748353319</v>
       </c>
       <c r="J2" t="n">
-        <v>780.6101405223998</v>
+        <v>172.4369464705608</v>
       </c>
       <c r="K2" t="n">
-        <v>370.536319148063</v>
+        <v>172.0416520226946</v>
       </c>
       <c r="L2" t="n">
-        <v>219.5569386356866</v>
+        <v>172.3699671992365</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.116027450505908</v>
+        <v>174.3240940202469</v>
       </c>
       <c r="C3" t="n">
-        <v>5.967899912943417</v>
+        <v>179.297515452474</v>
       </c>
       <c r="D3" t="n">
-        <v>6.116027450505908</v>
+        <v>174.3240940202469</v>
       </c>
       <c r="E3" t="n">
-        <v>6.071094753107386</v>
+        <v>179.297515452474</v>
       </c>
       <c r="F3" t="n">
-        <v>6.071094753107364</v>
+        <v>179.297515452474</v>
       </c>
       <c r="G3" t="n">
-        <v>6.118710984388352</v>
+        <v>174.3122704100263</v>
       </c>
       <c r="H3" t="n">
-        <v>6.116027450505908</v>
+        <v>174.3240940202469</v>
       </c>
       <c r="I3" t="n">
-        <v>6.13330360642926</v>
+        <v>179.297515452474</v>
       </c>
       <c r="J3" t="n">
-        <v>6.116027450505908</v>
+        <v>174.3240940202469</v>
       </c>
       <c r="K3" t="n">
-        <v>6.116027450505908</v>
+        <v>174.3240940202469</v>
       </c>
       <c r="L3" t="n">
-        <v>6.116027450505908</v>
+        <v>174.3240940202469</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685.1809146360032</v>
+        <v>209.2554450735237</v>
       </c>
       <c r="C4" t="n">
-        <v>685.1217623073821</v>
+        <v>347.1066907474907</v>
       </c>
       <c r="D4" t="n">
-        <v>685.2787644461835</v>
+        <v>419.7047469670049</v>
       </c>
       <c r="E4" t="n">
-        <v>617.6323547644744</v>
+        <v>347.1066907474907</v>
       </c>
       <c r="F4" t="n">
-        <v>685.2391544507103</v>
+        <v>347.1066907474907</v>
       </c>
       <c r="G4" t="n">
-        <v>820.5276561826005</v>
+        <v>412.2738247660014</v>
       </c>
       <c r="H4" t="n">
-        <v>821.2870037832765</v>
+        <v>818.8148297677686</v>
       </c>
       <c r="I4" t="n">
-        <v>820.5422488046421</v>
+        <v>347.1066907474907</v>
       </c>
       <c r="J4" t="n">
-        <v>820.9129055906166</v>
+        <v>780.6101405223994</v>
       </c>
       <c r="K4" t="n">
-        <v>685.1930306767127</v>
+        <v>370.5363191480635</v>
       </c>
       <c r="L4" t="n">
-        <v>685.3421533395087</v>
+        <v>219.5569386356881</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.6526811708047</v>
+        <v>6.116027450505923</v>
       </c>
       <c r="C5" t="n">
-        <v>12.66995732672801</v>
+        <v>5.967899912943404</v>
       </c>
       <c r="D5" t="n">
-        <v>12.65262098206365</v>
+        <v>6.116027450505923</v>
       </c>
       <c r="E5" t="n">
-        <v>12.66356419467174</v>
+        <v>6.071094753107374</v>
       </c>
       <c r="F5" t="n">
-        <v>12.66356419467174</v>
+        <v>6.071094753107374</v>
       </c>
       <c r="G5" t="n">
-        <v>12.65536470468705</v>
+        <v>6.118710984388329</v>
       </c>
       <c r="H5" t="n">
-        <v>12.6526811708047</v>
+        <v>6.116027450505923</v>
       </c>
       <c r="I5" t="n">
-        <v>12.66995732672801</v>
+        <v>6.13330360642925</v>
       </c>
       <c r="J5" t="n">
-        <v>12.6526811708047</v>
+        <v>6.116027450505923</v>
       </c>
       <c r="K5" t="n">
-        <v>12.6526811708047</v>
+        <v>6.116027450505923</v>
       </c>
       <c r="L5" t="n">
-        <v>12.6526811708047</v>
+        <v>6.116027450505923</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.21258570635869</v>
+        <v>685.1809146360044</v>
       </c>
       <c r="C6" t="n">
-        <v>22.10622366080017</v>
+        <v>685.1217623073818</v>
       </c>
       <c r="D6" t="n">
-        <v>23.52055307477703</v>
+        <v>685.2787644461841</v>
       </c>
       <c r="E6" t="n">
-        <v>20.22485615331568</v>
+        <v>617.6323547644748</v>
       </c>
       <c r="F6" t="n">
-        <v>15.44420489967659</v>
+        <v>685.2391544507107</v>
       </c>
       <c r="G6" t="n">
-        <v>22.09639115423155</v>
+        <v>820.5276561825999</v>
       </c>
       <c r="H6" t="n">
-        <v>22.09370762035461</v>
+        <v>821.2870037832768</v>
       </c>
       <c r="I6" t="n">
-        <v>22.11098377627251</v>
+        <v>820.542248804641</v>
       </c>
       <c r="J6" t="n">
-        <v>22.09505994788205</v>
+        <v>820.9129055906164</v>
       </c>
       <c r="K6" t="n">
-        <v>15.08476533490724</v>
+        <v>685.1930306767131</v>
       </c>
       <c r="L6" t="n">
-        <v>29.28161484016784</v>
+        <v>685.3421533395093</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.87968158569789</v>
+        <v>12.65268117080469</v>
       </c>
       <c r="C7" t="n">
-        <v>38.22480409958549</v>
+        <v>12.669957326728</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20752927872326</v>
+        <v>12.65262098206366</v>
       </c>
       <c r="E7" t="n">
-        <v>46.68097194443088</v>
+        <v>12.66356419467174</v>
       </c>
       <c r="F7" t="n">
-        <v>38.22479395264797</v>
+        <v>12.66356419467174</v>
       </c>
       <c r="G7" t="n">
-        <v>38.21021147754443</v>
+        <v>12.65536470468708</v>
       </c>
       <c r="H7" t="n">
-        <v>38.20752794366214</v>
+        <v>12.65268117080469</v>
       </c>
       <c r="I7" t="n">
-        <v>38.22480409958549</v>
+        <v>12.669957326728</v>
       </c>
       <c r="J7" t="n">
-        <v>38.20752794366214</v>
+        <v>12.65268117080469</v>
       </c>
       <c r="K7" t="n">
-        <v>33.96174554670601</v>
+        <v>12.65268117080469</v>
       </c>
       <c r="L7" t="n">
-        <v>38.20752794366214</v>
+        <v>12.65268117080469</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>169.4649912777722</v>
+        <v>15.21258570635865</v>
       </c>
       <c r="C8" t="n">
-        <v>170.9666710066144</v>
+        <v>22.10622366080015</v>
       </c>
       <c r="D8" t="n">
-        <v>164.2944725063373</v>
+        <v>23.52055307477722</v>
       </c>
       <c r="E8" t="n">
-        <v>170.9666710066144</v>
+        <v>20.22485615331568</v>
       </c>
       <c r="F8" t="n">
-        <v>170.9666710066144</v>
+        <v>15.44420489967659</v>
       </c>
       <c r="G8" t="n">
-        <v>164.8506391760573</v>
+        <v>22.09639115423161</v>
       </c>
       <c r="H8" t="n">
-        <v>156.2218583229034</v>
+        <v>22.09370762035467</v>
       </c>
       <c r="I8" t="n">
-        <v>170.9666710066144</v>
+        <v>22.11098377627254</v>
       </c>
       <c r="J8" t="n">
-        <v>157.5164491198476</v>
+        <v>22.09505994788203</v>
       </c>
       <c r="K8" t="n">
-        <v>165.6770475304355</v>
+        <v>15.08476533490726</v>
       </c>
       <c r="L8" t="n">
-        <v>159.0288026519805</v>
+        <v>29.28161484016787</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30.87968158569795</v>
+      </c>
+      <c r="C9" t="n">
+        <v>38.2248040995855</v>
+      </c>
+      <c r="D9" t="n">
+        <v>38.20752927872326</v>
+      </c>
+      <c r="E9" t="n">
+        <v>46.68097194443089</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38.22479395264796</v>
+      </c>
+      <c r="G9" t="n">
+        <v>38.21021147754458</v>
+      </c>
+      <c r="H9" t="n">
+        <v>38.20752794366216</v>
+      </c>
+      <c r="I9" t="n">
+        <v>38.2248040995855</v>
+      </c>
+      <c r="J9" t="n">
+        <v>38.20752794366216</v>
+      </c>
+      <c r="K9" t="n">
+        <v>33.96174554670608</v>
+      </c>
+      <c r="L9" t="n">
+        <v>38.20752794366216</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>169.4649912777722</v>
+      </c>
+      <c r="C10" t="n">
+        <v>170.9666710066142</v>
+      </c>
+      <c r="D10" t="n">
+        <v>164.2944725063373</v>
+      </c>
+      <c r="E10" t="n">
+        <v>170.9666710066142</v>
+      </c>
+      <c r="F10" t="n">
+        <v>170.9666710066142</v>
+      </c>
+      <c r="G10" t="n">
+        <v>164.8506391760573</v>
+      </c>
+      <c r="H10" t="n">
+        <v>156.2218583229033</v>
+      </c>
+      <c r="I10" t="n">
+        <v>170.9666710066142</v>
+      </c>
+      <c r="J10" t="n">
+        <v>157.5164491198476</v>
+      </c>
+      <c r="K10" t="n">
+        <v>165.6770475304354</v>
+      </c>
+      <c r="L10" t="n">
+        <v>159.0288026519804</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>169.6495660846567</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>169.6495660846568</v>
+      </c>
+      <c r="C11" t="n">
         <v>173.1311875816269</v>
       </c>
-      <c r="D9" t="n">
-        <v>167.5439128712752</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>167.5439128712753</v>
+      </c>
+      <c r="E11" t="n">
         <v>173.1311875816269</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>173.1311875816269</v>
       </c>
-      <c r="G9" t="n">
-        <v>167.7653934767318</v>
-      </c>
-      <c r="H9" t="n">
-        <v>164.2725779881565</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>167.7653934767317</v>
+      </c>
+      <c r="H11" t="n">
+        <v>164.2725779881566</v>
+      </c>
+      <c r="I11" t="n">
         <v>173.1311875816269</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>164.7894144780929</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>168.1072183133283</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>169.8407352326215</v>
       </c>
     </row>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.70289843105977</v>
+        <v>170.5918728207717</v>
       </c>
       <c r="C2" t="n">
-        <v>210.4159433237725</v>
+        <v>175.6661372334641</v>
       </c>
       <c r="D2" t="n">
-        <v>328.9336053313743</v>
+        <v>170.9825971616683</v>
       </c>
       <c r="E2" t="n">
-        <v>210.4159433237725</v>
+        <v>175.6661372334641</v>
       </c>
       <c r="F2" t="n">
-        <v>210.4159433237725</v>
+        <v>175.6661372334641</v>
       </c>
       <c r="G2" t="n">
-        <v>261.5706787711156</v>
+        <v>170.8676703811706</v>
       </c>
       <c r="H2" t="n">
-        <v>258.2960407722238</v>
+        <v>170.8619628006543</v>
       </c>
       <c r="I2" t="n">
-        <v>210.4159433237725</v>
+        <v>175.6661372334641</v>
       </c>
       <c r="J2" t="n">
-        <v>552.0751121092056</v>
+        <v>171.1746740576757</v>
       </c>
       <c r="K2" t="n">
-        <v>148.3853257188758</v>
+        <v>170.7451661278284</v>
       </c>
       <c r="L2" t="n">
-        <v>557.6878014776809</v>
+        <v>170.655298614238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.970664711016147</v>
+        <v>173.2455294593584</v>
       </c>
       <c r="C3" t="n">
-        <v>4.789416540477665</v>
+        <v>178.1657625932715</v>
       </c>
       <c r="D3" t="n">
-        <v>4.970664711016147</v>
+        <v>173.2455294593584</v>
       </c>
       <c r="E3" t="n">
-        <v>4.872284262234994</v>
+        <v>178.1657625932715</v>
       </c>
       <c r="F3" t="n">
-        <v>4.872284262234994</v>
+        <v>178.1657625932715</v>
       </c>
       <c r="G3" t="n">
-        <v>4.973513692045548</v>
+        <v>173.2338223243845</v>
       </c>
       <c r="H3" t="n">
-        <v>4.970664711016147</v>
+        <v>173.2455294593584</v>
       </c>
       <c r="I3" t="n">
-        <v>4.988877766756772</v>
+        <v>178.1657625932715</v>
       </c>
       <c r="J3" t="n">
-        <v>4.970664711016147</v>
+        <v>173.2455294593584</v>
       </c>
       <c r="K3" t="n">
-        <v>4.970664711016147</v>
+        <v>173.2455294593584</v>
       </c>
       <c r="L3" t="n">
-        <v>4.970664711016147</v>
+        <v>173.2455294593584</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>762.3455331340626</v>
+        <v>29.70289843105974</v>
       </c>
       <c r="C4" t="n">
-        <v>637.0511875181369</v>
+        <v>210.4159433237724</v>
       </c>
       <c r="D4" t="n">
-        <v>637.3393315469383</v>
+        <v>328.9336053313738</v>
       </c>
       <c r="E4" t="n">
-        <v>574.2085370840422</v>
+        <v>210.4159433237724</v>
       </c>
       <c r="F4" t="n">
-        <v>637.1494377171086</v>
+        <v>210.4159433237724</v>
       </c>
       <c r="G4" t="n">
-        <v>762.3483821150926</v>
+        <v>261.5706787711158</v>
       </c>
       <c r="H4" t="n">
-        <v>762.9530973604981</v>
+        <v>258.2960407722242</v>
       </c>
       <c r="I4" t="n">
-        <v>762.3637461898031</v>
+        <v>210.4159433237724</v>
       </c>
       <c r="J4" t="n">
-        <v>669.4574835074056</v>
+        <v>552.075112109206</v>
       </c>
       <c r="K4" t="n">
-        <v>636.9583517212761</v>
+        <v>148.3853257188759</v>
       </c>
       <c r="L4" t="n">
-        <v>637.2441024631647</v>
+        <v>557.6878014776794</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.25610017899659</v>
+        <v>4.970664711016128</v>
       </c>
       <c r="C5" t="n">
-        <v>10.27431323473724</v>
+        <v>4.789416540477678</v>
       </c>
       <c r="D5" t="n">
-        <v>10.25607305967668</v>
+        <v>4.970664711016128</v>
       </c>
       <c r="E5" t="n">
-        <v>10.25223910823254</v>
+        <v>4.872284262234994</v>
       </c>
       <c r="F5" t="n">
-        <v>10.25223910823254</v>
+        <v>4.872284262235</v>
       </c>
       <c r="G5" t="n">
-        <v>10.258949160026</v>
+        <v>4.973513692045544</v>
       </c>
       <c r="H5" t="n">
-        <v>10.25610017899659</v>
+        <v>4.970664711016128</v>
       </c>
       <c r="I5" t="n">
-        <v>10.27431323473724</v>
+        <v>4.988877766756778</v>
       </c>
       <c r="J5" t="n">
-        <v>10.25610017899659</v>
+        <v>4.970664711016128</v>
       </c>
       <c r="K5" t="n">
-        <v>10.25610017899659</v>
+        <v>4.970664711016128</v>
       </c>
       <c r="L5" t="n">
-        <v>10.25610017899659</v>
+        <v>4.970664711016128</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.99576467836348</v>
+        <v>762.3455331340627</v>
       </c>
       <c r="C6" t="n">
-        <v>17.27491319868624</v>
+        <v>637.0511875181364</v>
       </c>
       <c r="D6" t="n">
-        <v>18.37186967046586</v>
+        <v>637.3393315469382</v>
       </c>
       <c r="E6" t="n">
-        <v>15.83278881392584</v>
+        <v>574.2085370840417</v>
       </c>
       <c r="F6" t="n">
-        <v>12.16822662451316</v>
+        <v>637.1494377171093</v>
       </c>
       <c r="G6" t="n">
-        <v>17.27965941237142</v>
+        <v>762.348382115092</v>
       </c>
       <c r="H6" t="n">
-        <v>17.27681043135021</v>
+        <v>762.9530973604978</v>
       </c>
       <c r="I6" t="n">
-        <v>17.29502348708267</v>
+        <v>762.3637461898034</v>
       </c>
       <c r="J6" t="n">
-        <v>17.27784830066386</v>
+        <v>669.4574835074052</v>
       </c>
       <c r="K6" t="n">
-        <v>11.89766654286723</v>
+        <v>636.9583517212762</v>
       </c>
       <c r="L6" t="n">
-        <v>22.79330430721528</v>
+        <v>637.2441024631652</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.80618643562445</v>
+        <v>10.25610017899659</v>
       </c>
       <c r="C7" t="n">
-        <v>28.11266539537586</v>
+        <v>10.27431323473723</v>
       </c>
       <c r="D7" t="n">
-        <v>28.09445740346672</v>
+        <v>10.25607305967668</v>
       </c>
       <c r="E7" t="n">
-        <v>34.21521295458713</v>
+        <v>10.25223910823255</v>
       </c>
       <c r="F7" t="n">
-        <v>28.11266240156459</v>
+        <v>10.25223910823255</v>
       </c>
       <c r="G7" t="n">
-        <v>28.09730132066458</v>
+        <v>10.25894916002601</v>
       </c>
       <c r="H7" t="n">
-        <v>28.09445233963518</v>
+        <v>10.25610017899659</v>
       </c>
       <c r="I7" t="n">
-        <v>28.11266539537586</v>
+        <v>10.27431323473723</v>
       </c>
       <c r="J7" t="n">
-        <v>28.09445233963518</v>
+        <v>10.25610017899659</v>
       </c>
       <c r="K7" t="n">
-        <v>25.03041243605633</v>
+        <v>10.25610017899659</v>
       </c>
       <c r="L7" t="n">
-        <v>28.09445233963518</v>
+        <v>10.25610017899659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172.6260146688737</v>
+        <v>11.99576467836349</v>
       </c>
       <c r="C8" t="n">
-        <v>172.7003326788731</v>
+        <v>17.27491319868628</v>
       </c>
       <c r="D8" t="n">
-        <v>164.4412651735375</v>
+        <v>18.37186967046591</v>
       </c>
       <c r="E8" t="n">
-        <v>172.7003326788731</v>
+        <v>15.83278881392589</v>
       </c>
       <c r="F8" t="n">
-        <v>172.7003326788731</v>
+        <v>12.16822662451321</v>
       </c>
       <c r="G8" t="n">
-        <v>166.6208664003757</v>
+        <v>17.27965941237148</v>
       </c>
       <c r="H8" t="n">
-        <v>167.0851416156287</v>
+        <v>17.27681043135026</v>
       </c>
       <c r="I8" t="n">
-        <v>172.7003326788731</v>
+        <v>17.29502348708272</v>
       </c>
       <c r="J8" t="n">
-        <v>160.5122489163815</v>
+        <v>17.2778483006639</v>
       </c>
       <c r="K8" t="n">
-        <v>169.4172092786861</v>
+        <v>11.89766654286726</v>
       </c>
       <c r="L8" t="n">
-        <v>161.2649657974194</v>
+        <v>22.79330430721534</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>22.80618643562442</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28.1126653953758</v>
+      </c>
+      <c r="D9" t="n">
+        <v>28.09445740346665</v>
+      </c>
+      <c r="E9" t="n">
+        <v>34.21521295458707</v>
+      </c>
+      <c r="F9" t="n">
+        <v>28.11266240156452</v>
+      </c>
+      <c r="G9" t="n">
+        <v>28.09730132066459</v>
+      </c>
+      <c r="H9" t="n">
+        <v>28.09445233963514</v>
+      </c>
+      <c r="I9" t="n">
+        <v>28.1126653953758</v>
+      </c>
+      <c r="J9" t="n">
+        <v>28.09445233963514</v>
+      </c>
+      <c r="K9" t="n">
+        <v>25.03041243605633</v>
+      </c>
+      <c r="L9" t="n">
+        <v>28.09445233963514</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>172.6260146688739</v>
+      </c>
+      <c r="C10" t="n">
+        <v>172.7003326788733</v>
+      </c>
+      <c r="D10" t="n">
+        <v>164.4412651735376</v>
+      </c>
+      <c r="E10" t="n">
+        <v>172.7003326788733</v>
+      </c>
+      <c r="F10" t="n">
+        <v>172.7003326788733</v>
+      </c>
+      <c r="G10" t="n">
+        <v>166.6208664003758</v>
+      </c>
+      <c r="H10" t="n">
+        <v>167.0851416156289</v>
+      </c>
+      <c r="I10" t="n">
+        <v>172.7003326788733</v>
+      </c>
+      <c r="J10" t="n">
+        <v>160.5122489163816</v>
+      </c>
+      <c r="K10" t="n">
+        <v>169.4172092786862</v>
+      </c>
+      <c r="L10" t="n">
+        <v>161.2649657974197</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>170.3099916168245</v>
-      </c>
-      <c r="C9" t="n">
-        <v>173.179349205121</v>
-      </c>
-      <c r="D9" t="n">
-        <v>166.9766288540941</v>
-      </c>
-      <c r="E9" t="n">
-        <v>173.179349205121</v>
-      </c>
-      <c r="F9" t="n">
-        <v>173.179349205121</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>170.3099916168248</v>
+      </c>
+      <c r="C11" t="n">
+        <v>173.1793492051212</v>
+      </c>
+      <c r="D11" t="n">
+        <v>166.9766288540942</v>
+      </c>
+      <c r="E11" t="n">
+        <v>173.1793492051212</v>
+      </c>
+      <c r="F11" t="n">
+        <v>173.1793492051212</v>
+      </c>
+      <c r="G11" t="n">
         <v>167.8587543615066</v>
       </c>
-      <c r="H9" t="n">
-        <v>168.0589666997661</v>
-      </c>
-      <c r="I9" t="n">
-        <v>173.179349205121</v>
-      </c>
-      <c r="J9" t="n">
-        <v>165.3809908320638</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="H11" t="n">
+        <v>168.0589666997662</v>
+      </c>
+      <c r="I11" t="n">
+        <v>173.1793492051212</v>
+      </c>
+      <c r="J11" t="n">
+        <v>165.3809908320639</v>
+      </c>
+      <c r="K11" t="n">
         <v>169.0032682454899</v>
       </c>
-      <c r="L9" t="n">
-        <v>165.6917855220081</v>
+      <c r="L11" t="n">
+        <v>165.6917855220082</v>
       </c>
     </row>
   </sheetData>
